--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$340</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K337"/>
+  <dimension ref="A1:K340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6705,7 +6705,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-64</t>
+          <t>CP-HTML-67</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Barra del bloque no tapa</t>
+          <t>Alineación en 3 casillas</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Seleccionar un bloque</t>
+          <t>Seleccionar un bloque y usar el control de Alineación</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr"/>
@@ -6738,7 +6738,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-65</t>
+          <t>CP-HTML-68</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6748,17 +6748,17 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Plantillas prediseñadas</t>
+          <t>La miniatura imita el bloque</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Abrir "Plantillas" y cargar una de las 5 integradas</t>
+          <t>Comparar el control en un bloque de imagen, uno de botón y uno de texto</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr"/>
@@ -6771,7 +6771,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-66</t>
+          <t>CP-HTML-69</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Móvil</t>
+          <t>Alineación con teclado</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Abrir el constructor en un móvil</t>
+          <t>Enfocar el control y usar ←, →, Inicio y Fin</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr"/>
@@ -6804,27 +6804,27 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-01</t>
+          <t>CP-HTML-64</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Editor básico tipo Word</t>
+          <t>Barra del bloque no tapa</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
+          <t>Seleccionar un bloque</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr"/>
@@ -6837,27 +6837,27 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-02</t>
+          <t>CP-HTML-65</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Vista previa PDF (básico)</t>
+          <t>Plantillas prediseñadas</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Botón "Vista previa PDF"</t>
+          <t>Abrir "Plantillas" y cargar una de las 5 integradas</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr"/>
@@ -6870,27 +6870,27 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-03</t>
+          <t>CP-HTML-66</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Estudio PDF (lienzo)</t>
+          <t>Móvil</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Crear un diseño con texto, formas, tabla y guardar</t>
+          <t>Abrir el constructor en un móvil</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr"/>
@@ -6903,7 +6903,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-04</t>
+          <t>CP-PDF-01</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Estudio: variables con datos reales</t>
+          <t>Editor básico tipo Word</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Elegir una base en el panel de datos → Vista previa</t>
+          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr"/>
@@ -6936,7 +6936,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-05</t>
+          <t>CP-PDF-02</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Estudio: unidades y reglas</t>
+          <t>Vista previa PDF (básico)</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
+          <t>Botón "Vista previa PDF"</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr"/>
@@ -6969,7 +6969,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-06</t>
+          <t>CP-PDF-03</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Estudio: seleccionar elemento rotado</t>
+          <t>Estudio PDF (lienzo)</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Girar un texto y hacer clic dentro de su caja visual</t>
+          <t>Crear un diseño con texto, formas, tabla y guardar</t>
         </is>
       </c>
       <c r="F195" s="8" t="inlineStr"/>
@@ -7002,7 +7002,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-07</t>
+          <t>CP-PDF-04</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Estudio: estilos vinculados</t>
+          <t>Estudio: variables con datos reales</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Vincular un estilo de texto/párrafo y editarlo</t>
+          <t>Elegir una base en el panel de datos → Vista previa</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr"/>
@@ -7035,7 +7035,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-08</t>
+          <t>CP-PDF-05</t>
         </is>
       </c>
       <c r="B197" s="8" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Diseñador PDF (full)</t>
+          <t>Estudio: unidades y reglas</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Abrir el Diseñador y crear un documento</t>
+          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr"/>
@@ -7068,7 +7068,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-09</t>
+          <t>CP-PDF-06</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -7078,17 +7078,17 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF de punta a punta</t>
+          <t>Estudio: seleccionar elemento rotado</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
+          <t>Girar un texto y hacer clic dentro de su caja visual</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr"/>
@@ -7101,7 +7101,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-10</t>
+          <t>CP-PDF-07</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Tabla que desborda pagina</t>
+          <t>Estudio: estilos vinculados</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
+          <t>Vincular un estilo de texto/párrafo y editarlo</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr"/>
@@ -7134,7 +7134,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-11</t>
+          <t>CP-PDF-08</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Celdas con JSON (multiregistro)</t>
+          <t>Diseñador PDF (full)</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Base con una columna que trae un array JSON</t>
+          <t>Abrir el Diseñador y crear un documento</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr"/>
@@ -7167,7 +7167,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-12</t>
+          <t>CP-PDF-09</t>
         </is>
       </c>
       <c r="B201" s="8" t="inlineStr">
@@ -7177,17 +7177,17 @@
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>Encabezados con BOM/espacios</t>
+          <t>Campaña EAP-PDF de punta a punta</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
+          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr"/>
@@ -7200,7 +7200,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-13</t>
+          <t>CP-PDF-10</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -7210,17 +7210,17 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Bordes y degradados</t>
+          <t>Tabla que desborda pagina</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Formas con borde discontinuo y relleno degradado</t>
+          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr"/>
@@ -7233,27 +7233,27 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-PDF-11</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Celdas con JSON (multiregistro)</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>Base con una columna que trae un array JSON</t>
         </is>
       </c>
       <c r="F203" s="8" t="inlineStr"/>
@@ -7266,27 +7266,27 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-PDF-12</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>Encabezados con BOM/espacios</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr"/>
@@ -7299,27 +7299,27 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-PDF-13</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>Bordes y degradados</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Formas con borde discontinuo y relleno degradado</t>
         </is>
       </c>
       <c r="F205" s="8" t="inlineStr"/>
@@ -7332,7 +7332,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr"/>
@@ -7365,7 +7365,7 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F207" s="8" t="inlineStr"/>
@@ -7398,7 +7398,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -7408,17 +7408,17 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr"/>
@@ -7431,7 +7431,7 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
@@ -7441,17 +7441,17 @@
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F209" s="8" t="inlineStr"/>
@@ -7464,7 +7464,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr"/>
@@ -7497,7 +7497,7 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B211" s="8" t="inlineStr">
@@ -7507,17 +7507,17 @@
       </c>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F211" s="8" t="inlineStr"/>
@@ -7530,7 +7530,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7545,12 +7545,12 @@
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr"/>
@@ -7563,7 +7563,7 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B213" s="8" t="inlineStr">
@@ -7573,17 +7573,17 @@
       </c>
       <c r="C213" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F213" s="8" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7606,17 +7606,17 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr"/>
@@ -7629,7 +7629,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr"/>
@@ -7662,7 +7662,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7677,12 +7677,12 @@
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr"/>
@@ -7695,27 +7695,27 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F217" s="8" t="inlineStr"/>
@@ -7728,27 +7728,27 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr"/>
@@ -7761,12 +7761,12 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F219" s="8" t="inlineStr"/>
@@ -7794,7 +7794,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7804,17 +7804,17 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr"/>
@@ -7827,7 +7827,7 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F221" s="8" t="inlineStr"/>
@@ -7860,7 +7860,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr"/>
@@ -7893,7 +7893,7 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F223" s="8" t="inlineStr"/>
@@ -7926,7 +7926,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr"/>
@@ -7959,27 +7959,27 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr"/>
@@ -7992,27 +7992,27 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr"/>
@@ -8025,12 +8025,12 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr"/>
@@ -8058,7 +8058,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -8068,17 +8068,17 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr"/>
@@ -8091,7 +8091,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B229" s="8" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F229" s="8" t="inlineStr"/>
@@ -8124,7 +8124,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr"/>
@@ -8157,7 +8157,7 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B231" s="8" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F231" s="8" t="inlineStr"/>
@@ -8190,7 +8190,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -8200,17 +8200,17 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr"/>
@@ -8223,12 +8223,12 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F233" s="8" t="inlineStr"/>
@@ -8256,27 +8256,27 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr"/>
@@ -8289,27 +8289,27 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr"/>
@@ -8322,7 +8322,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr"/>
@@ -8355,7 +8355,7 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B237" s="8" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr"/>
@@ -8388,7 +8388,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -8398,17 +8398,17 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr"/>
@@ -8421,7 +8421,7 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B239" s="8" t="inlineStr">
@@ -8431,17 +8431,17 @@
       </c>
       <c r="C239" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F239" s="8" t="inlineStr"/>
@@ -8454,7 +8454,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr"/>
@@ -8487,7 +8487,7 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B241" s="8" t="inlineStr">
@@ -8497,17 +8497,17 @@
       </c>
       <c r="C241" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F241" s="8" t="inlineStr"/>
@@ -8520,7 +8520,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -8530,17 +8530,17 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr"/>
@@ -8553,7 +8553,7 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B243" s="8" t="inlineStr">
@@ -8563,17 +8563,17 @@
       </c>
       <c r="C243" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr"/>
@@ -8586,7 +8586,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr"/>
@@ -8619,7 +8619,7 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B245" s="8" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F245" s="8" t="inlineStr"/>
@@ -8652,7 +8652,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -8662,17 +8662,17 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr"/>
@@ -8685,7 +8685,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B247" s="8" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F247" s="8" t="inlineStr"/>
@@ -8718,7 +8718,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -8728,17 +8728,17 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr"/>
@@ -8751,7 +8751,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B249" s="8" t="inlineStr">
@@ -8761,17 +8761,17 @@
       </c>
       <c r="C249" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F249" s="8" t="inlineStr"/>
@@ -8784,7 +8784,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -8794,17 +8794,17 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr"/>
@@ -8817,27 +8817,27 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C251" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F251" s="8" t="inlineStr"/>
@@ -8850,27 +8850,27 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr"/>
@@ -8883,27 +8883,27 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F253" s="8" t="inlineStr"/>
@@ -8916,7 +8916,7 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr"/>
@@ -8949,7 +8949,7 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B255" s="8" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F255" s="8" t="inlineStr"/>
@@ -8982,7 +8982,7 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
@@ -8992,17 +8992,17 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr"/>
@@ -9015,7 +9015,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B257" s="8" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F257" s="8" t="inlineStr"/>
@@ -9048,7 +9048,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -9058,17 +9058,17 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B259" s="8" t="inlineStr">
@@ -9091,17 +9091,17 @@
       </c>
       <c r="C259" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F259" s="8" t="inlineStr"/>
@@ -9114,7 +9114,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -9124,17 +9124,17 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B261" s="8" t="inlineStr">
@@ -9157,17 +9157,17 @@
       </c>
       <c r="C261" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F261" s="8" t="inlineStr"/>
@@ -9180,7 +9180,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -9190,17 +9190,17 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr"/>
@@ -9213,7 +9213,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B263" s="8" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F263" s="8" t="inlineStr"/>
@@ -9246,7 +9246,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr"/>
@@ -9279,7 +9279,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B265" s="8" t="inlineStr">
@@ -9289,17 +9289,17 @@
       </c>
       <c r="C265" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F265" s="8" t="inlineStr"/>
@@ -9312,7 +9312,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr"/>
@@ -9345,7 +9345,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F267" s="8" t="inlineStr"/>
@@ -9378,7 +9378,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -9388,17 +9388,17 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr"/>
@@ -9411,7 +9411,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr"/>
@@ -9444,7 +9444,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr"/>
@@ -9477,7 +9477,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr"/>
@@ -9510,7 +9510,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -9520,17 +9520,17 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr"/>
@@ -9543,7 +9543,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
@@ -9553,17 +9553,17 @@
       </c>
       <c r="C273" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr"/>
@@ -9576,7 +9576,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr"/>
@@ -9609,7 +9609,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
@@ -9619,17 +9619,17 @@
       </c>
       <c r="C275" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -9652,17 +9652,17 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr"/>
@@ -9675,7 +9675,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
@@ -9685,17 +9685,17 @@
       </c>
       <c r="C277" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr"/>
@@ -9708,12 +9708,12 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr"/>
@@ -9741,27 +9741,27 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C279" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr"/>
@@ -9774,27 +9774,27 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr"/>
@@ -9807,7 +9807,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
@@ -9817,17 +9817,17 @@
       </c>
       <c r="C281" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr"/>
@@ -9840,7 +9840,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -9850,17 +9850,17 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr"/>
@@ -9873,7 +9873,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr"/>
@@ -9906,7 +9906,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr"/>
@@ -9939,7 +9939,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr"/>
@@ -9972,7 +9972,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr"/>
@@ -10005,7 +10005,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr"/>
@@ -10038,7 +10038,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr"/>
@@ -10071,7 +10071,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr"/>
@@ -10104,7 +10104,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr"/>
@@ -10170,12 +10170,12 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr"/>
@@ -10203,12 +10203,12 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C293" s="7" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr"/>
@@ -10236,12 +10236,12 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr"/>
@@ -10269,7 +10269,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
@@ -10279,17 +10279,17 @@
       </c>
       <c r="C295" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr"/>
@@ -10302,7 +10302,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr"/>
@@ -10335,7 +10335,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
@@ -10411,17 +10411,17 @@
       </c>
       <c r="C299" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr"/>
@@ -10434,7 +10434,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr"/>
@@ -10467,7 +10467,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr"/>
@@ -10500,7 +10500,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -10510,17 +10510,17 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr"/>
@@ -10533,27 +10533,27 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr"/>
@@ -10566,27 +10566,27 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr"/>
@@ -10599,12 +10599,12 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C305" s="7" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr"/>
@@ -10632,7 +10632,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -10642,17 +10642,17 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr"/>
@@ -10665,7 +10665,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
@@ -10675,17 +10675,17 @@
       </c>
       <c r="C307" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr"/>
@@ -10698,7 +10698,7 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr"/>
@@ -10731,7 +10731,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -10774,17 +10774,17 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr"/>
@@ -10797,7 +10797,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr"/>
@@ -10830,7 +10830,7 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -10840,17 +10840,17 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr"/>
@@ -10863,7 +10863,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
@@ -10873,17 +10873,17 @@
       </c>
       <c r="C313" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr"/>
@@ -10896,7 +10896,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr"/>
@@ -10929,7 +10929,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr"/>
@@ -10962,7 +10962,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
@@ -10972,17 +10972,17 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr"/>
@@ -10995,7 +10995,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr"/>
@@ -11028,12 +11028,12 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -11043,12 +11043,12 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr"/>
@@ -11061,27 +11061,27 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr"/>
@@ -11094,12 +11094,12 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -11109,12 +11109,12 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr"/>
@@ -11127,7 +11127,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr"/>
@@ -11160,7 +11160,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -11170,17 +11170,17 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr"/>
@@ -11193,7 +11193,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr"/>
@@ -11226,7 +11226,7 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
@@ -11241,12 +11241,12 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr"/>
@@ -11259,7 +11259,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-CAS-05</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>Consentimiento por canal</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Contacto sin consentimiento del canal 0</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-CAS-06</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>Listado de cascadas</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Abrir el listado</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr"/>
@@ -11325,7 +11325,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-SER-01</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -11335,17 +11335,17 @@
       </c>
       <c r="C327" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Serie de 30 días (cliente)</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,7 +11358,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-SER-02</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -11368,17 +11368,17 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Serie global (admin)</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Panel de control → gráfico</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-SER-03</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -11401,17 +11401,17 @@
       </c>
       <c r="C329" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Muestras excluidas</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Enviar muestras y revisar la serie</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,27 +11424,27 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-SER-04</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Aislamiento</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Comparar la serie de dos clientes</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,27 +11457,27 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-SER-05</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Adiós "(parcial)"</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,27 +11490,27 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-SER-06</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Leyenda interactiva</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Ocultar/mostrar series en el gráfico</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,7 +11523,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-REG-01</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -11533,17 +11533,17 @@
       </c>
       <c r="C333" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Aislamiento multi-tenant</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,7 +11556,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-REG-02</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
@@ -11566,17 +11566,17 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Suite automática</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,7 +11589,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-REG-03</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -11599,17 +11599,17 @@
       </c>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Build del front</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>npm run build</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,7 +11622,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-REG-06</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Pruebas del frontend</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>npm test en 05_Frontend/Front/page</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-REG-07</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
@@ -11665,17 +11665,17 @@
       </c>
       <c r="C337" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Sesión y tenant en TODA ruta nueva</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11685,13 +11685,112 @@
       <c r="J337" s="6" t="inlineStr"/>
       <c r="K337" s="5" t="inlineStr"/>
     </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F338" s="3" t="inlineStr"/>
+      <c r="G338" s="4" t="inlineStr"/>
+      <c r="H338" s="5" t="inlineStr"/>
+      <c r="I338" s="4" t="inlineStr"/>
+      <c r="J338" s="6" t="inlineStr"/>
+      <c r="K338" s="5" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B339" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C339" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D339" s="8" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E339" s="8" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F339" s="8" t="inlineStr"/>
+      <c r="G339" s="4" t="inlineStr"/>
+      <c r="H339" s="5" t="inlineStr"/>
+      <c r="I339" s="4" t="inlineStr"/>
+      <c r="J339" s="6" t="inlineStr"/>
+      <c r="K339" s="5" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E340" s="3" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F340" s="3" t="inlineStr"/>
+      <c r="G340" s="4" t="inlineStr"/>
+      <c r="H340" s="5" t="inlineStr"/>
+      <c r="I340" s="4" t="inlineStr"/>
+      <c r="J340" s="6" t="inlineStr"/>
+      <c r="K340" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K337"/>
+  <autoFilter ref="A1:K340"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H337" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H340" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K337" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K340" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -11751,7 +11850,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A337)</f>
+        <f>COUNTA(Casos!A2:A340)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -11765,7 +11864,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$337,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$340,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -11782,7 +11881,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$337,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$340,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -11799,7 +11898,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$337,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$340,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -11816,7 +11915,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$337,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$340,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -11872,11 +11971,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$337,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$340,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$337,A12,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$340,A12,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -11889,11 +11988,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$337,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$340,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$337,A13,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$340,A13,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -11906,11 +12005,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$337,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$340,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$337,A14,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$340,A14,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -11968,19 +12067,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A18,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A18,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A18,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A18,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$337,$A18,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$340,$A18,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -11991,19 +12090,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A19,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A19,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A19,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A19,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$337,$A19,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$340,$A19,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12014,19 +12113,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A20,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A20,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A20,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A20,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$337,$A20,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$340,$A20,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12037,19 +12136,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A21,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A21,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A21,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A21,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$337,$A21,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$340,$A21,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12060,19 +12159,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A22,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A22,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A22,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A22,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$337,$A22,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$340,$A22,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12083,19 +12182,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A23,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A23,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A23,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A23,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$337,$A23,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$340,$A23,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12106,19 +12205,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A24,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A24,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A24,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A24,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$337,$A24,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$340,$A24,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12129,19 +12228,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A25,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A25,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A25,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A25,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$337,$A25,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$340,$A25,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12152,19 +12251,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A26,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A26,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A26,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A26,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$337,$A26,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$340,$A26,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12175,19 +12274,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A27,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A27,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A27,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A27,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$337,$A27,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$340,$A27,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12198,19 +12297,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A28,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A28,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A28,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A28,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$337,$A28,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$340,$A28,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12221,19 +12320,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A29,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A29,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A29,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A29,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$337,$A29,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$340,$A29,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12244,19 +12343,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A30,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A30,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A30,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A30,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$337,$A30,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$340,$A30,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12267,19 +12366,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A31,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A31,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A31,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A31,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$337,$A31,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$340,$A31,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12290,19 +12389,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A32,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A32,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A32,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A32,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$337,$A32,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$340,$A32,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12313,19 +12412,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A33,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A33,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A33,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A33,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$337,$A33,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$340,$A33,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12336,19 +12435,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A34,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A34,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A34,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A34,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$337,$A34,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$340,$A34,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12359,19 +12458,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A35,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A35,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A35,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A35,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$337,$A35,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$340,$A35,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12382,19 +12481,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A36,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A36,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A36,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A36,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$337,$A36,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$340,$A36,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12405,19 +12504,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A37,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A37,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A37,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A37,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$337,$A37,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$340,$A37,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12428,19 +12527,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A38,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A38,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A38,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A38,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$337,$A38,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$340,$A38,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12451,19 +12550,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$337,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$340,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A39,Casos!$H$2:$H$337,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A39,Casos!$H$2:$H$340,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$337,$A39,Casos!$H$2:$H$337,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$340,$A39,Casos!$H$2:$H$340,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$337,$A39,Casos!$H$2:$H$337,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$340,$A39,Casos!$H$2:$H$340,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$340</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$351</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K340"/>
+  <dimension ref="A1:K351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6705,7 +6705,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-67</t>
+          <t>CP-HTML-70</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -6715,17 +6715,17 @@
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Alineación en 3 casillas</t>
+          <t>Insertar debajo del seleccionado</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Seleccionar un bloque y usar el control de Alineación</t>
+          <t>Con 2 bloques, seleccionar el PRIMERO y hacer clic en un tipo de la paleta</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr"/>
@@ -6738,7 +6738,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-68</t>
+          <t>CP-HTML-71</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6748,17 +6748,17 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>La miniatura imita el bloque</t>
+          <t>"Agregar bloque" sigue agregando al final</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Comparar el control en un bloque de imagen, uno de botón y uno de texto</t>
+          <t>Usar el botón de la zona final del lienzo con un bloque seleccionado arriba</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr"/>
@@ -6771,7 +6771,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-69</t>
+          <t>CP-HTML-72</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Alineación con teclado</t>
+          <t>Fondo de página en el editor</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Enfocar el control y usar ←, →, Inicio y Fin</t>
+          <t>Ajustes → cambiar "Fondo de página"</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr"/>
@@ -6804,7 +6804,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-64</t>
+          <t>CP-HTML-73</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6814,17 +6814,17 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Barra del bloque no tapa</t>
+          <t>Color de texto global</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Seleccionar un bloque</t>
+          <t>Ajustes → cambiar "Color de texto"</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr"/>
@@ -6837,7 +6837,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-65</t>
+          <t>CP-HTML-74</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Plantillas prediseñadas</t>
+          <t>Color propio del bloque manda</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Abrir "Plantillas" y cargar una de las 5 integradas</t>
+          <t>Fijar un color al bloque y cambiar el global</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr"/>
@@ -6870,7 +6870,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-66</t>
+          <t>CP-HTML-75</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6880,17 +6880,17 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Móvil</t>
+          <t>Fuente global</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Abrir el constructor en un móvil</t>
+          <t>Ajustes → cambiar "Fuente"</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr"/>
@@ -6903,12 +6903,12 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-01</t>
+          <t>CP-HTML-76</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Editor básico tipo Word</t>
+          <t>Publicar guarda las DOS formas</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
+          <t>Publicar una plantilla → abrir "Cargar"</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr"/>
@@ -6936,12 +6936,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-02</t>
+          <t>CP-HTML-77</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Vista previa PDF (básico)</t>
+          <t>Cargar devuelve algo EDITABLE</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Botón "Vista previa PDF"</t>
+          <t>Abrir un diseño desde "Cargar"</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr"/>
@@ -6969,27 +6969,27 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-03</t>
+          <t>CP-HTML-78</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Estudio PDF (lienzo)</t>
+          <t>Republicar no duplica</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Crear un diseño con texto, formas, tabla y guardar</t>
+          <t>Abrir un diseño, cambiar algo y Publicar</t>
         </is>
       </c>
       <c r="F195" s="8" t="inlineStr"/>
@@ -7002,27 +7002,27 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-04</t>
+          <t>CP-HTML-79</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Estudio: variables con datos reales</t>
+          <t>Solo-en-SES lista lo que no tiene diseño</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Elegir una base en el panel de datos → Vista previa</t>
+          <t>Revisar la 2ª sección de "Cargar"</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr"/>
@@ -7035,27 +7035,27 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-05</t>
+          <t>CP-HTML-80</t>
         </is>
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>Estudio: unidades y reglas</t>
+          <t>"Nuevo" cancelado no pierde la identidad</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
+          <t>Con un diseño abierto, pulsar Nuevo y CANCELAR el confirm</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr"/>
@@ -7068,12 +7068,12 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-06</t>
+          <t>CP-HTML-67</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Estudio: seleccionar elemento rotado</t>
+          <t>Alineación en 3 casillas</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Girar un texto y hacer clic dentro de su caja visual</t>
+          <t>Seleccionar un bloque y usar el control de Alineación</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr"/>
@@ -7101,27 +7101,27 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-07</t>
+          <t>CP-HTML-68</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Estudio: estilos vinculados</t>
+          <t>La miniatura imita el bloque</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Vincular un estilo de texto/párrafo y editarlo</t>
+          <t>Comparar el control en un bloque de imagen, uno de botón y uno de texto</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr"/>
@@ -7134,27 +7134,27 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-08</t>
+          <t>CP-HTML-69</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Diseñador PDF (full)</t>
+          <t>Alineación con teclado</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Abrir el Diseñador y crear un documento</t>
+          <t>Enfocar el control y usar ←, →, Inicio y Fin</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr"/>
@@ -7167,27 +7167,27 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-09</t>
+          <t>CP-HTML-64</t>
         </is>
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF de punta a punta</t>
+          <t>Barra del bloque no tapa</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
+          <t>Seleccionar un bloque</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr"/>
@@ -7200,27 +7200,27 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-10</t>
+          <t>CP-HTML-65</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Tabla que desborda pagina</t>
+          <t>Plantillas prediseñadas</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
+          <t>Abrir "Plantillas" y cargar una de las 5 integradas</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr"/>
@@ -7233,27 +7233,27 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-11</t>
+          <t>CP-HTML-66</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>Celdas con JSON (multiregistro)</t>
+          <t>Móvil</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Base con una columna que trae un array JSON</t>
+          <t>Abrir el constructor en un móvil</t>
         </is>
       </c>
       <c r="F203" s="8" t="inlineStr"/>
@@ -7266,7 +7266,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-12</t>
+          <t>CP-PDF-01</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -7276,17 +7276,17 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Encabezados con BOM/espacios</t>
+          <t>Editor básico tipo Word</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
+          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr"/>
@@ -7299,7 +7299,7 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-13</t>
+          <t>CP-PDF-02</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
@@ -7309,17 +7309,17 @@
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>Bordes y degradados</t>
+          <t>Vista previa PDF (básico)</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>Formas con borde discontinuo y relleno degradado</t>
+          <t>Botón "Vista previa PDF"</t>
         </is>
       </c>
       <c r="F205" s="8" t="inlineStr"/>
@@ -7332,12 +7332,12 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-PDF-03</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Estudio PDF (lienzo)</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>Crear un diseño con texto, formas, tabla y guardar</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr"/>
@@ -7365,12 +7365,12 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-PDF-04</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C207" s="7" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>Estudio: variables con datos reales</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Elegir una base en el panel de datos → Vista previa</t>
         </is>
       </c>
       <c r="F207" s="8" t="inlineStr"/>
@@ -7398,27 +7398,27 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-PDF-05</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>Estudio: unidades y reglas</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr"/>
@@ -7431,27 +7431,27 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-PDF-06</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Estudio: seleccionar elemento rotado</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Girar un texto y hacer clic dentro de su caja visual</t>
         </is>
       </c>
       <c r="F209" s="8" t="inlineStr"/>
@@ -7464,27 +7464,27 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-PDF-07</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>Estudio: estilos vinculados</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Vincular un estilo de texto/párrafo y editarlo</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr"/>
@@ -7497,12 +7497,12 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-PDF-08</t>
         </is>
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C211" s="7" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Diseñador PDF (full)</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Abrir el Diseñador y crear un documento</t>
         </is>
       </c>
       <c r="F211" s="8" t="inlineStr"/>
@@ -7530,27 +7530,27 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-PDF-09</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Campaña EAP-PDF de punta a punta</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr"/>
@@ -7563,12 +7563,12 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-PDF-10</t>
         </is>
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
@@ -7578,12 +7578,12 @@
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Tabla que desborda pagina</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
         </is>
       </c>
       <c r="F213" s="8" t="inlineStr"/>
@@ -7596,27 +7596,27 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-PDF-11</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>Celdas con JSON (multiregistro)</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Base con una columna que trae un array JSON</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr"/>
@@ -7629,12 +7629,12 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-PDF-12</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Encabezados con BOM/espacios</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr"/>
@@ -7662,27 +7662,27 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-PDF-13</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Bordes y degradados</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Formas con borde discontinuo y relleno degradado</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr"/>
@@ -7695,7 +7695,7 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
@@ -7705,17 +7705,17 @@
       </c>
       <c r="C217" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F217" s="8" t="inlineStr"/>
@@ -7728,7 +7728,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7738,17 +7738,17 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr"/>
@@ -7761,7 +7761,7 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B219" s="8" t="inlineStr">
@@ -7771,17 +7771,17 @@
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F219" s="8" t="inlineStr"/>
@@ -7794,12 +7794,12 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr"/>
@@ -7827,12 +7827,12 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F221" s="8" t="inlineStr"/>
@@ -7860,12 +7860,12 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -7875,12 +7875,12 @@
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr"/>
@@ -7893,12 +7893,12 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F223" s="8" t="inlineStr"/>
@@ -7926,12 +7926,12 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr"/>
@@ -7959,27 +7959,27 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr"/>
@@ -7992,12 +7992,12 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr"/>
@@ -8025,27 +8025,27 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr"/>
@@ -8058,27 +8058,27 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr"/>
@@ -8091,27 +8091,27 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F229" s="8" t="inlineStr"/>
@@ -8124,27 +8124,27 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr"/>
@@ -8157,27 +8157,27 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F231" s="8" t="inlineStr"/>
@@ -8190,12 +8190,12 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr"/>
@@ -8223,27 +8223,27 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F233" s="8" t="inlineStr"/>
@@ -8256,12 +8256,12 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr"/>
@@ -8289,27 +8289,27 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr"/>
@@ -8322,27 +8322,27 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr"/>
@@ -8355,27 +8355,27 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C237" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr"/>
@@ -8388,12 +8388,12 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr"/>
@@ -8421,12 +8421,12 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C239" s="7" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F239" s="8" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr"/>
@@ -8487,27 +8487,27 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F241" s="8" t="inlineStr"/>
@@ -8520,12 +8520,12 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr"/>
@@ -8553,12 +8553,12 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C243" s="7" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr"/>
@@ -8586,12 +8586,12 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr"/>
@@ -8619,27 +8619,27 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F245" s="8" t="inlineStr"/>
@@ -8652,12 +8652,12 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr"/>
@@ -8685,7 +8685,7 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B247" s="8" t="inlineStr">
@@ -8700,12 +8700,12 @@
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F247" s="8" t="inlineStr"/>
@@ -8718,7 +8718,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr"/>
@@ -8751,7 +8751,7 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B249" s="8" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F249" s="8" t="inlineStr"/>
@@ -8784,7 +8784,7 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr"/>
@@ -8817,7 +8817,7 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B251" s="8" t="inlineStr">
@@ -8827,17 +8827,17 @@
       </c>
       <c r="C251" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F251" s="8" t="inlineStr"/>
@@ -8850,7 +8850,7 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
@@ -8865,12 +8865,12 @@
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr"/>
@@ -8883,7 +8883,7 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B253" s="8" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F253" s="8" t="inlineStr"/>
@@ -8916,12 +8916,12 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr"/>
@@ -8949,12 +8949,12 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C255" s="7" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F255" s="8" t="inlineStr"/>
@@ -8982,12 +8982,12 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr"/>
@@ -9015,12 +9015,12 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C257" s="7" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F257" s="8" t="inlineStr"/>
@@ -9048,12 +9048,12 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr"/>
@@ -9081,27 +9081,27 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F259" s="8" t="inlineStr"/>
@@ -9114,27 +9114,27 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr"/>
@@ -9147,27 +9147,27 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F261" s="8" t="inlineStr"/>
@@ -9180,27 +9180,27 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr"/>
@@ -9213,27 +9213,27 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F263" s="8" t="inlineStr"/>
@@ -9246,12 +9246,12 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr"/>
@@ -9279,7 +9279,7 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B265" s="8" t="inlineStr">
@@ -9289,17 +9289,17 @@
       </c>
       <c r="C265" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F265" s="8" t="inlineStr"/>
@@ -9312,7 +9312,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr"/>
@@ -9345,7 +9345,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
@@ -9355,17 +9355,17 @@
       </c>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F267" s="8" t="inlineStr"/>
@@ -9378,7 +9378,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr"/>
@@ -9411,7 +9411,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr"/>
@@ -9444,7 +9444,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr"/>
@@ -9477,7 +9477,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
@@ -9487,17 +9487,17 @@
       </c>
       <c r="C271" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr"/>
@@ -9510,7 +9510,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -9520,17 +9520,17 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr"/>
@@ -9543,7 +9543,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
@@ -9553,17 +9553,17 @@
       </c>
       <c r="C273" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr"/>
@@ -9576,7 +9576,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr"/>
@@ -9609,7 +9609,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -9652,17 +9652,17 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr"/>
@@ -9675,7 +9675,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr"/>
@@ -9708,7 +9708,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr"/>
@@ -9741,7 +9741,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -9784,17 +9784,17 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr"/>
@@ -9807,27 +9807,27 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C281" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr"/>
@@ -9840,12 +9840,12 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr"/>
@@ -9873,12 +9873,12 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C283" s="7" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr"/>
@@ -9906,12 +9906,12 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr"/>
@@ -9939,27 +9939,27 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C285" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr"/>
@@ -9972,27 +9972,27 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr"/>
@@ -10005,27 +10005,27 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C287" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr"/>
@@ -10038,27 +10038,27 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr"/>
@@ -10071,12 +10071,12 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C289" s="7" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr"/>
@@ -10104,12 +10104,12 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr"/>
@@ -10137,12 +10137,12 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C291" s="7" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr"/>
@@ -10170,7 +10170,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr"/>
@@ -10203,7 +10203,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
@@ -10213,17 +10213,17 @@
       </c>
       <c r="C293" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr"/>
@@ -10236,7 +10236,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -10246,17 +10246,17 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr"/>
@@ -10269,27 +10269,27 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr"/>
@@ -10302,12 +10302,12 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr"/>
@@ -10335,27 +10335,27 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr"/>
@@ -10368,12 +10368,12 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr"/>
@@ -10401,12 +10401,12 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C299" s="7" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr"/>
@@ -10434,27 +10434,27 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr"/>
@@ -10467,27 +10467,27 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr"/>
@@ -10500,27 +10500,27 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr"/>
@@ -10533,27 +10533,27 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr"/>
@@ -10566,27 +10566,27 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr"/>
@@ -10599,12 +10599,12 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C305" s="7" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr"/>
@@ -10632,12 +10632,12 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr"/>
@@ -10665,12 +10665,12 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr"/>
@@ -10698,12 +10698,12 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr"/>
@@ -10731,12 +10731,12 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr"/>
@@ -10764,27 +10764,27 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr"/>
@@ -10797,12 +10797,12 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C311" s="7" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr"/>
@@ -10830,27 +10830,27 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr"/>
@@ -10863,27 +10863,27 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr"/>
@@ -10896,12 +10896,12 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr"/>
@@ -10929,12 +10929,12 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C315" s="7" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr"/>
@@ -10962,27 +10962,27 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr"/>
@@ -10995,7 +10995,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="C317" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr"/>
@@ -11028,7 +11028,7 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
@@ -11038,17 +11038,17 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr"/>
@@ -11061,7 +11061,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr"/>
@@ -11094,7 +11094,7 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
@@ -11109,12 +11109,12 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr"/>
@@ -11127,12 +11127,12 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr"/>
@@ -11160,27 +11160,27 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr"/>
@@ -11193,12 +11193,12 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr"/>
@@ -11226,27 +11226,27 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr"/>
@@ -11259,12 +11259,12 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr"/>
@@ -11292,27 +11292,27 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr"/>
@@ -11325,12 +11325,12 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,12 +11358,12 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,27 +11391,27 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,12 +11424,12 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,27 +11457,27 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,7 +11490,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
@@ -11500,17 +11500,17 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,12 +11523,12 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,12 +11556,12 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,27 +11589,27 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,12 +11622,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-CAS-05</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Consentimiento por canal</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Contacto sin consentimiento del canal 0</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,27 +11655,27 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-CAS-06</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Listado de cascadas</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Abrir el listado</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,27 +11688,27 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-SER-01</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Serie de 30 días (cliente)</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,27 +11721,27 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-SER-02</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Serie global (admin)</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Panel de control → gráfico</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,27 +11754,27 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-SER-03</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Muestras excluidas</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Enviar muestras y revisar la serie</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11784,13 +11784,376 @@
       <c r="J340" s="6" t="inlineStr"/>
       <c r="K340" s="5" t="inlineStr"/>
     </row>
+    <row r="341">
+      <c r="A341" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-04</t>
+        </is>
+      </c>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C341" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D341" s="8" t="inlineStr">
+        <is>
+          <t>Aislamiento</t>
+        </is>
+      </c>
+      <c r="E341" s="8" t="inlineStr">
+        <is>
+          <t>Comparar la serie de dos clientes</t>
+        </is>
+      </c>
+      <c r="F341" s="8" t="inlineStr"/>
+      <c r="G341" s="4" t="inlineStr"/>
+      <c r="H341" s="5" t="inlineStr"/>
+      <c r="I341" s="4" t="inlineStr"/>
+      <c r="J341" s="6" t="inlineStr"/>
+      <c r="K341" s="5" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-05</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>Adiós "(parcial)"</t>
+        </is>
+      </c>
+      <c r="E342" s="3" t="inlineStr">
+        <is>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+        </is>
+      </c>
+      <c r="F342" s="3" t="inlineStr"/>
+      <c r="G342" s="4" t="inlineStr"/>
+      <c r="H342" s="5" t="inlineStr"/>
+      <c r="I342" s="4" t="inlineStr"/>
+      <c r="J342" s="6" t="inlineStr"/>
+      <c r="K342" s="5" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-06</t>
+        </is>
+      </c>
+      <c r="B343" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C343" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D343" s="8" t="inlineStr">
+        <is>
+          <t>Leyenda interactiva</t>
+        </is>
+      </c>
+      <c r="E343" s="8" t="inlineStr">
+        <is>
+          <t>Ocultar/mostrar series en el gráfico</t>
+        </is>
+      </c>
+      <c r="F343" s="8" t="inlineStr"/>
+      <c r="G343" s="4" t="inlineStr"/>
+      <c r="H343" s="5" t="inlineStr"/>
+      <c r="I343" s="4" t="inlineStr"/>
+      <c r="J343" s="6" t="inlineStr"/>
+      <c r="K343" s="5" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E344" s="3" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F344" s="3" t="inlineStr"/>
+      <c r="G344" s="4" t="inlineStr"/>
+      <c r="H344" s="5" t="inlineStr"/>
+      <c r="I344" s="4" t="inlineStr"/>
+      <c r="J344" s="6" t="inlineStr"/>
+      <c r="K344" s="5" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B345" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C345" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D345" s="8" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E345" s="8" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F345" s="8" t="inlineStr"/>
+      <c r="G345" s="4" t="inlineStr"/>
+      <c r="H345" s="5" t="inlineStr"/>
+      <c r="I345" s="4" t="inlineStr"/>
+      <c r="J345" s="6" t="inlineStr"/>
+      <c r="K345" s="5" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E346" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F346" s="3" t="inlineStr"/>
+      <c r="G346" s="4" t="inlineStr"/>
+      <c r="H346" s="5" t="inlineStr"/>
+      <c r="I346" s="4" t="inlineStr"/>
+      <c r="J346" s="6" t="inlineStr"/>
+      <c r="K346" s="5" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B347" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C347" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D347" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E347" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F347" s="8" t="inlineStr"/>
+      <c r="G347" s="4" t="inlineStr"/>
+      <c r="H347" s="5" t="inlineStr"/>
+      <c r="I347" s="4" t="inlineStr"/>
+      <c r="J347" s="6" t="inlineStr"/>
+      <c r="K347" s="5" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E348" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F348" s="3" t="inlineStr"/>
+      <c r="G348" s="4" t="inlineStr"/>
+      <c r="H348" s="5" t="inlineStr"/>
+      <c r="I348" s="4" t="inlineStr"/>
+      <c r="J348" s="6" t="inlineStr"/>
+      <c r="K348" s="5" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B349" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C349" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D349" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E349" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F349" s="8" t="inlineStr"/>
+      <c r="G349" s="4" t="inlineStr"/>
+      <c r="H349" s="5" t="inlineStr"/>
+      <c r="I349" s="4" t="inlineStr"/>
+      <c r="J349" s="6" t="inlineStr"/>
+      <c r="K349" s="5" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E350" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F350" s="3" t="inlineStr"/>
+      <c r="G350" s="4" t="inlineStr"/>
+      <c r="H350" s="5" t="inlineStr"/>
+      <c r="I350" s="4" t="inlineStr"/>
+      <c r="J350" s="6" t="inlineStr"/>
+      <c r="K350" s="5" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B351" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C351" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D351" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E351" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F351" s="8" t="inlineStr"/>
+      <c r="G351" s="4" t="inlineStr"/>
+      <c r="H351" s="5" t="inlineStr"/>
+      <c r="I351" s="4" t="inlineStr"/>
+      <c r="J351" s="6" t="inlineStr"/>
+      <c r="K351" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K340"/>
+  <autoFilter ref="A1:K351"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H340" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K340" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -11850,7 +12213,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A340)</f>
+        <f>COUNTA(Casos!A2:A351)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -11864,7 +12227,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$340,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$351,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -11881,7 +12244,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$340,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$351,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -11898,7 +12261,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$340,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$351,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -11915,7 +12278,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$340,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$351,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -11971,11 +12334,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$340,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$351,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$340,A12,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$351,A12,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -11988,11 +12351,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$340,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$351,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$340,A13,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$351,A13,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -12005,11 +12368,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$340,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$351,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$340,A14,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$351,A14,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -12067,19 +12430,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A18,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A18,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A18,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A18,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$340,$A18,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$351,$A18,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12090,19 +12453,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A19,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A19,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A19,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A19,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$340,$A19,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$351,$A19,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12113,19 +12476,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A20,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A20,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A20,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A20,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$340,$A20,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$351,$A20,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12136,19 +12499,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A21,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A21,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A21,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A21,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$340,$A21,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$351,$A21,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12159,19 +12522,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A22,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A22,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A22,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A22,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$340,$A22,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$351,$A22,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12182,19 +12545,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A23,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A23,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A23,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A23,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$340,$A23,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$351,$A23,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12205,19 +12568,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A24,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A24,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A24,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A24,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$340,$A24,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$351,$A24,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12228,19 +12591,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A25,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A25,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A25,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A25,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$340,$A25,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$351,$A25,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12251,19 +12614,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A26,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A26,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A26,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A26,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$340,$A26,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$351,$A26,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12274,19 +12637,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A27,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A27,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A27,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A27,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$340,$A27,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$351,$A27,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12297,19 +12660,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A28,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A28,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A28,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A28,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$340,$A28,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$351,$A28,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12320,19 +12683,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A29,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A29,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A29,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A29,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$340,$A29,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$351,$A29,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12343,19 +12706,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A30,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A30,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A30,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A30,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$340,$A30,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$351,$A30,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12366,19 +12729,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A31,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A31,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A31,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A31,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$340,$A31,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$351,$A31,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12389,19 +12752,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A32,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A32,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A32,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A32,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$340,$A32,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$351,$A32,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12412,19 +12775,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A33,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A33,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A33,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A33,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$340,$A33,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$351,$A33,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12435,19 +12798,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A34,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A34,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A34,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A34,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$340,$A34,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$351,$A34,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12458,19 +12821,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A35,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A35,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A35,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A35,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$340,$A35,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$351,$A35,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12481,19 +12844,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A36,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A36,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A36,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A36,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$340,$A36,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$351,$A36,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12504,19 +12867,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A37,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A37,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A37,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A37,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$340,$A37,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$351,$A37,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12527,19 +12890,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A38,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A38,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A38,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A38,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$340,$A38,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$351,$A38,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12550,19 +12913,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$340,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$351,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A39,Casos!$H$2:$H$340,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A39,Casos!$H$2:$H$351,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$340,$A39,Casos!$H$2:$H$340,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$351,$A39,Casos!$H$2:$H$351,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$340,$A39,Casos!$H$2:$H$340,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$351,$A39,Casos!$H$2:$H$351,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$351</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$361</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K351"/>
+  <dimension ref="A1:K361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6705,7 +6705,7 @@
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-70</t>
+          <t>CP-HTML-81</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
@@ -6715,17 +6715,17 @@
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>Insertar debajo del seleccionado</t>
+          <t>Color del bloque de TEXTO</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>Con 2 bloques, seleccionar el PRIMERO y hacer clic en un tipo de la paleta</t>
+          <t>Seleccionar un texto → "Color del texto"</t>
         </is>
       </c>
       <c r="F187" s="8" t="inlineStr"/>
@@ -6738,7 +6738,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-71</t>
+          <t>CP-HTML-82</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6748,17 +6748,17 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>"Agregar bloque" sigue agregando al final</t>
+          <t>Logos reales por defecto</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Usar el botón de la zona final del lienzo con un bloque seleccionado arriba</t>
+          <t>Poner enlaces en 3 redes</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr"/>
@@ -6771,7 +6771,7 @@
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-72</t>
+          <t>CP-HTML-83</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Fondo de página en el editor</t>
+          <t>Colores de cada red sobre el logo real</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>Ajustes → cambiar "Fondo de página"</t>
+          <t>Estilo "Colores de cada red"</t>
         </is>
       </c>
       <c r="F189" s="8" t="inlineStr"/>
@@ -6804,7 +6804,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-73</t>
+          <t>CP-HTML-84</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6814,17 +6814,17 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Color de texto global</t>
+          <t>Un solo color</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Ajustes → cambiar "Color de texto"</t>
+          <t>Estilo "Un solo color" + hex de marca</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr"/>
@@ -6837,7 +6837,7 @@
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-74</t>
+          <t>CP-HTML-85</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>Color propio del bloque manda</t>
+          <t>Solo el logo (sin insignia)</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>Fijar un color al bloque y cambiar el global</t>
+          <t>Fondo → "Solo el logo"</t>
         </is>
       </c>
       <c r="F191" s="8" t="inlineStr"/>
@@ -6870,7 +6870,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-75</t>
+          <t>CP-HTML-86</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6880,17 +6880,17 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Fuente global</t>
+          <t>Los iconos se suben al PUBLICAR</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Ajustes → cambiar "Fuente"</t>
+          <t>Configurar redes y publicar</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr"/>
@@ -6903,7 +6903,7 @@
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-76</t>
+          <t>CP-HTML-87</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>Publicar guarda las DOS formas</t>
+          <t>Fallo de subida no publica</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>Publicar una plantilla → abrir "Cargar"</t>
+          <t>Simular fallo al subir un icono</t>
         </is>
       </c>
       <c r="F193" s="8" t="inlineStr"/>
@@ -6936,7 +6936,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-77</t>
+          <t>CP-HTML-88</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Cargar devuelve algo EDITABLE</t>
+          <t>Vista previa en oscuro</t>
         </is>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Abrir un diseño desde "Cargar"</t>
+          <t>Vista previa → "Oscuro" con modo oscuro activo en Ajustes</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr"/>
@@ -6969,7 +6969,7 @@
     <row r="195">
       <c r="A195" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-78</t>
+          <t>CP-HTML-89</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>Republicar no duplica</t>
+          <t>Oscuro sin reglas</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>Abrir un diseño, cambiar algo y Publicar</t>
+          <t>"Oscuro" con el modo oscuro APAGADO en Ajustes</t>
         </is>
       </c>
       <c r="F195" s="8" t="inlineStr"/>
@@ -7002,7 +7002,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-79</t>
+          <t>CP-HTML-90</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -7017,12 +7017,12 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Solo-en-SES lista lo que no tiene diseño</t>
+          <t>Cargar no ofrece SES</t>
         </is>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>Revisar la 2ª sección de "Cargar"</t>
+          <t>Abrir "Cargar"</t>
         </is>
       </c>
       <c r="F196" s="3" t="inlineStr"/>
@@ -7035,7 +7035,7 @@
     <row r="197">
       <c r="A197" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-80</t>
+          <t>CP-HTML-70</t>
         </is>
       </c>
       <c r="B197" s="8" t="inlineStr">
@@ -7045,17 +7045,17 @@
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>"Nuevo" cancelado no pierde la identidad</t>
+          <t>Insertar debajo del seleccionado</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>Con un diseño abierto, pulsar Nuevo y CANCELAR el confirm</t>
+          <t>Con 2 bloques, seleccionar el PRIMERO y hacer clic en un tipo de la paleta</t>
         </is>
       </c>
       <c r="F197" s="8" t="inlineStr"/>
@@ -7068,7 +7068,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-67</t>
+          <t>CP-HTML-71</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Alineación en 3 casillas</t>
+          <t>"Agregar bloque" sigue agregando al final</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Seleccionar un bloque y usar el control de Alineación</t>
+          <t>Usar el botón de la zona final del lienzo con un bloque seleccionado arriba</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr"/>
@@ -7101,7 +7101,7 @@
     <row r="199">
       <c r="A199" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-68</t>
+          <t>CP-HTML-72</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
@@ -7111,17 +7111,17 @@
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>La miniatura imita el bloque</t>
+          <t>Fondo de página en el editor</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Comparar el control en un bloque de imagen, uno de botón y uno de texto</t>
+          <t>Ajustes → cambiar "Fondo de página"</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr"/>
@@ -7134,7 +7134,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-69</t>
+          <t>CP-HTML-73</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -7144,17 +7144,17 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Alineación con teclado</t>
+          <t>Color de texto global</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Enfocar el control y usar ←, →, Inicio y Fin</t>
+          <t>Ajustes → cambiar "Color de texto"</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr"/>
@@ -7167,7 +7167,7 @@
     <row r="201">
       <c r="A201" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-64</t>
+          <t>CP-HTML-74</t>
         </is>
       </c>
       <c r="B201" s="8" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>Barra del bloque no tapa</t>
+          <t>Color propio del bloque manda</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Seleccionar un bloque</t>
+          <t>Fijar un color al bloque y cambiar el global</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr"/>
@@ -7200,7 +7200,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>CP-HTML-65</t>
+          <t>CP-HTML-75</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Plantillas prediseñadas</t>
+          <t>Fuente global</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Abrir "Plantillas" y cargar una de las 5 integradas</t>
+          <t>Ajustes → cambiar "Fuente"</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr"/>
@@ -7233,7 +7233,7 @@
     <row r="203">
       <c r="A203" s="7" t="inlineStr">
         <is>
-          <t>CP-HTML-66</t>
+          <t>CP-HTML-76</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
@@ -7243,17 +7243,17 @@
       </c>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>Móvil</t>
+          <t>Publicar guarda las DOS formas</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Abrir el constructor en un móvil</t>
+          <t>Publicar una plantilla → abrir "Cargar"</t>
         </is>
       </c>
       <c r="F203" s="8" t="inlineStr"/>
@@ -7266,12 +7266,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-01</t>
+          <t>CP-HTML-77</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -7281,12 +7281,12 @@
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Editor básico tipo Word</t>
+          <t>Cargar devuelve algo EDITABLE</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
+          <t>Abrir un diseño desde "Cargar"</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr"/>
@@ -7299,27 +7299,27 @@
     <row r="205">
       <c r="A205" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-02</t>
+          <t>CP-HTML-78</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>Vista previa PDF (básico)</t>
+          <t>Republicar no duplica</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>Botón "Vista previa PDF"</t>
+          <t>Abrir un diseño, cambiar algo y Publicar</t>
         </is>
       </c>
       <c r="F205" s="8" t="inlineStr"/>
@@ -7332,27 +7332,27 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-03</t>
+          <t>CP-HTML-79</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Estudio PDF (lienzo)</t>
+          <t>Solo-en-SES lista lo que no tiene diseño</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>Crear un diseño con texto, formas, tabla y guardar</t>
+          <t>Revisar la 2ª sección de "Cargar"</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr"/>
@@ -7365,27 +7365,27 @@
     <row r="207">
       <c r="A207" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-04</t>
+          <t>CP-HTML-80</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C207" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>Estudio: variables con datos reales</t>
+          <t>"Nuevo" cancelado no pierde la identidad</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>Elegir una base en el panel de datos → Vista previa</t>
+          <t>Con un diseño abierto, pulsar Nuevo y CANCELAR el confirm</t>
         </is>
       </c>
       <c r="F207" s="8" t="inlineStr"/>
@@ -7398,12 +7398,12 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-05</t>
+          <t>CP-HTML-67</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Estudio: unidades y reglas</t>
+          <t>Alineación en 3 casillas</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
+          <t>Seleccionar un bloque y usar el control de Alineación</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr"/>
@@ -7431,27 +7431,27 @@
     <row r="209">
       <c r="A209" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-06</t>
+          <t>CP-HTML-68</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>Estudio: seleccionar elemento rotado</t>
+          <t>La miniatura imita el bloque</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>Girar un texto y hacer clic dentro de su caja visual</t>
+          <t>Comparar el control en un bloque de imagen, uno de botón y uno de texto</t>
         </is>
       </c>
       <c r="F209" s="8" t="inlineStr"/>
@@ -7464,27 +7464,27 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-07</t>
+          <t>CP-HTML-69</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Estudio: estilos vinculados</t>
+          <t>Alineación con teclado</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>Vincular un estilo de texto/párrafo y editarlo</t>
+          <t>Enfocar el control y usar ←, →, Inicio y Fin</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr"/>
@@ -7497,12 +7497,12 @@
     <row r="211">
       <c r="A211" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-08</t>
+          <t>CP-HTML-64</t>
         </is>
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C211" s="7" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Diseñador PDF (full)</t>
+          <t>Barra del bloque no tapa</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>Abrir el Diseñador y crear un documento</t>
+          <t>Seleccionar un bloque</t>
         </is>
       </c>
       <c r="F211" s="8" t="inlineStr"/>
@@ -7530,27 +7530,27 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-09</t>
+          <t>CP-HTML-65</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF de punta a punta</t>
+          <t>Plantillas prediseñadas</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
+          <t>Abrir "Plantillas" y cargar una de las 5 integradas</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr"/>
@@ -7563,27 +7563,27 @@
     <row r="213">
       <c r="A213" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-10</t>
+          <t>CP-HTML-66</t>
         </is>
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>Tabla que desborda pagina</t>
+          <t>Móvil</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
+          <t>Abrir el constructor en un móvil</t>
         </is>
       </c>
       <c r="F213" s="8" t="inlineStr"/>
@@ -7596,7 +7596,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-11</t>
+          <t>CP-PDF-01</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7606,17 +7606,17 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Celdas con JSON (multiregistro)</t>
+          <t>Editor básico tipo Word</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Base con una columna que trae un array JSON</t>
+          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr"/>
@@ -7629,7 +7629,7 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-12</t>
+          <t>CP-PDF-02</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
@@ -7639,17 +7639,17 @@
       </c>
       <c r="C215" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Encabezados con BOM/espacios</t>
+          <t>Vista previa PDF (básico)</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
+          <t>Botón "Vista previa PDF"</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr"/>
@@ -7662,7 +7662,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-13</t>
+          <t>CP-PDF-03</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7672,17 +7672,17 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Bordes y degradados</t>
+          <t>Estudio PDF (lienzo)</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>Formas con borde discontinuo y relleno degradado</t>
+          <t>Crear un diseño con texto, formas, tabla y guardar</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr"/>
@@ -7695,12 +7695,12 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-PDF-04</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Estudio: variables con datos reales</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>Elegir una base en el panel de datos → Vista previa</t>
         </is>
       </c>
       <c r="F217" s="8" t="inlineStr"/>
@@ -7728,27 +7728,27 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-PDF-05</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>Estudio: unidades y reglas</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr"/>
@@ -7761,27 +7761,27 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-PDF-06</t>
         </is>
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>Estudio: seleccionar elemento rotado</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Girar un texto y hacer clic dentro de su caja visual</t>
         </is>
       </c>
       <c r="F219" s="8" t="inlineStr"/>
@@ -7794,27 +7794,27 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-PDF-07</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Estudio: estilos vinculados</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Vincular un estilo de texto/párrafo y editarlo</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr"/>
@@ -7827,27 +7827,27 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-PDF-08</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>Diseñador PDF (full)</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Abrir el Diseñador y crear un documento</t>
         </is>
       </c>
       <c r="F221" s="8" t="inlineStr"/>
@@ -7860,27 +7860,27 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-PDF-09</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Campaña EAP-PDF de punta a punta</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr"/>
@@ -7893,27 +7893,27 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-PDF-10</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Tabla que desborda pagina</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
         </is>
       </c>
       <c r="F223" s="8" t="inlineStr"/>
@@ -7926,27 +7926,27 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-PDF-11</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Celdas con JSON (multiregistro)</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>Base con una columna que trae un array JSON</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr"/>
@@ -7959,27 +7959,27 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-PDF-12</t>
         </is>
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>Encabezados con BOM/espacios</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr"/>
@@ -7992,27 +7992,27 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-PDF-13</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Bordes y degradados</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Formas con borde discontinuo y relleno degradado</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr"/>
@@ -8025,7 +8025,7 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
@@ -8035,17 +8035,17 @@
       </c>
       <c r="C227" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr"/>
@@ -8058,7 +8058,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -8068,17 +8068,17 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr"/>
@@ -8091,7 +8091,7 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B229" s="8" t="inlineStr">
@@ -8101,17 +8101,17 @@
       </c>
       <c r="C229" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F229" s="8" t="inlineStr"/>
@@ -8124,7 +8124,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -8134,17 +8134,17 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr"/>
@@ -8157,12 +8157,12 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F231" s="8" t="inlineStr"/>
@@ -8190,27 +8190,27 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr"/>
@@ -8223,12 +8223,12 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F233" s="8" t="inlineStr"/>
@@ -8256,27 +8256,27 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr"/>
@@ -8289,12 +8289,12 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr"/>
@@ -8322,12 +8322,12 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr"/>
@@ -8355,12 +8355,12 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C237" s="7" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr"/>
@@ -8388,27 +8388,27 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr"/>
@@ -8421,27 +8421,27 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C239" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F239" s="8" t="inlineStr"/>
@@ -8454,27 +8454,27 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr"/>
@@ -8487,12 +8487,12 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F241" s="8" t="inlineStr"/>
@@ -8520,27 +8520,27 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr"/>
@@ -8553,27 +8553,27 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C243" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr"/>
@@ -8586,27 +8586,27 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr"/>
@@ -8619,27 +8619,27 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F245" s="8" t="inlineStr"/>
@@ -8652,12 +8652,12 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr"/>
@@ -8685,27 +8685,27 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C247" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F247" s="8" t="inlineStr"/>
@@ -8718,12 +8718,12 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr"/>
@@ -8751,12 +8751,12 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C249" s="7" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F249" s="8" t="inlineStr"/>
@@ -8784,12 +8784,12 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr"/>
@@ -8817,12 +8817,12 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C251" s="7" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F251" s="8" t="inlineStr"/>
@@ -8850,12 +8850,12 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -8865,12 +8865,12 @@
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr"/>
@@ -8883,27 +8883,27 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F253" s="8" t="inlineStr"/>
@@ -8916,12 +8916,12 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr"/>
@@ -8949,27 +8949,27 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C255" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F255" s="8" t="inlineStr"/>
@@ -8982,27 +8982,27 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr"/>
@@ -9015,7 +9015,7 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B257" s="8" t="inlineStr">
@@ -9025,17 +9025,17 @@
       </c>
       <c r="C257" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F257" s="8" t="inlineStr"/>
@@ -9048,7 +9048,7 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr"/>
@@ -9081,7 +9081,7 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B259" s="8" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F259" s="8" t="inlineStr"/>
@@ -9114,7 +9114,7 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B261" s="8" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F261" s="8" t="inlineStr"/>
@@ -9180,7 +9180,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr"/>
@@ -9213,7 +9213,7 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B263" s="8" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F263" s="8" t="inlineStr"/>
@@ -9246,7 +9246,7 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
@@ -9256,17 +9256,17 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr"/>
@@ -9279,12 +9279,12 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F265" s="8" t="inlineStr"/>
@@ -9312,12 +9312,12 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr"/>
@@ -9345,27 +9345,27 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F267" s="8" t="inlineStr"/>
@@ -9378,27 +9378,27 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr"/>
@@ -9411,12 +9411,12 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr"/>
@@ -9444,27 +9444,27 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr"/>
@@ -9477,27 +9477,27 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C271" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr"/>
@@ -9510,27 +9510,27 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr"/>
@@ -9543,27 +9543,27 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C273" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr"/>
@@ -9576,27 +9576,27 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr"/>
@@ -9609,7 +9609,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
@@ -9619,17 +9619,17 @@
       </c>
       <c r="C275" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -9652,17 +9652,17 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr"/>
@@ -9675,7 +9675,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr"/>
@@ -9708,7 +9708,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr"/>
@@ -9741,7 +9741,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
@@ -9751,17 +9751,17 @@
       </c>
       <c r="C279" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -9784,17 +9784,17 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr"/>
@@ -9807,7 +9807,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
@@ -9822,12 +9822,12 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr"/>
@@ -9840,7 +9840,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -9850,17 +9850,17 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr"/>
@@ -9873,7 +9873,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr"/>
@@ -9906,7 +9906,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -9916,17 +9916,17 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr"/>
@@ -9939,7 +9939,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
@@ -9949,17 +9949,17 @@
       </c>
       <c r="C285" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr"/>
@@ -9972,7 +9972,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -9982,17 +9982,17 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr"/>
@@ -10005,7 +10005,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr"/>
@@ -10038,7 +10038,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -10048,17 +10048,17 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr"/>
@@ -10071,7 +10071,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
@@ -10081,17 +10081,17 @@
       </c>
       <c r="C289" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr"/>
@@ -10104,7 +10104,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -10114,17 +10114,17 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr"/>
@@ -10170,12 +10170,12 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr"/>
@@ -10203,12 +10203,12 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C293" s="7" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr"/>
@@ -10236,27 +10236,27 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr"/>
@@ -10269,27 +10269,27 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr"/>
@@ -10302,12 +10302,12 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr"/>
@@ -10335,12 +10335,12 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr"/>
@@ -10368,27 +10368,27 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr"/>
@@ -10401,27 +10401,27 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C299" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr"/>
@@ -10434,27 +10434,27 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr"/>
@@ -10467,12 +10467,12 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr"/>
@@ -10500,7 +10500,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -10510,17 +10510,17 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr"/>
@@ -10533,7 +10533,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr"/>
@@ -10566,7 +10566,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -10576,17 +10576,17 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr"/>
@@ -10599,7 +10599,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr"/>
@@ -10632,27 +10632,27 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr"/>
@@ -10665,27 +10665,27 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr"/>
@@ -10698,12 +10698,12 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr"/>
@@ -10731,12 +10731,12 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr"/>
@@ -10764,27 +10764,27 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr"/>
@@ -10797,12 +10797,12 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C311" s="7" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr"/>
@@ -10830,27 +10830,27 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr"/>
@@ -10863,12 +10863,12 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr"/>
@@ -10896,12 +10896,12 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr"/>
@@ -10929,27 +10929,27 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C315" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr"/>
@@ -10962,7 +10962,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
@@ -10972,17 +10972,17 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr"/>
@@ -10995,27 +10995,27 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C317" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr"/>
@@ -11028,12 +11028,12 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -11043,12 +11043,12 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr"/>
@@ -11061,12 +11061,12 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr"/>
@@ -11094,12 +11094,12 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -11109,12 +11109,12 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr"/>
@@ -11127,27 +11127,27 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr"/>
@@ -11160,27 +11160,27 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr"/>
@@ -11193,27 +11193,27 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr"/>
@@ -11226,27 +11226,27 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr"/>
@@ -11259,27 +11259,27 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr"/>
@@ -11292,27 +11292,27 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr"/>
@@ -11325,7 +11325,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,7 +11358,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -11401,17 +11401,17 @@
       </c>
       <c r="C329" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,7 +11424,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,7 +11457,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -11467,17 +11467,17 @@
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,27 +11490,27 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,27 +11523,27 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,27 +11556,27 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,27 +11589,27 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,27 +11622,27 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,27 +11655,27 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,27 +11688,27 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,27 +11721,27 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,12 +11754,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11787,12 +11787,12 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,7 +11820,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -11830,17 +11830,17 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,7 +11853,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
@@ -11863,17 +11863,17 @@
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,27 +11886,27 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,27 +11919,27 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,12 +11952,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-CAS-05</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Consentimiento por canal</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Contacto sin consentimiento del canal 0</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,12 +11985,12 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-CAS-06</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C347" s="7" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Listado de cascadas</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Abrir el listado</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,12 +12018,12 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-SER-01</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Serie de 30 días (cliente)</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,27 +12051,27 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-SER-02</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Serie global (admin)</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Panel de control → gráfico</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,27 +12084,27 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-SER-03</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Muestras excluidas</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Enviar muestras y revisar la serie</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,27 +12117,27 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-SER-04</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Aislamiento</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Comparar la serie de dos clientes</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12147,13 +12147,343 @@
       <c r="J351" s="6" t="inlineStr"/>
       <c r="K351" s="5" t="inlineStr"/>
     </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-05</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>Adiós "(parcial)"</t>
+        </is>
+      </c>
+      <c r="E352" s="3" t="inlineStr">
+        <is>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+        </is>
+      </c>
+      <c r="F352" s="3" t="inlineStr"/>
+      <c r="G352" s="4" t="inlineStr"/>
+      <c r="H352" s="5" t="inlineStr"/>
+      <c r="I352" s="4" t="inlineStr"/>
+      <c r="J352" s="6" t="inlineStr"/>
+      <c r="K352" s="5" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-06</t>
+        </is>
+      </c>
+      <c r="B353" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C353" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D353" s="8" t="inlineStr">
+        <is>
+          <t>Leyenda interactiva</t>
+        </is>
+      </c>
+      <c r="E353" s="8" t="inlineStr">
+        <is>
+          <t>Ocultar/mostrar series en el gráfico</t>
+        </is>
+      </c>
+      <c r="F353" s="8" t="inlineStr"/>
+      <c r="G353" s="4" t="inlineStr"/>
+      <c r="H353" s="5" t="inlineStr"/>
+      <c r="I353" s="4" t="inlineStr"/>
+      <c r="J353" s="6" t="inlineStr"/>
+      <c r="K353" s="5" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E354" s="3" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F354" s="3" t="inlineStr"/>
+      <c r="G354" s="4" t="inlineStr"/>
+      <c r="H354" s="5" t="inlineStr"/>
+      <c r="I354" s="4" t="inlineStr"/>
+      <c r="J354" s="6" t="inlineStr"/>
+      <c r="K354" s="5" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B355" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C355" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D355" s="8" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E355" s="8" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F355" s="8" t="inlineStr"/>
+      <c r="G355" s="4" t="inlineStr"/>
+      <c r="H355" s="5" t="inlineStr"/>
+      <c r="I355" s="4" t="inlineStr"/>
+      <c r="J355" s="6" t="inlineStr"/>
+      <c r="K355" s="5" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E356" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F356" s="3" t="inlineStr"/>
+      <c r="G356" s="4" t="inlineStr"/>
+      <c r="H356" s="5" t="inlineStr"/>
+      <c r="I356" s="4" t="inlineStr"/>
+      <c r="J356" s="6" t="inlineStr"/>
+      <c r="K356" s="5" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B357" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C357" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D357" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E357" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F357" s="8" t="inlineStr"/>
+      <c r="G357" s="4" t="inlineStr"/>
+      <c r="H357" s="5" t="inlineStr"/>
+      <c r="I357" s="4" t="inlineStr"/>
+      <c r="J357" s="6" t="inlineStr"/>
+      <c r="K357" s="5" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E358" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F358" s="3" t="inlineStr"/>
+      <c r="G358" s="4" t="inlineStr"/>
+      <c r="H358" s="5" t="inlineStr"/>
+      <c r="I358" s="4" t="inlineStr"/>
+      <c r="J358" s="6" t="inlineStr"/>
+      <c r="K358" s="5" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B359" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C359" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D359" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E359" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F359" s="8" t="inlineStr"/>
+      <c r="G359" s="4" t="inlineStr"/>
+      <c r="H359" s="5" t="inlineStr"/>
+      <c r="I359" s="4" t="inlineStr"/>
+      <c r="J359" s="6" t="inlineStr"/>
+      <c r="K359" s="5" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E360" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F360" s="3" t="inlineStr"/>
+      <c r="G360" s="4" t="inlineStr"/>
+      <c r="H360" s="5" t="inlineStr"/>
+      <c r="I360" s="4" t="inlineStr"/>
+      <c r="J360" s="6" t="inlineStr"/>
+      <c r="K360" s="5" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B361" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C361" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D361" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E361" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F361" s="8" t="inlineStr"/>
+      <c r="G361" s="4" t="inlineStr"/>
+      <c r="H361" s="5" t="inlineStr"/>
+      <c r="I361" s="4" t="inlineStr"/>
+      <c r="J361" s="6" t="inlineStr"/>
+      <c r="K361" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K351"/>
+  <autoFilter ref="A1:K361"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H361" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K361" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -12213,7 +12543,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A351)</f>
+        <f>COUNTA(Casos!A2:A361)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -12227,7 +12557,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$351,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$361,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -12244,7 +12574,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$351,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$361,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -12261,7 +12591,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$351,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$361,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -12278,7 +12608,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$351,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$361,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -12334,11 +12664,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$351,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$361,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$351,A12,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$361,A12,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -12351,11 +12681,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$351,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$361,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$351,A13,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$361,A13,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -12368,11 +12698,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$351,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$361,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$351,A14,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$361,A14,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -12430,19 +12760,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A18,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A18,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A18,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A18,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$351,$A18,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$361,$A18,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12453,19 +12783,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A19,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A19,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A19,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A19,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$351,$A19,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$361,$A19,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12476,19 +12806,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A20,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A20,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A20,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A20,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$351,$A20,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$361,$A20,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12499,19 +12829,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A21,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A21,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A21,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A21,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$351,$A21,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$361,$A21,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12522,19 +12852,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A22,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A22,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A22,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A22,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$351,$A22,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$361,$A22,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12545,19 +12875,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A23,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A23,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A23,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A23,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$351,$A23,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$361,$A23,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12568,19 +12898,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A24,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A24,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A24,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A24,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$351,$A24,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$361,$A24,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12591,19 +12921,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A25,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A25,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A25,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A25,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$351,$A25,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$361,$A25,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12614,19 +12944,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A26,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A26,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A26,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A26,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$351,$A26,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$361,$A26,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12637,19 +12967,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A27,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A27,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A27,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A27,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$351,$A27,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$361,$A27,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12660,19 +12990,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A28,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A28,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A28,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A28,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$351,$A28,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$361,$A28,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12683,19 +13013,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A29,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A29,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A29,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A29,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$351,$A29,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$361,$A29,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12706,19 +13036,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A30,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A30,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A30,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A30,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$351,$A30,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$361,$A30,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12729,19 +13059,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A31,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A31,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A31,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A31,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$351,$A31,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$361,$A31,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12752,19 +13082,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A32,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A32,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A32,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A32,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$351,$A32,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$361,$A32,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12775,19 +13105,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A33,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A33,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A33,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A33,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$351,$A33,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$361,$A33,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12798,19 +13128,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A34,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A34,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A34,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A34,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$351,$A34,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$361,$A34,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12821,19 +13151,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A35,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A35,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A35,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A35,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$351,$A35,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$361,$A35,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12844,19 +13174,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A36,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A36,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A36,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A36,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$351,$A36,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$361,$A36,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12867,19 +13197,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A37,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A37,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A37,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A37,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$351,$A37,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$361,$A37,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12890,19 +13220,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A38,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A38,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A38,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A38,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$351,$A38,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$361,$A38,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12913,19 +13243,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$351,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$361,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A39,Casos!$H$2:$H$351,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A39,Casos!$H$2:$H$361,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$351,$A39,Casos!$H$2:$H$351,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$361,$A39,Casos!$H$2:$H$361,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$351,$A39,Casos!$H$2:$H$351,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$361,$A39,Casos!$H$2:$H$361,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$377</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K361"/>
+  <dimension ref="A1:K377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11325,12 +11325,12 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-CAM-01</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Aviso de campaña por aprobar</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,27 +11358,27 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-CAM-02</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Solo a quien puede aprobar</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Revisar la campanita de otro operator del mismo equipo</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,27 +11391,27 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-CAM-03</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Quien la pide no se avisa a sí mismo</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Revisar la campanita del operator que la solicitó</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,27 +11424,27 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-CAM-04</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Aislamiento entre empresas</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Revisar la campanita de un usuario de OTRA empresa</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,12 +11457,12 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-CAM-05</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Aviso de aprobada</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>El owner aprueba la campaña</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,27 +11490,27 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-CAM-06</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Aviso de rechazada con el motivo</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,27 +11523,27 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-CAM-07</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>Saldo bajo in-app</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Hacer un envío que deje el saldo bajo el umbral</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,27 +11556,27 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-CAM-08</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>Avisos nuevos abajo a la derecha</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,12 +11589,12 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-CAM-09</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Los nuevos NO saltan al entrar</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Con avisos viejos sin leer, entrar al portal</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,27 +11622,27 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-CAM-10</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>La tarjeta se retira sola</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Esperar unos segundos tras el aviso</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,12 +11655,12 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-CAM-11</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
@@ -11670,12 +11670,12 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Clic lleva al lugar correcto</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Hacer clic en "Campaña por aprobar"</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,12 +11688,12 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-CAM-12</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Marcar leídas</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Abrir el panel y pulsar "Marcar leídas"</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,12 +11721,12 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-CAM-13</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>No se puede marcar la de otro</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,12 +11754,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-CAM-14</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Sin notificaciones</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Usuario nuevo abre la campanita</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11787,27 +11787,27 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-CAM-15</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>No molesta en impersonación</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Entrar como admin con "Ver como cliente"</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,27 +11820,27 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-CAM-16</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>La aprobación funciona sin la tabla</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,12 +11853,12 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,12 +11886,12 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -11901,12 +11901,12 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,27 +11919,27 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,12 +11952,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,27 +11985,27 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C347" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,27 +12018,27 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,12 +12051,12 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
@@ -12066,12 +12066,12 @@
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,27 +12084,27 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,12 +12117,12 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C351" s="7" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12150,27 +12150,27 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -12183,27 +12183,27 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr"/>
@@ -12216,27 +12216,27 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -12249,27 +12249,27 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr"/>
@@ -12282,12 +12282,12 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -12315,12 +12315,12 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C357" s="7" t="inlineStr">
@@ -12330,12 +12330,12 @@
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr"/>
@@ -12348,12 +12348,12 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -12363,12 +12363,12 @@
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -12381,27 +12381,27 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr"/>
@@ -12414,27 +12414,27 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -12447,27 +12447,27 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr"/>
@@ -12477,13 +12477,541 @@
       <c r="J361" s="6" t="inlineStr"/>
       <c r="K361" s="5" t="inlineStr"/>
     </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>CP-CAS-05</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="inlineStr">
+        <is>
+          <t>Consentimiento por canal</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="inlineStr">
+        <is>
+          <t>Contacto sin consentimiento del canal 0</t>
+        </is>
+      </c>
+      <c r="F362" s="3" t="inlineStr"/>
+      <c r="G362" s="4" t="inlineStr"/>
+      <c r="H362" s="5" t="inlineStr"/>
+      <c r="I362" s="4" t="inlineStr"/>
+      <c r="J362" s="6" t="inlineStr"/>
+      <c r="K362" s="5" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="7" t="inlineStr">
+        <is>
+          <t>CP-CAS-06</t>
+        </is>
+      </c>
+      <c r="B363" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C363" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D363" s="8" t="inlineStr">
+        <is>
+          <t>Listado de cascadas</t>
+        </is>
+      </c>
+      <c r="E363" s="8" t="inlineStr">
+        <is>
+          <t>Abrir el listado</t>
+        </is>
+      </c>
+      <c r="F363" s="8" t="inlineStr"/>
+      <c r="G363" s="4" t="inlineStr"/>
+      <c r="H363" s="5" t="inlineStr"/>
+      <c r="I363" s="4" t="inlineStr"/>
+      <c r="J363" s="6" t="inlineStr"/>
+      <c r="K363" s="5" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-01</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D364" s="3" t="inlineStr">
+        <is>
+          <t>Serie de 30 días (cliente)</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="inlineStr">
+        <is>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+        </is>
+      </c>
+      <c r="F364" s="3" t="inlineStr"/>
+      <c r="G364" s="4" t="inlineStr"/>
+      <c r="H364" s="5" t="inlineStr"/>
+      <c r="I364" s="4" t="inlineStr"/>
+      <c r="J364" s="6" t="inlineStr"/>
+      <c r="K364" s="5" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-02</t>
+        </is>
+      </c>
+      <c r="B365" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C365" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D365" s="8" t="inlineStr">
+        <is>
+          <t>Serie global (admin)</t>
+        </is>
+      </c>
+      <c r="E365" s="8" t="inlineStr">
+        <is>
+          <t>Panel de control → gráfico</t>
+        </is>
+      </c>
+      <c r="F365" s="8" t="inlineStr"/>
+      <c r="G365" s="4" t="inlineStr"/>
+      <c r="H365" s="5" t="inlineStr"/>
+      <c r="I365" s="4" t="inlineStr"/>
+      <c r="J365" s="6" t="inlineStr"/>
+      <c r="K365" s="5" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-03</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>Muestras excluidas</t>
+        </is>
+      </c>
+      <c r="E366" s="3" t="inlineStr">
+        <is>
+          <t>Enviar muestras y revisar la serie</t>
+        </is>
+      </c>
+      <c r="F366" s="3" t="inlineStr"/>
+      <c r="G366" s="4" t="inlineStr"/>
+      <c r="H366" s="5" t="inlineStr"/>
+      <c r="I366" s="4" t="inlineStr"/>
+      <c r="J366" s="6" t="inlineStr"/>
+      <c r="K366" s="5" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-04</t>
+        </is>
+      </c>
+      <c r="B367" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C367" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D367" s="8" t="inlineStr">
+        <is>
+          <t>Aislamiento</t>
+        </is>
+      </c>
+      <c r="E367" s="8" t="inlineStr">
+        <is>
+          <t>Comparar la serie de dos clientes</t>
+        </is>
+      </c>
+      <c r="F367" s="8" t="inlineStr"/>
+      <c r="G367" s="4" t="inlineStr"/>
+      <c r="H367" s="5" t="inlineStr"/>
+      <c r="I367" s="4" t="inlineStr"/>
+      <c r="J367" s="6" t="inlineStr"/>
+      <c r="K367" s="5" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-05</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D368" s="3" t="inlineStr">
+        <is>
+          <t>Adiós "(parcial)"</t>
+        </is>
+      </c>
+      <c r="E368" s="3" t="inlineStr">
+        <is>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+        </is>
+      </c>
+      <c r="F368" s="3" t="inlineStr"/>
+      <c r="G368" s="4" t="inlineStr"/>
+      <c r="H368" s="5" t="inlineStr"/>
+      <c r="I368" s="4" t="inlineStr"/>
+      <c r="J368" s="6" t="inlineStr"/>
+      <c r="K368" s="5" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-06</t>
+        </is>
+      </c>
+      <c r="B369" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C369" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D369" s="8" t="inlineStr">
+        <is>
+          <t>Leyenda interactiva</t>
+        </is>
+      </c>
+      <c r="E369" s="8" t="inlineStr">
+        <is>
+          <t>Ocultar/mostrar series en el gráfico</t>
+        </is>
+      </c>
+      <c r="F369" s="8" t="inlineStr"/>
+      <c r="G369" s="4" t="inlineStr"/>
+      <c r="H369" s="5" t="inlineStr"/>
+      <c r="I369" s="4" t="inlineStr"/>
+      <c r="J369" s="6" t="inlineStr"/>
+      <c r="K369" s="5" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D370" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E370" s="3" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F370" s="3" t="inlineStr"/>
+      <c r="G370" s="4" t="inlineStr"/>
+      <c r="H370" s="5" t="inlineStr"/>
+      <c r="I370" s="4" t="inlineStr"/>
+      <c r="J370" s="6" t="inlineStr"/>
+      <c r="K370" s="5" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B371" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C371" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D371" s="8" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E371" s="8" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F371" s="8" t="inlineStr"/>
+      <c r="G371" s="4" t="inlineStr"/>
+      <c r="H371" s="5" t="inlineStr"/>
+      <c r="I371" s="4" t="inlineStr"/>
+      <c r="J371" s="6" t="inlineStr"/>
+      <c r="K371" s="5" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D372" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E372" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F372" s="3" t="inlineStr"/>
+      <c r="G372" s="4" t="inlineStr"/>
+      <c r="H372" s="5" t="inlineStr"/>
+      <c r="I372" s="4" t="inlineStr"/>
+      <c r="J372" s="6" t="inlineStr"/>
+      <c r="K372" s="5" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B373" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C373" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D373" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E373" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F373" s="8" t="inlineStr"/>
+      <c r="G373" s="4" t="inlineStr"/>
+      <c r="H373" s="5" t="inlineStr"/>
+      <c r="I373" s="4" t="inlineStr"/>
+      <c r="J373" s="6" t="inlineStr"/>
+      <c r="K373" s="5" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D374" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E374" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F374" s="3" t="inlineStr"/>
+      <c r="G374" s="4" t="inlineStr"/>
+      <c r="H374" s="5" t="inlineStr"/>
+      <c r="I374" s="4" t="inlineStr"/>
+      <c r="J374" s="6" t="inlineStr"/>
+      <c r="K374" s="5" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B375" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C375" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D375" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E375" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F375" s="8" t="inlineStr"/>
+      <c r="G375" s="4" t="inlineStr"/>
+      <c r="H375" s="5" t="inlineStr"/>
+      <c r="I375" s="4" t="inlineStr"/>
+      <c r="J375" s="6" t="inlineStr"/>
+      <c r="K375" s="5" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D376" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E376" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F376" s="3" t="inlineStr"/>
+      <c r="G376" s="4" t="inlineStr"/>
+      <c r="H376" s="5" t="inlineStr"/>
+      <c r="I376" s="4" t="inlineStr"/>
+      <c r="J376" s="6" t="inlineStr"/>
+      <c r="K376" s="5" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B377" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C377" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D377" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E377" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F377" s="8" t="inlineStr"/>
+      <c r="G377" s="4" t="inlineStr"/>
+      <c r="H377" s="5" t="inlineStr"/>
+      <c r="I377" s="4" t="inlineStr"/>
+      <c r="J377" s="6" t="inlineStr"/>
+      <c r="K377" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K361"/>
+  <autoFilter ref="A1:K377"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H361" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H377" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K361" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K377" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -12543,7 +13071,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A361)</f>
+        <f>COUNTA(Casos!A2:A377)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -12557,7 +13085,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$361,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$377,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -12574,7 +13102,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$361,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$377,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -12591,7 +13119,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$361,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$377,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -12608,7 +13136,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$361,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$377,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -12664,11 +13192,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$361,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$377,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$361,A12,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$377,A12,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -12681,11 +13209,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$361,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$377,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$361,A13,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$377,A13,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -12698,11 +13226,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$361,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$377,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$361,A14,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$377,A14,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -12760,19 +13288,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A18,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A18,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A18,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A18,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$361,$A18,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$377,$A18,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12783,19 +13311,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A19,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A19,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A19,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A19,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$361,$A19,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$377,$A19,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12806,19 +13334,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A20,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A20,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A20,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A20,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$361,$A20,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$377,$A20,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12829,19 +13357,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A21,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A21,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A21,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A21,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$361,$A21,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$377,$A21,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12852,19 +13380,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A22,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A22,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A22,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A22,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$361,$A22,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$377,$A22,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12875,19 +13403,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A23,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A23,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A23,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A23,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$361,$A23,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$377,$A23,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12898,19 +13426,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A24,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A24,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A24,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A24,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$361,$A24,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$377,$A24,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12921,19 +13449,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A25,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A25,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A25,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A25,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$361,$A25,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$377,$A25,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12944,19 +13472,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A26,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A26,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A26,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A26,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$361,$A26,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$377,$A26,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12967,19 +13495,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A27,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A27,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A27,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A27,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$361,$A27,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$377,$A27,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -12990,19 +13518,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A28,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A28,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A28,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A28,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$361,$A28,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$377,$A28,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13013,19 +13541,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A29,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A29,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A29,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A29,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$361,$A29,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$377,$A29,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13036,19 +13564,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A30,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A30,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A30,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A30,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$361,$A30,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$377,$A30,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13059,19 +13587,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A31,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A31,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A31,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A31,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$361,$A31,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$377,$A31,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13082,19 +13610,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A32,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A32,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A32,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A32,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$361,$A32,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$377,$A32,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13105,19 +13633,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A33,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A33,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A33,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A33,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$361,$A33,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$377,$A33,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13128,19 +13656,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A34,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A34,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A34,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A34,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$361,$A34,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$377,$A34,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13151,19 +13679,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A35,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A35,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A35,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A35,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$361,$A35,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$377,$A35,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13174,19 +13702,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A36,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A36,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A36,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A36,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$361,$A36,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$377,$A36,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13197,19 +13725,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A37,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A37,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A37,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A37,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$361,$A37,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$377,$A37,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13220,19 +13748,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A38,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A38,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A38,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A38,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$361,$A38,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$377,$A38,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13243,19 +13771,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$361,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$377,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A39,Casos!$H$2:$H$361,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A39,Casos!$H$2:$H$377,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$361,$A39,Casos!$H$2:$H$361,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$377,$A39,Casos!$H$2:$H$377,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$361,$A39,Casos!$H$2:$H$361,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$377,$A39,Casos!$H$2:$H$377,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$377</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$401</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K377"/>
+  <dimension ref="A1:K401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7596,12 +7596,12 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-01</t>
+          <t>CP-TXT-01</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Editor básico tipo Word</t>
+          <t>La barra de formato se ve sin buscarla</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
+          <t>Seleccionar un bloque de texto en el lienzo</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr"/>
@@ -7629,12 +7629,12 @@
     <row r="215">
       <c r="A215" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-02</t>
+          <t>CP-TXT-02</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Vista previa PDF (básico)</t>
+          <t>No se recorta en el primer bloque</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>Botón "Vista previa PDF"</t>
+          <t>Agregar texto como PRIMER bloque del correo y seleccionarlo</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr"/>
@@ -7662,27 +7662,27 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-03</t>
+          <t>CP-TXT-03</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Estudio PDF (lienzo)</t>
+          <t>Todas las herramientas visibles</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>Crear un diseño con texto, formas, tabla y guardar</t>
+          <t>Mirar la barra en un bloque angosto</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr"/>
@@ -7695,12 +7695,12 @@
     <row r="217">
       <c r="A217" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-04</t>
+          <t>CP-TXT-04</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>Estudio: variables con datos reales</t>
+          <t>Negrita/color sobre una palabra</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>Elegir una base en el panel de datos → Vista previa</t>
+          <t>Seleccionar una palabra → Negrita → color</t>
         </is>
       </c>
       <c r="F217" s="8" t="inlineStr"/>
@@ -7728,12 +7728,12 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-05</t>
+          <t>CP-TXT-05</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Estudio: unidades y reglas</t>
+          <t>Botones que reflejan el estado</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
+          <t>Poner el cursor dentro de una palabra en negrita</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr"/>
@@ -7761,12 +7761,12 @@
     <row r="219">
       <c r="A219" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-06</t>
+          <t>CP-TXT-06</t>
         </is>
       </c>
       <c r="B219" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
@@ -7776,12 +7776,12 @@
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>Estudio: seleccionar elemento rotado</t>
+          <t>Resaltado</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>Girar un texto y hacer clic dentro de su caja visual</t>
+          <t>Seleccionar texto → botón de resaltar → elegir color</t>
         </is>
       </c>
       <c r="F219" s="8" t="inlineStr"/>
@@ -7794,12 +7794,12 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-07</t>
+          <t>CP-TXT-07</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Estudio: estilos vinculados</t>
+          <t>Familia de fuente</t>
         </is>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>Vincular un estilo de texto/párrafo y editarlo</t>
+          <t>Seleccionar texto → Fuente → Georgia</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr"/>
@@ -7827,12 +7827,12 @@
     <row r="221">
       <c r="A221" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-08</t>
+          <t>CP-TXT-08</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Diseñador PDF (full)</t>
+          <t>El cursor no salta</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>Abrir el Diseñador y crear un documento</t>
+          <t>Escribir varias palabras seguidas al final del texto</t>
         </is>
       </c>
       <c r="F221" s="8" t="inlineStr"/>
@@ -7860,27 +7860,27 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-09</t>
+          <t>CP-TXT-09</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF de punta a punta</t>
+          <t>Pegar desde Word</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
+          <t>Pegar texto con formato de Word</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr"/>
@@ -7893,12 +7893,12 @@
     <row r="223">
       <c r="A223" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-10</t>
+          <t>CP-RED-01</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Tabla que desborda pagina</t>
+          <t>Los iconos son los logos REALES</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
+          <t>Agregar bloque de Redes y mirar el panel de propiedades</t>
         </is>
       </c>
       <c r="F223" s="8" t="inlineStr"/>
@@ -7926,12 +7926,12 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-11</t>
+          <t>CP-RED-02</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>Celdas con JSON (multiregistro)</t>
+          <t>"Colores de cada red" ya no se ofrece</t>
         </is>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>Base con una columna que trae un array JSON</t>
+          <t>Abrir el desplegable Estilo</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr"/>
@@ -7959,12 +7959,12 @@
     <row r="225">
       <c r="A225" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-12</t>
+          <t>CP-RED-03</t>
         </is>
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Encabezados con BOM/espacios</t>
+          <t>Plantilla vieja con ese estilo</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
+          <t>Cargar un diseño guardado con "Colores de cada red"</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr"/>
@@ -7992,27 +7992,27 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-13</t>
+          <t>CP-RED-04</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>Bordes y degradados</t>
+          <t>Contorno para logos oscuros</t>
         </is>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>Formas con borde discontinuo y relleno degradado</t>
+          <t>Activar "Contorno" y elegir un color claro</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr"/>
@@ -8025,12 +8025,12 @@
     <row r="227">
       <c r="A227" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-RED-05</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Aviso de icono invisible</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>Poner color de marca oscuro Y color de logo oscuro → "Revisar"</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr"/>
@@ -8058,27 +8058,27 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-RED-06</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>Logo blanco no dispara el aviso</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Color de marca oscuro + logo blanco → "Revisar"</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr"/>
@@ -8091,27 +8091,27 @@
     <row r="229">
       <c r="A229" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-RED-07</t>
         </is>
       </c>
       <c r="B229" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>Alineación de los iconos</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Alinear a izquierda / derecha</t>
         </is>
       </c>
       <c r="F229" s="8" t="inlineStr"/>
@@ -8124,12 +8124,12 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-PDF-01</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -8139,12 +8139,12 @@
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Editor básico tipo Word</t>
         </is>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr"/>
@@ -8157,12 +8157,12 @@
     <row r="231">
       <c r="A231" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-PDF-02</t>
         </is>
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>Vista previa PDF (básico)</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Botón "Vista previa PDF"</t>
         </is>
       </c>
       <c r="F231" s="8" t="inlineStr"/>
@@ -8190,27 +8190,27 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-PDF-03</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Estudio PDF (lienzo)</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Crear un diseño con texto, formas, tabla y guardar</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr"/>
@@ -8223,27 +8223,27 @@
     <row r="233">
       <c r="A233" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-PDF-04</t>
         </is>
       </c>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Estudio: variables con datos reales</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>Elegir una base en el panel de datos → Vista previa</t>
         </is>
       </c>
       <c r="F233" s="8" t="inlineStr"/>
@@ -8256,27 +8256,27 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-PDF-05</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Estudio: unidades y reglas</t>
         </is>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr"/>
@@ -8289,27 +8289,27 @@
     <row r="235">
       <c r="A235" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-PDF-06</t>
         </is>
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>Estudio: seleccionar elemento rotado</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Girar un texto y hacer clic dentro de su caja visual</t>
         </is>
       </c>
       <c r="F235" s="8" t="inlineStr"/>
@@ -8322,12 +8322,12 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-PDF-07</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Estudio: estilos vinculados</t>
         </is>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Vincular un estilo de texto/párrafo y editarlo</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr"/>
@@ -8355,12 +8355,12 @@
     <row r="237">
       <c r="A237" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-PDF-08</t>
         </is>
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C237" s="7" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Diseñador PDF (full)</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Abrir el Diseñador y crear un documento</t>
         </is>
       </c>
       <c r="F237" s="8" t="inlineStr"/>
@@ -8388,27 +8388,27 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-PDF-09</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Campaña EAP-PDF de punta a punta</t>
         </is>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr"/>
@@ -8421,27 +8421,27 @@
     <row r="239">
       <c r="A239" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-PDF-10</t>
         </is>
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C239" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Tabla que desborda pagina</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
         </is>
       </c>
       <c r="F239" s="8" t="inlineStr"/>
@@ -8454,12 +8454,12 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-PDF-11</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Celdas con JSON (multiregistro)</t>
         </is>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Base con una columna que trae un array JSON</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr"/>
@@ -8487,27 +8487,27 @@
     <row r="241">
       <c r="A241" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-PDF-12</t>
         </is>
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Encabezados con BOM/espacios</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
         </is>
       </c>
       <c r="F241" s="8" t="inlineStr"/>
@@ -8520,27 +8520,27 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-PDF-13</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Bordes y degradados</t>
         </is>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Formas con borde discontinuo y relleno degradado</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr"/>
@@ -8553,27 +8553,27 @@
     <row r="243">
       <c r="A243" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C243" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F243" s="8" t="inlineStr"/>
@@ -8586,27 +8586,27 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr"/>
@@ -8619,12 +8619,12 @@
     <row r="245">
       <c r="A245" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F245" s="8" t="inlineStr"/>
@@ -8652,27 +8652,27 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr"/>
@@ -8685,27 +8685,27 @@
     <row r="247">
       <c r="A247" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C247" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F247" s="8" t="inlineStr"/>
@@ -8718,27 +8718,27 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr"/>
@@ -8751,27 +8751,27 @@
     <row r="249">
       <c r="A249" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C249" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F249" s="8" t="inlineStr"/>
@@ -8784,12 +8784,12 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr"/>
@@ -8817,12 +8817,12 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C251" s="7" t="inlineStr">
@@ -8832,12 +8832,12 @@
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F251" s="8" t="inlineStr"/>
@@ -8850,12 +8850,12 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -8865,12 +8865,12 @@
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr"/>
@@ -8883,27 +8883,27 @@
     <row r="253">
       <c r="A253" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F253" s="8" t="inlineStr"/>
@@ -8916,27 +8916,27 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr"/>
@@ -8949,12 +8949,12 @@
     <row r="255">
       <c r="A255" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C255" s="7" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F255" s="8" t="inlineStr"/>
@@ -8982,12 +8982,12 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr"/>
@@ -9015,12 +9015,12 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C257" s="7" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F257" s="8" t="inlineStr"/>
@@ -9048,12 +9048,12 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr"/>
@@ -9081,27 +9081,27 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F259" s="8" t="inlineStr"/>
@@ -9114,27 +9114,27 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr"/>
@@ -9147,12 +9147,12 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F261" s="8" t="inlineStr"/>
@@ -9180,12 +9180,12 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr"/>
@@ -9213,12 +9213,12 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F263" s="8" t="inlineStr"/>
@@ -9246,12 +9246,12 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr"/>
@@ -9279,12 +9279,12 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F265" s="8" t="inlineStr"/>
@@ -9312,12 +9312,12 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr"/>
@@ -9345,27 +9345,27 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F267" s="8" t="inlineStr"/>
@@ -9378,27 +9378,27 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr"/>
@@ -9411,12 +9411,12 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr"/>
@@ -9444,12 +9444,12 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr"/>
@@ -9477,27 +9477,27 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C271" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr"/>
@@ -9510,12 +9510,12 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr"/>
@@ -9543,7 +9543,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
@@ -9553,17 +9553,17 @@
       </c>
       <c r="C273" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr"/>
@@ -9576,7 +9576,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -9586,17 +9586,17 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr"/>
@@ -9609,12 +9609,12 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C275" s="7" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr"/>
@@ -9642,12 +9642,12 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr"/>
@@ -9675,12 +9675,12 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C277" s="7" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr"/>
@@ -9708,12 +9708,12 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr"/>
@@ -9741,27 +9741,27 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C279" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr"/>
@@ -9774,27 +9774,27 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr"/>
@@ -9807,27 +9807,27 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C281" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr"/>
@@ -9840,27 +9840,27 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr"/>
@@ -9873,27 +9873,27 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C283" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr"/>
@@ -9906,12 +9906,12 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr"/>
@@ -9939,27 +9939,27 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C285" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr"/>
@@ -9972,27 +9972,27 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr"/>
@@ -10005,12 +10005,12 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C287" s="7" t="inlineStr">
@@ -10020,12 +10020,12 @@
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr"/>
@@ -10038,12 +10038,12 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr"/>
@@ -10071,12 +10071,12 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C289" s="7" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr"/>
@@ -10104,27 +10104,27 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
@@ -10147,17 +10147,17 @@
       </c>
       <c r="C291" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr"/>
@@ -10170,7 +10170,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr"/>
@@ -10203,7 +10203,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr"/>
@@ -10236,7 +10236,7 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr"/>
@@ -10269,7 +10269,7 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr"/>
@@ -10302,7 +10302,7 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr"/>
@@ -10335,7 +10335,7 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
@@ -10345,17 +10345,17 @@
       </c>
       <c r="C297" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
@@ -10378,17 +10378,17 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr"/>
@@ -10434,7 +10434,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -10444,17 +10444,17 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr"/>
@@ -10467,7 +10467,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr"/>
@@ -10500,27 +10500,27 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr"/>
@@ -10533,12 +10533,12 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr"/>
@@ -10566,27 +10566,27 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr"/>
@@ -10599,12 +10599,12 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C305" s="7" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr"/>
@@ -10632,27 +10632,27 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr"/>
@@ -10665,27 +10665,27 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr"/>
@@ -10698,27 +10698,27 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr"/>
@@ -10731,27 +10731,27 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr"/>
@@ -10764,27 +10764,27 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr"/>
@@ -10797,27 +10797,27 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C311" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr"/>
@@ -10830,12 +10830,12 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr"/>
@@ -10863,12 +10863,12 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr"/>
@@ -10896,27 +10896,27 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr"/>
@@ -10929,27 +10929,27 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C315" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr"/>
@@ -10962,27 +10962,27 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr"/>
@@ -10995,12 +10995,12 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C317" s="7" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr"/>
@@ -11028,27 +11028,27 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr"/>
@@ -11061,27 +11061,27 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr"/>
@@ -11094,27 +11094,27 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr"/>
@@ -11127,12 +11127,12 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr"/>
@@ -11160,27 +11160,27 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr"/>
@@ -11193,12 +11193,12 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr"/>
@@ -11226,12 +11226,12 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -11241,12 +11241,12 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr"/>
@@ -11259,27 +11259,27 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr"/>
@@ -11292,27 +11292,27 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr"/>
@@ -11325,27 +11325,27 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-01</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Aviso de campaña por aprobar</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,27 +11358,27 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-02</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Solo a quien puede aprobar</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de otro operator del mismo equipo</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,12 +11391,12 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-03</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
@@ -11406,12 +11406,12 @@
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>Quien la pide no se avisa a sí mismo</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita del operator que la solicitó</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,27 +11424,27 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-04</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento entre empresas</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de un usuario de OTRA empresa</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,27 +11457,27 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-05</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Aviso de aprobada</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>El owner aprueba la campaña</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,7 +11490,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-06</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Aviso de rechazada con el motivo</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,7 +11523,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-07</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -11533,17 +11533,17 @@
       </c>
       <c r="C333" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>Saldo bajo in-app</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Hacer un envío que deje el saldo bajo el umbral</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,7 +11556,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-08</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Avisos nuevos abajo a la derecha</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,7 +11589,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-09</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Los nuevos NO saltan al entrar</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Con avisos viejos sin leer, entrar al portal</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,7 +11622,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-10</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>La tarjeta se retira sola</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Esperar unos segundos tras el aviso</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-11</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
@@ -11665,17 +11665,17 @@
       </c>
       <c r="C337" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Clic lleva al lugar correcto</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Hacer clic en "Campaña por aprobar"</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,7 +11688,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-12</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
@@ -11698,17 +11698,17 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Marcar leídas</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Abrir el panel y pulsar "Marcar leídas"</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,7 +11721,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-13</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>No se puede marcar la de otro</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,7 +11754,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-14</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Sin notificaciones</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Usuario nuevo abre la campanita</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11787,7 +11787,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-15</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
@@ -11797,17 +11797,17 @@
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>No molesta en impersonación</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Entrar como admin con "Ver como cliente"</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,7 +11820,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-16</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -11830,17 +11830,17 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>La aprobación funciona sin la tabla</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,12 +11853,12 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-CAM-01</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Aviso de campaña por aprobar</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,27 +11886,27 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-CAM-02</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Solo a quien puede aprobar</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Revisar la campanita de otro operator del mismo equipo</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,27 +11919,27 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-CAM-03</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Quien la pide no se avisa a sí mismo</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Revisar la campanita del operator que la solicitó</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,27 +11952,27 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-CAM-04</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Aislamiento entre empresas</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Revisar la campanita de un usuario de OTRA empresa</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,12 +11985,12 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-CAM-05</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C347" s="7" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Aviso de aprobada</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>El owner aprueba la campaña</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,27 +12018,27 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-CAM-06</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Aviso de rechazada con el motivo</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,27 +12051,27 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-CAM-07</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>Saldo bajo in-app</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Hacer un envío que deje el saldo bajo el umbral</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,27 +12084,27 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-CAM-08</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>Avisos nuevos abajo a la derecha</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,12 +12117,12 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-CAM-09</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C351" s="7" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Los nuevos NO saltan al entrar</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Con avisos viejos sin leer, entrar al portal</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12150,27 +12150,27 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-CAM-10</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>La tarjeta se retira sola</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Esperar unos segundos tras el aviso</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -12183,12 +12183,12 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-CAM-11</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C353" s="7" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Clic lleva al lugar correcto</t>
         </is>
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Hacer clic en "Campaña por aprobar"</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr"/>
@@ -12216,12 +12216,12 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-CAM-12</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Marcar leídas</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Abrir el panel y pulsar "Marcar leídas"</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -12249,12 +12249,12 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-CAM-13</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C355" s="7" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>No se puede marcar la de otro</t>
         </is>
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr"/>
@@ -12282,12 +12282,12 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-CAM-14</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Sin notificaciones</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Usuario nuevo abre la campanita</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -12315,27 +12315,27 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-CAM-15</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>No molesta en impersonación</t>
         </is>
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Entrar como admin con "Ver como cliente"</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr"/>
@@ -12348,27 +12348,27 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-CAM-16</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>La aprobación funciona sin la tabla</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -12381,12 +12381,12 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr"/>
@@ -12414,12 +12414,12 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -12447,27 +12447,27 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr"/>
@@ -12480,12 +12480,12 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
@@ -12513,27 +12513,27 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B363" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr"/>
@@ -12546,27 +12546,27 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr"/>
@@ -12579,12 +12579,12 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B365" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C365" s="7" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr"/>
@@ -12612,27 +12612,27 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr"/>
@@ -12645,12 +12645,12 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B367" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C367" s="7" t="inlineStr">
@@ -12660,12 +12660,12 @@
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr"/>
@@ -12678,27 +12678,27 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr"/>
@@ -12711,27 +12711,27 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B369" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr"/>
@@ -12744,27 +12744,27 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr"/>
@@ -12777,27 +12777,27 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B371" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr"/>
@@ -12810,12 +12810,12 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr"/>
@@ -12843,12 +12843,12 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C373" s="7" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr"/>
@@ -12876,12 +12876,12 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-TAR-01</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Segmentos calculados, no declarados</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Muestras con una campaña SMS</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
@@ -12909,27 +12909,27 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-TAR-02</t>
         </is>
       </c>
       <c r="B375" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Un SMS largo cuesta el doble</t>
         </is>
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Campaña con más de 160 caracteres</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr"/>
@@ -12942,27 +12942,27 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-TAR-03</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Una emoji parte el mensaje</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr"/>
@@ -12975,27 +12975,27 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-TAR-04</t>
         </is>
       </c>
       <c r="B377" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Lo estimado es lo que se cobra</t>
         </is>
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr"/>
@@ -13005,13 +13005,805 @@
       <c r="J377" s="6" t="inlineStr"/>
       <c r="K377" s="5" t="inlineStr"/>
     </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>CP-TAR-05</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="inlineStr">
+        <is>
+          <t>Higiene, límites de uso y costo del adjunto</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D378" s="3" t="inlineStr">
+        <is>
+          <t>Tarifas nuevas visibles</t>
+        </is>
+      </c>
+      <c r="E378" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Tarifas → canal SMS y Voz</t>
+        </is>
+      </c>
+      <c r="F378" s="3" t="inlineStr"/>
+      <c r="G378" s="4" t="inlineStr"/>
+      <c r="H378" s="5" t="inlineStr"/>
+      <c r="I378" s="4" t="inlineStr"/>
+      <c r="J378" s="6" t="inlineStr"/>
+      <c r="K378" s="5" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="7" t="inlineStr">
+        <is>
+          <t>CP-TAR-06</t>
+        </is>
+      </c>
+      <c r="B379" s="8" t="inlineStr">
+        <is>
+          <t>Higiene, límites de uso y costo del adjunto</t>
+        </is>
+      </c>
+      <c r="C379" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D379" s="8" t="inlineStr">
+        <is>
+          <t>Ningún cliente por debajo del costo</t>
+        </is>
+      </c>
+      <c r="E379" s="8" t="inlineStr">
+        <is>
+          <t>Admin → Tarifas → revisar overrides por cliente</t>
+        </is>
+      </c>
+      <c r="F379" s="8" t="inlineStr"/>
+      <c r="G379" s="4" t="inlineStr"/>
+      <c r="H379" s="5" t="inlineStr"/>
+      <c r="I379" s="4" t="inlineStr"/>
+      <c r="J379" s="6" t="inlineStr"/>
+      <c r="K379" s="5" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>CP-TAR-07</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="inlineStr">
+        <is>
+          <t>Higiene, límites de uso y costo del adjunto</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
+          <t>Contador del editor SMS</t>
+        </is>
+      </c>
+      <c r="E380" s="3" t="inlineStr">
+        <is>
+          <t>Escribir un SMS con emoji en Plantillas SMS</t>
+        </is>
+      </c>
+      <c r="F380" s="3" t="inlineStr"/>
+      <c r="G380" s="4" t="inlineStr"/>
+      <c r="H380" s="5" t="inlineStr"/>
+      <c r="I380" s="4" t="inlineStr"/>
+      <c r="J380" s="6" t="inlineStr"/>
+      <c r="K380" s="5" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="7" t="inlineStr">
+        <is>
+          <t>CP-PUB-01</t>
+        </is>
+      </c>
+      <c r="B381" s="8" t="inlineStr">
+        <is>
+          <t>Higiene, límites de uso y costo del adjunto</t>
+        </is>
+      </c>
+      <c r="C381" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D381" s="8" t="inlineStr">
+        <is>
+          <t>La landing no publica precios</t>
+        </is>
+      </c>
+      <c r="E381" s="8" t="inlineStr">
+        <is>
+          <t>Abrir la landing → sección Precios</t>
+        </is>
+      </c>
+      <c r="F381" s="8" t="inlineStr"/>
+      <c r="G381" s="4" t="inlineStr"/>
+      <c r="H381" s="5" t="inlineStr"/>
+      <c r="I381" s="4" t="inlineStr"/>
+      <c r="J381" s="6" t="inlineStr"/>
+      <c r="K381" s="5" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>CP-CAS-01</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D382" s="3" t="inlineStr">
+        <is>
+          <t>Lanzar cascada</t>
+        </is>
+      </c>
+      <c r="E382" s="3" t="inlineStr">
+        <is>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+        </is>
+      </c>
+      <c r="F382" s="3" t="inlineStr"/>
+      <c r="G382" s="4" t="inlineStr"/>
+      <c r="H382" s="5" t="inlineStr"/>
+      <c r="I382" s="4" t="inlineStr"/>
+      <c r="J382" s="6" t="inlineStr"/>
+      <c r="K382" s="5" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="7" t="inlineStr">
+        <is>
+          <t>CP-CAS-02</t>
+        </is>
+      </c>
+      <c r="B383" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C383" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D383" s="8" t="inlineStr">
+        <is>
+          <t>Escalado al siguiente canal</t>
+        </is>
+      </c>
+      <c r="E383" s="8" t="inlineStr">
+        <is>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
+        </is>
+      </c>
+      <c r="F383" s="8" t="inlineStr"/>
+      <c r="G383" s="4" t="inlineStr"/>
+      <c r="H383" s="5" t="inlineStr"/>
+      <c r="I383" s="4" t="inlineStr"/>
+      <c r="J383" s="6" t="inlineStr"/>
+      <c r="K383" s="5" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>CP-CAS-03</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D384" s="3" t="inlineStr">
+        <is>
+          <t>Confirmado no escala</t>
+        </is>
+      </c>
+      <c r="E384" s="3" t="inlineStr">
+        <is>
+          <t>Contacto que sí cumple el criterio</t>
+        </is>
+      </c>
+      <c r="F384" s="3" t="inlineStr"/>
+      <c r="G384" s="4" t="inlineStr"/>
+      <c r="H384" s="5" t="inlineStr"/>
+      <c r="I384" s="4" t="inlineStr"/>
+      <c r="J384" s="6" t="inlineStr"/>
+      <c r="K384" s="5" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="7" t="inlineStr">
+        <is>
+          <t>CP-CAS-04</t>
+        </is>
+      </c>
+      <c r="B385" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C385" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D385" s="8" t="inlineStr">
+        <is>
+          <t>Saldo insuficiente</t>
+        </is>
+      </c>
+      <c r="E385" s="8" t="inlineStr">
+        <is>
+          <t>Cascada sin saldo</t>
+        </is>
+      </c>
+      <c r="F385" s="8" t="inlineStr"/>
+      <c r="G385" s="4" t="inlineStr"/>
+      <c r="H385" s="5" t="inlineStr"/>
+      <c r="I385" s="4" t="inlineStr"/>
+      <c r="J385" s="6" t="inlineStr"/>
+      <c r="K385" s="5" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>CP-CAS-05</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>Consentimiento por canal</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="inlineStr">
+        <is>
+          <t>Contacto sin consentimiento del canal 0</t>
+        </is>
+      </c>
+      <c r="F386" s="3" t="inlineStr"/>
+      <c r="G386" s="4" t="inlineStr"/>
+      <c r="H386" s="5" t="inlineStr"/>
+      <c r="I386" s="4" t="inlineStr"/>
+      <c r="J386" s="6" t="inlineStr"/>
+      <c r="K386" s="5" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="7" t="inlineStr">
+        <is>
+          <t>CP-CAS-06</t>
+        </is>
+      </c>
+      <c r="B387" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C387" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D387" s="8" t="inlineStr">
+        <is>
+          <t>Listado de cascadas</t>
+        </is>
+      </c>
+      <c r="E387" s="8" t="inlineStr">
+        <is>
+          <t>Abrir el listado</t>
+        </is>
+      </c>
+      <c r="F387" s="8" t="inlineStr"/>
+      <c r="G387" s="4" t="inlineStr"/>
+      <c r="H387" s="5" t="inlineStr"/>
+      <c r="I387" s="4" t="inlineStr"/>
+      <c r="J387" s="6" t="inlineStr"/>
+      <c r="K387" s="5" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-01</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>Serie de 30 días (cliente)</t>
+        </is>
+      </c>
+      <c r="E388" s="3" t="inlineStr">
+        <is>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+        </is>
+      </c>
+      <c r="F388" s="3" t="inlineStr"/>
+      <c r="G388" s="4" t="inlineStr"/>
+      <c r="H388" s="5" t="inlineStr"/>
+      <c r="I388" s="4" t="inlineStr"/>
+      <c r="J388" s="6" t="inlineStr"/>
+      <c r="K388" s="5" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-02</t>
+        </is>
+      </c>
+      <c r="B389" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C389" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D389" s="8" t="inlineStr">
+        <is>
+          <t>Serie global (admin)</t>
+        </is>
+      </c>
+      <c r="E389" s="8" t="inlineStr">
+        <is>
+          <t>Panel de control → gráfico</t>
+        </is>
+      </c>
+      <c r="F389" s="8" t="inlineStr"/>
+      <c r="G389" s="4" t="inlineStr"/>
+      <c r="H389" s="5" t="inlineStr"/>
+      <c r="I389" s="4" t="inlineStr"/>
+      <c r="J389" s="6" t="inlineStr"/>
+      <c r="K389" s="5" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-03</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D390" s="3" t="inlineStr">
+        <is>
+          <t>Muestras excluidas</t>
+        </is>
+      </c>
+      <c r="E390" s="3" t="inlineStr">
+        <is>
+          <t>Enviar muestras y revisar la serie</t>
+        </is>
+      </c>
+      <c r="F390" s="3" t="inlineStr"/>
+      <c r="G390" s="4" t="inlineStr"/>
+      <c r="H390" s="5" t="inlineStr"/>
+      <c r="I390" s="4" t="inlineStr"/>
+      <c r="J390" s="6" t="inlineStr"/>
+      <c r="K390" s="5" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-04</t>
+        </is>
+      </c>
+      <c r="B391" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C391" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D391" s="8" t="inlineStr">
+        <is>
+          <t>Aislamiento</t>
+        </is>
+      </c>
+      <c r="E391" s="8" t="inlineStr">
+        <is>
+          <t>Comparar la serie de dos clientes</t>
+        </is>
+      </c>
+      <c r="F391" s="8" t="inlineStr"/>
+      <c r="G391" s="4" t="inlineStr"/>
+      <c r="H391" s="5" t="inlineStr"/>
+      <c r="I391" s="4" t="inlineStr"/>
+      <c r="J391" s="6" t="inlineStr"/>
+      <c r="K391" s="5" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-05</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D392" s="3" t="inlineStr">
+        <is>
+          <t>Adiós "(parcial)"</t>
+        </is>
+      </c>
+      <c r="E392" s="3" t="inlineStr">
+        <is>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+        </is>
+      </c>
+      <c r="F392" s="3" t="inlineStr"/>
+      <c r="G392" s="4" t="inlineStr"/>
+      <c r="H392" s="5" t="inlineStr"/>
+      <c r="I392" s="4" t="inlineStr"/>
+      <c r="J392" s="6" t="inlineStr"/>
+      <c r="K392" s="5" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-06</t>
+        </is>
+      </c>
+      <c r="B393" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C393" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D393" s="8" t="inlineStr">
+        <is>
+          <t>Leyenda interactiva</t>
+        </is>
+      </c>
+      <c r="E393" s="8" t="inlineStr">
+        <is>
+          <t>Ocultar/mostrar series en el gráfico</t>
+        </is>
+      </c>
+      <c r="F393" s="8" t="inlineStr"/>
+      <c r="G393" s="4" t="inlineStr"/>
+      <c r="H393" s="5" t="inlineStr"/>
+      <c r="I393" s="4" t="inlineStr"/>
+      <c r="J393" s="6" t="inlineStr"/>
+      <c r="K393" s="5" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D394" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E394" s="3" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F394" s="3" t="inlineStr"/>
+      <c r="G394" s="4" t="inlineStr"/>
+      <c r="H394" s="5" t="inlineStr"/>
+      <c r="I394" s="4" t="inlineStr"/>
+      <c r="J394" s="6" t="inlineStr"/>
+      <c r="K394" s="5" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B395" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C395" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D395" s="8" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E395" s="8" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F395" s="8" t="inlineStr"/>
+      <c r="G395" s="4" t="inlineStr"/>
+      <c r="H395" s="5" t="inlineStr"/>
+      <c r="I395" s="4" t="inlineStr"/>
+      <c r="J395" s="6" t="inlineStr"/>
+      <c r="K395" s="5" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D396" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E396" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F396" s="3" t="inlineStr"/>
+      <c r="G396" s="4" t="inlineStr"/>
+      <c r="H396" s="5" t="inlineStr"/>
+      <c r="I396" s="4" t="inlineStr"/>
+      <c r="J396" s="6" t="inlineStr"/>
+      <c r="K396" s="5" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B397" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C397" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D397" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E397" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F397" s="8" t="inlineStr"/>
+      <c r="G397" s="4" t="inlineStr"/>
+      <c r="H397" s="5" t="inlineStr"/>
+      <c r="I397" s="4" t="inlineStr"/>
+      <c r="J397" s="6" t="inlineStr"/>
+      <c r="K397" s="5" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D398" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E398" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F398" s="3" t="inlineStr"/>
+      <c r="G398" s="4" t="inlineStr"/>
+      <c r="H398" s="5" t="inlineStr"/>
+      <c r="I398" s="4" t="inlineStr"/>
+      <c r="J398" s="6" t="inlineStr"/>
+      <c r="K398" s="5" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B399" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C399" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D399" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E399" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F399" s="8" t="inlineStr"/>
+      <c r="G399" s="4" t="inlineStr"/>
+      <c r="H399" s="5" t="inlineStr"/>
+      <c r="I399" s="4" t="inlineStr"/>
+      <c r="J399" s="6" t="inlineStr"/>
+      <c r="K399" s="5" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D400" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E400" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F400" s="3" t="inlineStr"/>
+      <c r="G400" s="4" t="inlineStr"/>
+      <c r="H400" s="5" t="inlineStr"/>
+      <c r="I400" s="4" t="inlineStr"/>
+      <c r="J400" s="6" t="inlineStr"/>
+      <c r="K400" s="5" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B401" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C401" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D401" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E401" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F401" s="8" t="inlineStr"/>
+      <c r="G401" s="4" t="inlineStr"/>
+      <c r="H401" s="5" t="inlineStr"/>
+      <c r="I401" s="4" t="inlineStr"/>
+      <c r="J401" s="6" t="inlineStr"/>
+      <c r="K401" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K377"/>
+  <autoFilter ref="A1:K401"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H377" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K377" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -13071,7 +13863,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A377)</f>
+        <f>COUNTA(Casos!A2:A401)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -13085,7 +13877,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$377,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$401,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -13102,7 +13894,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$377,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$401,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -13119,7 +13911,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$377,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$401,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -13136,7 +13928,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$377,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$401,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -13192,11 +13984,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$377,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$401,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$377,A12,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$401,A12,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -13209,11 +14001,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$377,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$401,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$377,A13,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$401,A13,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -13226,11 +14018,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$377,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$401,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$377,A14,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$401,A14,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -13288,19 +14080,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A18,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A18,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A18,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A18,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$377,$A18,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$401,$A18,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13311,19 +14103,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A19,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A19,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A19,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A19,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$377,$A19,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$401,$A19,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13334,19 +14126,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A20,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A20,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A20,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A20,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$377,$A20,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$401,$A20,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13357,19 +14149,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A21,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A21,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A21,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A21,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$377,$A21,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$401,$A21,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13380,19 +14172,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A22,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A22,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A22,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A22,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$377,$A22,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$401,$A22,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13403,19 +14195,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A23,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A23,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A23,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A23,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$377,$A23,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$401,$A23,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13426,19 +14218,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A24,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A24,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A24,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A24,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$377,$A24,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$401,$A24,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13449,19 +14241,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A25,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A25,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A25,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A25,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$377,$A25,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$401,$A25,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13472,19 +14264,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A26,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A26,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A26,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A26,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$377,$A26,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$401,$A26,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13495,19 +14287,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A27,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A27,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A27,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A27,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$377,$A27,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$401,$A27,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13518,19 +14310,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A28,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A28,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A28,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A28,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$377,$A28,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$401,$A28,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13541,19 +14333,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A29,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A29,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A29,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A29,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$377,$A29,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$401,$A29,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13564,19 +14356,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A30,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A30,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A30,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A30,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$377,$A30,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$401,$A30,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13587,19 +14379,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A31,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A31,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A31,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A31,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$377,$A31,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$401,$A31,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13610,19 +14402,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A32,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A32,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A32,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A32,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$377,$A32,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$401,$A32,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13633,19 +14425,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A33,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A33,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A33,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A33,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$377,$A33,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$401,$A33,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13656,19 +14448,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A34,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A34,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A34,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A34,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$377,$A34,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$401,$A34,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13679,19 +14471,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A35,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A35,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A35,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A35,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$377,$A35,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$401,$A35,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13702,19 +14494,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A36,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A36,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A36,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A36,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$377,$A36,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$401,$A36,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13725,19 +14517,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A37,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A37,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A37,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A37,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$377,$A37,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$401,$A37,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13748,19 +14540,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A38,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A38,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A38,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A38,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$377,$A38,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$401,$A38,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -13771,19 +14563,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$377,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$401,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A39,Casos!$H$2:$H$377,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A39,Casos!$H$2:$H$401,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$377,$A39,Casos!$H$2:$H$377,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$401,$A39,Casos!$H$2:$H$401,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$377,$A39,Casos!$H$2:$H$377,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$401,$A39,Casos!$H$2:$H$401,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$415</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K401"/>
+  <dimension ref="A1:K415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13140,12 +13140,12 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-SEO-01</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -13155,12 +13155,12 @@
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>Título e idioma</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Ver el código fuente de la landing</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr"/>
@@ -13173,12 +13173,12 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-SEO-02</t>
         </is>
       </c>
       <c r="B383" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C383" s="7" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Vista previa al compartir</t>
         </is>
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr"/>
@@ -13206,12 +13206,12 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-SEO-03</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Favicon</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Abrir la landing y mirar la pestaña</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr"/>
@@ -13239,27 +13239,27 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-SEO-04</t>
         </is>
       </c>
       <c r="B385" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Icono en iOS</t>
         </is>
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>"Añadir a pantalla de inicio" desde Safari</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr"/>
@@ -13272,12 +13272,12 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-SEO-05</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Datos estructurados</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr"/>
@@ -13305,12 +13305,12 @@
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-SEO-06</t>
         </is>
       </c>
       <c r="B387" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C387" s="7" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Canonical y robots</t>
         </is>
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Abrir /robots.txt y /sitemap.xml</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr"/>
@@ -13338,12 +13338,12 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-LAN-01</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Tabla de precios por canal</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Landing → Precios</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr"/>
@@ -13371,12 +13371,12 @@
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-LAN-02</t>
         </is>
       </c>
       <c r="B389" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C389" s="7" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>Letra pequeña de precios</t>
         </is>
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Leer bajo la tabla</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr"/>
@@ -13404,12 +13404,12 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-LAN-03</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>Icono de WhatsApp</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Sección Canales</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr"/>
@@ -13437,12 +13437,12 @@
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-LAN-04</t>
         </is>
       </c>
       <c r="B391" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C391" s="7" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Sin promesa de 500 correos</t>
         </is>
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Recorrer toda la landing</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr"/>
@@ -13470,27 +13470,27 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-LAN-05</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Footer sin enlaces rotos</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Hacer clic en cada enlace del footer</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr"/>
@@ -13503,27 +13503,27 @@
     <row r="393">
       <c r="A393" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-A11Y-01</t>
         </is>
       </c>
       <c r="B393" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Cerrar el modal con teclado</t>
         </is>
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Abrir /?activacion=ok y pulsar Escape</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr"/>
@@ -13536,27 +13536,27 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-A11Y-02</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Foco en el modal</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Abrir /?activacion=ok y pulsar Tab</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr"/>
@@ -13569,12 +13569,12 @@
     <row r="395">
       <c r="A395" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-A11Y-03</t>
         </is>
       </c>
       <c r="B395" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C395" s="7" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Lector de pantalla</t>
         </is>
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Abrir el modal con un lector activo</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr"/>
@@ -13602,27 +13602,27 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr"/>
@@ -13635,27 +13635,27 @@
     <row r="397">
       <c r="A397" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B397" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C397" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr"/>
@@ -13668,27 +13668,27 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr"/>
@@ -13701,27 +13701,27 @@
     <row r="399">
       <c r="A399" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B399" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr"/>
@@ -13734,27 +13734,27 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-CAS-05</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Consentimiento por canal</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Contacto sin consentimiento del canal 0</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr"/>
@@ -13767,27 +13767,27 @@
     <row r="401">
       <c r="A401" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-CAS-06</t>
         </is>
       </c>
       <c r="B401" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Listado de cascadas</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Abrir el listado</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr"/>
@@ -13797,13 +13797,475 @@
       <c r="J401" s="6" t="inlineStr"/>
       <c r="K401" s="5" t="inlineStr"/>
     </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-01</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D402" s="3" t="inlineStr">
+        <is>
+          <t>Serie de 30 días (cliente)</t>
+        </is>
+      </c>
+      <c r="E402" s="3" t="inlineStr">
+        <is>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+        </is>
+      </c>
+      <c r="F402" s="3" t="inlineStr"/>
+      <c r="G402" s="4" t="inlineStr"/>
+      <c r="H402" s="5" t="inlineStr"/>
+      <c r="I402" s="4" t="inlineStr"/>
+      <c r="J402" s="6" t="inlineStr"/>
+      <c r="K402" s="5" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-02</t>
+        </is>
+      </c>
+      <c r="B403" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C403" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D403" s="8" t="inlineStr">
+        <is>
+          <t>Serie global (admin)</t>
+        </is>
+      </c>
+      <c r="E403" s="8" t="inlineStr">
+        <is>
+          <t>Panel de control → gráfico</t>
+        </is>
+      </c>
+      <c r="F403" s="8" t="inlineStr"/>
+      <c r="G403" s="4" t="inlineStr"/>
+      <c r="H403" s="5" t="inlineStr"/>
+      <c r="I403" s="4" t="inlineStr"/>
+      <c r="J403" s="6" t="inlineStr"/>
+      <c r="K403" s="5" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-03</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D404" s="3" t="inlineStr">
+        <is>
+          <t>Muestras excluidas</t>
+        </is>
+      </c>
+      <c r="E404" s="3" t="inlineStr">
+        <is>
+          <t>Enviar muestras y revisar la serie</t>
+        </is>
+      </c>
+      <c r="F404" s="3" t="inlineStr"/>
+      <c r="G404" s="4" t="inlineStr"/>
+      <c r="H404" s="5" t="inlineStr"/>
+      <c r="I404" s="4" t="inlineStr"/>
+      <c r="J404" s="6" t="inlineStr"/>
+      <c r="K404" s="5" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-04</t>
+        </is>
+      </c>
+      <c r="B405" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C405" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D405" s="8" t="inlineStr">
+        <is>
+          <t>Aislamiento</t>
+        </is>
+      </c>
+      <c r="E405" s="8" t="inlineStr">
+        <is>
+          <t>Comparar la serie de dos clientes</t>
+        </is>
+      </c>
+      <c r="F405" s="8" t="inlineStr"/>
+      <c r="G405" s="4" t="inlineStr"/>
+      <c r="H405" s="5" t="inlineStr"/>
+      <c r="I405" s="4" t="inlineStr"/>
+      <c r="J405" s="6" t="inlineStr"/>
+      <c r="K405" s="5" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-05</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D406" s="3" t="inlineStr">
+        <is>
+          <t>Adiós "(parcial)"</t>
+        </is>
+      </c>
+      <c r="E406" s="3" t="inlineStr">
+        <is>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+        </is>
+      </c>
+      <c r="F406" s="3" t="inlineStr"/>
+      <c r="G406" s="4" t="inlineStr"/>
+      <c r="H406" s="5" t="inlineStr"/>
+      <c r="I406" s="4" t="inlineStr"/>
+      <c r="J406" s="6" t="inlineStr"/>
+      <c r="K406" s="5" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-06</t>
+        </is>
+      </c>
+      <c r="B407" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C407" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D407" s="8" t="inlineStr">
+        <is>
+          <t>Leyenda interactiva</t>
+        </is>
+      </c>
+      <c r="E407" s="8" t="inlineStr">
+        <is>
+          <t>Ocultar/mostrar series en el gráfico</t>
+        </is>
+      </c>
+      <c r="F407" s="8" t="inlineStr"/>
+      <c r="G407" s="4" t="inlineStr"/>
+      <c r="H407" s="5" t="inlineStr"/>
+      <c r="I407" s="4" t="inlineStr"/>
+      <c r="J407" s="6" t="inlineStr"/>
+      <c r="K407" s="5" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D408" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E408" s="3" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F408" s="3" t="inlineStr"/>
+      <c r="G408" s="4" t="inlineStr"/>
+      <c r="H408" s="5" t="inlineStr"/>
+      <c r="I408" s="4" t="inlineStr"/>
+      <c r="J408" s="6" t="inlineStr"/>
+      <c r="K408" s="5" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B409" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C409" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D409" s="8" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E409" s="8" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F409" s="8" t="inlineStr"/>
+      <c r="G409" s="4" t="inlineStr"/>
+      <c r="H409" s="5" t="inlineStr"/>
+      <c r="I409" s="4" t="inlineStr"/>
+      <c r="J409" s="6" t="inlineStr"/>
+      <c r="K409" s="5" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D410" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E410" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F410" s="3" t="inlineStr"/>
+      <c r="G410" s="4" t="inlineStr"/>
+      <c r="H410" s="5" t="inlineStr"/>
+      <c r="I410" s="4" t="inlineStr"/>
+      <c r="J410" s="6" t="inlineStr"/>
+      <c r="K410" s="5" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B411" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C411" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D411" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E411" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F411" s="8" t="inlineStr"/>
+      <c r="G411" s="4" t="inlineStr"/>
+      <c r="H411" s="5" t="inlineStr"/>
+      <c r="I411" s="4" t="inlineStr"/>
+      <c r="J411" s="6" t="inlineStr"/>
+      <c r="K411" s="5" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D412" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E412" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F412" s="3" t="inlineStr"/>
+      <c r="G412" s="4" t="inlineStr"/>
+      <c r="H412" s="5" t="inlineStr"/>
+      <c r="I412" s="4" t="inlineStr"/>
+      <c r="J412" s="6" t="inlineStr"/>
+      <c r="K412" s="5" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B413" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C413" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D413" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E413" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F413" s="8" t="inlineStr"/>
+      <c r="G413" s="4" t="inlineStr"/>
+      <c r="H413" s="5" t="inlineStr"/>
+      <c r="I413" s="4" t="inlineStr"/>
+      <c r="J413" s="6" t="inlineStr"/>
+      <c r="K413" s="5" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D414" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E414" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F414" s="3" t="inlineStr"/>
+      <c r="G414" s="4" t="inlineStr"/>
+      <c r="H414" s="5" t="inlineStr"/>
+      <c r="I414" s="4" t="inlineStr"/>
+      <c r="J414" s="6" t="inlineStr"/>
+      <c r="K414" s="5" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B415" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C415" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D415" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E415" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F415" s="8" t="inlineStr"/>
+      <c r="G415" s="4" t="inlineStr"/>
+      <c r="H415" s="5" t="inlineStr"/>
+      <c r="I415" s="4" t="inlineStr"/>
+      <c r="J415" s="6" t="inlineStr"/>
+      <c r="K415" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K401"/>
+  <autoFilter ref="A1:K415"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H415" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K401" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K415" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -13863,7 +14325,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A401)</f>
+        <f>COUNTA(Casos!A2:A415)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -13877,7 +14339,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$401,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$415,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -13894,7 +14356,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$401,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$415,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -13911,7 +14373,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$401,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$415,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -13928,7 +14390,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$401,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$415,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -13984,11 +14446,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$401,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$415,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$401,A12,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$415,A12,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -14001,11 +14463,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$401,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$415,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$401,A13,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$415,A13,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -14018,11 +14480,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$401,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$415,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$401,A14,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$415,A14,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -14080,19 +14542,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A18,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A18,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A18,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A18,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$401,$A18,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$415,$A18,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14103,19 +14565,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A19,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A19,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A19,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A19,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$401,$A19,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$415,$A19,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14126,19 +14588,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A20,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A20,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A20,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A20,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$401,$A20,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$415,$A20,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14149,19 +14611,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A21,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A21,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A21,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A21,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$401,$A21,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$415,$A21,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14172,19 +14634,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A22,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A22,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A22,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A22,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$401,$A22,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$415,$A22,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14195,19 +14657,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A23,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A23,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A23,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A23,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$401,$A23,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$415,$A23,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14218,19 +14680,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A24,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A24,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A24,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A24,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$401,$A24,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$415,$A24,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14241,19 +14703,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A25,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A25,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A25,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A25,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$401,$A25,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$415,$A25,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14264,19 +14726,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A26,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A26,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A26,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A26,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$401,$A26,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$415,$A26,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14287,19 +14749,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A27,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A27,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A27,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A27,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$401,$A27,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$415,$A27,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14310,19 +14772,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A28,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A28,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A28,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A28,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$401,$A28,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$415,$A28,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14333,19 +14795,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A29,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A29,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A29,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A29,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$401,$A29,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$415,$A29,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14356,19 +14818,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A30,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A30,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A30,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A30,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$401,$A30,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$415,$A30,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14379,19 +14841,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A31,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A31,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A31,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A31,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$401,$A31,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$415,$A31,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14402,19 +14864,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A32,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A32,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A32,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A32,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$401,$A32,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$415,$A32,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14425,19 +14887,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A33,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A33,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A33,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A33,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$401,$A33,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$415,$A33,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14448,19 +14910,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A34,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A34,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A34,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A34,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$401,$A34,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$415,$A34,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14471,19 +14933,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A35,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A35,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A35,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A35,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$401,$A35,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$415,$A35,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14494,19 +14956,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A36,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A36,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A36,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A36,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$401,$A36,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$415,$A36,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14517,19 +14979,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A37,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A37,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A37,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A37,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$401,$A37,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$415,$A37,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14540,19 +15002,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A38,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A38,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A38,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A38,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$401,$A38,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$415,$A38,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14563,19 +15025,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$401,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$415,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A39,Casos!$H$2:$H$401,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A39,Casos!$H$2:$H$415,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$401,$A39,Casos!$H$2:$H$401,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$415,$A39,Casos!$H$2:$H$415,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$401,$A39,Casos!$H$2:$H$401,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$415,$A39,Casos!$H$2:$H$415,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$415</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$423</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K415"/>
+  <dimension ref="A1:K423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9543,12 +9543,12 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-AUT-01</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C273" s="7" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>DKIM verificado en verde</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Abrir el detalle de un dominio con DKIM firmando</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr"/>
@@ -9576,27 +9576,27 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-AUT-02</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>SPF/DMARC sin publicar en gris</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Abrir el detalle de un dominio recién creado</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr"/>
@@ -9609,27 +9609,27 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-AUT-03</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C275" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>SPF verde al publicarlo</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr"/>
@@ -9642,27 +9642,27 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-AUT-04</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>DMARC verde al publicarlo</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr"/>
@@ -9675,27 +9675,27 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-AUT-05</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C277" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>Tooltip explica el motivo</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Pasar el mouse sobre un chip gris</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr"/>
@@ -9708,27 +9708,27 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-AUT-06</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>Sin el layer de DNS</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr"/>
@@ -9741,27 +9741,27 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-AUT-07</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C279" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>Correos sueltos sin el panel</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr"/>
@@ -9774,27 +9774,27 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-AUT-08</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>No es bloqueante</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr"/>
@@ -9807,7 +9807,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
@@ -9822,12 +9822,12 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr"/>
@@ -9840,7 +9840,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr"/>
@@ -9873,7 +9873,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
@@ -9883,17 +9883,17 @@
       </c>
       <c r="C283" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr"/>
@@ -9906,7 +9906,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr"/>
@@ -9939,7 +9939,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr"/>
@@ -9972,7 +9972,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -9982,17 +9982,17 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr"/>
@@ -10005,7 +10005,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
@@ -10015,17 +10015,17 @@
       </c>
       <c r="C287" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr"/>
@@ -10038,7 +10038,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -10048,17 +10048,17 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr"/>
@@ -10071,7 +10071,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
@@ -10081,17 +10081,17 @@
       </c>
       <c r="C289" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr"/>
@@ -10104,7 +10104,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -10114,17 +10114,17 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr"/>
@@ -10137,27 +10137,27 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C291" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr"/>
@@ -10170,12 +10170,12 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr"/>
@@ -10203,12 +10203,12 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C293" s="7" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr"/>
@@ -10236,27 +10236,27 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr"/>
@@ -10269,12 +10269,12 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr"/>
@@ -10302,12 +10302,12 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr"/>
@@ -10335,12 +10335,12 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr"/>
@@ -10368,27 +10368,27 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr"/>
@@ -10401,7 +10401,7 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr"/>
@@ -10434,7 +10434,7 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr"/>
@@ -10467,7 +10467,7 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
@@ -10477,17 +10477,17 @@
       </c>
       <c r="C301" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr"/>
@@ -10500,7 +10500,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -10510,17 +10510,17 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr"/>
@@ -10533,7 +10533,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr"/>
@@ -10566,7 +10566,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr"/>
@@ -10599,7 +10599,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr"/>
@@ -10632,7 +10632,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -10642,17 +10642,17 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr"/>
@@ -10665,7 +10665,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
@@ -10675,17 +10675,17 @@
       </c>
       <c r="C307" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr"/>
@@ -10698,7 +10698,7 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr"/>
@@ -10731,7 +10731,7 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
@@ -10741,17 +10741,17 @@
       </c>
       <c r="C309" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
@@ -10774,17 +10774,17 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr"/>
@@ -10797,7 +10797,7 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr"/>
@@ -10830,7 +10830,7 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr"/>
@@ -10863,7 +10863,7 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
@@ -10873,17 +10873,17 @@
       </c>
       <c r="C313" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr"/>
@@ -10896,7 +10896,7 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr"/>
@@ -10929,7 +10929,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
@@ -10939,17 +10939,17 @@
       </c>
       <c r="C315" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr"/>
@@ -10962,7 +10962,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
@@ -10972,17 +10972,17 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr"/>
@@ -10995,7 +10995,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="C317" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr"/>
@@ -11028,27 +11028,27 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr"/>
@@ -11061,12 +11061,12 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr"/>
@@ -11094,27 +11094,27 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr"/>
@@ -11127,27 +11127,27 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr"/>
@@ -11160,27 +11160,27 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr"/>
@@ -11193,12 +11193,12 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr"/>
@@ -11226,12 +11226,12 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -11241,12 +11241,12 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr"/>
@@ -11259,12 +11259,12 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr"/>
@@ -11325,7 +11325,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -11335,17 +11335,17 @@
       </c>
       <c r="C327" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,7 +11358,7 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
@@ -11368,17 +11368,17 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,7 +11391,7 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
@@ -11401,17 +11401,17 @@
       </c>
       <c r="C329" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,7 +11424,7 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,7 +11457,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -11467,17 +11467,17 @@
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,27 +11490,27 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,12 +11523,12 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,27 +11556,27 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,12 +11589,12 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,12 +11622,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,27 +11655,27 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,27 +11688,27 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,27 +11721,27 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,7 +11754,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
@@ -11764,17 +11764,17 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11787,7 +11787,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
@@ -11797,17 +11797,17 @@
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,7 +11820,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,7 +11853,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-01</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
@@ -11863,17 +11863,17 @@
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>Aviso de campaña por aprobar</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,7 +11886,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-02</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
@@ -11896,17 +11896,17 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Solo a quien puede aprobar</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de otro operator del mismo equipo</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,7 +11919,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-03</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
@@ -11929,17 +11929,17 @@
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Quien la pide no se avisa a sí mismo</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita del operator que la solicitó</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,7 +11952,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-04</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento entre empresas</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de un usuario de OTRA empresa</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-05</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Aviso de aprobada</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>El owner aprueba la campaña</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,7 +12018,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-06</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
@@ -12028,17 +12028,17 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Aviso de rechazada con el motivo</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,7 +12051,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-07</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
@@ -12066,12 +12066,12 @@
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>Saldo bajo in-app</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Hacer un envío que deje el saldo bajo el umbral</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,7 +12084,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-08</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Avisos nuevos abajo a la derecha</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,7 +12117,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-09</t>
+          <t>CP-CAM-01</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>Los nuevos NO saltan al entrar</t>
+          <t>Aviso de campaña por aprobar</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Con avisos viejos sin leer, entrar al portal</t>
+          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12150,7 +12150,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-10</t>
+          <t>CP-CAM-02</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
@@ -12160,17 +12160,17 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>La tarjeta se retira sola</t>
+          <t>Solo a quien puede aprobar</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Esperar unos segundos tras el aviso</t>
+          <t>Revisar la campanita de otro operator del mismo equipo</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -12183,7 +12183,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-11</t>
+          <t>CP-CAM-03</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>Clic lleva al lugar correcto</t>
+          <t>Quien la pide no se avisa a sí mismo</t>
         </is>
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Hacer clic en "Campaña por aprobar"</t>
+          <t>Revisar la campanita del operator que la solicitó</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr"/>
@@ -12216,7 +12216,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-12</t>
+          <t>CP-CAM-04</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -12226,17 +12226,17 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Marcar leídas</t>
+          <t>Aislamiento entre empresas</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>Abrir el panel y pulsar "Marcar leídas"</t>
+          <t>Revisar la campanita de un usuario de OTRA empresa</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -12249,7 +12249,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-13</t>
+          <t>CP-CAM-05</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>No se puede marcar la de otro</t>
+          <t>Aviso de aprobada</t>
         </is>
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
+          <t>El owner aprueba la campaña</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr"/>
@@ -12282,7 +12282,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-14</t>
+          <t>CP-CAM-06</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>Sin notificaciones</t>
+          <t>Aviso de rechazada con el motivo</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>Usuario nuevo abre la campanita</t>
+          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -12315,7 +12315,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-15</t>
+          <t>CP-CAM-07</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
@@ -12325,17 +12325,17 @@
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>No molesta en impersonación</t>
+          <t>Saldo bajo in-app</t>
         </is>
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Entrar como admin con "Ver como cliente"</t>
+          <t>Hacer un envío que deje el saldo bajo el umbral</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr"/>
@@ -12348,7 +12348,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-16</t>
+          <t>CP-CAM-08</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -12358,17 +12358,17 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>La aprobación funciona sin la tabla</t>
+          <t>Avisos nuevos abajo a la derecha</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
+          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -12381,27 +12381,27 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-CAM-09</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Los nuevos NO saltan al entrar</t>
         </is>
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Con avisos viejos sin leer, entrar al portal</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr"/>
@@ -12414,12 +12414,12 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-CAM-10</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>La tarjeta se retira sola</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Esperar unos segundos tras el aviso</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -12447,27 +12447,27 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-CAM-11</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Clic lleva al lugar correcto</t>
         </is>
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Hacer clic en "Campaña por aprobar"</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr"/>
@@ -12480,12 +12480,12 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-CAM-12</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Marcar leídas</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Abrir el panel y pulsar "Marcar leídas"</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
@@ -12513,12 +12513,12 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-CAM-13</t>
         </is>
       </c>
       <c r="B363" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C363" s="7" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>No se puede marcar la de otro</t>
         </is>
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr"/>
@@ -12546,12 +12546,12 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-CAM-14</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Sin notificaciones</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>Usuario nuevo abre la campanita</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr"/>
@@ -12579,27 +12579,27 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-CAM-15</t>
         </is>
       </c>
       <c r="B365" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>No molesta en impersonación</t>
         </is>
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Entrar como admin con "Ver como cliente"</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr"/>
@@ -12612,12 +12612,12 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-CAM-16</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>La aprobación funciona sin la tabla</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B367" s="8" t="inlineStr">
@@ -12655,17 +12655,17 @@
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr"/>
@@ -12678,7 +12678,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
@@ -12688,17 +12688,17 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr"/>
@@ -12711,7 +12711,7 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B369" s="8" t="inlineStr">
@@ -12721,17 +12721,17 @@
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr"/>
@@ -12744,7 +12744,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr"/>
@@ -12777,7 +12777,7 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B371" s="8" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr"/>
@@ -12810,7 +12810,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr"/>
@@ -12843,7 +12843,7 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr"/>
@@ -12876,7 +12876,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-01</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -12886,17 +12886,17 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>Segmentos calculados, no declarados</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>Muestras con una campaña SMS</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-02</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B375" s="8" t="inlineStr">
@@ -12919,17 +12919,17 @@
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>Un SMS largo cuesta el doble</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Campaña con más de 160 caracteres</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr"/>
@@ -12942,7 +12942,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-03</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Una emoji parte el mensaje</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-04</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B377" s="8" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>Lo estimado es lo que se cobra</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr"/>
@@ -13008,7 +13008,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-05</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -13018,17 +13018,17 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Tarifas nuevas visibles</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → canal SMS y Voz</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr"/>
@@ -13041,7 +13041,7 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-06</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B379" s="8" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>Ningún cliente por debajo del costo</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → revisar overrides por cliente</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr"/>
@@ -13074,7 +13074,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-07</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
@@ -13089,12 +13089,12 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>Contador del editor SMS</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>Escribir un SMS con emoji en Plantillas SMS</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr"/>
@@ -13107,7 +13107,7 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>CP-PUB-01</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B381" s="8" t="inlineStr">
@@ -13122,12 +13122,12 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>La landing no publica precios</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Abrir la landing → sección Precios</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr"/>
@@ -13140,7 +13140,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-01</t>
+          <t>CP-TAR-01</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
@@ -13155,12 +13155,12 @@
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>Título e idioma</t>
+          <t>Segmentos calculados, no declarados</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>Ver el código fuente de la landing</t>
+          <t>Muestras con una campaña SMS</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr"/>
@@ -13173,7 +13173,7 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-02</t>
+          <t>CP-TAR-02</t>
         </is>
       </c>
       <c r="B383" s="8" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>Vista previa al compartir</t>
+          <t>Un SMS largo cuesta el doble</t>
         </is>
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
+          <t>Campaña con más de 160 caracteres</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr"/>
@@ -13206,7 +13206,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-03</t>
+          <t>CP-TAR-03</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
@@ -13216,17 +13216,17 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Una emoji parte el mensaje</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>Abrir la landing y mirar la pestaña</t>
+          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr"/>
@@ -13239,7 +13239,7 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-04</t>
+          <t>CP-TAR-04</t>
         </is>
       </c>
       <c r="B385" s="8" t="inlineStr">
@@ -13249,17 +13249,17 @@
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>Icono en iOS</t>
+          <t>Lo estimado es lo que se cobra</t>
         </is>
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>"Añadir a pantalla de inicio" desde Safari</t>
+          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr"/>
@@ -13272,7 +13272,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-05</t>
+          <t>CP-TAR-05</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
@@ -13282,17 +13282,17 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Datos estructurados</t>
+          <t>Tarifas nuevas visibles</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
+          <t>Admin → Tarifas → canal SMS y Voz</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr"/>
@@ -13305,7 +13305,7 @@
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-06</t>
+          <t>CP-TAR-06</t>
         </is>
       </c>
       <c r="B387" s="8" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>Canonical y robots</t>
+          <t>Ningún cliente por debajo del costo</t>
         </is>
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Abrir /robots.txt y /sitemap.xml</t>
+          <t>Admin → Tarifas → revisar overrides por cliente</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-01</t>
+          <t>CP-TAR-07</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -13348,17 +13348,17 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>Tabla de precios por canal</t>
+          <t>Contador del editor SMS</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>Landing → Precios</t>
+          <t>Escribir un SMS con emoji en Plantillas SMS</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr"/>
@@ -13371,7 +13371,7 @@
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-02</t>
+          <t>CP-PUB-01</t>
         </is>
       </c>
       <c r="B389" s="8" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>Letra pequeña de precios</t>
+          <t>La landing no publica precios</t>
         </is>
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Leer bajo la tabla</t>
+          <t>Abrir la landing → sección Precios</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr"/>
@@ -13404,7 +13404,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-03</t>
+          <t>CP-SEO-01</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
@@ -13414,17 +13414,17 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Icono de WhatsApp</t>
+          <t>Título e idioma</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>Sección Canales</t>
+          <t>Ver el código fuente de la landing</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr"/>
@@ -13437,7 +13437,7 @@
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-04</t>
+          <t>CP-SEO-02</t>
         </is>
       </c>
       <c r="B391" s="8" t="inlineStr">
@@ -13447,17 +13447,17 @@
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>Sin promesa de 500 correos</t>
+          <t>Vista previa al compartir</t>
         </is>
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Recorrer toda la landing</t>
+          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-05</t>
+          <t>CP-SEO-03</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Footer sin enlaces rotos</t>
+          <t>Favicon</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>Hacer clic en cada enlace del footer</t>
+          <t>Abrir la landing y mirar la pestaña</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr"/>
@@ -13503,7 +13503,7 @@
     <row r="393">
       <c r="A393" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-01</t>
+          <t>CP-SEO-04</t>
         </is>
       </c>
       <c r="B393" s="8" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>Cerrar el modal con teclado</t>
+          <t>Icono en iOS</t>
         </is>
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Escape</t>
+          <t>"Añadir a pantalla de inicio" desde Safari</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr"/>
@@ -13536,7 +13536,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>CP-A11Y-02</t>
+          <t>CP-SEO-05</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -13551,12 +13551,12 @@
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>Foco en el modal</t>
+          <t>Datos estructurados</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Tab</t>
+          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr"/>
@@ -13569,7 +13569,7 @@
     <row r="395">
       <c r="A395" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-03</t>
+          <t>CP-SEO-06</t>
         </is>
       </c>
       <c r="B395" s="8" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>Lector de pantalla</t>
+          <t>Canonical y robots</t>
         </is>
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Abrir el modal con un lector activo</t>
+          <t>Abrir /robots.txt y /sitemap.xml</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr"/>
@@ -13602,12 +13602,12 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-LAN-01</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
@@ -13617,12 +13617,12 @@
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>Tabla de precios por canal</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Landing → Precios</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr"/>
@@ -13635,27 +13635,27 @@
     <row r="397">
       <c r="A397" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-LAN-02</t>
         </is>
       </c>
       <c r="B397" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C397" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Letra pequeña de precios</t>
         </is>
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Leer bajo la tabla</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr"/>
@@ -13668,12 +13668,12 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-LAN-03</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -13683,12 +13683,12 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Icono de WhatsApp</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Sección Canales</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr"/>
@@ -13701,27 +13701,27 @@
     <row r="399">
       <c r="A399" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-LAN-04</t>
         </is>
       </c>
       <c r="B399" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Sin promesa de 500 correos</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Recorrer toda la landing</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr"/>
@@ -13734,12 +13734,12 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-LAN-05</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
@@ -13749,12 +13749,12 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Footer sin enlaces rotos</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Hacer clic en cada enlace del footer</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr"/>
@@ -13767,27 +13767,27 @@
     <row r="401">
       <c r="A401" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-A11Y-01</t>
         </is>
       </c>
       <c r="B401" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Cerrar el modal con teclado</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Abrir /?activacion=ok y pulsar Escape</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr"/>
@@ -13800,27 +13800,27 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-A11Y-02</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Foco en el modal</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Abrir /?activacion=ok y pulsar Tab</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr"/>
@@ -13833,12 +13833,12 @@
     <row r="403">
       <c r="A403" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-A11Y-03</t>
         </is>
       </c>
       <c r="B403" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C403" s="7" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>Lector de pantalla</t>
         </is>
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Abrir el modal con un lector activo</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr"/>
@@ -13866,7 +13866,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -13876,17 +13876,17 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
     <row r="405">
       <c r="A405" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B405" s="8" t="inlineStr">
@@ -13909,17 +13909,17 @@
       </c>
       <c r="C405" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr"/>
@@ -13932,7 +13932,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
@@ -13942,17 +13942,17 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr"/>
@@ -13965,7 +13965,7 @@
     <row r="407">
       <c r="A407" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B407" s="8" t="inlineStr">
@@ -13975,17 +13975,17 @@
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr"/>
@@ -13998,27 +13998,27 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-CAS-05</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Consentimiento por canal</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Contacto sin consentimiento del canal 0</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr"/>
@@ -14031,12 +14031,12 @@
     <row r="409">
       <c r="A409" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-CAS-06</t>
         </is>
       </c>
       <c r="B409" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C409" s="7" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Listado de cascadas</t>
         </is>
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Abrir el listado</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr"/>
@@ -14064,27 +14064,27 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-SER-01</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Serie de 30 días (cliente)</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr"/>
@@ -14097,12 +14097,12 @@
     <row r="411">
       <c r="A411" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-SER-02</t>
         </is>
       </c>
       <c r="B411" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C411" s="7" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Serie global (admin)</t>
         </is>
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Panel de control → gráfico</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr"/>
@@ -14130,27 +14130,27 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-SER-03</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Muestras excluidas</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Enviar muestras y revisar la serie</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr"/>
@@ -14163,27 +14163,27 @@
     <row r="413">
       <c r="A413" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-SER-04</t>
         </is>
       </c>
       <c r="B413" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C413" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Aislamiento</t>
         </is>
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Comparar la serie de dos clientes</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr"/>
@@ -14196,12 +14196,12 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-SER-05</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
@@ -14211,12 +14211,12 @@
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Adiós "(parcial)"</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr"/>
@@ -14229,12 +14229,12 @@
     <row r="415">
       <c r="A415" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-SER-06</t>
         </is>
       </c>
       <c r="B415" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C415" s="7" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Leyenda interactiva</t>
         </is>
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Ocultar/mostrar series en el gráfico</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr"/>
@@ -14259,13 +14259,277 @@
       <c r="J415" s="6" t="inlineStr"/>
       <c r="K415" s="5" t="inlineStr"/>
     </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D416" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E416" s="3" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F416" s="3" t="inlineStr"/>
+      <c r="G416" s="4" t="inlineStr"/>
+      <c r="H416" s="5" t="inlineStr"/>
+      <c r="I416" s="4" t="inlineStr"/>
+      <c r="J416" s="6" t="inlineStr"/>
+      <c r="K416" s="5" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B417" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C417" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D417" s="8" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E417" s="8" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F417" s="8" t="inlineStr"/>
+      <c r="G417" s="4" t="inlineStr"/>
+      <c r="H417" s="5" t="inlineStr"/>
+      <c r="I417" s="4" t="inlineStr"/>
+      <c r="J417" s="6" t="inlineStr"/>
+      <c r="K417" s="5" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D418" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E418" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F418" s="3" t="inlineStr"/>
+      <c r="G418" s="4" t="inlineStr"/>
+      <c r="H418" s="5" t="inlineStr"/>
+      <c r="I418" s="4" t="inlineStr"/>
+      <c r="J418" s="6" t="inlineStr"/>
+      <c r="K418" s="5" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B419" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C419" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D419" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E419" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F419" s="8" t="inlineStr"/>
+      <c r="G419" s="4" t="inlineStr"/>
+      <c r="H419" s="5" t="inlineStr"/>
+      <c r="I419" s="4" t="inlineStr"/>
+      <c r="J419" s="6" t="inlineStr"/>
+      <c r="K419" s="5" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D420" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E420" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F420" s="3" t="inlineStr"/>
+      <c r="G420" s="4" t="inlineStr"/>
+      <c r="H420" s="5" t="inlineStr"/>
+      <c r="I420" s="4" t="inlineStr"/>
+      <c r="J420" s="6" t="inlineStr"/>
+      <c r="K420" s="5" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B421" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C421" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D421" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E421" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F421" s="8" t="inlineStr"/>
+      <c r="G421" s="4" t="inlineStr"/>
+      <c r="H421" s="5" t="inlineStr"/>
+      <c r="I421" s="4" t="inlineStr"/>
+      <c r="J421" s="6" t="inlineStr"/>
+      <c r="K421" s="5" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D422" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E422" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F422" s="3" t="inlineStr"/>
+      <c r="G422" s="4" t="inlineStr"/>
+      <c r="H422" s="5" t="inlineStr"/>
+      <c r="I422" s="4" t="inlineStr"/>
+      <c r="J422" s="6" t="inlineStr"/>
+      <c r="K422" s="5" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B423" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C423" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D423" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E423" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F423" s="8" t="inlineStr"/>
+      <c r="G423" s="4" t="inlineStr"/>
+      <c r="H423" s="5" t="inlineStr"/>
+      <c r="I423" s="4" t="inlineStr"/>
+      <c r="J423" s="6" t="inlineStr"/>
+      <c r="K423" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K415"/>
+  <autoFilter ref="A1:K423"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H415" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H423" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K415" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K423" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -14325,7 +14589,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A415)</f>
+        <f>COUNTA(Casos!A2:A423)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -14339,7 +14603,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$415,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$423,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -14356,7 +14620,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$415,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$423,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -14373,7 +14637,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$415,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$423,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -14390,7 +14654,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$415,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$423,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -14446,11 +14710,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$415,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$423,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$415,A12,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$423,A12,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -14463,11 +14727,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$415,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$423,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$415,A13,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$423,A13,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -14480,11 +14744,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$415,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$423,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$415,A14,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$423,A14,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -14542,19 +14806,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A18,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A18,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A18,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A18,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$415,$A18,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$423,$A18,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14565,19 +14829,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A19,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A19,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A19,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A19,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$415,$A19,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$423,$A19,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14588,19 +14852,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A20,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A20,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A20,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A20,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$415,$A20,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$423,$A20,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14611,19 +14875,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A21,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A21,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A21,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A21,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$415,$A21,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$423,$A21,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14634,19 +14898,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A22,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A22,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A22,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A22,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$415,$A22,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$423,$A22,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14657,19 +14921,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A23,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A23,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A23,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A23,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$415,$A23,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$423,$A23,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14680,19 +14944,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A24,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A24,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A24,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A24,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$415,$A24,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$423,$A24,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14703,19 +14967,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A25,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A25,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A25,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A25,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$415,$A25,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$423,$A25,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14726,19 +14990,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A26,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A26,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A26,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A26,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$415,$A26,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$423,$A26,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14749,19 +15013,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A27,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A27,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A27,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A27,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$415,$A27,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$423,$A27,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14772,19 +15036,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A28,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A28,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A28,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A28,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$415,$A28,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$423,$A28,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14795,19 +15059,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A29,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A29,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A29,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A29,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$415,$A29,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$423,$A29,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14818,19 +15082,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A30,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A30,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A30,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A30,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$415,$A30,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$423,$A30,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14841,19 +15105,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A31,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A31,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A31,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A31,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$415,$A31,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$423,$A31,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14864,19 +15128,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A32,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A32,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A32,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A32,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$415,$A32,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$423,$A32,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14887,19 +15151,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A33,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A33,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A33,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A33,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$415,$A33,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$423,$A33,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14910,19 +15174,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A34,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A34,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A34,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A34,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$415,$A34,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$423,$A34,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14933,19 +15197,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A35,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A35,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A35,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A35,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$415,$A35,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$423,$A35,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14956,19 +15220,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A36,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A36,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A36,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A36,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$415,$A36,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$423,$A36,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -14979,19 +15243,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A37,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A37,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A37,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A37,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$415,$A37,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$423,$A37,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15002,19 +15266,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A38,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A38,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A38,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A38,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$415,$A38,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$423,$A38,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15025,19 +15289,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$415,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$423,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A39,Casos!$H$2:$H$415,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A39,Casos!$H$2:$H$423,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$415,$A39,Casos!$H$2:$H$415,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$423,$A39,Casos!$H$2:$H$423,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$415,$A39,Casos!$H$2:$H$415,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$423,$A39,Casos!$H$2:$H$423,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$452</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$462</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K452"/>
+  <dimension ref="A1:K462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9015,27 +9015,27 @@
     <row r="257">
       <c r="A257" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-01</t>
+          <t>CP-LNK-01</t>
         </is>
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C257" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>Editor básico tipo Word</t>
+          <t>Enlace sin popup del navegador</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
+          <t>Plantillas PDF básicas → seleccionar una palabra → botón de enlace</t>
         </is>
       </c>
       <c r="F257" s="8" t="inlineStr"/>
@@ -9048,12 +9048,12 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-02</t>
+          <t>CP-LNK-02</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Vista previa PDF (básico)</t>
+          <t>La selección sobrevive al diálogo</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>Botón "Vista previa PDF"</t>
+          <t>Con una palabra seleccionada, poner https://empresa.com → Insertar</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr"/>
@@ -9081,12 +9081,12 @@
     <row r="259">
       <c r="A259" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-03</t>
+          <t>CP-LNK-03</t>
         </is>
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
@@ -9096,12 +9096,12 @@
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>Estudio PDF (lienzo)</t>
+          <t>Sin selección inserta el enlace completo</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>Crear un diseño con texto, formas, tabla y guardar</t>
+          <t>Poner el cursor al final de un párrafo (sin seleccionar) → enlace → URL + "Texto que se ve"</t>
         </is>
       </c>
       <c r="F259" s="8" t="inlineStr"/>
@@ -9114,27 +9114,27 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-04</t>
+          <t>CP-LNK-04</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>Estudio: variables con datos reales</t>
+          <t>Clic a la derecha del título no engaña</t>
         </is>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>Elegir una base en el panel de datos → Vista previa</t>
+          <t>Hacer clic en un &lt;h1&gt; pasado el final de su texto → enlace</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr"/>
@@ -9147,27 +9147,27 @@
     <row r="261">
       <c r="A261" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-05</t>
+          <t>CP-LNK-05</t>
         </is>
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>Estudio: unidades y reglas</t>
+          <t>URL insegura rechazada</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
+          <t>Escribir javascript:alert(1) → Insertar</t>
         </is>
       </c>
       <c r="F261" s="8" t="inlineStr"/>
@@ -9180,12 +9180,12 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-06</t>
+          <t>CP-LNK-06</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>Estudio: seleccionar elemento rotado</t>
+          <t>Esquemas aceptados</t>
         </is>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
-          <t>Girar un texto y hacer clic dentro de su caja visual</t>
+          <t>Probar https://, mailto: y tel:</t>
         </is>
       </c>
       <c r="F262" s="3" t="inlineStr"/>
@@ -9213,12 +9213,12 @@
     <row r="263">
       <c r="A263" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-07</t>
+          <t>CP-2FA-08</t>
         </is>
       </c>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>Estudio: estilos vinculados</t>
+          <t>Desactivar 2FA en un solo diálogo</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>Vincular un estilo de texto/párrafo y editarlo</t>
+          <t>Mi cuenta → Desactivar 2FA</t>
         </is>
       </c>
       <c r="F263" s="8" t="inlineStr"/>
@@ -9246,12 +9246,12 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-08</t>
+          <t>CP-2FA-09</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -9261,12 +9261,12 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>Diseñador PDF (full)</t>
+          <t>Código errado no cierra el diálogo</t>
         </is>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
-          <t>Abrir el Diseñador y crear un documento</t>
+          <t>En ese diálogo poner 000000 → Desactivar</t>
         </is>
       </c>
       <c r="F264" s="3" t="inlineStr"/>
@@ -9279,27 +9279,27 @@
     <row r="265">
       <c r="A265" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-09</t>
+          <t>CP-2FA-10</t>
         </is>
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF de punta a punta</t>
+          <t>Cabe un código de respaldo</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
+          <t>Pegar un código de respaldo completo (más largo que 6 dígitos)</t>
         </is>
       </c>
       <c r="F265" s="8" t="inlineStr"/>
@@ -9312,27 +9312,27 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-10</t>
+          <t>CP-2FA-11</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr">
         <is>
-          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
+          <t>Constructor de correos HTML</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>Tabla que desborda pagina</t>
+          <t>Botón deshabilitado sin código</t>
         </is>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
+          <t>Abrir el diálogo y no escribir nada</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr"/>
@@ -9345,7 +9345,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-11</t>
+          <t>CP-PDF-01</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
@@ -9355,17 +9355,17 @@
       </c>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>Celdas con JSON (multiregistro)</t>
+          <t>Editor básico tipo Word</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>Base con una columna que trae un array JSON</t>
+          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
         </is>
       </c>
       <c r="F267" s="8" t="inlineStr"/>
@@ -9378,7 +9378,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-12</t>
+          <t>CP-PDF-02</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -9388,17 +9388,17 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Encabezados con BOM/espacios</t>
+          <t>Vista previa PDF (básico)</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
+          <t>Botón "Vista previa PDF"</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr"/>
@@ -9411,7 +9411,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-13</t>
+          <t>CP-PDF-03</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
@@ -9421,17 +9421,17 @@
       </c>
       <c r="C269" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>Bordes y degradados</t>
+          <t>Estudio PDF (lienzo)</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>Formas con borde discontinuo y relleno degradado</t>
+          <t>Crear un diseño con texto, formas, tabla y guardar</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr"/>
@@ -9444,12 +9444,12 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-PDF-04</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Estudio: variables con datos reales</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>Elegir una base en el panel de datos → Vista previa</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr"/>
@@ -9477,27 +9477,27 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-PDF-05</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C271" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>Estudio: unidades y reglas</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr"/>
@@ -9510,27 +9510,27 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-PDF-06</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>Estudio: seleccionar elemento rotado</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Girar un texto y hacer clic dentro de su caja visual</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr"/>
@@ -9543,27 +9543,27 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-PDF-07</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C273" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Estudio: estilos vinculados</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Vincular un estilo de texto/párrafo y editarlo</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr"/>
@@ -9576,27 +9576,27 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-PDF-08</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>Diseñador PDF (full)</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Abrir el Diseñador y crear un documento</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr"/>
@@ -9609,27 +9609,27 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-PDF-09</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C275" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Campaña EAP-PDF de punta a punta</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr"/>
@@ -9642,27 +9642,27 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-PDF-10</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Tabla que desborda pagina</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr"/>
@@ -9675,27 +9675,27 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-PDF-11</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C277" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Celdas con JSON (multiregistro)</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>Base con una columna que trae un array JSON</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr"/>
@@ -9708,27 +9708,27 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-PDF-12</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>Encabezados con BOM/espacios</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr"/>
@@ -9741,27 +9741,27 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-PDF-13</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C279" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Bordes y degradados</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Formas con borde discontinuo y relleno degradado</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr"/>
@@ -9774,7 +9774,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -9784,17 +9784,17 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr"/>
@@ -9807,7 +9807,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
@@ -9817,17 +9817,17 @@
       </c>
       <c r="C281" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr"/>
@@ -9840,7 +9840,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -9850,17 +9850,17 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr"/>
@@ -9873,7 +9873,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
@@ -9883,17 +9883,17 @@
       </c>
       <c r="C283" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr"/>
@@ -9906,12 +9906,12 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr"/>
@@ -9939,27 +9939,27 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C285" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr"/>
@@ -9972,12 +9972,12 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr"/>
@@ -10005,27 +10005,27 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C287" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr"/>
@@ -10038,12 +10038,12 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr"/>
@@ -10071,12 +10071,12 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C289" s="7" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr"/>
@@ -10104,12 +10104,12 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr"/>
@@ -10137,27 +10137,27 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C291" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr"/>
@@ -10170,27 +10170,27 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr"/>
@@ -10203,27 +10203,27 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C293" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr"/>
@@ -10236,12 +10236,12 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr"/>
@@ -10269,27 +10269,27 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr"/>
@@ -10302,27 +10302,27 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr"/>
@@ -10335,27 +10335,27 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr"/>
@@ -10368,27 +10368,27 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr"/>
@@ -10401,12 +10401,12 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C299" s="7" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr"/>
@@ -10434,27 +10434,27 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-01</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>DKIM verificado en verde</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio con DKIM firmando</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr"/>
@@ -10467,27 +10467,27 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-02</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>SPF/DMARC sin publicar en gris</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio recién creado</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr"/>
@@ -10500,7 +10500,7 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-03</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
@@ -10510,17 +10510,17 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>SPF verde al publicarlo</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr"/>
@@ -10533,7 +10533,7 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-04</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
@@ -10543,17 +10543,17 @@
       </c>
       <c r="C303" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>DMARC verde al publicarlo</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr"/>
@@ -10566,7 +10566,7 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-05</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
@@ -10576,17 +10576,17 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>Tooltip explica el motivo</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Pasar el mouse sobre un chip gris</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr"/>
@@ -10599,7 +10599,7 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-06</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="C305" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Sin el layer de DNS</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr"/>
@@ -10632,7 +10632,7 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-07</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
@@ -10642,17 +10642,17 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>Correos sueltos sin el panel</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr"/>
@@ -10665,7 +10665,7 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-08</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
@@ -10675,17 +10675,17 @@
       </c>
       <c r="C307" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>No es bloqueante</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr"/>
@@ -10698,27 +10698,27 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr"/>
@@ -10731,27 +10731,27 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr"/>
@@ -10764,12 +10764,12 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-AUT-01</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>DKIM verificado en verde</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Abrir el detalle de un dominio con DKIM firmando</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr"/>
@@ -10797,27 +10797,27 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-AUT-02</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C311" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>SPF/DMARC sin publicar en gris</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Abrir el detalle de un dominio recién creado</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr"/>
@@ -10830,27 +10830,27 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-AUT-03</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>SPF verde al publicarlo</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr"/>
@@ -10863,12 +10863,12 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-AUT-04</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>DMARC verde al publicarlo</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr"/>
@@ -10896,27 +10896,27 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-AUT-05</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>Tooltip explica el motivo</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Pasar el mouse sobre un chip gris</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr"/>
@@ -10929,27 +10929,27 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-AUT-06</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C315" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>Sin el layer de DNS</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr"/>
@@ -10962,27 +10962,27 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-AUT-07</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>Correos sueltos sin el panel</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr"/>
@@ -10995,27 +10995,27 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-AUT-08</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C317" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>No es bloqueante</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr"/>
@@ -11028,7 +11028,7 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
@@ -11038,17 +11038,17 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr"/>
@@ -11061,7 +11061,7 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-35</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>El bloqueo escalado explica por qué fue inmediato</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr"/>
@@ -11094,7 +11094,7 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-36</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
@@ -11104,17 +11104,17 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>El primer bloqueo no repite la explicación</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>En una cuenta nueva, fallar 3 veces</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr"/>
@@ -11127,7 +11127,7 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr"/>
@@ -11160,7 +11160,7 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr"/>
@@ -11193,7 +11193,7 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
@@ -11203,17 +11203,17 @@
       </c>
       <c r="C323" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr"/>
@@ -11226,7 +11226,7 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
@@ -11236,17 +11236,17 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr"/>
@@ -11259,7 +11259,7 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
@@ -11269,17 +11269,17 @@
       </c>
       <c r="C325" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
@@ -11302,17 +11302,17 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr"/>
@@ -11325,7 +11325,7 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
@@ -11335,17 +11335,17 @@
       </c>
       <c r="C327" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,27 +11358,27 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,12 +11391,12 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-SEC-35</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
@@ -11406,12 +11406,12 @@
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>El bloqueo escalado explica por qué fue inmediato</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,27 +11424,27 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-SEC-36</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>El primer bloqueo no repite la explicación</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>En una cuenta nueva, fallar 3 veces</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,27 +11457,27 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,12 +11490,12 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,27 +11523,27 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,27 +11556,27 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,27 +11589,27 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,27 +11622,27 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,27 +11655,27 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,7 +11688,7 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
@@ -11698,17 +11698,17 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,7 +11721,7 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
@@ -11731,17 +11731,17 @@
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,7 +11754,7 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11787,7 +11787,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,7 +11820,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -11830,17 +11830,17 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,7 +11853,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
@@ -11863,17 +11863,17 @@
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,7 +11886,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
@@ -11901,12 +11901,12 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,7 +11919,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
@@ -11929,17 +11929,17 @@
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,7 +11952,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
@@ -11995,17 +11995,17 @@
       </c>
       <c r="C347" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,7 +12018,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
@@ -12028,17 +12028,17 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,7 +12051,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
@@ -12061,17 +12061,17 @@
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,7 +12084,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
@@ -12099,12 +12099,12 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,7 +12117,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12150,7 +12150,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
@@ -12160,17 +12160,17 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -12183,7 +12183,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
@@ -12193,17 +12193,17 @@
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr"/>
@@ -12216,7 +12216,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -12249,12 +12249,12 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C355" s="7" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr"/>
@@ -12282,12 +12282,12 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -12315,27 +12315,27 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr"/>
@@ -12348,27 +12348,27 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -12381,12 +12381,12 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr"/>
@@ -12414,12 +12414,12 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -12447,27 +12447,27 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr"/>
@@ -12480,27 +12480,27 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
@@ -12513,27 +12513,27 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B363" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr"/>
@@ -12546,12 +12546,12 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr"/>
@@ -12579,7 +12579,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B365" s="8" t="inlineStr">
@@ -12589,17 +12589,17 @@
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr"/>
@@ -12612,7 +12612,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B367" s="8" t="inlineStr">
@@ -12655,17 +12655,17 @@
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr"/>
@@ -12678,7 +12678,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr"/>
@@ -12711,27 +12711,27 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B369" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr"/>
@@ -12744,27 +12744,27 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr"/>
@@ -12777,12 +12777,12 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B371" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C371" s="7" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr"/>
@@ -12810,12 +12810,12 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr"/>
@@ -12843,27 +12843,27 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr"/>
@@ -12876,12 +12876,12 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
@@ -12909,27 +12909,27 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B375" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr"/>
@@ -12942,12 +12942,12 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr"/>
@@ -12975,12 +12975,12 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B377" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C377" s="7" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr"/>
@@ -13008,27 +13008,27 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr"/>
@@ -13041,7 +13041,7 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B379" s="8" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr"/>
@@ -13074,7 +13074,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-01</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
@@ -13084,17 +13084,17 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>Aviso de campaña por aprobar</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr"/>
@@ -13107,7 +13107,7 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-02</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B381" s="8" t="inlineStr">
@@ -13117,17 +13117,17 @@
       </c>
       <c r="C381" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>Solo a quien puede aprobar</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita de otro operator del mismo equipo</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr"/>
@@ -13140,7 +13140,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-03</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
@@ -13150,17 +13150,17 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>Quien la pide no se avisa a sí mismo</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita del operator que la solicitó</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr"/>
@@ -13173,7 +13173,7 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-04</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B383" s="8" t="inlineStr">
@@ -13183,17 +13183,17 @@
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento entre empresas</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita de un usuario de OTRA empresa</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr"/>
@@ -13206,7 +13206,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-05</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
@@ -13216,17 +13216,17 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>Aviso de aprobada</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>El owner aprueba la campaña</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr"/>
@@ -13239,7 +13239,7 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-06</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B385" s="8" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>Aviso de rechazada con el motivo</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr"/>
@@ -13272,7 +13272,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-07</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Saldo bajo in-app</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>Hacer un envío que deje el saldo bajo el umbral</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr"/>
@@ -13305,7 +13305,7 @@
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-08</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B387" s="8" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>Avisos nuevos abajo a la derecha</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-09</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -13348,17 +13348,17 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>Los nuevos NO saltan al entrar</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>Con avisos viejos sin leer, entrar al portal</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr"/>
@@ -13371,7 +13371,7 @@
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-10</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B389" s="8" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>La tarjeta se retira sola</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Esperar unos segundos tras el aviso</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr"/>
@@ -13404,7 +13404,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-11</t>
+          <t>CP-CAM-01</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Clic lleva al lugar correcto</t>
+          <t>Aviso de campaña por aprobar</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>Hacer clic en "Campaña por aprobar"</t>
+          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr"/>
@@ -13437,7 +13437,7 @@
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-12</t>
+          <t>CP-CAM-02</t>
         </is>
       </c>
       <c r="B391" s="8" t="inlineStr">
@@ -13447,17 +13447,17 @@
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>Marcar leídas</t>
+          <t>Solo a quien puede aprobar</t>
         </is>
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Abrir el panel y pulsar "Marcar leídas"</t>
+          <t>Revisar la campanita de otro operator del mismo equipo</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-13</t>
+          <t>CP-CAM-03</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>No se puede marcar la de otro</t>
+          <t>Quien la pide no se avisa a sí mismo</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
+          <t>Revisar la campanita del operator que la solicitó</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr"/>
@@ -13503,7 +13503,7 @@
     <row r="393">
       <c r="A393" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-14</t>
+          <t>CP-CAM-04</t>
         </is>
       </c>
       <c r="B393" s="8" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>Sin notificaciones</t>
+          <t>Aislamiento entre empresas</t>
         </is>
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Usuario nuevo abre la campanita</t>
+          <t>Revisar la campanita de un usuario de OTRA empresa</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr"/>
@@ -13536,7 +13536,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-15</t>
+          <t>CP-CAM-05</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -13546,17 +13546,17 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>No molesta en impersonación</t>
+          <t>Aviso de aprobada</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>Entrar como admin con "Ver como cliente"</t>
+          <t>El owner aprueba la campaña</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr"/>
@@ -13569,7 +13569,7 @@
     <row r="395">
       <c r="A395" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-16</t>
+          <t>CP-CAM-06</t>
         </is>
       </c>
       <c r="B395" s="8" t="inlineStr">
@@ -13579,17 +13579,17 @@
       </c>
       <c r="C395" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>La aprobación funciona sin la tabla</t>
+          <t>Aviso de rechazada con el motivo</t>
         </is>
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
+          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr"/>
@@ -13602,12 +13602,12 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-CAM-07</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
@@ -13617,12 +13617,12 @@
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Saldo bajo in-app</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Hacer un envío que deje el saldo bajo el umbral</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr"/>
@@ -13635,12 +13635,12 @@
     <row r="397">
       <c r="A397" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-CAM-08</t>
         </is>
       </c>
       <c r="B397" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C397" s="7" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Avisos nuevos abajo a la derecha</t>
         </is>
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr"/>
@@ -13668,12 +13668,12 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-CAM-09</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -13683,12 +13683,12 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Los nuevos NO saltan al entrar</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Con avisos viejos sin leer, entrar al portal</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr"/>
@@ -13701,12 +13701,12 @@
     <row r="399">
       <c r="A399" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-CAM-10</t>
         </is>
       </c>
       <c r="B399" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C399" s="7" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>La tarjeta se retira sola</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Esperar unos segundos tras el aviso</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr"/>
@@ -13734,12 +13734,12 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-CAM-11</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
@@ -13749,12 +13749,12 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Clic lleva al lugar correcto</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>Hacer clic en "Campaña por aprobar"</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr"/>
@@ -13767,12 +13767,12 @@
     <row r="401">
       <c r="A401" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-CAM-12</t>
         </is>
       </c>
       <c r="B401" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C401" s="7" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Marcar leídas</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>Abrir el panel y pulsar "Marcar leídas"</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr"/>
@@ -13800,27 +13800,27 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-CAM-13</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>No se puede marcar la de otro</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr"/>
@@ -13833,27 +13833,27 @@
     <row r="403">
       <c r="A403" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-CAM-14</t>
         </is>
       </c>
       <c r="B403" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C403" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>Sin notificaciones</t>
         </is>
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Usuario nuevo abre la campanita</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr"/>
@@ -13866,27 +13866,27 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-CAM-15</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>No molesta en impersonación</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Entrar como admin con "Ver como cliente"</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr"/>
@@ -13899,27 +13899,27 @@
     <row r="405">
       <c r="A405" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-CAM-16</t>
         </is>
       </c>
       <c r="B405" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C405" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>La aprobación funciona sin la tabla</t>
         </is>
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr"/>
@@ -13932,7 +13932,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr"/>
@@ -13965,7 +13965,7 @@
     <row r="407">
       <c r="A407" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B407" s="8" t="inlineStr">
@@ -13980,12 +13980,12 @@
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr"/>
@@ -13998,7 +13998,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
@@ -14008,17 +14008,17 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr"/>
@@ -14031,7 +14031,7 @@
     <row r="409">
       <c r="A409" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B409" s="8" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr"/>
@@ -14064,7 +14064,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -14074,17 +14074,17 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr"/>
@@ -14097,7 +14097,7 @@
     <row r="411">
       <c r="A411" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-01</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B411" s="8" t="inlineStr">
@@ -14107,17 +14107,17 @@
       </c>
       <c r="C411" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>Segmentos calculados, no declarados</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>Muestras con una campaña SMS</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr"/>
@@ -14130,7 +14130,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-02</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
@@ -14140,17 +14140,17 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Un SMS largo cuesta el doble</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>Campaña con más de 160 caracteres</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
     <row r="413">
       <c r="A413" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-03</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B413" s="8" t="inlineStr">
@@ -14173,17 +14173,17 @@
       </c>
       <c r="C413" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>Una emoji parte el mensaje</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr"/>
@@ -14196,7 +14196,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-04</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
@@ -14206,17 +14206,17 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>Lo estimado es lo que se cobra</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr"/>
@@ -14229,7 +14229,7 @@
     <row r="415">
       <c r="A415" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-05</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B415" s="8" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>Tarifas nuevas visibles</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → canal SMS y Voz</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr"/>
@@ -14262,7 +14262,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-06</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
@@ -14272,17 +14272,17 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>Ningún cliente por debajo del costo</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → revisar overrides por cliente</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr"/>
@@ -14295,7 +14295,7 @@
     <row r="417">
       <c r="A417" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-07</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B417" s="8" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>Contador del editor SMS</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>Escribir un SMS con emoji en Plantillas SMS</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F417" s="8" t="inlineStr"/>
@@ -14328,7 +14328,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>CP-PUB-01</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -14338,17 +14338,17 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>La landing no publica precios</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>Abrir la landing → sección Precios</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr"/>
@@ -14361,7 +14361,7 @@
     <row r="419">
       <c r="A419" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-01</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B419" s="8" t="inlineStr">
@@ -14371,17 +14371,17 @@
       </c>
       <c r="C419" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Título e idioma</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>Ver el código fuente de la landing</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F419" s="8" t="inlineStr"/>
@@ -14394,7 +14394,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-02</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
@@ -14404,17 +14404,17 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>Vista previa al compartir</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr"/>
@@ -14427,7 +14427,7 @@
     <row r="421">
       <c r="A421" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-03</t>
+          <t>CP-TAR-01</t>
         </is>
       </c>
       <c r="B421" s="8" t="inlineStr">
@@ -14437,17 +14437,17 @@
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Segmentos calculados, no declarados</t>
         </is>
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Abrir la landing y mirar la pestaña</t>
+          <t>Muestras con una campaña SMS</t>
         </is>
       </c>
       <c r="F421" s="8" t="inlineStr"/>
@@ -14460,7 +14460,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-04</t>
+          <t>CP-TAR-02</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>Icono en iOS</t>
+          <t>Un SMS largo cuesta el doble</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>"Añadir a pantalla de inicio" desde Safari</t>
+          <t>Campaña con más de 160 caracteres</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr"/>
@@ -14493,7 +14493,7 @@
     <row r="423">
       <c r="A423" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-05</t>
+          <t>CP-TAR-03</t>
         </is>
       </c>
       <c r="B423" s="8" t="inlineStr">
@@ -14503,17 +14503,17 @@
       </c>
       <c r="C423" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Datos estructurados</t>
+          <t>Una emoji parte el mensaje</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
+          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
         </is>
       </c>
       <c r="F423" s="8" t="inlineStr"/>
@@ -14526,7 +14526,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-06</t>
+          <t>CP-TAR-04</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>Canonical y robots</t>
+          <t>Lo estimado es lo que se cobra</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>Abrir /robots.txt y /sitemap.xml</t>
+          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr"/>
@@ -14559,7 +14559,7 @@
     <row r="425">
       <c r="A425" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-01</t>
+          <t>CP-TAR-05</t>
         </is>
       </c>
       <c r="B425" s="8" t="inlineStr">
@@ -14574,12 +14574,12 @@
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>Tabla de precios por canal</t>
+          <t>Tarifas nuevas visibles</t>
         </is>
       </c>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>Landing → Precios</t>
+          <t>Admin → Tarifas → canal SMS y Voz</t>
         </is>
       </c>
       <c r="F425" s="8" t="inlineStr"/>
@@ -14592,7 +14592,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-02</t>
+          <t>CP-TAR-06</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>Letra pequeña de precios</t>
+          <t>Ningún cliente por debajo del costo</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>Leer bajo la tabla</t>
+          <t>Admin → Tarifas → revisar overrides por cliente</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr"/>
@@ -14625,7 +14625,7 @@
     <row r="427">
       <c r="A427" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-03</t>
+          <t>CP-TAR-07</t>
         </is>
       </c>
       <c r="B427" s="8" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>Icono de WhatsApp</t>
+          <t>Contador del editor SMS</t>
         </is>
       </c>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>Sección Canales</t>
+          <t>Escribir un SMS con emoji en Plantillas SMS</t>
         </is>
       </c>
       <c r="F427" s="8" t="inlineStr"/>
@@ -14658,7 +14658,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-04</t>
+          <t>CP-PUB-01</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
@@ -14673,12 +14673,12 @@
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>Sin promesa de 500 correos</t>
+          <t>La landing no publica precios</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>Recorrer toda la landing</t>
+          <t>Abrir la landing → sección Precios</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr"/>
@@ -14691,7 +14691,7 @@
     <row r="429">
       <c r="A429" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-05</t>
+          <t>CP-SEO-01</t>
         </is>
       </c>
       <c r="B429" s="8" t="inlineStr">
@@ -14701,17 +14701,17 @@
       </c>
       <c r="C429" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>Footer sin enlaces rotos</t>
+          <t>Título e idioma</t>
         </is>
       </c>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>Hacer clic en cada enlace del footer</t>
+          <t>Ver el código fuente de la landing</t>
         </is>
       </c>
       <c r="F429" s="8" t="inlineStr"/>
@@ -14724,7 +14724,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>CP-A11Y-01</t>
+          <t>CP-SEO-02</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
@@ -14739,12 +14739,12 @@
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>Cerrar el modal con teclado</t>
+          <t>Vista previa al compartir</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Escape</t>
+          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr"/>
@@ -14757,7 +14757,7 @@
     <row r="431">
       <c r="A431" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-02</t>
+          <t>CP-SEO-03</t>
         </is>
       </c>
       <c r="B431" s="8" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>Foco en el modal</t>
+          <t>Favicon</t>
         </is>
       </c>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Tab</t>
+          <t>Abrir la landing y mirar la pestaña</t>
         </is>
       </c>
       <c r="F431" s="8" t="inlineStr"/>
@@ -14790,7 +14790,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>CP-A11Y-03</t>
+          <t>CP-SEO-04</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
@@ -14805,12 +14805,12 @@
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>Lector de pantalla</t>
+          <t>Icono en iOS</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>Abrir el modal con un lector activo</t>
+          <t>"Añadir a pantalla de inicio" desde Safari</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr"/>
@@ -14823,27 +14823,27 @@
     <row r="433">
       <c r="A433" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-SEO-05</t>
         </is>
       </c>
       <c r="B433" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C433" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>Datos estructurados</t>
         </is>
       </c>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
         </is>
       </c>
       <c r="F433" s="8" t="inlineStr"/>
@@ -14856,27 +14856,27 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-SEO-06</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Canonical y robots</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Abrir /robots.txt y /sitemap.xml</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr"/>
@@ -14889,27 +14889,27 @@
     <row r="435">
       <c r="A435" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-LAN-01</t>
         </is>
       </c>
       <c r="B435" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C435" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Tabla de precios por canal</t>
         </is>
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Landing → Precios</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr"/>
@@ -14922,27 +14922,27 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-LAN-02</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Letra pequeña de precios</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Leer bajo la tabla</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr"/>
@@ -14955,12 +14955,12 @@
     <row r="437">
       <c r="A437" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-LAN-03</t>
         </is>
       </c>
       <c r="B437" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C437" s="7" t="inlineStr">
@@ -14970,12 +14970,12 @@
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Icono de WhatsApp</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Sección Canales</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr"/>
@@ -14988,12 +14988,12 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-LAN-04</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Sin promesa de 500 correos</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Recorrer toda la landing</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr"/>
@@ -15021,27 +15021,27 @@
     <row r="439">
       <c r="A439" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-LAN-05</t>
         </is>
       </c>
       <c r="B439" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C439" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Footer sin enlaces rotos</t>
         </is>
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Hacer clic en cada enlace del footer</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr"/>
@@ -15054,27 +15054,27 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-A11Y-01</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>Cerrar el modal con teclado</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Abrir /?activacion=ok y pulsar Escape</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr"/>
@@ -15087,12 +15087,12 @@
     <row r="441">
       <c r="A441" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-A11Y-02</t>
         </is>
       </c>
       <c r="B441" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C441" s="7" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>Foco en el modal</t>
         </is>
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Abrir /?activacion=ok y pulsar Tab</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr"/>
@@ -15120,12 +15120,12 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-A11Y-03</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
@@ -15135,12 +15135,12 @@
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Lector de pantalla</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Abrir el modal con un lector activo</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
     <row r="443">
       <c r="A443" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B443" s="8" t="inlineStr">
@@ -15163,17 +15163,17 @@
       </c>
       <c r="C443" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr"/>
@@ -15186,7 +15186,7 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
@@ -15196,17 +15196,17 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr"/>
@@ -15219,27 +15219,27 @@
     <row r="445">
       <c r="A445" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B445" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C445" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr"/>
@@ -15252,27 +15252,27 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr"/>
@@ -15285,12 +15285,12 @@
     <row r="447">
       <c r="A447" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-CAS-05</t>
         </is>
       </c>
       <c r="B447" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C447" s="7" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Consentimiento por canal</t>
         </is>
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Contacto sin consentimiento del canal 0</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr"/>
@@ -15318,12 +15318,12 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-CAS-06</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Listado de cascadas</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Abrir el listado</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr"/>
@@ -15351,12 +15351,12 @@
     <row r="449">
       <c r="A449" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-SER-01</t>
         </is>
       </c>
       <c r="B449" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C449" s="7" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Serie de 30 días (cliente)</t>
         </is>
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr"/>
@@ -15384,27 +15384,27 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-SER-02</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Serie global (admin)</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Panel de control → gráfico</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr"/>
@@ -15417,27 +15417,27 @@
     <row r="451">
       <c r="A451" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-SER-03</t>
         </is>
       </c>
       <c r="B451" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C451" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Muestras excluidas</t>
         </is>
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Enviar muestras y revisar la serie</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr"/>
@@ -15450,27 +15450,27 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-SER-04</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Aislamiento</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Comparar la serie de dos clientes</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr"/>
@@ -15480,13 +15480,343 @@
       <c r="J452" s="6" t="inlineStr"/>
       <c r="K452" s="5" t="inlineStr"/>
     </row>
+    <row r="453">
+      <c r="A453" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-05</t>
+        </is>
+      </c>
+      <c r="B453" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C453" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D453" s="8" t="inlineStr">
+        <is>
+          <t>Adiós "(parcial)"</t>
+        </is>
+      </c>
+      <c r="E453" s="8" t="inlineStr">
+        <is>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+        </is>
+      </c>
+      <c r="F453" s="8" t="inlineStr"/>
+      <c r="G453" s="4" t="inlineStr"/>
+      <c r="H453" s="5" t="inlineStr"/>
+      <c r="I453" s="4" t="inlineStr"/>
+      <c r="J453" s="6" t="inlineStr"/>
+      <c r="K453" s="5" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-06</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D454" s="3" t="inlineStr">
+        <is>
+          <t>Leyenda interactiva</t>
+        </is>
+      </c>
+      <c r="E454" s="3" t="inlineStr">
+        <is>
+          <t>Ocultar/mostrar series en el gráfico</t>
+        </is>
+      </c>
+      <c r="F454" s="3" t="inlineStr"/>
+      <c r="G454" s="4" t="inlineStr"/>
+      <c r="H454" s="5" t="inlineStr"/>
+      <c r="I454" s="4" t="inlineStr"/>
+      <c r="J454" s="6" t="inlineStr"/>
+      <c r="K454" s="5" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B455" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C455" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D455" s="8" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E455" s="8" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F455" s="8" t="inlineStr"/>
+      <c r="G455" s="4" t="inlineStr"/>
+      <c r="H455" s="5" t="inlineStr"/>
+      <c r="I455" s="4" t="inlineStr"/>
+      <c r="J455" s="6" t="inlineStr"/>
+      <c r="K455" s="5" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D456" s="3" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E456" s="3" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F456" s="3" t="inlineStr"/>
+      <c r="G456" s="4" t="inlineStr"/>
+      <c r="H456" s="5" t="inlineStr"/>
+      <c r="I456" s="4" t="inlineStr"/>
+      <c r="J456" s="6" t="inlineStr"/>
+      <c r="K456" s="5" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B457" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C457" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D457" s="8" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E457" s="8" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F457" s="8" t="inlineStr"/>
+      <c r="G457" s="4" t="inlineStr"/>
+      <c r="H457" s="5" t="inlineStr"/>
+      <c r="I457" s="4" t="inlineStr"/>
+      <c r="J457" s="6" t="inlineStr"/>
+      <c r="K457" s="5" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D458" s="3" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E458" s="3" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F458" s="3" t="inlineStr"/>
+      <c r="G458" s="4" t="inlineStr"/>
+      <c r="H458" s="5" t="inlineStr"/>
+      <c r="I458" s="4" t="inlineStr"/>
+      <c r="J458" s="6" t="inlineStr"/>
+      <c r="K458" s="5" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B459" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C459" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D459" s="8" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E459" s="8" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F459" s="8" t="inlineStr"/>
+      <c r="G459" s="4" t="inlineStr"/>
+      <c r="H459" s="5" t="inlineStr"/>
+      <c r="I459" s="4" t="inlineStr"/>
+      <c r="J459" s="6" t="inlineStr"/>
+      <c r="K459" s="5" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D460" s="3" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E460" s="3" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F460" s="3" t="inlineStr"/>
+      <c r="G460" s="4" t="inlineStr"/>
+      <c r="H460" s="5" t="inlineStr"/>
+      <c r="I460" s="4" t="inlineStr"/>
+      <c r="J460" s="6" t="inlineStr"/>
+      <c r="K460" s="5" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B461" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C461" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D461" s="8" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E461" s="8" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F461" s="8" t="inlineStr"/>
+      <c r="G461" s="4" t="inlineStr"/>
+      <c r="H461" s="5" t="inlineStr"/>
+      <c r="I461" s="4" t="inlineStr"/>
+      <c r="J461" s="6" t="inlineStr"/>
+      <c r="K461" s="5" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B462" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D462" s="3" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E462" s="3" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F462" s="3" t="inlineStr"/>
+      <c r="G462" s="4" t="inlineStr"/>
+      <c r="H462" s="5" t="inlineStr"/>
+      <c r="I462" s="4" t="inlineStr"/>
+      <c r="J462" s="6" t="inlineStr"/>
+      <c r="K462" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K452"/>
+  <autoFilter ref="A1:K462"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H452" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H462" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K452" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K462" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -15546,7 +15876,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A452)</f>
+        <f>COUNTA(Casos!A2:A462)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -15560,7 +15890,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$452,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$462,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -15577,7 +15907,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$452,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$462,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -15594,7 +15924,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$452,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$462,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -15611,7 +15941,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$452,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$462,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -15667,11 +15997,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$452,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$462,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$452,A12,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$462,A12,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -15684,11 +16014,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$452,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$462,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$452,A13,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$462,A13,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -15701,11 +16031,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$452,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$462,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$452,A14,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$462,A14,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -15763,19 +16093,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A18,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A18,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A18,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A18,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$452,$A18,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$462,$A18,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15786,19 +16116,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A19,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A19,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A19,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A19,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$452,$A19,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$462,$A19,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15809,19 +16139,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A20,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A20,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A20,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A20,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$452,$A20,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$462,$A20,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15832,19 +16162,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A21,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A21,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A21,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A21,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$452,$A21,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$462,$A21,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15855,19 +16185,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A22,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A22,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A22,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A22,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$452,$A22,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$462,$A22,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15878,19 +16208,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A23,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A23,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A23,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A23,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$452,$A23,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$462,$A23,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15901,19 +16231,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A24,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A24,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A24,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A24,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$452,$A24,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$462,$A24,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15924,19 +16254,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A25,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A25,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A25,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A25,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$452,$A25,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$462,$A25,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15947,19 +16277,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A26,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A26,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A26,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A26,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$452,$A26,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$462,$A26,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15970,19 +16300,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A27,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A27,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A27,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A27,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$452,$A27,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$462,$A27,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -15993,19 +16323,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A28,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A28,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A28,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A28,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$452,$A28,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$462,$A28,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16016,19 +16346,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A29,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A29,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A29,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A29,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$452,$A29,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$462,$A29,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16039,19 +16369,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A30,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A30,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A30,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A30,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$452,$A30,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$462,$A30,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16062,19 +16392,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A31,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A31,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A31,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A31,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$452,$A31,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$462,$A31,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16085,19 +16415,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A32,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A32,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A32,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A32,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$452,$A32,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$462,$A32,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16108,19 +16438,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A33,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A33,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A33,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A33,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$452,$A33,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$462,$A33,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16131,19 +16461,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A34,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A34,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A34,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A34,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$452,$A34,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$462,$A34,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16154,19 +16484,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A35,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A35,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A35,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A35,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$452,$A35,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$462,$A35,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16177,19 +16507,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A36,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A36,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A36,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A36,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$452,$A36,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$462,$A36,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16200,19 +16530,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A37,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A37,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A37,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A37,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$452,$A37,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$462,$A37,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16223,19 +16553,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A38,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A38,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A38,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A38,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$452,$A38,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$462,$A38,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16246,19 +16576,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$452,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$462,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A39,Casos!$H$2:$H$452,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A39,Casos!$H$2:$H$462,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$452,$A39,Casos!$H$2:$H$452,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$462,$A39,Casos!$H$2:$H$462,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$452,$A39,Casos!$H$2:$H$452,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$462,$A39,Casos!$H$2:$H$462,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Casos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$462</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$475</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K462"/>
+  <dimension ref="A1:K475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9345,7 +9345,7 @@
     <row r="267">
       <c r="A267" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-01</t>
+          <t>CP-PDFB-01</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>Editor básico tipo Word</t>
+          <t>Variables desde la base real</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
+          <t>Plantillas PDF básicas → panel Datos → elegir una base → botón "Variable"</t>
         </is>
       </c>
       <c r="F267" s="8" t="inlineStr"/>
@@ -9378,7 +9378,7 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-02</t>
+          <t>CP-PDFB-02</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>Vista previa PDF (básico)</t>
+          <t>Sin base no ofrece variables inventadas</t>
         </is>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>Botón "Vista previa PDF"</t>
+          <t>Abrir "Variable" sin base elegida</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr"/>
@@ -9411,7 +9411,7 @@
     <row r="269">
       <c r="A269" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-03</t>
+          <t>CP-PDFB-03</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>Estudio PDF (lienzo)</t>
+          <t>La variable resuelve en el envío real</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>Crear un diseño con texto, formas, tabla y guardar</t>
+          <t>Insertar {{&lt;columna real&gt;}}, guardar, crear campaña EAP-PDF con esa base y enviar una muestra</t>
         </is>
       </c>
       <c r="F269" s="8" t="inlineStr"/>
@@ -9444,7 +9444,7 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-04</t>
+          <t>CP-PDFB-04</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>Estudio: variables con datos reales</t>
+          <t>Vista previa con datos reales</t>
         </is>
       </c>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Elegir una base en el panel de datos → Vista previa</t>
+          <t>Con base elegida, insertar 2 variables → "Vista previa PDF"</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr"/>
@@ -9477,7 +9477,7 @@
     <row r="271">
       <c r="A271" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-05</t>
+          <t>CP-PDFB-05</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>Estudio: unidades y reglas</t>
+          <t>Variable sin dato se ve sin resolver</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
+          <t>Escribir a mano {{no_existe}} → Vista previa</t>
         </is>
       </c>
       <c r="F271" s="8" t="inlineStr"/>
@@ -9510,7 +9510,7 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-06</t>
+          <t>CP-PDFB-06</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>Estudio: seleccionar elemento rotado</t>
+          <t>Base sin filas de muestra</t>
         </is>
       </c>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Girar un texto y hacer clic dentro de su caja visual</t>
+          <t>Elegir una base cargada antes de previewRows</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr"/>
@@ -9543,7 +9543,7 @@
     <row r="273">
       <c r="A273" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-07</t>
+          <t>CP-PDFB-07</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
@@ -9553,17 +9553,17 @@
       </c>
       <c r="C273" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>Estudio: estilos vinculados</t>
+          <t>Margen del lienzo = margen del PDF</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>Vincular un estilo de texto/párrafo y editarlo</t>
+          <t>Escribir un párrafo largo hasta el borde derecho → Vista previa</t>
         </is>
       </c>
       <c r="F273" s="8" t="inlineStr"/>
@@ -9576,7 +9576,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-08</t>
+          <t>CP-PDFB-08</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>Diseñador PDF (full)</t>
+          <t>Tamaños de cuerpo y títulos</t>
         </is>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
-          <t>Abrir el Diseñador y crear un documento</t>
+          <t>Comparar un h1 y un párrafo en el lienzo contra el PDF</t>
         </is>
       </c>
       <c r="F274" s="3" t="inlineStr"/>
@@ -9609,7 +9609,7 @@
     <row r="275">
       <c r="A275" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-09</t>
+          <t>CP-PDFB-09</t>
         </is>
       </c>
       <c r="B275" s="8" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF de punta a punta</t>
+          <t>La fuente elegida llega al PDF</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
+          <t>Elegir "Times New Roman · con serifa" y generar la vista previa sin seleccionar texto</t>
         </is>
       </c>
       <c r="F275" s="8" t="inlineStr"/>
@@ -9642,7 +9642,7 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-10</t>
+          <t>CP-PDFB-10</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr">
@@ -9652,17 +9652,17 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>Tabla que desborda pagina</t>
+          <t>Fuente al guardar y volver a cargar</t>
         </is>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
+          <t>Guardar con Times, "Nueva", y cargar la plantilla</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr"/>
@@ -9675,7 +9675,7 @@
     <row r="277">
       <c r="A277" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-11</t>
+          <t>CP-PDFB-11</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
@@ -9690,12 +9690,12 @@
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>Celdas con JSON (multiregistro)</t>
+          <t>Catálogo de fuentes honesto</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>Base con una columna que trae un array JSON</t>
+          <t>Abrir el desplegable de fuente</t>
         </is>
       </c>
       <c r="F277" s="8" t="inlineStr"/>
@@ -9708,7 +9708,7 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-12</t>
+          <t>CP-PDFB-12</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr">
@@ -9718,17 +9718,17 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>Encabezados con BOM/espacios</t>
+          <t>Plantilla vieja con fuente retirada</t>
         </is>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
+          <t>Cargar una plantilla guardada con Georgia</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr"/>
@@ -9741,7 +9741,7 @@
     <row r="279">
       <c r="A279" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-13</t>
+          <t>CP-PDFB-13</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
@@ -9756,12 +9756,12 @@
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>Bordes y degradados</t>
+          <t>Panel de datos no se desborda</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>Formas con borde discontinuo y relleno degradado</t>
+          <t>Elegir una base de nombre largo</t>
         </is>
       </c>
       <c r="F279" s="8" t="inlineStr"/>
@@ -9774,12 +9774,12 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-PDF-01</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Editor básico tipo Word</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr"/>
@@ -9807,12 +9807,12 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-PDF-02</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C281" s="7" t="inlineStr">
@@ -9822,12 +9822,12 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>Vista previa PDF (básico)</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Botón "Vista previa PDF"</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr"/>
@@ -9840,12 +9840,12 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-PDF-03</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>Estudio PDF (lienzo)</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Crear un diseño con texto, formas, tabla y guardar</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr"/>
@@ -9873,12 +9873,12 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-PDF-04</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C283" s="7" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Estudio: variables con datos reales</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Elegir una base en el panel de datos → Vista previa</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr"/>
@@ -9906,27 +9906,27 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-PDF-05</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>Estudio: unidades y reglas</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr"/>
@@ -9939,12 +9939,12 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-PDF-06</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C285" s="7" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Estudio: seleccionar elemento rotado</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Girar un texto y hacer clic dentro de su caja visual</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr"/>
@@ -9972,12 +9972,12 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-PDF-07</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Estudio: estilos vinculados</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>Vincular un estilo de texto/párrafo y editarlo</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr"/>
@@ -10005,27 +10005,27 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-PDF-08</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C287" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Diseñador PDF (full)</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>Abrir el Diseñador y crear un documento</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr"/>
@@ -10038,12 +10038,12 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-PDF-09</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>Campaña EAP-PDF de punta a punta</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr"/>
@@ -10071,27 +10071,27 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-PDF-10</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C289" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Tabla que desborda pagina</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr"/>
@@ -10104,12 +10104,12 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-PDF-11</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Celdas con JSON (multiregistro)</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Base con una columna que trae un array JSON</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr"/>
@@ -10137,12 +10137,12 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-PDF-12</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C291" s="7" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Encabezados con BOM/espacios</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr"/>
@@ -10170,27 +10170,27 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-PDF-13</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Bordes y degradados</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Formas con borde discontinuo y relleno degradado</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr"/>
@@ -10203,7 +10203,7 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
@@ -10213,17 +10213,17 @@
       </c>
       <c r="C293" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr"/>
@@ -10236,12 +10236,12 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr"/>
@@ -10269,12 +10269,12 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr"/>
@@ -10302,27 +10302,27 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr"/>
@@ -10335,27 +10335,27 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr"/>
@@ -10368,27 +10368,27 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr"/>
@@ -10401,12 +10401,12 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C299" s="7" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr"/>
@@ -10434,27 +10434,27 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr"/>
@@ -10467,12 +10467,12 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr"/>
@@ -10500,27 +10500,27 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr"/>
@@ -10533,27 +10533,27 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr"/>
@@ -10566,27 +10566,27 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr"/>
@@ -10599,12 +10599,12 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C305" s="7" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr"/>
@@ -10632,27 +10632,27 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr"/>
@@ -10665,12 +10665,12 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr"/>
@@ -10698,27 +10698,27 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr"/>
@@ -10731,12 +10731,12 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr"/>
@@ -10764,27 +10764,27 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-01</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>DKIM verificado en verde</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio con DKIM firmando</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr"/>
@@ -10797,27 +10797,27 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-02</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C311" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>SPF/DMARC sin publicar en gris</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio recién creado</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr"/>
@@ -10830,12 +10830,12 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-03</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
@@ -10845,12 +10845,12 @@
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>SPF verde al publicarlo</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr"/>
@@ -10863,12 +10863,12 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-04</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>DMARC verde al publicarlo</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr"/>
@@ -10896,27 +10896,27 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-05</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>Tooltip explica el motivo</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>Pasar el mouse sobre un chip gris</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr"/>
@@ -10929,7 +10929,7 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-06</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
@@ -10939,17 +10939,17 @@
       </c>
       <c r="C315" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>Sin el layer de DNS</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr"/>
@@ -10962,7 +10962,7 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-07</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
@@ -10972,17 +10972,17 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Correos sueltos sin el panel</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr"/>
@@ -10995,7 +10995,7 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-08</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
@@ -11005,17 +11005,17 @@
       </c>
       <c r="C317" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>No es bloqueante</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr"/>
@@ -11028,27 +11028,27 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr"/>
@@ -11061,12 +11061,12 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr"/>
@@ -11094,12 +11094,12 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -11109,12 +11109,12 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr"/>
@@ -11127,27 +11127,27 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr"/>
@@ -11160,27 +11160,27 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr"/>
@@ -11193,27 +11193,27 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-AUT-01</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>DKIM verificado en verde</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Abrir el detalle de un dominio con DKIM firmando</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr"/>
@@ -11226,12 +11226,12 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-AUT-02</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -11241,12 +11241,12 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>SPF/DMARC sin publicar en gris</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Abrir el detalle de un dominio recién creado</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr"/>
@@ -11259,27 +11259,27 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-AUT-03</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>SPF verde al publicarlo</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr"/>
@@ -11292,27 +11292,27 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-AUT-04</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>DMARC verde al publicarlo</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr"/>
@@ -11325,27 +11325,27 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-AUT-05</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>Tooltip explica el motivo</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Pasar el mouse sobre un chip gris</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,27 +11358,27 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-AUT-06</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Sin el layer de DNS</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,27 +11391,27 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-35</t>
+          <t>CP-AUT-07</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>El bloqueo escalado explica por qué fue inmediato</t>
+          <t>Correos sueltos sin el panel</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
+          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,27 +11424,27 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-36</t>
+          <t>CP-AUT-08</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>El primer bloqueo no repite la explicación</t>
+          <t>No es bloqueante</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>En una cuenta nueva, fallar 3 veces</t>
+          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,7 +11457,7 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,7 +11490,7 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,7 +11523,7 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,7 +11556,7 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,7 +11589,7 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
@@ -11599,17 +11599,17 @@
       </c>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,7 +11622,7 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,7 +11655,7 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
@@ -11670,12 +11670,12 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,12 +11688,12 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,12 +11721,12 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,12 +11754,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11787,12 +11787,12 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,12 +11820,12 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-SEC-35</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>El bloqueo escalado explica por qué fue inmediato</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,12 +11853,12 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-36</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>El primer bloqueo no repite la explicación</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>En una cuenta nueva, fallar 3 veces</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,27 +11886,27 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,27 +11919,27 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,12 +11952,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,12 +11985,12 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C347" s="7" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,12 +12018,12 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,27 +12051,27 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,27 +12084,27 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,7 +12117,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12150,7 +12150,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
@@ -12160,17 +12160,17 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -12183,7 +12183,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr"/>
@@ -12216,7 +12216,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -12249,7 +12249,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr"/>
@@ -12282,7 +12282,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -12315,7 +12315,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
@@ -12330,12 +12330,12 @@
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr"/>
@@ -12348,7 +12348,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -12358,17 +12358,17 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -12381,7 +12381,7 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
@@ -12391,17 +12391,17 @@
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr"/>
@@ -12414,7 +12414,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -12447,7 +12447,7 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
@@ -12457,17 +12457,17 @@
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr"/>
@@ -12480,7 +12480,7 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
@@ -12490,17 +12490,17 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
@@ -12513,7 +12513,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B363" s="8" t="inlineStr">
@@ -12523,17 +12523,17 @@
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr"/>
@@ -12546,7 +12546,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr"/>
@@ -12579,27 +12579,27 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B365" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr"/>
@@ -12612,12 +12612,12 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr"/>
@@ -12645,27 +12645,27 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B367" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr"/>
@@ -12678,27 +12678,27 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr"/>
@@ -12711,27 +12711,27 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B369" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr"/>
@@ -12744,27 +12744,27 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr"/>
@@ -12777,27 +12777,27 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B371" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr"/>
@@ -12810,12 +12810,12 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr"/>
@@ -12843,12 +12843,12 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C373" s="7" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr"/>
@@ -12876,27 +12876,27 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
@@ -12909,27 +12909,27 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B375" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr"/>
@@ -12942,27 +12942,27 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr"/>
@@ -12975,12 +12975,12 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B377" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C377" s="7" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr"/>
@@ -13008,7 +13008,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -13018,17 +13018,17 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr"/>
@@ -13041,12 +13041,12 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B379" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C379" s="7" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr"/>
@@ -13074,27 +13074,27 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr"/>
@@ -13107,12 +13107,12 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B381" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C381" s="7" t="inlineStr">
@@ -13122,12 +13122,12 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr"/>
@@ -13140,12 +13140,12 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -13155,12 +13155,12 @@
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr"/>
@@ -13173,27 +13173,27 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B383" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr"/>
@@ -13206,12 +13206,12 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr"/>
@@ -13239,27 +13239,27 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B385" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr"/>
@@ -13272,12 +13272,12 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr"/>
@@ -13305,12 +13305,12 @@
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B387" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C387" s="7" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr"/>
@@ -13338,27 +13338,27 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr"/>
@@ -13371,27 +13371,27 @@
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B389" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr"/>
@@ -13404,27 +13404,27 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-01</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Aviso de campaña por aprobar</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr"/>
@@ -13437,27 +13437,27 @@
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-02</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B391" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>Solo a quien puede aprobar</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita de otro operator del mismo equipo</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-03</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Quien la pide no se avisa a sí mismo</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita del operator que la solicitó</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr"/>
@@ -13503,7 +13503,7 @@
     <row r="393">
       <c r="A393" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-04</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B393" s="8" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento entre empresas</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita de un usuario de OTRA empresa</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr"/>
@@ -13536,7 +13536,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-05</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -13546,17 +13546,17 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>Aviso de aprobada</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>El owner aprueba la campaña</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr"/>
@@ -13569,7 +13569,7 @@
     <row r="395">
       <c r="A395" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-06</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B395" s="8" t="inlineStr">
@@ -13579,17 +13579,17 @@
       </c>
       <c r="C395" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>Aviso de rechazada con el motivo</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr"/>
@@ -13602,7 +13602,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-07</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
@@ -13612,17 +13612,17 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Saldo bajo in-app</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>Hacer un envío que deje el saldo bajo el umbral</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr"/>
@@ -13635,7 +13635,7 @@
     <row r="397">
       <c r="A397" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-08</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B397" s="8" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>Avisos nuevos abajo a la derecha</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr"/>
@@ -13668,7 +13668,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-09</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
@@ -13678,17 +13678,17 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Los nuevos NO saltan al entrar</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Con avisos viejos sin leer, entrar al portal</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr"/>
@@ -13701,7 +13701,7 @@
     <row r="399">
       <c r="A399" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-10</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B399" s="8" t="inlineStr">
@@ -13711,17 +13711,17 @@
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>La tarjeta se retira sola</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Esperar unos segundos tras el aviso</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr"/>
@@ -13734,7 +13734,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-11</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
@@ -13744,17 +13744,17 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Clic lleva al lugar correcto</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>Hacer clic en "Campaña por aprobar"</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr"/>
@@ -13767,7 +13767,7 @@
     <row r="401">
       <c r="A401" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-12</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B401" s="8" t="inlineStr">
@@ -13777,17 +13777,17 @@
       </c>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>Marcar leídas</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Abrir el panel y pulsar "Marcar leídas"</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr"/>
@@ -13800,7 +13800,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-13</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
@@ -13810,17 +13810,17 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>No se puede marcar la de otro</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr"/>
@@ -13833,7 +13833,7 @@
     <row r="403">
       <c r="A403" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-14</t>
+          <t>CP-CAM-01</t>
         </is>
       </c>
       <c r="B403" s="8" t="inlineStr">
@@ -13843,17 +13843,17 @@
       </c>
       <c r="C403" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>Sin notificaciones</t>
+          <t>Aviso de campaña por aprobar</t>
         </is>
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Usuario nuevo abre la campanita</t>
+          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr"/>
@@ -13866,7 +13866,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-15</t>
+          <t>CP-CAM-02</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -13876,17 +13876,17 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>No molesta en impersonación</t>
+          <t>Solo a quien puede aprobar</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>Entrar como admin con "Ver como cliente"</t>
+          <t>Revisar la campanita de otro operator del mismo equipo</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
     <row r="405">
       <c r="A405" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-16</t>
+          <t>CP-CAM-03</t>
         </is>
       </c>
       <c r="B405" s="8" t="inlineStr">
@@ -13909,17 +13909,17 @@
       </c>
       <c r="C405" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>La aprobación funciona sin la tabla</t>
+          <t>Quien la pide no se avisa a sí mismo</t>
         </is>
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
+          <t>Revisar la campanita del operator que la solicitó</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr"/>
@@ -13932,12 +13932,12 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-CAM-04</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Aislamiento entre empresas</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Revisar la campanita de un usuario de OTRA empresa</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr"/>
@@ -13965,27 +13965,27 @@
     <row r="407">
       <c r="A407" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-CAM-05</t>
         </is>
       </c>
       <c r="B407" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Aviso de aprobada</t>
         </is>
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>El owner aprueba la campaña</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr"/>
@@ -13998,27 +13998,27 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-CAM-06</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Aviso de rechazada con el motivo</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr"/>
@@ -14031,27 +14031,27 @@
     <row r="409">
       <c r="A409" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-CAM-07</t>
         </is>
       </c>
       <c r="B409" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C409" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Saldo bajo in-app</t>
         </is>
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Hacer un envío que deje el saldo bajo el umbral</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr"/>
@@ -14064,27 +14064,27 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-CAM-08</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Avisos nuevos abajo a la derecha</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr"/>
@@ -14097,12 +14097,12 @@
     <row r="411">
       <c r="A411" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-CAM-09</t>
         </is>
       </c>
       <c r="B411" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C411" s="7" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Los nuevos NO saltan al entrar</t>
         </is>
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>Con avisos viejos sin leer, entrar al portal</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr"/>
@@ -14130,12 +14130,12 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-CAM-10</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
@@ -14145,12 +14145,12 @@
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>La tarjeta se retira sola</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Esperar unos segundos tras el aviso</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr"/>
@@ -14163,27 +14163,27 @@
     <row r="413">
       <c r="A413" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-CAM-11</t>
         </is>
       </c>
       <c r="B413" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C413" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>Clic lleva al lugar correcto</t>
         </is>
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Hacer clic en "Campaña por aprobar"</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr"/>
@@ -14196,12 +14196,12 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-CAM-12</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
@@ -14211,12 +14211,12 @@
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Marcar leídas</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Abrir el panel y pulsar "Marcar leídas"</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr"/>
@@ -14229,12 +14229,12 @@
     <row r="415">
       <c r="A415" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-CAM-13</t>
         </is>
       </c>
       <c r="B415" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C415" s="7" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>No se puede marcar la de otro</t>
         </is>
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr"/>
@@ -14262,27 +14262,27 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-CAM-14</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Sin notificaciones</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Usuario nuevo abre la campanita</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr"/>
@@ -14295,27 +14295,27 @@
     <row r="417">
       <c r="A417" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-CAM-15</t>
         </is>
       </c>
       <c r="B417" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C417" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>No molesta en impersonación</t>
         </is>
       </c>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Entrar como admin con "Ver como cliente"</t>
         </is>
       </c>
       <c r="F417" s="8" t="inlineStr"/>
@@ -14328,27 +14328,27 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-CAM-16</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>La aprobación funciona sin la tabla</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr"/>
@@ -14361,7 +14361,7 @@
     <row r="419">
       <c r="A419" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B419" s="8" t="inlineStr">
@@ -14371,17 +14371,17 @@
       </c>
       <c r="C419" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F419" s="8" t="inlineStr"/>
@@ -14394,7 +14394,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
@@ -14409,12 +14409,12 @@
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr"/>
@@ -14427,7 +14427,7 @@
     <row r="421">
       <c r="A421" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-01</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B421" s="8" t="inlineStr">
@@ -14437,17 +14437,17 @@
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>Segmentos calculados, no declarados</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Muestras con una campaña SMS</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F421" s="8" t="inlineStr"/>
@@ -14460,7 +14460,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-02</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>Un SMS largo cuesta el doble</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>Campaña con más de 160 caracteres</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr"/>
@@ -14493,7 +14493,7 @@
     <row r="423">
       <c r="A423" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-03</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B423" s="8" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Una emoji parte el mensaje</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F423" s="8" t="inlineStr"/>
@@ -14526,7 +14526,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-04</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
@@ -14536,17 +14536,17 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>Lo estimado es lo que se cobra</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr"/>
@@ -14559,7 +14559,7 @@
     <row r="425">
       <c r="A425" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-05</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B425" s="8" t="inlineStr">
@@ -14569,17 +14569,17 @@
       </c>
       <c r="C425" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>Tarifas nuevas visibles</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → canal SMS y Voz</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F425" s="8" t="inlineStr"/>
@@ -14592,7 +14592,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-06</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
@@ -14602,17 +14602,17 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>Ningún cliente por debajo del costo</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → revisar overrides por cliente</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr"/>
@@ -14625,7 +14625,7 @@
     <row r="427">
       <c r="A427" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-07</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B427" s="8" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>Contador del editor SMS</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>Escribir un SMS con emoji en Plantillas SMS</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F427" s="8" t="inlineStr"/>
@@ -14658,7 +14658,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>CP-PUB-01</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>La landing no publica precios</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>Abrir la landing → sección Precios</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr"/>
@@ -14691,7 +14691,7 @@
     <row r="429">
       <c r="A429" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-01</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B429" s="8" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>Título e idioma</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>Ver el código fuente de la landing</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F429" s="8" t="inlineStr"/>
@@ -14724,7 +14724,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-02</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
@@ -14734,17 +14734,17 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>Vista previa al compartir</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr"/>
@@ -14757,7 +14757,7 @@
     <row r="431">
       <c r="A431" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-03</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B431" s="8" t="inlineStr">
@@ -14767,17 +14767,17 @@
       </c>
       <c r="C431" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>Abrir la landing y mirar la pestaña</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F431" s="8" t="inlineStr"/>
@@ -14790,7 +14790,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-04</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
@@ -14805,12 +14805,12 @@
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>Icono en iOS</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>"Añadir a pantalla de inicio" desde Safari</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr"/>
@@ -14823,7 +14823,7 @@
     <row r="433">
       <c r="A433" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-05</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B433" s="8" t="inlineStr">
@@ -14838,12 +14838,12 @@
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>Datos estructurados</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F433" s="8" t="inlineStr"/>
@@ -14856,7 +14856,7 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-06</t>
+          <t>CP-TAR-01</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
@@ -14866,17 +14866,17 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>Canonical y robots</t>
+          <t>Segmentos calculados, no declarados</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>Abrir /robots.txt y /sitemap.xml</t>
+          <t>Muestras con una campaña SMS</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr"/>
@@ -14889,7 +14889,7 @@
     <row r="435">
       <c r="A435" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-01</t>
+          <t>CP-TAR-02</t>
         </is>
       </c>
       <c r="B435" s="8" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>Tabla de precios por canal</t>
+          <t>Un SMS largo cuesta el doble</t>
         </is>
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>Landing → Precios</t>
+          <t>Campaña con más de 160 caracteres</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr"/>
@@ -14922,7 +14922,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-02</t>
+          <t>CP-TAR-03</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -14932,17 +14932,17 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>Letra pequeña de precios</t>
+          <t>Una emoji parte el mensaje</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>Leer bajo la tabla</t>
+          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr"/>
@@ -14955,7 +14955,7 @@
     <row r="437">
       <c r="A437" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-03</t>
+          <t>CP-TAR-04</t>
         </is>
       </c>
       <c r="B437" s="8" t="inlineStr">
@@ -14965,17 +14965,17 @@
       </c>
       <c r="C437" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>Icono de WhatsApp</t>
+          <t>Lo estimado es lo que se cobra</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>Sección Canales</t>
+          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr"/>
@@ -14988,7 +14988,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-04</t>
+          <t>CP-TAR-05</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -14998,17 +14998,17 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>Sin promesa de 500 correos</t>
+          <t>Tarifas nuevas visibles</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>Recorrer toda la landing</t>
+          <t>Admin → Tarifas → canal SMS y Voz</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr"/>
@@ -15021,7 +15021,7 @@
     <row r="439">
       <c r="A439" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-05</t>
+          <t>CP-TAR-06</t>
         </is>
       </c>
       <c r="B439" s="8" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>Footer sin enlaces rotos</t>
+          <t>Ningún cliente por debajo del costo</t>
         </is>
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>Hacer clic en cada enlace del footer</t>
+          <t>Admin → Tarifas → revisar overrides por cliente</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr"/>
@@ -15054,7 +15054,7 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>CP-A11Y-01</t>
+          <t>CP-TAR-07</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -15064,17 +15064,17 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>Cerrar el modal con teclado</t>
+          <t>Contador del editor SMS</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Escape</t>
+          <t>Escribir un SMS con emoji en Plantillas SMS</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr"/>
@@ -15087,7 +15087,7 @@
     <row r="441">
       <c r="A441" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-02</t>
+          <t>CP-PUB-01</t>
         </is>
       </c>
       <c r="B441" s="8" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>Foco en el modal</t>
+          <t>La landing no publica precios</t>
         </is>
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Tab</t>
+          <t>Abrir la landing → sección Precios</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr"/>
@@ -15120,7 +15120,7 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>CP-A11Y-03</t>
+          <t>CP-SEO-01</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -15130,17 +15130,17 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>Lector de pantalla</t>
+          <t>Título e idioma</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>Abrir el modal con un lector activo</t>
+          <t>Ver el código fuente de la landing</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr"/>
@@ -15153,12 +15153,12 @@
     <row r="443">
       <c r="A443" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-SEO-02</t>
         </is>
       </c>
       <c r="B443" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C443" s="7" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>Vista previa al compartir</t>
         </is>
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr"/>
@@ -15186,27 +15186,27 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-SEO-03</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Favicon</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Abrir la landing y mirar la pestaña</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr"/>
@@ -15219,12 +15219,12 @@
     <row r="445">
       <c r="A445" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-SEO-04</t>
         </is>
       </c>
       <c r="B445" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C445" s="7" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Icono en iOS</t>
         </is>
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>"Añadir a pantalla de inicio" desde Safari</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr"/>
@@ -15252,27 +15252,27 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-SEO-05</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Datos estructurados</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr"/>
@@ -15285,12 +15285,12 @@
     <row r="447">
       <c r="A447" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-SEO-06</t>
         </is>
       </c>
       <c r="B447" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C447" s="7" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Canonical y robots</t>
         </is>
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Abrir /robots.txt y /sitemap.xml</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr"/>
@@ -15318,27 +15318,27 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-LAN-01</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Tabla de precios por canal</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Landing → Precios</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr"/>
@@ -15351,27 +15351,27 @@
     <row r="449">
       <c r="A449" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-LAN-02</t>
         </is>
       </c>
       <c r="B449" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C449" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Letra pequeña de precios</t>
         </is>
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Leer bajo la tabla</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr"/>
@@ -15384,12 +15384,12 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-LAN-03</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
@@ -15399,12 +15399,12 @@
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>Icono de WhatsApp</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Sección Canales</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr"/>
@@ -15417,12 +15417,12 @@
     <row r="451">
       <c r="A451" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-LAN-04</t>
         </is>
       </c>
       <c r="B451" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C451" s="7" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>Sin promesa de 500 correos</t>
         </is>
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Recorrer toda la landing</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr"/>
@@ -15450,12 +15450,12 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-LAN-05</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Footer sin enlaces rotos</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Hacer clic en cada enlace del footer</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr"/>
@@ -15483,27 +15483,27 @@
     <row r="453">
       <c r="A453" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-A11Y-01</t>
         </is>
       </c>
       <c r="B453" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C453" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Cerrar el modal con teclado</t>
         </is>
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Abrir /?activacion=ok y pulsar Escape</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr"/>
@@ -15516,27 +15516,27 @@
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-A11Y-02</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Foco en el modal</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Abrir /?activacion=ok y pulsar Tab</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr"/>
@@ -15549,27 +15549,27 @@
     <row r="455">
       <c r="A455" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-A11Y-03</t>
         </is>
       </c>
       <c r="B455" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C455" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Lector de pantalla</t>
         </is>
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Abrir el modal con un lector activo</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr"/>
@@ -15582,27 +15582,27 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F456" s="3" t="inlineStr"/>
@@ -15615,27 +15615,27 @@
     <row r="457">
       <c r="A457" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B457" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C457" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E457" s="8" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F457" s="8" t="inlineStr"/>
@@ -15648,12 +15648,12 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
@@ -15663,12 +15663,12 @@
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr"/>
@@ -15681,12 +15681,12 @@
     <row r="459">
       <c r="A459" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B459" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C459" s="7" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E459" s="8" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F459" s="8" t="inlineStr"/>
@@ -15714,27 +15714,27 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-CAS-05</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Consentimiento por canal</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Contacto sin consentimiento del canal 0</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr"/>
@@ -15747,27 +15747,27 @@
     <row r="461">
       <c r="A461" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-CAS-06</t>
         </is>
       </c>
       <c r="B461" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C461" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Listado de cascadas</t>
         </is>
       </c>
       <c r="E461" s="8" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Abrir el listado</t>
         </is>
       </c>
       <c r="F461" s="8" t="inlineStr"/>
@@ -15780,27 +15780,27 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-SER-01</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Serie de 30 días (cliente)</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr"/>
@@ -15810,13 +15810,442 @@
       <c r="J462" s="6" t="inlineStr"/>
       <c r="K462" s="5" t="inlineStr"/>
     </row>
+    <row r="463">
+      <c r="A463" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-02</t>
+        </is>
+      </c>
+      <c r="B463" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C463" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D463" s="8" t="inlineStr">
+        <is>
+          <t>Serie global (admin)</t>
+        </is>
+      </c>
+      <c r="E463" s="8" t="inlineStr">
+        <is>
+          <t>Panel de control → gráfico</t>
+        </is>
+      </c>
+      <c r="F463" s="8" t="inlineStr"/>
+      <c r="G463" s="4" t="inlineStr"/>
+      <c r="H463" s="5" t="inlineStr"/>
+      <c r="I463" s="4" t="inlineStr"/>
+      <c r="J463" s="6" t="inlineStr"/>
+      <c r="K463" s="5" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-03</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D464" s="3" t="inlineStr">
+        <is>
+          <t>Muestras excluidas</t>
+        </is>
+      </c>
+      <c r="E464" s="3" t="inlineStr">
+        <is>
+          <t>Enviar muestras y revisar la serie</t>
+        </is>
+      </c>
+      <c r="F464" s="3" t="inlineStr"/>
+      <c r="G464" s="4" t="inlineStr"/>
+      <c r="H464" s="5" t="inlineStr"/>
+      <c r="I464" s="4" t="inlineStr"/>
+      <c r="J464" s="6" t="inlineStr"/>
+      <c r="K464" s="5" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-04</t>
+        </is>
+      </c>
+      <c r="B465" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C465" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D465" s="8" t="inlineStr">
+        <is>
+          <t>Aislamiento</t>
+        </is>
+      </c>
+      <c r="E465" s="8" t="inlineStr">
+        <is>
+          <t>Comparar la serie de dos clientes</t>
+        </is>
+      </c>
+      <c r="F465" s="8" t="inlineStr"/>
+      <c r="G465" s="4" t="inlineStr"/>
+      <c r="H465" s="5" t="inlineStr"/>
+      <c r="I465" s="4" t="inlineStr"/>
+      <c r="J465" s="6" t="inlineStr"/>
+      <c r="K465" s="5" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-05</t>
+        </is>
+      </c>
+      <c r="B466" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D466" s="3" t="inlineStr">
+        <is>
+          <t>Adiós "(parcial)"</t>
+        </is>
+      </c>
+      <c r="E466" s="3" t="inlineStr">
+        <is>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+        </is>
+      </c>
+      <c r="F466" s="3" t="inlineStr"/>
+      <c r="G466" s="4" t="inlineStr"/>
+      <c r="H466" s="5" t="inlineStr"/>
+      <c r="I466" s="4" t="inlineStr"/>
+      <c r="J466" s="6" t="inlineStr"/>
+      <c r="K466" s="5" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-06</t>
+        </is>
+      </c>
+      <c r="B467" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C467" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D467" s="8" t="inlineStr">
+        <is>
+          <t>Leyenda interactiva</t>
+        </is>
+      </c>
+      <c r="E467" s="8" t="inlineStr">
+        <is>
+          <t>Ocultar/mostrar series en el gráfico</t>
+        </is>
+      </c>
+      <c r="F467" s="8" t="inlineStr"/>
+      <c r="G467" s="4" t="inlineStr"/>
+      <c r="H467" s="5" t="inlineStr"/>
+      <c r="I467" s="4" t="inlineStr"/>
+      <c r="J467" s="6" t="inlineStr"/>
+      <c r="K467" s="5" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D468" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E468" s="3" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F468" s="3" t="inlineStr"/>
+      <c r="G468" s="4" t="inlineStr"/>
+      <c r="H468" s="5" t="inlineStr"/>
+      <c r="I468" s="4" t="inlineStr"/>
+      <c r="J468" s="6" t="inlineStr"/>
+      <c r="K468" s="5" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B469" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C469" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D469" s="8" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E469" s="8" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F469" s="8" t="inlineStr"/>
+      <c r="G469" s="4" t="inlineStr"/>
+      <c r="H469" s="5" t="inlineStr"/>
+      <c r="I469" s="4" t="inlineStr"/>
+      <c r="J469" s="6" t="inlineStr"/>
+      <c r="K469" s="5" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D470" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E470" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F470" s="3" t="inlineStr"/>
+      <c r="G470" s="4" t="inlineStr"/>
+      <c r="H470" s="5" t="inlineStr"/>
+      <c r="I470" s="4" t="inlineStr"/>
+      <c r="J470" s="6" t="inlineStr"/>
+      <c r="K470" s="5" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B471" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C471" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D471" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E471" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F471" s="8" t="inlineStr"/>
+      <c r="G471" s="4" t="inlineStr"/>
+      <c r="H471" s="5" t="inlineStr"/>
+      <c r="I471" s="4" t="inlineStr"/>
+      <c r="J471" s="6" t="inlineStr"/>
+      <c r="K471" s="5" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B472" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D472" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E472" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F472" s="3" t="inlineStr"/>
+      <c r="G472" s="4" t="inlineStr"/>
+      <c r="H472" s="5" t="inlineStr"/>
+      <c r="I472" s="4" t="inlineStr"/>
+      <c r="J472" s="6" t="inlineStr"/>
+      <c r="K472" s="5" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B473" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C473" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D473" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E473" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F473" s="8" t="inlineStr"/>
+      <c r="G473" s="4" t="inlineStr"/>
+      <c r="H473" s="5" t="inlineStr"/>
+      <c r="I473" s="4" t="inlineStr"/>
+      <c r="J473" s="6" t="inlineStr"/>
+      <c r="K473" s="5" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D474" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E474" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F474" s="3" t="inlineStr"/>
+      <c r="G474" s="4" t="inlineStr"/>
+      <c r="H474" s="5" t="inlineStr"/>
+      <c r="I474" s="4" t="inlineStr"/>
+      <c r="J474" s="6" t="inlineStr"/>
+      <c r="K474" s="5" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B475" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C475" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D475" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E475" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F475" s="8" t="inlineStr"/>
+      <c r="G475" s="4" t="inlineStr"/>
+      <c r="H475" s="5" t="inlineStr"/>
+      <c r="I475" s="4" t="inlineStr"/>
+      <c r="J475" s="6" t="inlineStr"/>
+      <c r="K475" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K462"/>
+  <autoFilter ref="A1:K475"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H462" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H475" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K462" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K475" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -15876,7 +16305,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A462)</f>
+        <f>COUNTA(Casos!A2:A475)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -15890,7 +16319,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$462,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$475,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -15907,7 +16336,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$462,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$475,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -15924,7 +16353,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$462,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$475,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -15941,7 +16370,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$462,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$475,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -15997,11 +16426,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$462,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$475,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$462,A12,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$475,A12,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -16014,11 +16443,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$462,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$475,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$462,A13,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$475,A13,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -16031,11 +16460,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$462,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$475,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$462,A14,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$475,A14,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -16093,19 +16522,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A18,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A18,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A18,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A18,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$462,$A18,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$475,$A18,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16116,19 +16545,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A19,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A19,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A19,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A19,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$462,$A19,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$475,$A19,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16139,19 +16568,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A20,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A20,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A20,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A20,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$462,$A20,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$475,$A20,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16162,19 +16591,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A21,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A21,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A21,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A21,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$462,$A21,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$475,$A21,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16185,19 +16614,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A22,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A22,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A22,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A22,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$462,$A22,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$475,$A22,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16208,19 +16637,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A23,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A23,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A23,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A23,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$462,$A23,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$475,$A23,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16231,19 +16660,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A24,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A24,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A24,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A24,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$462,$A24,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$475,$A24,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16254,19 +16683,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A25,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A25,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A25,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A25,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$462,$A25,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$475,$A25,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16277,19 +16706,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A26,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A26,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A26,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A26,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$462,$A26,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$475,$A26,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16300,19 +16729,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A27,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A27,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A27,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A27,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$462,$A27,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$475,$A27,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16323,19 +16752,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A28,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A28,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A28,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A28,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$462,$A28,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$475,$A28,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16346,19 +16775,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A29,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A29,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A29,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A29,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$462,$A29,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$475,$A29,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16369,19 +16798,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A30,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A30,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A30,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A30,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$462,$A30,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$475,$A30,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16392,19 +16821,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A31,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A31,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A31,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A31,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$462,$A31,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$475,$A31,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16415,19 +16844,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A32,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A32,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A32,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A32,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$462,$A32,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$475,$A32,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16438,19 +16867,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A33,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A33,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A33,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A33,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$462,$A33,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$475,$A33,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16461,19 +16890,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A34,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A34,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A34,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A34,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$462,$A34,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$475,$A34,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16484,19 +16913,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A35,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A35,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A35,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A35,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$462,$A35,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$475,$A35,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16507,19 +16936,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A36,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A36,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A36,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A36,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$462,$A36,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$475,$A36,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16530,19 +16959,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A37,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A37,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A37,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A37,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$462,$A37,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$475,$A37,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16553,19 +16982,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A38,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A38,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A38,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A38,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$462,$A38,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$475,$A38,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16576,19 +17005,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$462,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$475,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A39,Casos!$H$2:$H$462,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A39,Casos!$H$2:$H$475,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$462,$A39,Casos!$H$2:$H$462,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$475,$A39,Casos!$H$2:$H$475,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$462,$A39,Casos!$H$2:$H$462,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$475,$A39,Casos!$H$2:$H$475,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$475</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$491</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K475"/>
+  <dimension ref="A1:K491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9774,7 +9774,7 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-01</t>
+          <t>CP-PDFP-01</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>Editor básico tipo Word</t>
+          <t>Encabezado en TODAS las hojas</t>
         </is>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
+          <t>Configurar página → Encabezado "ACME" → escribir contenido de 3 hojas → Vista previa PDF</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr"/>
@@ -9807,7 +9807,7 @@
     <row r="281">
       <c r="A281" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-02</t>
+          <t>CP-PDFP-02</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
@@ -9822,12 +9822,12 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>Vista previa PDF (básico)</t>
+          <t>Numeración del pie</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>Botón "Vista previa PDF"</t>
+          <t>Pie = Página [[pagina]] de [[paginas]] (botones) → Vista previa</t>
         </is>
       </c>
       <c r="F281" s="8" t="inlineStr"/>
@@ -9840,7 +9840,7 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-03</t>
+          <t>CP-PDFP-03</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>Estudio PDF (lienzo)</t>
+          <t>El membrete llega al ENVÍO REAL</t>
         </is>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Crear un diseño con texto, formas, tabla y guardar</t>
+          <t>Guardar esa plantilla, usarla en campaña EAP-PDF y enviar muestra</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr"/>
@@ -9873,7 +9873,7 @@
     <row r="283">
       <c r="A283" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-04</t>
+          <t>CP-PDFP-04</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
@@ -9883,17 +9883,17 @@
       </c>
       <c r="C283" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>Estudio: variables con datos reales</t>
+          <t>El membrete no se duplica</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>Elegir una base en el panel de datos → Vista previa</t>
+          <t>Vista previa con encabezado y pie</t>
         </is>
       </c>
       <c r="F283" s="8" t="inlineStr"/>
@@ -9906,7 +9906,7 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-05</t>
+          <t>CP-PDFP-05</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>Estudio: unidades y reglas</t>
+          <t>Variables de la base en el membrete</t>
         </is>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
+          <t>Encabezado = Extracto de {{Nombre}} con base elegida</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr"/>
@@ -9939,7 +9939,7 @@
     <row r="285">
       <c r="A285" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-06</t>
+          <t>CP-PDFP-06</t>
         </is>
       </c>
       <c r="B285" s="8" t="inlineStr">
@@ -9949,17 +9949,17 @@
       </c>
       <c r="C285" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>Estudio: seleccionar elemento rotado</t>
+          <t>Columna llamada "pagina" no rompe la numeración</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>Girar un texto y hacer clic dentro de su caja visual</t>
+          <t>Base con una columna pagina + pie con [[pagina]]</t>
         </is>
       </c>
       <c r="F285" s="8" t="inlineStr"/>
@@ -9972,7 +9972,7 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-07</t>
+          <t>CP-PDFP-07</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr">
@@ -9982,17 +9982,17 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>Estudio: estilos vinculados</t>
+          <t>Orientación horizontal</t>
         </is>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Vincular un estilo de texto/párrafo y editarlo</t>
+          <t>Configurar página → Horizontal → Vista previa</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr"/>
@@ -10005,7 +10005,7 @@
     <row r="287">
       <c r="A287" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-08</t>
+          <t>CP-PDFP-08</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
@@ -10015,17 +10015,17 @@
       </c>
       <c r="C287" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>Diseñador PDF (full)</t>
+          <t>Márgenes por lado</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>Abrir el Diseñador y crear un documento</t>
+          <t>Poner arriba 3 e izquierda 1,5 → Vista previa</t>
         </is>
       </c>
       <c r="F287" s="8" t="inlineStr"/>
@@ -10038,7 +10038,7 @@
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-09</t>
+          <t>CP-PDFP-09</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr">
@@ -10048,17 +10048,17 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF de punta a punta</t>
+          <t>Margen absurdo se acota</t>
         </is>
       </c>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
+          <t>Escribir 99 en un margen</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr"/>
@@ -10071,7 +10071,7 @@
     <row r="289">
       <c r="A289" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-10</t>
+          <t>CP-PDFP-10</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
@@ -10086,12 +10086,12 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>Tabla que desborda pagina</t>
+          <t>Salto de página manual</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
+          <t>Botón "Salto de página" a mitad del texto → Vista previa</t>
         </is>
       </c>
       <c r="F289" s="8" t="inlineStr"/>
@@ -10104,7 +10104,7 @@
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-11</t>
+          <t>CP-PDFP-11</t>
         </is>
       </c>
       <c r="B290" s="3" t="inlineStr">
@@ -10119,12 +10119,12 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>Celdas con JSON (multiregistro)</t>
+          <t>El salto se ve en el lienzo</t>
         </is>
       </c>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Base con una columna que trae un array JSON</t>
+          <t>Insertarlo</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr"/>
@@ -10137,7 +10137,7 @@
     <row r="291">
       <c r="A291" s="7" t="inlineStr">
         <is>
-          <t>CP-PDF-12</t>
+          <t>CP-PDFP-12</t>
         </is>
       </c>
       <c r="B291" s="8" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>Encabezados con BOM/espacios</t>
+          <t>Guías de corte</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
+          <t>Escribir contenido que pase de una hoja</t>
         </is>
       </c>
       <c r="F291" s="8" t="inlineStr"/>
@@ -10170,7 +10170,7 @@
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>CP-PDF-13</t>
+          <t>CP-PDFP-13</t>
         </is>
       </c>
       <c r="B292" s="3" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>Bordes y degradados</t>
+          <t>Guías en apaisado</t>
         </is>
       </c>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Formas con borde discontinuo y relleno degradado</t>
+          <t>Con hoja horizontal, mirar las guías</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr"/>
@@ -10203,12 +10203,12 @@
     <row r="293">
       <c r="A293" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-PDFP-14</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C293" s="7" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Plantilla vieja sin configuración</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>Cargar una guardada antes de esta función</t>
         </is>
       </c>
       <c r="F293" s="8" t="inlineStr"/>
@@ -10236,27 +10236,27 @@
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-PDFP-15</t>
         </is>
       </c>
       <c r="B294" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>La configuración sobrevive al guardado</t>
         </is>
       </c>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Configurar, guardar, "Nueva" y volver a cargar</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr"/>
@@ -10269,27 +10269,27 @@
     <row r="295">
       <c r="A295" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-PDFP-16</t>
         </is>
       </c>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>Restablecer</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Botón "Restablecer" del diálogo</t>
         </is>
       </c>
       <c r="F295" s="8" t="inlineStr"/>
@@ -10302,12 +10302,12 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-PDF-01</t>
         </is>
       </c>
       <c r="B296" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Editor básico tipo Word</t>
         </is>
       </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Crear plantilla con títulos, imagen, tabla y variables</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr"/>
@@ -10335,12 +10335,12 @@
     <row r="297">
       <c r="A297" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-PDF-02</t>
         </is>
       </c>
       <c r="B297" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>Vista previa PDF (básico)</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Botón "Vista previa PDF"</t>
         </is>
       </c>
       <c r="F297" s="8" t="inlineStr"/>
@@ -10368,27 +10368,27 @@
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-PDF-03</t>
         </is>
       </c>
       <c r="B298" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Estudio PDF (lienzo)</t>
         </is>
       </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Crear un diseño con texto, formas, tabla y guardar</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr"/>
@@ -10401,27 +10401,27 @@
     <row r="299">
       <c r="A299" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-PDF-04</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C299" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Estudio: variables con datos reales</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>Elegir una base en el panel de datos → Vista previa</t>
         </is>
       </c>
       <c r="F299" s="8" t="inlineStr"/>
@@ -10434,27 +10434,27 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-PDF-05</t>
         </is>
       </c>
       <c r="B300" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Estudio: unidades y reglas</t>
         </is>
       </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>Cambiar la unidad (mm/cm/pt/px/in) y usar 1:1 / ajustar a ventana</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr"/>
@@ -10467,27 +10467,27 @@
     <row r="301">
       <c r="A301" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-PDF-06</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>Estudio: seleccionar elemento rotado</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Girar un texto y hacer clic dentro de su caja visual</t>
         </is>
       </c>
       <c r="F301" s="8" t="inlineStr"/>
@@ -10500,12 +10500,12 @@
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-PDF-07</t>
         </is>
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Estudio: estilos vinculados</t>
         </is>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Vincular un estilo de texto/párrafo y editarlo</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr"/>
@@ -10533,12 +10533,12 @@
     <row r="303">
       <c r="A303" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-PDF-08</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Diseñador PDF (full)</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Abrir el Diseñador y crear un documento</t>
         </is>
       </c>
       <c r="F303" s="8" t="inlineStr"/>
@@ -10566,27 +10566,27 @@
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-PDF-09</t>
         </is>
       </c>
       <c r="B304" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Campaña EAP-PDF de punta a punta</t>
         </is>
       </c>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Crear campaña EAP tipo PDF con una plantilla del Estudio, muestras y envío real</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr"/>
@@ -10599,27 +10599,27 @@
     <row r="305">
       <c r="A305" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-PDF-10</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C305" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Tabla que desborda pagina</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Plantilla con tabla repeatBy y un registro con 30+ filas</t>
         </is>
       </c>
       <c r="F305" s="8" t="inlineStr"/>
@@ -10632,12 +10632,12 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-PDF-11</t>
         </is>
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -10647,12 +10647,12 @@
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Celdas con JSON (multiregistro)</t>
         </is>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Base con una columna que trae un array JSON</t>
         </is>
       </c>
       <c r="F306" s="3" t="inlineStr"/>
@@ -10665,27 +10665,27 @@
     <row r="307">
       <c r="A307" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-PDF-12</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Encabezados con BOM/espacios</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Base exportada de Excel (BOM en la 1ª columna)</t>
         </is>
       </c>
       <c r="F307" s="8" t="inlineStr"/>
@@ -10698,27 +10698,27 @@
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-PDF-13</t>
         </is>
       </c>
       <c r="B308" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Bordes y degradados</t>
         </is>
       </c>
       <c r="E308" s="3" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Formas con borde discontinuo y relleno degradado</t>
         </is>
       </c>
       <c r="F308" s="3" t="inlineStr"/>
@@ -10731,27 +10731,27 @@
     <row r="309">
       <c r="A309" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F309" s="8" t="inlineStr"/>
@@ -10764,27 +10764,27 @@
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B310" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E310" s="3" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F310" s="3" t="inlineStr"/>
@@ -10797,12 +10797,12 @@
     <row r="311">
       <c r="A311" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C311" s="7" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E311" s="8" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F311" s="8" t="inlineStr"/>
@@ -10830,27 +10830,27 @@
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E312" s="3" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F312" s="3" t="inlineStr"/>
@@ -10863,27 +10863,27 @@
     <row r="313">
       <c r="A313" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B313" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E313" s="8" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F313" s="8" t="inlineStr"/>
@@ -10896,27 +10896,27 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B314" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E314" s="3" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F314" s="3" t="inlineStr"/>
@@ -10929,27 +10929,27 @@
     <row r="315">
       <c r="A315" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C315" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E315" s="8" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F315" s="8" t="inlineStr"/>
@@ -10962,12 +10962,12 @@
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B316" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E316" s="3" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F316" s="3" t="inlineStr"/>
@@ -10995,12 +10995,12 @@
     <row r="317">
       <c r="A317" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C317" s="7" t="inlineStr">
@@ -11010,12 +11010,12 @@
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E317" s="8" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F317" s="8" t="inlineStr"/>
@@ -11028,12 +11028,12 @@
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B318" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -11043,12 +11043,12 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E318" s="3" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F318" s="3" t="inlineStr"/>
@@ -11061,27 +11061,27 @@
     <row r="319">
       <c r="A319" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E319" s="8" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F319" s="8" t="inlineStr"/>
@@ -11094,27 +11094,27 @@
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B320" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F320" s="3" t="inlineStr"/>
@@ -11127,12 +11127,12 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr"/>
@@ -11160,12 +11160,12 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr"/>
@@ -11193,12 +11193,12 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-01</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>DKIM verificado en verde</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio con DKIM firmando</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr"/>
@@ -11226,27 +11226,27 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-02</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>SPF/DMARC sin publicar en gris</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio recién creado</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr"/>
@@ -11259,12 +11259,12 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-03</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>SPF verde al publicarlo</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr"/>
@@ -11292,12 +11292,12 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-04</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>DMARC verde al publicarlo</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr"/>
@@ -11325,27 +11325,27 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-05</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Tooltip explica el motivo</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Pasar el mouse sobre un chip gris</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,27 +11358,27 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-06</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Sin el layer de DNS</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,27 +11391,27 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-07</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>Correos sueltos sin el panel</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,27 +11424,27 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-08</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>No es bloqueante</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,12 +11457,12 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,12 +11490,12 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,12 +11523,12 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,27 +11556,27 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,12 +11589,12 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,27 +11622,27 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,12 +11655,12 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
@@ -11670,12 +11670,12 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,27 +11688,27 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,12 +11721,12 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-AUT-01</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>DKIM verificado en verde</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Abrir el detalle de un dominio con DKIM firmando</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,27 +11754,27 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-AUT-02</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>SPF/DMARC sin publicar en gris</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Abrir el detalle de un dominio recién creado</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11787,12 +11787,12 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-AUT-03</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>SPF verde al publicarlo</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,27 +11820,27 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-35</t>
+          <t>CP-AUT-04</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>El bloqueo escalado explica por qué fue inmediato</t>
+          <t>DMARC verde al publicarlo</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
+          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,27 +11853,27 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-36</t>
+          <t>CP-AUT-05</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>El primer bloqueo no repite la explicación</t>
+          <t>Tooltip explica el motivo</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>En una cuenta nueva, fallar 3 veces</t>
+          <t>Pasar el mouse sobre un chip gris</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,27 +11886,27 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-AUT-06</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Sin el layer de DNS</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,27 +11919,27 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-AUT-07</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Correos sueltos sin el panel</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,27 +11952,27 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-AUT-08</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>No es bloqueante</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,7 +12018,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
@@ -12028,17 +12028,17 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,7 +12051,7 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
@@ -12061,17 +12061,17 @@
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,7 +12084,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
@@ -12094,17 +12094,17 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,12 +12117,12 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C351" s="7" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12150,27 +12150,27 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -12183,27 +12183,27 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr"/>
@@ -12216,27 +12216,27 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -12249,12 +12249,12 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C355" s="7" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr"/>
@@ -12282,27 +12282,27 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -12315,12 +12315,12 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C357" s="7" t="inlineStr">
@@ -12330,12 +12330,12 @@
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr"/>
@@ -12348,27 +12348,27 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-SEC-35</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>El bloqueo escalado explica por qué fue inmediato</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -12381,27 +12381,27 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-SEC-36</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>El primer bloqueo no repite la explicación</t>
         </is>
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>En una cuenta nueva, fallar 3 veces</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr"/>
@@ -12414,12 +12414,12 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -12447,27 +12447,27 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr"/>
@@ -12480,27 +12480,27 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
@@ -12513,12 +12513,12 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B363" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C363" s="7" t="inlineStr">
@@ -12528,12 +12528,12 @@
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr"/>
@@ -12546,12 +12546,12 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr"/>
@@ -12579,12 +12579,12 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B365" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C365" s="7" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr"/>
@@ -12612,27 +12612,27 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B367" s="8" t="inlineStr">
@@ -12655,17 +12655,17 @@
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr"/>
@@ -12678,7 +12678,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr"/>
@@ -12711,7 +12711,7 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B369" s="8" t="inlineStr">
@@ -12726,12 +12726,12 @@
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr"/>
@@ -12744,7 +12744,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr"/>
@@ -12777,7 +12777,7 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B371" s="8" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr"/>
@@ -12810,7 +12810,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr"/>
@@ -12843,7 +12843,7 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
@@ -12853,17 +12853,17 @@
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr"/>
@@ -12876,7 +12876,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -12886,17 +12886,17 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B375" s="8" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr"/>
@@ -12942,7 +12942,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -12952,17 +12952,17 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B377" s="8" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr"/>
@@ -13008,27 +13008,27 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr"/>
@@ -13041,12 +13041,12 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B379" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C379" s="7" t="inlineStr">
@@ -13056,12 +13056,12 @@
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr"/>
@@ -13074,27 +13074,27 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr"/>
@@ -13107,12 +13107,12 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B381" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C381" s="7" t="inlineStr">
@@ -13122,12 +13122,12 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr"/>
@@ -13140,27 +13140,27 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr"/>
@@ -13173,27 +13173,27 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B383" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr"/>
@@ -13206,27 +13206,27 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr"/>
@@ -13239,27 +13239,27 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B385" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr"/>
@@ -13272,27 +13272,27 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr"/>
@@ -13305,27 +13305,27 @@
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B387" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C387" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr"/>
@@ -13338,12 +13338,12 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr"/>
@@ -13371,12 +13371,12 @@
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B389" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C389" s="7" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr"/>
@@ -13404,27 +13404,27 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr"/>
@@ -13437,27 +13437,27 @@
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B391" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr"/>
@@ -13470,27 +13470,27 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr"/>
@@ -13503,12 +13503,12 @@
     <row r="393">
       <c r="A393" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B393" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C393" s="7" t="inlineStr">
@@ -13518,12 +13518,12 @@
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr"/>
@@ -13536,27 +13536,27 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr"/>
@@ -13569,27 +13569,27 @@
     <row r="395">
       <c r="A395" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B395" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C395" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr"/>
@@ -13602,27 +13602,27 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr"/>
@@ -13635,12 +13635,12 @@
     <row r="397">
       <c r="A397" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B397" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C397" s="7" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr"/>
@@ -13668,27 +13668,27 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr"/>
@@ -13701,12 +13701,12 @@
     <row r="399">
       <c r="A399" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B399" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C399" s="7" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr"/>
@@ -13734,12 +13734,12 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
@@ -13749,12 +13749,12 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr"/>
@@ -13767,27 +13767,27 @@
     <row r="401">
       <c r="A401" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B401" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr"/>
@@ -13800,27 +13800,27 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr"/>
@@ -13833,27 +13833,27 @@
     <row r="403">
       <c r="A403" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-01</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B403" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C403" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>Aviso de campaña por aprobar</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr"/>
@@ -13866,27 +13866,27 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-02</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Solo a quien puede aprobar</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de otro operator del mismo equipo</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr"/>
@@ -13899,12 +13899,12 @@
     <row r="405">
       <c r="A405" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-03</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B405" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C405" s="7" t="inlineStr">
@@ -13914,12 +13914,12 @@
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>Quien la pide no se avisa a sí mismo</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita del operator que la solicitó</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr"/>
@@ -13932,27 +13932,27 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-04</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento entre empresas</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de un usuario de OTRA empresa</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr"/>
@@ -13965,27 +13965,27 @@
     <row r="407">
       <c r="A407" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-05</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B407" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>Aviso de aprobada</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>El owner aprueba la campaña</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr"/>
@@ -13998,7 +13998,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-06</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>Aviso de rechazada con el motivo</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr"/>
@@ -14031,7 +14031,7 @@
     <row r="409">
       <c r="A409" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-07</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B409" s="8" t="inlineStr">
@@ -14041,17 +14041,17 @@
       </c>
       <c r="C409" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>Saldo bajo in-app</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Hacer un envío que deje el saldo bajo el umbral</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr"/>
@@ -14064,7 +14064,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-08</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>Avisos nuevos abajo a la derecha</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr"/>
@@ -14097,7 +14097,7 @@
     <row r="411">
       <c r="A411" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-09</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B411" s="8" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>Los nuevos NO saltan al entrar</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>Con avisos viejos sin leer, entrar al portal</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr"/>
@@ -14130,7 +14130,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-10</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
@@ -14145,12 +14145,12 @@
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>La tarjeta se retira sola</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>Esperar unos segundos tras el aviso</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
     <row r="413">
       <c r="A413" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-11</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B413" s="8" t="inlineStr">
@@ -14173,17 +14173,17 @@
       </c>
       <c r="C413" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>Clic lleva al lugar correcto</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Hacer clic en "Campaña por aprobar"</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr"/>
@@ -14196,7 +14196,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-12</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
@@ -14206,17 +14206,17 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>Marcar leídas</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>Abrir el panel y pulsar "Marcar leídas"</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr"/>
@@ -14229,7 +14229,7 @@
     <row r="415">
       <c r="A415" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-13</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B415" s="8" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>No se puede marcar la de otro</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr"/>
@@ -14262,7 +14262,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-14</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
@@ -14277,12 +14277,12 @@
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>Sin notificaciones</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>Usuario nuevo abre la campanita</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr"/>
@@ -14295,7 +14295,7 @@
     <row r="417">
       <c r="A417" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-15</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B417" s="8" t="inlineStr">
@@ -14305,17 +14305,17 @@
       </c>
       <c r="C417" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>No molesta en impersonación</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>Entrar como admin con "Ver como cliente"</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F417" s="8" t="inlineStr"/>
@@ -14328,7 +14328,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-16</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -14338,17 +14338,17 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>La aprobación funciona sin la tabla</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr"/>
@@ -14361,12 +14361,12 @@
     <row r="419">
       <c r="A419" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-CAM-01</t>
         </is>
       </c>
       <c r="B419" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C419" s="7" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Aviso de campaña por aprobar</t>
         </is>
       </c>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
         </is>
       </c>
       <c r="F419" s="8" t="inlineStr"/>
@@ -14394,27 +14394,27 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-CAM-02</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Solo a quien puede aprobar</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Revisar la campanita de otro operator del mismo equipo</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr"/>
@@ -14427,27 +14427,27 @@
     <row r="421">
       <c r="A421" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-CAM-03</t>
         </is>
       </c>
       <c r="B421" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Quien la pide no se avisa a sí mismo</t>
         </is>
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Revisar la campanita del operator que la solicitó</t>
         </is>
       </c>
       <c r="F421" s="8" t="inlineStr"/>
@@ -14460,27 +14460,27 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-CAM-04</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Aislamiento entre empresas</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Revisar la campanita de un usuario de OTRA empresa</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr"/>
@@ -14493,12 +14493,12 @@
     <row r="423">
       <c r="A423" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-CAM-05</t>
         </is>
       </c>
       <c r="B423" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C423" s="7" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Aviso de aprobada</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>El owner aprueba la campaña</t>
         </is>
       </c>
       <c r="F423" s="8" t="inlineStr"/>
@@ -14526,27 +14526,27 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-CAM-06</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Aviso de rechazada con el motivo</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr"/>
@@ -14559,27 +14559,27 @@
     <row r="425">
       <c r="A425" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-CAM-07</t>
         </is>
       </c>
       <c r="B425" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C425" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>Saldo bajo in-app</t>
         </is>
       </c>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Hacer un envío que deje el saldo bajo el umbral</t>
         </is>
       </c>
       <c r="F425" s="8" t="inlineStr"/>
@@ -14592,27 +14592,27 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-CAM-08</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>Avisos nuevos abajo a la derecha</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr"/>
@@ -14625,12 +14625,12 @@
     <row r="427">
       <c r="A427" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-CAM-09</t>
         </is>
       </c>
       <c r="B427" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C427" s="7" t="inlineStr">
@@ -14640,12 +14640,12 @@
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Los nuevos NO saltan al entrar</t>
         </is>
       </c>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Con avisos viejos sin leer, entrar al portal</t>
         </is>
       </c>
       <c r="F427" s="8" t="inlineStr"/>
@@ -14658,27 +14658,27 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-CAM-10</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>La tarjeta se retira sola</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Esperar unos segundos tras el aviso</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr"/>
@@ -14691,12 +14691,12 @@
     <row r="429">
       <c r="A429" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-CAM-11</t>
         </is>
       </c>
       <c r="B429" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C429" s="7" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Clic lleva al lugar correcto</t>
         </is>
       </c>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Hacer clic en "Campaña por aprobar"</t>
         </is>
       </c>
       <c r="F429" s="8" t="inlineStr"/>
@@ -14724,12 +14724,12 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-CAM-12</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
@@ -14739,12 +14739,12 @@
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Marcar leídas</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Abrir el panel y pulsar "Marcar leídas"</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr"/>
@@ -14757,12 +14757,12 @@
     <row r="431">
       <c r="A431" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-CAM-13</t>
         </is>
       </c>
       <c r="B431" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C431" s="7" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>No se puede marcar la de otro</t>
         </is>
       </c>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
         </is>
       </c>
       <c r="F431" s="8" t="inlineStr"/>
@@ -14790,12 +14790,12 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-CAM-14</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
@@ -14805,12 +14805,12 @@
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Sin notificaciones</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Usuario nuevo abre la campanita</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr"/>
@@ -14823,27 +14823,27 @@
     <row r="433">
       <c r="A433" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-CAM-15</t>
         </is>
       </c>
       <c r="B433" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C433" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>No molesta en impersonación</t>
         </is>
       </c>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Entrar como admin con "Ver como cliente"</t>
         </is>
       </c>
       <c r="F433" s="8" t="inlineStr"/>
@@ -14856,27 +14856,27 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-01</t>
+          <t>CP-CAM-16</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>Segmentos calculados, no declarados</t>
+          <t>La aprobación funciona sin la tabla</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>Muestras con una campaña SMS</t>
+          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr"/>
@@ -14889,7 +14889,7 @@
     <row r="435">
       <c r="A435" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-02</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B435" s="8" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>Un SMS largo cuesta el doble</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>Campaña con más de 160 caracteres</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr"/>
@@ -14922,7 +14922,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-03</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -14932,17 +14932,17 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>Una emoji parte el mensaje</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr"/>
@@ -14955,7 +14955,7 @@
     <row r="437">
       <c r="A437" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-04</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B437" s="8" t="inlineStr">
@@ -14965,17 +14965,17 @@
       </c>
       <c r="C437" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>Lo estimado es lo que se cobra</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr"/>
@@ -14988,7 +14988,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-05</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -14998,17 +14998,17 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>Tarifas nuevas visibles</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → canal SMS y Voz</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr"/>
@@ -15021,7 +15021,7 @@
     <row r="439">
       <c r="A439" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-06</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B439" s="8" t="inlineStr">
@@ -15031,17 +15031,17 @@
       </c>
       <c r="C439" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>Ningún cliente por debajo del costo</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → revisar overrides por cliente</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr"/>
@@ -15054,7 +15054,7 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-07</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -15069,12 +15069,12 @@
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>Contador del editor SMS</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>Escribir un SMS con emoji en Plantillas SMS</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr"/>
@@ -15087,7 +15087,7 @@
     <row r="441">
       <c r="A441" s="7" t="inlineStr">
         <is>
-          <t>CP-PUB-01</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B441" s="8" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>La landing no publica precios</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>Abrir la landing → sección Precios</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr"/>
@@ -15120,7 +15120,7 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-01</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -15130,17 +15130,17 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>Título e idioma</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>Ver el código fuente de la landing</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
     <row r="443">
       <c r="A443" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-02</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B443" s="8" t="inlineStr">
@@ -15163,17 +15163,17 @@
       </c>
       <c r="C443" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>Vista previa al compartir</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr"/>
@@ -15186,7 +15186,7 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-03</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
@@ -15196,17 +15196,17 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>Abrir la landing y mirar la pestaña</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr"/>
@@ -15219,7 +15219,7 @@
     <row r="445">
       <c r="A445" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-04</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B445" s="8" t="inlineStr">
@@ -15229,17 +15229,17 @@
       </c>
       <c r="C445" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>Icono en iOS</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>"Añadir a pantalla de inicio" desde Safari</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr"/>
@@ -15252,7 +15252,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-05</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
@@ -15267,12 +15267,12 @@
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>Datos estructurados</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr"/>
@@ -15285,7 +15285,7 @@
     <row r="447">
       <c r="A447" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-06</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B447" s="8" t="inlineStr">
@@ -15295,17 +15295,17 @@
       </c>
       <c r="C447" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Canonical y robots</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>Abrir /robots.txt y /sitemap.xml</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr"/>
@@ -15318,7 +15318,7 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-01</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
@@ -15328,17 +15328,17 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>Tabla de precios por canal</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>Landing → Precios</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr"/>
@@ -15351,7 +15351,7 @@
     <row r="449">
       <c r="A449" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-02</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B449" s="8" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>Letra pequeña de precios</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>Leer bajo la tabla</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr"/>
@@ -15384,7 +15384,7 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-03</t>
+          <t>CP-TAR-01</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
@@ -15394,17 +15394,17 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>Icono de WhatsApp</t>
+          <t>Segmentos calculados, no declarados</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>Sección Canales</t>
+          <t>Muestras con una campaña SMS</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
     <row r="451">
       <c r="A451" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-04</t>
+          <t>CP-TAR-02</t>
         </is>
       </c>
       <c r="B451" s="8" t="inlineStr">
@@ -15427,17 +15427,17 @@
       </c>
       <c r="C451" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>Sin promesa de 500 correos</t>
+          <t>Un SMS largo cuesta el doble</t>
         </is>
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>Recorrer toda la landing</t>
+          <t>Campaña con más de 160 caracteres</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr"/>
@@ -15450,7 +15450,7 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-05</t>
+          <t>CP-TAR-03</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -15460,17 +15460,17 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>Footer sin enlaces rotos</t>
+          <t>Una emoji parte el mensaje</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>Hacer clic en cada enlace del footer</t>
+          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr"/>
@@ -15483,7 +15483,7 @@
     <row r="453">
       <c r="A453" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-01</t>
+          <t>CP-TAR-04</t>
         </is>
       </c>
       <c r="B453" s="8" t="inlineStr">
@@ -15498,12 +15498,12 @@
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>Cerrar el modal con teclado</t>
+          <t>Lo estimado es lo que se cobra</t>
         </is>
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Escape</t>
+          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr"/>
@@ -15516,7 +15516,7 @@
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>CP-A11Y-02</t>
+          <t>CP-TAR-05</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
@@ -15526,17 +15526,17 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>Foco en el modal</t>
+          <t>Tarifas nuevas visibles</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Tab</t>
+          <t>Admin → Tarifas → canal SMS y Voz</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr"/>
@@ -15549,7 +15549,7 @@
     <row r="455">
       <c r="A455" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-03</t>
+          <t>CP-TAR-06</t>
         </is>
       </c>
       <c r="B455" s="8" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>Lector de pantalla</t>
+          <t>Ningún cliente por debajo del costo</t>
         </is>
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>Abrir el modal con un lector activo</t>
+          <t>Admin → Tarifas → revisar overrides por cliente</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr"/>
@@ -15582,27 +15582,27 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-TAR-07</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>Contador del editor SMS</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Escribir un SMS con emoji en Plantillas SMS</t>
         </is>
       </c>
       <c r="F456" s="3" t="inlineStr"/>
@@ -15615,27 +15615,27 @@
     <row r="457">
       <c r="A457" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-PUB-01</t>
         </is>
       </c>
       <c r="B457" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C457" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>La landing no publica precios</t>
         </is>
       </c>
       <c r="E457" s="8" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Abrir la landing → sección Precios</t>
         </is>
       </c>
       <c r="F457" s="8" t="inlineStr"/>
@@ -15648,27 +15648,27 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-SEO-01</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Título e idioma</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Ver el código fuente de la landing</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr"/>
@@ -15681,12 +15681,12 @@
     <row r="459">
       <c r="A459" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-SEO-02</t>
         </is>
       </c>
       <c r="B459" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C459" s="7" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Vista previa al compartir</t>
         </is>
       </c>
       <c r="E459" s="8" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
         </is>
       </c>
       <c r="F459" s="8" t="inlineStr"/>
@@ -15714,12 +15714,12 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-SEO-03</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
@@ -15729,12 +15729,12 @@
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Favicon</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Abrir la landing y mirar la pestaña</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr"/>
@@ -15747,12 +15747,12 @@
     <row r="461">
       <c r="A461" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-SEO-04</t>
         </is>
       </c>
       <c r="B461" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C461" s="7" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Icono en iOS</t>
         </is>
       </c>
       <c r="E461" s="8" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>"Añadir a pantalla de inicio" desde Safari</t>
         </is>
       </c>
       <c r="F461" s="8" t="inlineStr"/>
@@ -15780,27 +15780,27 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-SEO-05</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Datos estructurados</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr"/>
@@ -15813,12 +15813,12 @@
     <row r="463">
       <c r="A463" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-SEO-06</t>
         </is>
       </c>
       <c r="B463" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C463" s="7" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="D463" s="8" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>Canonical y robots</t>
         </is>
       </c>
       <c r="E463" s="8" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Abrir /robots.txt y /sitemap.xml</t>
         </is>
       </c>
       <c r="F463" s="8" t="inlineStr"/>
@@ -15846,27 +15846,27 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-LAN-01</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>Tabla de precios por canal</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Landing → Precios</t>
         </is>
       </c>
       <c r="F464" s="3" t="inlineStr"/>
@@ -15879,12 +15879,12 @@
     <row r="465">
       <c r="A465" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-LAN-02</t>
         </is>
       </c>
       <c r="B465" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C465" s="7" t="inlineStr">
@@ -15894,12 +15894,12 @@
       </c>
       <c r="D465" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Letra pequeña de precios</t>
         </is>
       </c>
       <c r="E465" s="8" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Leer bajo la tabla</t>
         </is>
       </c>
       <c r="F465" s="8" t="inlineStr"/>
@@ -15912,27 +15912,27 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-LAN-03</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Icono de WhatsApp</t>
         </is>
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Sección Canales</t>
         </is>
       </c>
       <c r="F466" s="3" t="inlineStr"/>
@@ -15945,27 +15945,27 @@
     <row r="467">
       <c r="A467" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-LAN-04</t>
         </is>
       </c>
       <c r="B467" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C467" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D467" s="8" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Sin promesa de 500 correos</t>
         </is>
       </c>
       <c r="E467" s="8" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Recorrer toda la landing</t>
         </is>
       </c>
       <c r="F467" s="8" t="inlineStr"/>
@@ -15978,27 +15978,27 @@
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-LAN-05</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Footer sin enlaces rotos</t>
         </is>
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Hacer clic en cada enlace del footer</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr"/>
@@ -16011,27 +16011,27 @@
     <row r="469">
       <c r="A469" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-A11Y-01</t>
         </is>
       </c>
       <c r="B469" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C469" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D469" s="8" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Cerrar el modal con teclado</t>
         </is>
       </c>
       <c r="E469" s="8" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Abrir /?activacion=ok y pulsar Escape</t>
         </is>
       </c>
       <c r="F469" s="8" t="inlineStr"/>
@@ -16044,12 +16044,12 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-A11Y-02</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
@@ -16059,12 +16059,12 @@
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Foco en el modal</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Abrir /?activacion=ok y pulsar Tab</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr"/>
@@ -16077,12 +16077,12 @@
     <row r="471">
       <c r="A471" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-A11Y-03</t>
         </is>
       </c>
       <c r="B471" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C471" s="7" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="D471" s="8" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Lector de pantalla</t>
         </is>
       </c>
       <c r="E471" s="8" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Abrir el modal con un lector activo</t>
         </is>
       </c>
       <c r="F471" s="8" t="inlineStr"/>
@@ -16110,12 +16110,12 @@
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
@@ -16125,12 +16125,12 @@
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F472" s="3" t="inlineStr"/>
@@ -16143,27 +16143,27 @@
     <row r="473">
       <c r="A473" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B473" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C473" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D473" s="8" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E473" s="8" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F473" s="8" t="inlineStr"/>
@@ -16176,27 +16176,27 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F474" s="3" t="inlineStr"/>
@@ -16209,27 +16209,27 @@
     <row r="475">
       <c r="A475" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B475" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C475" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D475" s="8" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E475" s="8" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F475" s="8" t="inlineStr"/>
@@ -16239,13 +16239,541 @@
       <c r="J475" s="6" t="inlineStr"/>
       <c r="K475" s="5" t="inlineStr"/>
     </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>CP-CAS-05</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D476" s="3" t="inlineStr">
+        <is>
+          <t>Consentimiento por canal</t>
+        </is>
+      </c>
+      <c r="E476" s="3" t="inlineStr">
+        <is>
+          <t>Contacto sin consentimiento del canal 0</t>
+        </is>
+      </c>
+      <c r="F476" s="3" t="inlineStr"/>
+      <c r="G476" s="4" t="inlineStr"/>
+      <c r="H476" s="5" t="inlineStr"/>
+      <c r="I476" s="4" t="inlineStr"/>
+      <c r="J476" s="6" t="inlineStr"/>
+      <c r="K476" s="5" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="7" t="inlineStr">
+        <is>
+          <t>CP-CAS-06</t>
+        </is>
+      </c>
+      <c r="B477" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C477" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D477" s="8" t="inlineStr">
+        <is>
+          <t>Listado de cascadas</t>
+        </is>
+      </c>
+      <c r="E477" s="8" t="inlineStr">
+        <is>
+          <t>Abrir el listado</t>
+        </is>
+      </c>
+      <c r="F477" s="8" t="inlineStr"/>
+      <c r="G477" s="4" t="inlineStr"/>
+      <c r="H477" s="5" t="inlineStr"/>
+      <c r="I477" s="4" t="inlineStr"/>
+      <c r="J477" s="6" t="inlineStr"/>
+      <c r="K477" s="5" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-01</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D478" s="3" t="inlineStr">
+        <is>
+          <t>Serie de 30 días (cliente)</t>
+        </is>
+      </c>
+      <c r="E478" s="3" t="inlineStr">
+        <is>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+        </is>
+      </c>
+      <c r="F478" s="3" t="inlineStr"/>
+      <c r="G478" s="4" t="inlineStr"/>
+      <c r="H478" s="5" t="inlineStr"/>
+      <c r="I478" s="4" t="inlineStr"/>
+      <c r="J478" s="6" t="inlineStr"/>
+      <c r="K478" s="5" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-02</t>
+        </is>
+      </c>
+      <c r="B479" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C479" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D479" s="8" t="inlineStr">
+        <is>
+          <t>Serie global (admin)</t>
+        </is>
+      </c>
+      <c r="E479" s="8" t="inlineStr">
+        <is>
+          <t>Panel de control → gráfico</t>
+        </is>
+      </c>
+      <c r="F479" s="8" t="inlineStr"/>
+      <c r="G479" s="4" t="inlineStr"/>
+      <c r="H479" s="5" t="inlineStr"/>
+      <c r="I479" s="4" t="inlineStr"/>
+      <c r="J479" s="6" t="inlineStr"/>
+      <c r="K479" s="5" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-03</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D480" s="3" t="inlineStr">
+        <is>
+          <t>Muestras excluidas</t>
+        </is>
+      </c>
+      <c r="E480" s="3" t="inlineStr">
+        <is>
+          <t>Enviar muestras y revisar la serie</t>
+        </is>
+      </c>
+      <c r="F480" s="3" t="inlineStr"/>
+      <c r="G480" s="4" t="inlineStr"/>
+      <c r="H480" s="5" t="inlineStr"/>
+      <c r="I480" s="4" t="inlineStr"/>
+      <c r="J480" s="6" t="inlineStr"/>
+      <c r="K480" s="5" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-04</t>
+        </is>
+      </c>
+      <c r="B481" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C481" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D481" s="8" t="inlineStr">
+        <is>
+          <t>Aislamiento</t>
+        </is>
+      </c>
+      <c r="E481" s="8" t="inlineStr">
+        <is>
+          <t>Comparar la serie de dos clientes</t>
+        </is>
+      </c>
+      <c r="F481" s="8" t="inlineStr"/>
+      <c r="G481" s="4" t="inlineStr"/>
+      <c r="H481" s="5" t="inlineStr"/>
+      <c r="I481" s="4" t="inlineStr"/>
+      <c r="J481" s="6" t="inlineStr"/>
+      <c r="K481" s="5" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-05</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C482" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D482" s="3" t="inlineStr">
+        <is>
+          <t>Adiós "(parcial)"</t>
+        </is>
+      </c>
+      <c r="E482" s="3" t="inlineStr">
+        <is>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+        </is>
+      </c>
+      <c r="F482" s="3" t="inlineStr"/>
+      <c r="G482" s="4" t="inlineStr"/>
+      <c r="H482" s="5" t="inlineStr"/>
+      <c r="I482" s="4" t="inlineStr"/>
+      <c r="J482" s="6" t="inlineStr"/>
+      <c r="K482" s="5" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-06</t>
+        </is>
+      </c>
+      <c r="B483" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C483" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D483" s="8" t="inlineStr">
+        <is>
+          <t>Leyenda interactiva</t>
+        </is>
+      </c>
+      <c r="E483" s="8" t="inlineStr">
+        <is>
+          <t>Ocultar/mostrar series en el gráfico</t>
+        </is>
+      </c>
+      <c r="F483" s="8" t="inlineStr"/>
+      <c r="G483" s="4" t="inlineStr"/>
+      <c r="H483" s="5" t="inlineStr"/>
+      <c r="I483" s="4" t="inlineStr"/>
+      <c r="J483" s="6" t="inlineStr"/>
+      <c r="K483" s="5" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C484" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D484" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E484" s="3" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F484" s="3" t="inlineStr"/>
+      <c r="G484" s="4" t="inlineStr"/>
+      <c r="H484" s="5" t="inlineStr"/>
+      <c r="I484" s="4" t="inlineStr"/>
+      <c r="J484" s="6" t="inlineStr"/>
+      <c r="K484" s="5" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B485" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C485" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D485" s="8" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E485" s="8" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F485" s="8" t="inlineStr"/>
+      <c r="G485" s="4" t="inlineStr"/>
+      <c r="H485" s="5" t="inlineStr"/>
+      <c r="I485" s="4" t="inlineStr"/>
+      <c r="J485" s="6" t="inlineStr"/>
+      <c r="K485" s="5" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C486" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D486" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E486" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F486" s="3" t="inlineStr"/>
+      <c r="G486" s="4" t="inlineStr"/>
+      <c r="H486" s="5" t="inlineStr"/>
+      <c r="I486" s="4" t="inlineStr"/>
+      <c r="J486" s="6" t="inlineStr"/>
+      <c r="K486" s="5" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B487" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C487" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D487" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E487" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F487" s="8" t="inlineStr"/>
+      <c r="G487" s="4" t="inlineStr"/>
+      <c r="H487" s="5" t="inlineStr"/>
+      <c r="I487" s="4" t="inlineStr"/>
+      <c r="J487" s="6" t="inlineStr"/>
+      <c r="K487" s="5" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C488" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D488" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E488" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F488" s="3" t="inlineStr"/>
+      <c r="G488" s="4" t="inlineStr"/>
+      <c r="H488" s="5" t="inlineStr"/>
+      <c r="I488" s="4" t="inlineStr"/>
+      <c r="J488" s="6" t="inlineStr"/>
+      <c r="K488" s="5" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B489" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C489" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D489" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E489" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F489" s="8" t="inlineStr"/>
+      <c r="G489" s="4" t="inlineStr"/>
+      <c r="H489" s="5" t="inlineStr"/>
+      <c r="I489" s="4" t="inlineStr"/>
+      <c r="J489" s="6" t="inlineStr"/>
+      <c r="K489" s="5" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C490" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D490" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E490" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F490" s="3" t="inlineStr"/>
+      <c r="G490" s="4" t="inlineStr"/>
+      <c r="H490" s="5" t="inlineStr"/>
+      <c r="I490" s="4" t="inlineStr"/>
+      <c r="J490" s="6" t="inlineStr"/>
+      <c r="K490" s="5" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B491" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C491" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D491" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E491" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F491" s="8" t="inlineStr"/>
+      <c r="G491" s="4" t="inlineStr"/>
+      <c r="H491" s="5" t="inlineStr"/>
+      <c r="I491" s="4" t="inlineStr"/>
+      <c r="J491" s="6" t="inlineStr"/>
+      <c r="K491" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K475"/>
+  <autoFilter ref="A1:K491"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H475" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H491" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K475" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K491" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -16305,7 +16833,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A475)</f>
+        <f>COUNTA(Casos!A2:A491)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -16319,7 +16847,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$475,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$491,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -16336,7 +16864,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$475,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$491,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -16353,7 +16881,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$475,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$491,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -16370,7 +16898,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$475,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$491,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -16426,11 +16954,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$475,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$491,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$475,A12,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$491,A12,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -16443,11 +16971,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$475,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$491,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$475,A13,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$491,A13,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -16460,11 +16988,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$475,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$491,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$475,A14,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$491,A14,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -16522,19 +17050,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A18,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A18,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A18,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A18,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$475,$A18,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$491,$A18,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16545,19 +17073,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A19,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A19,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A19,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A19,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$475,$A19,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$491,$A19,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16568,19 +17096,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A20,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A20,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A20,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A20,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$475,$A20,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$491,$A20,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16591,19 +17119,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A21,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A21,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A21,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A21,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$475,$A21,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$491,$A21,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16614,19 +17142,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A22,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A22,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A22,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A22,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$475,$A22,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$491,$A22,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16637,19 +17165,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A23,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A23,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A23,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A23,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$475,$A23,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$491,$A23,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16660,19 +17188,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A24,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A24,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A24,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A24,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$475,$A24,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$491,$A24,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16683,19 +17211,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A25,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A25,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A25,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A25,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$475,$A25,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$491,$A25,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16706,19 +17234,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A26,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A26,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A26,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A26,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$475,$A26,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$491,$A26,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16729,19 +17257,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A27,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A27,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A27,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A27,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$475,$A27,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$491,$A27,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16752,19 +17280,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A28,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A28,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A28,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A28,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$475,$A28,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$491,$A28,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16775,19 +17303,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A29,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A29,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A29,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A29,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$475,$A29,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$491,$A29,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16798,19 +17326,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A30,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A30,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A30,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A30,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$475,$A30,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$491,$A30,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16821,19 +17349,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A31,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A31,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A31,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A31,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$475,$A31,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$491,$A31,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16844,19 +17372,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A32,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A32,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A32,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A32,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$475,$A32,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$491,$A32,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16867,19 +17395,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A33,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A33,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A33,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A33,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$475,$A33,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$491,$A33,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16890,19 +17418,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A34,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A34,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A34,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A34,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$475,$A34,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$491,$A34,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16913,19 +17441,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A35,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A35,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A35,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A35,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$475,$A35,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$491,$A35,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16936,19 +17464,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A36,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A36,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A36,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A36,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$475,$A36,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$491,$A36,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16959,19 +17487,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A37,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A37,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A37,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A37,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$475,$A37,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$491,$A37,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -16982,19 +17510,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A38,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A38,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A38,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A38,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$475,$A38,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$491,$A38,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17005,19 +17533,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$475,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$491,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A39,Casos!$H$2:$H$475,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A39,Casos!$H$2:$H$491,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$475,$A39,Casos!$H$2:$H$475,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$491,$A39,Casos!$H$2:$H$491,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$475,$A39,Casos!$H$2:$H$475,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$491,$A39,Casos!$H$2:$H$491,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$503</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$517</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K503"/>
+  <dimension ref="A1:K517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11127,12 +11127,12 @@
     <row r="321">
       <c r="A321" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-PDF-14</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
@@ -11142,12 +11142,12 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Agregar página</t>
         </is>
       </c>
       <c r="E321" s="8" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>En Plantillas PDF básicas, clic en "Agregar página"</t>
         </is>
       </c>
       <c r="F321" s="8" t="inlineStr"/>
@@ -11160,12 +11160,12 @@
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-PDF-15</t>
         </is>
       </c>
       <c r="B322" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>Cada hoja se edita por separado</t>
         </is>
       </c>
       <c r="E322" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Escribir en la página 1 y en la 2</t>
         </is>
       </c>
       <c r="F322" s="3" t="inlineStr"/>
@@ -11193,12 +11193,12 @@
     <row r="323">
       <c r="A323" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-PDF-16</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>Las páginas llegan al PDF</t>
         </is>
       </c>
       <c r="E323" s="8" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Con 2 hojas con contenido, "Vista previa PDF"</t>
         </is>
       </c>
       <c r="F323" s="8" t="inlineStr"/>
@@ -11226,27 +11226,27 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-PDF-17</t>
         </is>
       </c>
       <c r="B324" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Eliminar una página</t>
         </is>
       </c>
       <c r="E324" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Clic en la papelera de la página 2</t>
         </is>
       </c>
       <c r="F324" s="3" t="inlineStr"/>
@@ -11259,12 +11259,12 @@
     <row r="325">
       <c r="A325" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-PDF-18</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
@@ -11274,12 +11274,12 @@
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>Aviso de desborde</t>
         </is>
       </c>
       <c r="E325" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Escribir en una hoja hasta pasar el final</t>
         </is>
       </c>
       <c r="F325" s="8" t="inlineStr"/>
@@ -11292,12 +11292,12 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-PDF-19</t>
         </is>
       </c>
       <c r="B326" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Página vacía al final</t>
         </is>
       </c>
       <c r="E326" s="3" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Agregar una página y no escribir nada; ver el PDF</t>
         </is>
       </c>
       <c r="F326" s="3" t="inlineStr"/>
@@ -11325,12 +11325,12 @@
     <row r="327">
       <c r="A327" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-PDF-20</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Plantilla vieja con saltos</t>
         </is>
       </c>
       <c r="E327" s="8" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>Cargar una plantilla guardada antes del cambio</t>
         </is>
       </c>
       <c r="F327" s="8" t="inlineStr"/>
@@ -11358,12 +11358,12 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-PDF-21</t>
         </is>
       </c>
       <c r="B328" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -11373,12 +11373,12 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Insertar tabla configurable</t>
         </is>
       </c>
       <c r="E328" s="3" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>"Tabla" → 4 filas, 3 columnas, encabezado, cebra → Insertar</t>
         </is>
       </c>
       <c r="F328" s="3" t="inlineStr"/>
@@ -11391,12 +11391,12 @@
     <row r="329">
       <c r="A329" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-PDF-22</t>
         </is>
       </c>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
@@ -11406,12 +11406,12 @@
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>La tabla llega igual al PDF</t>
         </is>
       </c>
       <c r="E329" s="8" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Vista previa PDF de esa tabla</t>
         </is>
       </c>
       <c r="F329" s="8" t="inlineStr"/>
@@ -11424,27 +11424,27 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-PDF-23</t>
         </is>
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Editar una tabla existente</t>
         </is>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Cursor dentro de una tabla con texto y pulsar "Tabla"</t>
         </is>
       </c>
       <c r="F330" s="3" t="inlineStr"/>
@@ -11457,27 +11457,27 @@
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-PDF-24</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Editar sin perder lo escrito</t>
         </is>
       </c>
       <c r="E331" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Con texto en las celdas, cambiar de 2x2 a 4x3 y Aplicar</t>
         </is>
       </c>
       <c r="F331" s="8" t="inlineStr"/>
@@ -11490,12 +11490,12 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-PDF-25</t>
         </is>
       </c>
       <c r="B332" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Reducir una tabla</t>
         </is>
       </c>
       <c r="E332" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Cambiar de 5x4 a 2x2</t>
         </is>
       </c>
       <c r="F332" s="3" t="inlineStr"/>
@@ -11523,12 +11523,12 @@
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-PDF-26</t>
         </is>
       </c>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Borde y colores de la tabla</t>
         </is>
       </c>
       <c r="E333" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Estilo punteado, grosor 3, color rojo</t>
         </is>
       </c>
       <c r="F333" s="8" t="inlineStr"/>
@@ -11556,27 +11556,27 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-PDF-27</t>
         </is>
       </c>
       <c r="B334" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Topes de la tabla</t>
         </is>
       </c>
       <c r="E334" s="3" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Escribir 999 filas y 99 columnas</t>
         </is>
       </c>
       <c r="F334" s="3" t="inlineStr"/>
@@ -11589,12 +11589,12 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,12 +11622,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,27 +11655,27 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,27 +11688,27 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,12 +11721,12 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
@@ -11736,12 +11736,12 @@
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,12 +11754,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11787,12 +11787,12 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,12 +11820,12 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,12 +11853,12 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,27 +11886,27 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,27 +11919,27 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,12 +11952,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,27 +11985,27 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C347" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,27 +12018,27 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,27 +12051,27 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,27 +12084,27 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,27 +12117,27 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-01</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>DKIM verificado en verde</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio con DKIM firmando</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12150,12 +12150,12 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-02</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -12165,12 +12165,12 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>SPF/DMARC sin publicar en gris</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio recién creado</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -12183,27 +12183,27 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-03</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>SPF verde al publicarlo</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr"/>
@@ -12216,12 +12216,12 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-04</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>DMARC verde al publicarlo</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -12249,27 +12249,27 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-05</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>Tooltip explica el motivo</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Pasar el mouse sobre un chip gris</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr"/>
@@ -12282,27 +12282,27 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-06</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>Sin el layer de DNS</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -12315,7 +12315,7 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-07</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
@@ -12325,17 +12325,17 @@
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>Correos sueltos sin el panel</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr"/>
@@ -12348,7 +12348,7 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-08</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
@@ -12358,17 +12358,17 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>No es bloqueante</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -12381,12 +12381,12 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr"/>
@@ -12414,27 +12414,27 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -12447,12 +12447,12 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr"/>
@@ -12480,12 +12480,12 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
@@ -12513,27 +12513,27 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B363" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr"/>
@@ -12546,12 +12546,12 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr"/>
@@ -12579,27 +12579,27 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-AUT-01</t>
         </is>
       </c>
       <c r="B365" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>DKIM verificado en verde</t>
         </is>
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Abrir el detalle de un dominio con DKIM firmando</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr"/>
@@ -12612,27 +12612,27 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-AUT-02</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>SPF/DMARC sin publicar en gris</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Abrir el detalle de un dominio recién creado</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr"/>
@@ -12645,27 +12645,27 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-AUT-03</t>
         </is>
       </c>
       <c r="B367" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>SPF verde al publicarlo</t>
         </is>
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr"/>
@@ -12678,27 +12678,27 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-AUT-04</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>DMARC verde al publicarlo</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr"/>
@@ -12711,27 +12711,27 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-AUT-05</t>
         </is>
       </c>
       <c r="B369" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Tooltip explica el motivo</t>
         </is>
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Pasar el mouse sobre un chip gris</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr"/>
@@ -12744,27 +12744,27 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-35</t>
+          <t>CP-AUT-06</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>El bloqueo escalado explica por qué fue inmediato</t>
+          <t>Sin el layer de DNS</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
+          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr"/>
@@ -12777,27 +12777,27 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-36</t>
+          <t>CP-AUT-07</t>
         </is>
       </c>
       <c r="B371" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>El primer bloqueo no repite la explicación</t>
+          <t>Correos sueltos sin el panel</t>
         </is>
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>En una cuenta nueva, fallar 3 veces</t>
+          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr"/>
@@ -12810,27 +12810,27 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-AUT-08</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>No es bloqueante</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr"/>
@@ -12843,7 +12843,7 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr"/>
@@ -12876,7 +12876,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B375" s="8" t="inlineStr">
@@ -12924,12 +12924,12 @@
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr"/>
@@ -12942,7 +12942,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -12952,17 +12952,17 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B377" s="8" t="inlineStr">
@@ -12985,17 +12985,17 @@
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr"/>
@@ -13008,7 +13008,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr"/>
@@ -13041,27 +13041,27 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B379" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr"/>
@@ -13074,12 +13074,12 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -13089,12 +13089,12 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr"/>
@@ -13107,12 +13107,12 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B381" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C381" s="7" t="inlineStr">
@@ -13122,12 +13122,12 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr"/>
@@ -13140,27 +13140,27 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr"/>
@@ -13173,27 +13173,27 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B383" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr"/>
@@ -13206,27 +13206,27 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-35</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>El bloqueo escalado explica por qué fue inmediato</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr"/>
@@ -13239,12 +13239,12 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-SEC-36</t>
         </is>
       </c>
       <c r="B385" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C385" s="7" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>El primer bloqueo no repite la explicación</t>
         </is>
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>En una cuenta nueva, fallar 3 veces</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr"/>
@@ -13272,27 +13272,27 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr"/>
@@ -13305,12 +13305,12 @@
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B387" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C387" s="7" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr"/>
@@ -13338,12 +13338,12 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr"/>
@@ -13371,27 +13371,27 @@
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B389" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr"/>
@@ -13404,27 +13404,27 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr"/>
@@ -13437,27 +13437,27 @@
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B391" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr"/>
@@ -13470,12 +13470,12 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr"/>
@@ -13503,7 +13503,7 @@
     <row r="393">
       <c r="A393" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B393" s="8" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr"/>
@@ -13536,7 +13536,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -13551,12 +13551,12 @@
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr"/>
@@ -13569,7 +13569,7 @@
     <row r="395">
       <c r="A395" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B395" s="8" t="inlineStr">
@@ -13579,17 +13579,17 @@
       </c>
       <c r="C395" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr"/>
@@ -13602,7 +13602,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
@@ -13612,17 +13612,17 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr"/>
@@ -13635,7 +13635,7 @@
     <row r="397">
       <c r="A397" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B397" s="8" t="inlineStr">
@@ -13650,12 +13650,12 @@
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr"/>
@@ -13668,7 +13668,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
@@ -13683,12 +13683,12 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr"/>
@@ -13701,7 +13701,7 @@
     <row r="399">
       <c r="A399" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B399" s="8" t="inlineStr">
@@ -13711,17 +13711,17 @@
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr"/>
@@ -13734,7 +13734,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
@@ -13744,17 +13744,17 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr"/>
@@ -13767,7 +13767,7 @@
     <row r="401">
       <c r="A401" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B401" s="8" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr"/>
@@ -13800,7 +13800,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
@@ -13815,12 +13815,12 @@
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr"/>
@@ -13833,7 +13833,7 @@
     <row r="403">
       <c r="A403" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B403" s="8" t="inlineStr">
@@ -13843,17 +13843,17 @@
       </c>
       <c r="C403" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr"/>
@@ -13866,7 +13866,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -13876,17 +13876,17 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
     <row r="405">
       <c r="A405" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B405" s="8" t="inlineStr">
@@ -13909,17 +13909,17 @@
       </c>
       <c r="C405" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr"/>
@@ -13932,27 +13932,27 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr"/>
@@ -13965,27 +13965,27 @@
     <row r="407">
       <c r="A407" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B407" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr"/>
@@ -13998,12 +13998,12 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr"/>
@@ -14031,12 +14031,12 @@
     <row r="409">
       <c r="A409" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B409" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C409" s="7" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr"/>
@@ -14064,27 +14064,27 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr"/>
@@ -14097,12 +14097,12 @@
     <row r="411">
       <c r="A411" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B411" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C411" s="7" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr"/>
@@ -14130,12 +14130,12 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C412" s="2" t="inlineStr">
@@ -14145,12 +14145,12 @@
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr"/>
@@ -14163,27 +14163,27 @@
     <row r="413">
       <c r="A413" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B413" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C413" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr"/>
@@ -14196,27 +14196,27 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr"/>
@@ -14229,27 +14229,27 @@
     <row r="415">
       <c r="A415" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B415" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C415" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr"/>
@@ -14262,27 +14262,27 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr"/>
@@ -14295,12 +14295,12 @@
     <row r="417">
       <c r="A417" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B417" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C417" s="7" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F417" s="8" t="inlineStr"/>
@@ -14328,12 +14328,12 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C418" s="2" t="inlineStr">
@@ -14343,12 +14343,12 @@
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr"/>
@@ -14361,12 +14361,12 @@
     <row r="419">
       <c r="A419" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B419" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C419" s="7" t="inlineStr">
@@ -14376,12 +14376,12 @@
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F419" s="8" t="inlineStr"/>
@@ -14394,12 +14394,12 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
@@ -14409,12 +14409,12 @@
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr"/>
@@ -14427,27 +14427,27 @@
     <row r="421">
       <c r="A421" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B421" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F421" s="8" t="inlineStr"/>
@@ -14460,27 +14460,27 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr"/>
@@ -14493,12 +14493,12 @@
     <row r="423">
       <c r="A423" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B423" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C423" s="7" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F423" s="8" t="inlineStr"/>
@@ -14526,12 +14526,12 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr"/>
@@ -14559,27 +14559,27 @@
     <row r="425">
       <c r="A425" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B425" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C425" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F425" s="8" t="inlineStr"/>
@@ -14592,27 +14592,27 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr"/>
@@ -14625,27 +14625,27 @@
     <row r="427">
       <c r="A427" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B427" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C427" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F427" s="8" t="inlineStr"/>
@@ -14658,27 +14658,27 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr"/>
@@ -14691,27 +14691,27 @@
     <row r="429">
       <c r="A429" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B429" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C429" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F429" s="8" t="inlineStr"/>
@@ -14724,12 +14724,12 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
@@ -14739,12 +14739,12 @@
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr"/>
@@ -14757,12 +14757,12 @@
     <row r="431">
       <c r="A431" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-01</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B431" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C431" s="7" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>Aviso de campaña por aprobar</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F431" s="8" t="inlineStr"/>
@@ -14790,27 +14790,27 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-02</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>Solo a quien puede aprobar</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de otro operator del mismo equipo</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr"/>
@@ -14823,27 +14823,27 @@
     <row r="433">
       <c r="A433" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-03</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B433" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C433" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>Quien la pide no se avisa a sí mismo</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita del operator que la solicitó</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F433" s="8" t="inlineStr"/>
@@ -14856,7 +14856,7 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-04</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
@@ -14871,12 +14871,12 @@
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento entre empresas</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de un usuario de OTRA empresa</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr"/>
@@ -14889,7 +14889,7 @@
     <row r="435">
       <c r="A435" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-05</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B435" s="8" t="inlineStr">
@@ -14899,17 +14899,17 @@
       </c>
       <c r="C435" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>Aviso de aprobada</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>El owner aprueba la campaña</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr"/>
@@ -14922,7 +14922,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-06</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -14932,17 +14932,17 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>Aviso de rechazada con el motivo</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr"/>
@@ -14955,7 +14955,7 @@
     <row r="437">
       <c r="A437" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-07</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B437" s="8" t="inlineStr">
@@ -14965,17 +14965,17 @@
       </c>
       <c r="C437" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>Saldo bajo in-app</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>Hacer un envío que deje el saldo bajo el umbral</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr"/>
@@ -14988,7 +14988,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-08</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>Avisos nuevos abajo a la derecha</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr"/>
@@ -15021,7 +15021,7 @@
     <row r="439">
       <c r="A439" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-09</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B439" s="8" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>Los nuevos NO saltan al entrar</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>Con avisos viejos sin leer, entrar al portal</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr"/>
@@ -15054,7 +15054,7 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-10</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -15064,17 +15064,17 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>La tarjeta se retira sola</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>Esperar unos segundos tras el aviso</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr"/>
@@ -15087,7 +15087,7 @@
     <row r="441">
       <c r="A441" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-11</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B441" s="8" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>Clic lleva al lugar correcto</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>Hacer clic en "Campaña por aprobar"</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr"/>
@@ -15120,7 +15120,7 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-12</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -15135,12 +15135,12 @@
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>Marcar leídas</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>Abrir el panel y pulsar "Marcar leídas"</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
     <row r="443">
       <c r="A443" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-13</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B443" s="8" t="inlineStr">
@@ -15168,12 +15168,12 @@
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>No se puede marcar la de otro</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr"/>
@@ -15186,7 +15186,7 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-14</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
@@ -15201,12 +15201,12 @@
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>Sin notificaciones</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>Usuario nuevo abre la campanita</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr"/>
@@ -15219,7 +15219,7 @@
     <row r="445">
       <c r="A445" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-15</t>
+          <t>CP-CAM-01</t>
         </is>
       </c>
       <c r="B445" s="8" t="inlineStr">
@@ -15229,17 +15229,17 @@
       </c>
       <c r="C445" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>No molesta en impersonación</t>
+          <t>Aviso de campaña por aprobar</t>
         </is>
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>Entrar como admin con "Ver como cliente"</t>
+          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr"/>
@@ -15252,7 +15252,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-16</t>
+          <t>CP-CAM-02</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
@@ -15262,17 +15262,17 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>La aprobación funciona sin la tabla</t>
+          <t>Solo a quien puede aprobar</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
+          <t>Revisar la campanita de otro operator del mismo equipo</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr"/>
@@ -15285,12 +15285,12 @@
     <row r="447">
       <c r="A447" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-CAM-03</t>
         </is>
       </c>
       <c r="B447" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C447" s="7" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Quien la pide no se avisa a sí mismo</t>
         </is>
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Revisar la campanita del operator que la solicitó</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr"/>
@@ -15318,27 +15318,27 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-CAM-04</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Aislamiento entre empresas</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Revisar la campanita de un usuario de OTRA empresa</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr"/>
@@ -15351,27 +15351,27 @@
     <row r="449">
       <c r="A449" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-CAM-05</t>
         </is>
       </c>
       <c r="B449" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C449" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>Aviso de aprobada</t>
         </is>
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>El owner aprueba la campaña</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr"/>
@@ -15384,27 +15384,27 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-CAM-06</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Aviso de rechazada con el motivo</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr"/>
@@ -15417,12 +15417,12 @@
     <row r="451">
       <c r="A451" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-CAM-07</t>
         </is>
       </c>
       <c r="B451" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C451" s="7" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Saldo bajo in-app</t>
         </is>
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>Hacer un envío que deje el saldo bajo el umbral</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr"/>
@@ -15450,12 +15450,12 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-CAM-08</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C452" s="2" t="inlineStr">
@@ -15465,12 +15465,12 @@
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>Avisos nuevos abajo a la derecha</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr"/>
@@ -15483,12 +15483,12 @@
     <row r="453">
       <c r="A453" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-CAM-09</t>
         </is>
       </c>
       <c r="B453" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C453" s="7" t="inlineStr">
@@ -15498,12 +15498,12 @@
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>Los nuevos NO saltan al entrar</t>
         </is>
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Con avisos viejos sin leer, entrar al portal</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr"/>
@@ -15516,27 +15516,27 @@
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-CAM-10</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>La tarjeta se retira sola</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Esperar unos segundos tras el aviso</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr"/>
@@ -15549,27 +15549,27 @@
     <row r="455">
       <c r="A455" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-CAM-11</t>
         </is>
       </c>
       <c r="B455" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C455" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Clic lleva al lugar correcto</t>
         </is>
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Hacer clic en "Campaña por aprobar"</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr"/>
@@ -15582,27 +15582,27 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-CAM-12</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>Marcar leídas</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Abrir el panel y pulsar "Marcar leídas"</t>
         </is>
       </c>
       <c r="F456" s="3" t="inlineStr"/>
@@ -15615,12 +15615,12 @@
     <row r="457">
       <c r="A457" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-CAM-13</t>
         </is>
       </c>
       <c r="B457" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C457" s="7" t="inlineStr">
@@ -15630,12 +15630,12 @@
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>No se puede marcar la de otro</t>
         </is>
       </c>
       <c r="E457" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
         </is>
       </c>
       <c r="F457" s="8" t="inlineStr"/>
@@ -15648,12 +15648,12 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-CAM-14</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C458" s="2" t="inlineStr">
@@ -15663,12 +15663,12 @@
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Sin notificaciones</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Usuario nuevo abre la campanita</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr"/>
@@ -15681,27 +15681,27 @@
     <row r="459">
       <c r="A459" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-CAM-15</t>
         </is>
       </c>
       <c r="B459" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C459" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>No molesta en impersonación</t>
         </is>
       </c>
       <c r="E459" s="8" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Entrar como admin con "Ver como cliente"</t>
         </is>
       </c>
       <c r="F459" s="8" t="inlineStr"/>
@@ -15714,27 +15714,27 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-CAM-16</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>La aprobación funciona sin la tabla</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr"/>
@@ -15747,7 +15747,7 @@
     <row r="461">
       <c r="A461" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B461" s="8" t="inlineStr">
@@ -15757,17 +15757,17 @@
       </c>
       <c r="C461" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E461" s="8" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F461" s="8" t="inlineStr"/>
@@ -15780,7 +15780,7 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-01</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
@@ -15790,17 +15790,17 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>Segmentos calculados, no declarados</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>Muestras con una campaña SMS</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr"/>
@@ -15813,7 +15813,7 @@
     <row r="463">
       <c r="A463" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-02</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B463" s="8" t="inlineStr">
@@ -15823,17 +15823,17 @@
       </c>
       <c r="C463" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D463" s="8" t="inlineStr">
         <is>
-          <t>Un SMS largo cuesta el doble</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E463" s="8" t="inlineStr">
         <is>
-          <t>Campaña con más de 160 caracteres</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F463" s="8" t="inlineStr"/>
@@ -15846,7 +15846,7 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-03</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
@@ -15856,17 +15856,17 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>Una emoji parte el mensaje</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F464" s="3" t="inlineStr"/>
@@ -15879,7 +15879,7 @@
     <row r="465">
       <c r="A465" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-04</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B465" s="8" t="inlineStr">
@@ -15894,12 +15894,12 @@
       </c>
       <c r="D465" s="8" t="inlineStr">
         <is>
-          <t>Lo estimado es lo que se cobra</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E465" s="8" t="inlineStr">
         <is>
-          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F465" s="8" t="inlineStr"/>
@@ -15912,7 +15912,7 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-05</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
@@ -15922,17 +15922,17 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
-          <t>Tarifas nuevas visibles</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → canal SMS y Voz</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F466" s="3" t="inlineStr"/>
@@ -15945,7 +15945,7 @@
     <row r="467">
       <c r="A467" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-06</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B467" s="8" t="inlineStr">
@@ -15960,12 +15960,12 @@
       </c>
       <c r="D467" s="8" t="inlineStr">
         <is>
-          <t>Ningún cliente por debajo del costo</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E467" s="8" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → revisar overrides por cliente</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F467" s="8" t="inlineStr"/>
@@ -15978,7 +15978,7 @@
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-07</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
@@ -15988,17 +15988,17 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
         <is>
-          <t>Contador del editor SMS</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>Escribir un SMS con emoji en Plantillas SMS</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr"/>
@@ -16011,7 +16011,7 @@
     <row r="469">
       <c r="A469" s="7" t="inlineStr">
         <is>
-          <t>CP-PUB-01</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B469" s="8" t="inlineStr">
@@ -16026,12 +16026,12 @@
       </c>
       <c r="D469" s="8" t="inlineStr">
         <is>
-          <t>La landing no publica precios</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E469" s="8" t="inlineStr">
         <is>
-          <t>Abrir la landing → sección Precios</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F469" s="8" t="inlineStr"/>
@@ -16044,7 +16044,7 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-01</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
@@ -16059,12 +16059,12 @@
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>Título e idioma</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>Ver el código fuente de la landing</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr"/>
@@ -16077,7 +16077,7 @@
     <row r="471">
       <c r="A471" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-02</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B471" s="8" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="D471" s="8" t="inlineStr">
         <is>
-          <t>Vista previa al compartir</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E471" s="8" t="inlineStr">
         <is>
-          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F471" s="8" t="inlineStr"/>
@@ -16110,7 +16110,7 @@
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-03</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
@@ -16125,12 +16125,12 @@
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>Abrir la landing y mirar la pestaña</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F472" s="3" t="inlineStr"/>
@@ -16143,7 +16143,7 @@
     <row r="473">
       <c r="A473" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-04</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B473" s="8" t="inlineStr">
@@ -16153,17 +16153,17 @@
       </c>
       <c r="C473" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D473" s="8" t="inlineStr">
         <is>
-          <t>Icono en iOS</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E473" s="8" t="inlineStr">
         <is>
-          <t>"Añadir a pantalla de inicio" desde Safari</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F473" s="8" t="inlineStr"/>
@@ -16176,7 +16176,7 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-05</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
@@ -16191,12 +16191,12 @@
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>Datos estructurados</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F474" s="3" t="inlineStr"/>
@@ -16209,7 +16209,7 @@
     <row r="475">
       <c r="A475" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-06</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B475" s="8" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="D475" s="8" t="inlineStr">
         <is>
-          <t>Canonical y robots</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E475" s="8" t="inlineStr">
         <is>
-          <t>Abrir /robots.txt y /sitemap.xml</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F475" s="8" t="inlineStr"/>
@@ -16242,7 +16242,7 @@
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-01</t>
+          <t>CP-TAR-01</t>
         </is>
       </c>
       <c r="B476" s="3" t="inlineStr">
@@ -16257,12 +16257,12 @@
       </c>
       <c r="D476" s="3" t="inlineStr">
         <is>
-          <t>Tabla de precios por canal</t>
+          <t>Segmentos calculados, no declarados</t>
         </is>
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>Landing → Precios</t>
+          <t>Muestras con una campaña SMS</t>
         </is>
       </c>
       <c r="F476" s="3" t="inlineStr"/>
@@ -16275,7 +16275,7 @@
     <row r="477">
       <c r="A477" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-02</t>
+          <t>CP-TAR-02</t>
         </is>
       </c>
       <c r="B477" s="8" t="inlineStr">
@@ -16285,17 +16285,17 @@
       </c>
       <c r="C477" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D477" s="8" t="inlineStr">
         <is>
-          <t>Letra pequeña de precios</t>
+          <t>Un SMS largo cuesta el doble</t>
         </is>
       </c>
       <c r="E477" s="8" t="inlineStr">
         <is>
-          <t>Leer bajo la tabla</t>
+          <t>Campaña con más de 160 caracteres</t>
         </is>
       </c>
       <c r="F477" s="8" t="inlineStr"/>
@@ -16308,7 +16308,7 @@
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-03</t>
+          <t>CP-TAR-03</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
@@ -16318,17 +16318,17 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>Icono de WhatsApp</t>
+          <t>Una emoji parte el mensaje</t>
         </is>
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>Sección Canales</t>
+          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
         </is>
       </c>
       <c r="F478" s="3" t="inlineStr"/>
@@ -16341,7 +16341,7 @@
     <row r="479">
       <c r="A479" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-04</t>
+          <t>CP-TAR-04</t>
         </is>
       </c>
       <c r="B479" s="8" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="C479" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D479" s="8" t="inlineStr">
         <is>
-          <t>Sin promesa de 500 correos</t>
+          <t>Lo estimado es lo que se cobra</t>
         </is>
       </c>
       <c r="E479" s="8" t="inlineStr">
         <is>
-          <t>Recorrer toda la landing</t>
+          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
         </is>
       </c>
       <c r="F479" s="8" t="inlineStr"/>
@@ -16374,7 +16374,7 @@
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-05</t>
+          <t>CP-TAR-05</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
@@ -16384,17 +16384,17 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>Footer sin enlaces rotos</t>
+          <t>Tarifas nuevas visibles</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>Hacer clic en cada enlace del footer</t>
+          <t>Admin → Tarifas → canal SMS y Voz</t>
         </is>
       </c>
       <c r="F480" s="3" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
     <row r="481">
       <c r="A481" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-01</t>
+          <t>CP-TAR-06</t>
         </is>
       </c>
       <c r="B481" s="8" t="inlineStr">
@@ -16417,17 +16417,17 @@
       </c>
       <c r="C481" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D481" s="8" t="inlineStr">
         <is>
-          <t>Cerrar el modal con teclado</t>
+          <t>Ningún cliente por debajo del costo</t>
         </is>
       </c>
       <c r="E481" s="8" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Escape</t>
+          <t>Admin → Tarifas → revisar overrides por cliente</t>
         </is>
       </c>
       <c r="F481" s="8" t="inlineStr"/>
@@ -16440,7 +16440,7 @@
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>CP-A11Y-02</t>
+          <t>CP-TAR-07</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -16455,12 +16455,12 @@
       </c>
       <c r="D482" s="3" t="inlineStr">
         <is>
-          <t>Foco en el modal</t>
+          <t>Contador del editor SMS</t>
         </is>
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Tab</t>
+          <t>Escribir un SMS con emoji en Plantillas SMS</t>
         </is>
       </c>
       <c r="F482" s="3" t="inlineStr"/>
@@ -16473,7 +16473,7 @@
     <row r="483">
       <c r="A483" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-03</t>
+          <t>CP-PUB-01</t>
         </is>
       </c>
       <c r="B483" s="8" t="inlineStr">
@@ -16488,12 +16488,12 @@
       </c>
       <c r="D483" s="8" t="inlineStr">
         <is>
-          <t>Lector de pantalla</t>
+          <t>La landing no publica precios</t>
         </is>
       </c>
       <c r="E483" s="8" t="inlineStr">
         <is>
-          <t>Abrir el modal con un lector activo</t>
+          <t>Abrir la landing → sección Precios</t>
         </is>
       </c>
       <c r="F483" s="8" t="inlineStr"/>
@@ -16506,12 +16506,12 @@
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-SEO-01</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C484" s="2" t="inlineStr">
@@ -16521,12 +16521,12 @@
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>Título e idioma</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Ver el código fuente de la landing</t>
         </is>
       </c>
       <c r="F484" s="3" t="inlineStr"/>
@@ -16539,12 +16539,12 @@
     <row r="485">
       <c r="A485" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-SEO-02</t>
         </is>
       </c>
       <c r="B485" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C485" s="7" t="inlineStr">
@@ -16554,12 +16554,12 @@
       </c>
       <c r="D485" s="8" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Vista previa al compartir</t>
         </is>
       </c>
       <c r="E485" s="8" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
         </is>
       </c>
       <c r="F485" s="8" t="inlineStr"/>
@@ -16572,12 +16572,12 @@
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-SEO-03</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C486" s="2" t="inlineStr">
@@ -16587,12 +16587,12 @@
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Favicon</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Abrir la landing y mirar la pestaña</t>
         </is>
       </c>
       <c r="F486" s="3" t="inlineStr"/>
@@ -16605,27 +16605,27 @@
     <row r="487">
       <c r="A487" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-SEO-04</t>
         </is>
       </c>
       <c r="B487" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C487" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D487" s="8" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Icono en iOS</t>
         </is>
       </c>
       <c r="E487" s="8" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>"Añadir a pantalla de inicio" desde Safari</t>
         </is>
       </c>
       <c r="F487" s="8" t="inlineStr"/>
@@ -16638,12 +16638,12 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-SEO-05</t>
         </is>
       </c>
       <c r="B488" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C488" s="2" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Datos estructurados</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
         </is>
       </c>
       <c r="F488" s="3" t="inlineStr"/>
@@ -16671,12 +16671,12 @@
     <row r="489">
       <c r="A489" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-SEO-06</t>
         </is>
       </c>
       <c r="B489" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C489" s="7" t="inlineStr">
@@ -16686,12 +16686,12 @@
       </c>
       <c r="D489" s="8" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Canonical y robots</t>
         </is>
       </c>
       <c r="E489" s="8" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Abrir /robots.txt y /sitemap.xml</t>
         </is>
       </c>
       <c r="F489" s="8" t="inlineStr"/>
@@ -16704,12 +16704,12 @@
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-LAN-01</t>
         </is>
       </c>
       <c r="B490" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C490" s="2" t="inlineStr">
@@ -16719,12 +16719,12 @@
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Tabla de precios por canal</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Landing → Precios</t>
         </is>
       </c>
       <c r="F490" s="3" t="inlineStr"/>
@@ -16737,12 +16737,12 @@
     <row r="491">
       <c r="A491" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-LAN-02</t>
         </is>
       </c>
       <c r="B491" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C491" s="7" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="D491" s="8" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>Letra pequeña de precios</t>
         </is>
       </c>
       <c r="E491" s="8" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Leer bajo la tabla</t>
         </is>
       </c>
       <c r="F491" s="8" t="inlineStr"/>
@@ -16770,12 +16770,12 @@
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-LAN-03</t>
         </is>
       </c>
       <c r="B492" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C492" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>Icono de WhatsApp</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Sección Canales</t>
         </is>
       </c>
       <c r="F492" s="3" t="inlineStr"/>
@@ -16803,12 +16803,12 @@
     <row r="493">
       <c r="A493" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-LAN-04</t>
         </is>
       </c>
       <c r="B493" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C493" s="7" t="inlineStr">
@@ -16818,12 +16818,12 @@
       </c>
       <c r="D493" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Sin promesa de 500 correos</t>
         </is>
       </c>
       <c r="E493" s="8" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Recorrer toda la landing</t>
         </is>
       </c>
       <c r="F493" s="8" t="inlineStr"/>
@@ -16836,27 +16836,27 @@
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-LAN-05</t>
         </is>
       </c>
       <c r="B494" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Footer sin enlaces rotos</t>
         </is>
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Hacer clic en cada enlace del footer</t>
         </is>
       </c>
       <c r="F494" s="3" t="inlineStr"/>
@@ -16869,27 +16869,27 @@
     <row r="495">
       <c r="A495" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-A11Y-01</t>
         </is>
       </c>
       <c r="B495" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C495" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D495" s="8" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Cerrar el modal con teclado</t>
         </is>
       </c>
       <c r="E495" s="8" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Abrir /?activacion=ok y pulsar Escape</t>
         </is>
       </c>
       <c r="F495" s="8" t="inlineStr"/>
@@ -16902,27 +16902,27 @@
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-A11Y-02</t>
         </is>
       </c>
       <c r="B496" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Foco en el modal</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Abrir /?activacion=ok y pulsar Tab</t>
         </is>
       </c>
       <c r="F496" s="3" t="inlineStr"/>
@@ -16935,12 +16935,12 @@
     <row r="497">
       <c r="A497" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-A11Y-03</t>
         </is>
       </c>
       <c r="B497" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C497" s="7" t="inlineStr">
@@ -16950,12 +16950,12 @@
       </c>
       <c r="D497" s="8" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Lector de pantalla</t>
         </is>
       </c>
       <c r="E497" s="8" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Abrir el modal con un lector activo</t>
         </is>
       </c>
       <c r="F497" s="8" t="inlineStr"/>
@@ -16968,27 +16968,27 @@
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B498" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E498" s="3" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F498" s="3" t="inlineStr"/>
@@ -17001,27 +17001,27 @@
     <row r="499">
       <c r="A499" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B499" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C499" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D499" s="8" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E499" s="8" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F499" s="8" t="inlineStr"/>
@@ -17034,27 +17034,27 @@
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B500" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F500" s="3" t="inlineStr"/>
@@ -17067,27 +17067,27 @@
     <row r="501">
       <c r="A501" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B501" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C501" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D501" s="8" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E501" s="8" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F501" s="8" t="inlineStr"/>
@@ -17100,27 +17100,27 @@
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-CAS-05</t>
         </is>
       </c>
       <c r="B502" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Consentimiento por canal</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Contacto sin consentimiento del canal 0</t>
         </is>
       </c>
       <c r="F502" s="3" t="inlineStr"/>
@@ -17133,27 +17133,27 @@
     <row r="503">
       <c r="A503" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-CAS-06</t>
         </is>
       </c>
       <c r="B503" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C503" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D503" s="8" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Listado de cascadas</t>
         </is>
       </c>
       <c r="E503" s="8" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Abrir el listado</t>
         </is>
       </c>
       <c r="F503" s="8" t="inlineStr"/>
@@ -17163,13 +17163,475 @@
       <c r="J503" s="6" t="inlineStr"/>
       <c r="K503" s="5" t="inlineStr"/>
     </row>
+    <row r="504">
+      <c r="A504" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-01</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C504" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D504" s="3" t="inlineStr">
+        <is>
+          <t>Serie de 30 días (cliente)</t>
+        </is>
+      </c>
+      <c r="E504" s="3" t="inlineStr">
+        <is>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+        </is>
+      </c>
+      <c r="F504" s="3" t="inlineStr"/>
+      <c r="G504" s="4" t="inlineStr"/>
+      <c r="H504" s="5" t="inlineStr"/>
+      <c r="I504" s="4" t="inlineStr"/>
+      <c r="J504" s="6" t="inlineStr"/>
+      <c r="K504" s="5" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-02</t>
+        </is>
+      </c>
+      <c r="B505" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C505" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D505" s="8" t="inlineStr">
+        <is>
+          <t>Serie global (admin)</t>
+        </is>
+      </c>
+      <c r="E505" s="8" t="inlineStr">
+        <is>
+          <t>Panel de control → gráfico</t>
+        </is>
+      </c>
+      <c r="F505" s="8" t="inlineStr"/>
+      <c r="G505" s="4" t="inlineStr"/>
+      <c r="H505" s="5" t="inlineStr"/>
+      <c r="I505" s="4" t="inlineStr"/>
+      <c r="J505" s="6" t="inlineStr"/>
+      <c r="K505" s="5" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-03</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C506" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D506" s="3" t="inlineStr">
+        <is>
+          <t>Muestras excluidas</t>
+        </is>
+      </c>
+      <c r="E506" s="3" t="inlineStr">
+        <is>
+          <t>Enviar muestras y revisar la serie</t>
+        </is>
+      </c>
+      <c r="F506" s="3" t="inlineStr"/>
+      <c r="G506" s="4" t="inlineStr"/>
+      <c r="H506" s="5" t="inlineStr"/>
+      <c r="I506" s="4" t="inlineStr"/>
+      <c r="J506" s="6" t="inlineStr"/>
+      <c r="K506" s="5" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-04</t>
+        </is>
+      </c>
+      <c r="B507" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C507" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D507" s="8" t="inlineStr">
+        <is>
+          <t>Aislamiento</t>
+        </is>
+      </c>
+      <c r="E507" s="8" t="inlineStr">
+        <is>
+          <t>Comparar la serie de dos clientes</t>
+        </is>
+      </c>
+      <c r="F507" s="8" t="inlineStr"/>
+      <c r="G507" s="4" t="inlineStr"/>
+      <c r="H507" s="5" t="inlineStr"/>
+      <c r="I507" s="4" t="inlineStr"/>
+      <c r="J507" s="6" t="inlineStr"/>
+      <c r="K507" s="5" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>CP-SER-05</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C508" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D508" s="3" t="inlineStr">
+        <is>
+          <t>Adiós "(parcial)"</t>
+        </is>
+      </c>
+      <c r="E508" s="3" t="inlineStr">
+        <is>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+        </is>
+      </c>
+      <c r="F508" s="3" t="inlineStr"/>
+      <c r="G508" s="4" t="inlineStr"/>
+      <c r="H508" s="5" t="inlineStr"/>
+      <c r="I508" s="4" t="inlineStr"/>
+      <c r="J508" s="6" t="inlineStr"/>
+      <c r="K508" s="5" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="7" t="inlineStr">
+        <is>
+          <t>CP-SER-06</t>
+        </is>
+      </c>
+      <c r="B509" s="8" t="inlineStr">
+        <is>
+          <t>Cascada omnicanal y series</t>
+        </is>
+      </c>
+      <c r="C509" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D509" s="8" t="inlineStr">
+        <is>
+          <t>Leyenda interactiva</t>
+        </is>
+      </c>
+      <c r="E509" s="8" t="inlineStr">
+        <is>
+          <t>Ocultar/mostrar series en el gráfico</t>
+        </is>
+      </c>
+      <c r="F509" s="8" t="inlineStr"/>
+      <c r="G509" s="4" t="inlineStr"/>
+      <c r="H509" s="5" t="inlineStr"/>
+      <c r="I509" s="4" t="inlineStr"/>
+      <c r="J509" s="6" t="inlineStr"/>
+      <c r="K509" s="5" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-01</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C510" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D510" s="3" t="inlineStr">
+        <is>
+          <t>Aislamiento multi-tenant</t>
+        </is>
+      </c>
+      <c r="E510" s="3" t="inlineStr">
+        <is>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+        </is>
+      </c>
+      <c r="F510" s="3" t="inlineStr"/>
+      <c r="G510" s="4" t="inlineStr"/>
+      <c r="H510" s="5" t="inlineStr"/>
+      <c r="I510" s="4" t="inlineStr"/>
+      <c r="J510" s="6" t="inlineStr"/>
+      <c r="K510" s="5" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-02</t>
+        </is>
+      </c>
+      <c r="B511" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C511" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D511" s="8" t="inlineStr">
+        <is>
+          <t>Suite automática</t>
+        </is>
+      </c>
+      <c r="E511" s="8" t="inlineStr">
+        <is>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+        </is>
+      </c>
+      <c r="F511" s="8" t="inlineStr"/>
+      <c r="G511" s="4" t="inlineStr"/>
+      <c r="H511" s="5" t="inlineStr"/>
+      <c r="I511" s="4" t="inlineStr"/>
+      <c r="J511" s="6" t="inlineStr"/>
+      <c r="K511" s="5" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C512" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D512" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E512" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F512" s="3" t="inlineStr"/>
+      <c r="G512" s="4" t="inlineStr"/>
+      <c r="H512" s="5" t="inlineStr"/>
+      <c r="I512" s="4" t="inlineStr"/>
+      <c r="J512" s="6" t="inlineStr"/>
+      <c r="K512" s="5" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B513" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C513" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D513" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E513" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F513" s="8" t="inlineStr"/>
+      <c r="G513" s="4" t="inlineStr"/>
+      <c r="H513" s="5" t="inlineStr"/>
+      <c r="I513" s="4" t="inlineStr"/>
+      <c r="J513" s="6" t="inlineStr"/>
+      <c r="K513" s="5" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C514" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D514" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E514" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F514" s="3" t="inlineStr"/>
+      <c r="G514" s="4" t="inlineStr"/>
+      <c r="H514" s="5" t="inlineStr"/>
+      <c r="I514" s="4" t="inlineStr"/>
+      <c r="J514" s="6" t="inlineStr"/>
+      <c r="K514" s="5" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B515" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C515" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D515" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E515" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F515" s="8" t="inlineStr"/>
+      <c r="G515" s="4" t="inlineStr"/>
+      <c r="H515" s="5" t="inlineStr"/>
+      <c r="I515" s="4" t="inlineStr"/>
+      <c r="J515" s="6" t="inlineStr"/>
+      <c r="K515" s="5" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B516" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C516" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D516" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E516" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F516" s="3" t="inlineStr"/>
+      <c r="G516" s="4" t="inlineStr"/>
+      <c r="H516" s="5" t="inlineStr"/>
+      <c r="I516" s="4" t="inlineStr"/>
+      <c r="J516" s="6" t="inlineStr"/>
+      <c r="K516" s="5" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B517" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C517" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D517" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E517" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F517" s="8" t="inlineStr"/>
+      <c r="G517" s="4" t="inlineStr"/>
+      <c r="H517" s="5" t="inlineStr"/>
+      <c r="I517" s="4" t="inlineStr"/>
+      <c r="J517" s="6" t="inlineStr"/>
+      <c r="K517" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K503"/>
+  <autoFilter ref="A1:K517"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H503" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H517" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K503" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K517" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -17229,7 +17691,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A503)</f>
+        <f>COUNTA(Casos!A2:A517)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -17243,7 +17705,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$503,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$517,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -17260,7 +17722,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$503,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$517,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -17277,7 +17739,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$503,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$517,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -17294,7 +17756,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$503,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$517,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -17350,11 +17812,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$503,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$517,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$503,A12,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$517,A12,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -17367,11 +17829,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$503,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$517,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$503,A13,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$517,A13,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -17384,11 +17846,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$503,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$517,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$503,A14,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$517,A14,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -17446,19 +17908,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A18,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A18,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A18,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A18,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$503,$A18,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$517,$A18,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17469,19 +17931,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A19,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A19,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A19,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A19,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$503,$A19,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$517,$A19,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17492,19 +17954,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A20,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A20,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A20,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A20,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$503,$A20,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$517,$A20,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17515,19 +17977,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A21,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A21,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A21,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A21,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$503,$A21,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$517,$A21,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17538,19 +18000,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A22,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A22,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A22,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A22,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$503,$A22,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$517,$A22,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17561,19 +18023,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A23,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A23,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A23,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A23,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$503,$A23,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$517,$A23,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17584,19 +18046,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A24,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A24,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A24,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A24,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$503,$A24,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$517,$A24,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17607,19 +18069,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A25,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A25,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A25,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A25,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$503,$A25,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$517,$A25,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17630,19 +18092,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A26,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A26,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A26,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A26,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$503,$A26,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$517,$A26,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17653,19 +18115,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A27,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A27,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A27,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A27,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$503,$A27,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$517,$A27,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17676,19 +18138,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A28,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A28,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A28,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A28,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$503,$A28,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$517,$A28,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17699,19 +18161,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A29,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A29,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A29,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A29,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$503,$A29,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$517,$A29,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17722,19 +18184,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A30,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A30,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A30,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A30,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$503,$A30,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$517,$A30,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17745,19 +18207,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A31,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A31,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A31,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A31,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$503,$A31,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$517,$A31,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17768,19 +18230,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A32,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A32,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A32,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A32,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$503,$A32,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$517,$A32,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17791,19 +18253,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A33,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A33,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A33,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A33,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$503,$A33,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$517,$A33,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17814,19 +18276,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A34,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A34,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A34,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A34,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$503,$A34,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$517,$A34,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17837,19 +18299,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A35,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A35,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A35,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A35,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$503,$A35,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$517,$A35,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17860,19 +18322,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A36,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A36,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A36,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A36,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$503,$A36,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$517,$A36,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17883,19 +18345,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A37,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A37,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A37,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A37,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$503,$A37,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$517,$A37,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17906,19 +18368,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A38,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A38,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A38,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A38,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$503,$A38,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$517,$A38,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17929,19 +18391,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$503,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$517,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A39,Casos!$H$2:$H$503,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A39,Casos!$H$2:$H$517,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$503,$A39,Casos!$H$2:$H$503,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$517,$A39,Casos!$H$2:$H$517,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$503,$A39,Casos!$H$2:$H$503,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$517,$A39,Casos!$H$2:$H$517,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$517</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$523</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K517"/>
+  <dimension ref="A1:K523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11589,12 +11589,12 @@
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-PDF-28</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
@@ -11604,12 +11604,12 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Margen fiel</t>
         </is>
       </c>
       <c r="E335" s="8" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>Configurar margen superior 1,5 cm y mirar la regla</t>
         </is>
       </c>
       <c r="F335" s="8" t="inlineStr"/>
@@ -11622,12 +11622,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-PDF-29</t>
         </is>
       </c>
       <c r="B336" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>El margen coincide con el PDF</t>
         </is>
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Con 1,5 cm, "Vista previa PDF" y medir</t>
         </is>
       </c>
       <c r="F336" s="3" t="inlineStr"/>
@@ -11655,12 +11655,12 @@
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-PDF-44</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
@@ -11670,12 +11670,12 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>Diálogo movible</t>
         </is>
       </c>
       <c r="E337" s="8" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Abrir "Configurar página" y arrastrarlo por su barra</t>
         </is>
       </c>
       <c r="F337" s="8" t="inlineStr"/>
@@ -11688,12 +11688,12 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-PDF-45</t>
         </is>
       </c>
       <c r="B338" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Cambios en vivo</t>
         </is>
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Con el diálogo a un lado, cambiar márgenes y orientación</t>
         </is>
       </c>
       <c r="F338" s="3" t="inlineStr"/>
@@ -11721,27 +11721,27 @@
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-PDF-46</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>El diálogo no se pierde</t>
         </is>
       </c>
       <c r="E339" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Arrastrarlo al borde y achicar la ventana</t>
         </is>
       </c>
       <c r="F339" s="8" t="inlineStr"/>
@@ -11754,12 +11754,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-PDF-47</t>
         </is>
       </c>
       <c r="B340" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Cerrar el diálogo</t>
         </is>
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Pulsar la ✕ o Escape</t>
         </is>
       </c>
       <c r="F340" s="3" t="inlineStr"/>
@@ -11787,7 +11787,7 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
@@ -11797,17 +11797,17 @@
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,7 +11820,7 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,7 +11853,7 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,7 +11886,7 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
@@ -11896,17 +11896,17 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,7 +11919,7 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
@@ -11929,17 +11929,17 @@
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,7 +11952,7 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,7 +11985,7 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,7 +12018,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
@@ -12028,17 +12028,17 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,12 +12051,12 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
@@ -12066,12 +12066,12 @@
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,27 +12084,27 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,12 +12117,12 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C351" s="7" t="inlineStr">
@@ -12132,12 +12132,12 @@
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12150,12 +12150,12 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -12165,12 +12165,12 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -12183,27 +12183,27 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr"/>
@@ -12216,12 +12216,12 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -12249,7 +12249,7 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
@@ -12259,17 +12259,17 @@
       </c>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr"/>
@@ -12282,7 +12282,7 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -12315,27 +12315,27 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr"/>
@@ -12348,27 +12348,27 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -12381,12 +12381,12 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr"/>
@@ -12414,12 +12414,12 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -12447,27 +12447,27 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr"/>
@@ -12480,12 +12480,12 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -12495,12 +12495,12 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
@@ -12513,7 +12513,7 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B363" s="8" t="inlineStr">
@@ -12523,17 +12523,17 @@
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr"/>
@@ -12546,7 +12546,7 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
@@ -12556,17 +12556,17 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr"/>
@@ -12579,7 +12579,7 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-01</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B365" s="8" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>DKIM verificado en verde</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio con DKIM firmando</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr"/>
@@ -12612,7 +12612,7 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-02</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>SPF/DMARC sin publicar en gris</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio recién creado</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr"/>
@@ -12645,7 +12645,7 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-03</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B367" s="8" t="inlineStr">
@@ -12655,17 +12655,17 @@
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>SPF verde al publicarlo</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr"/>
@@ -12678,7 +12678,7 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-04</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
@@ -12688,17 +12688,17 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>DMARC verde al publicarlo</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr"/>
@@ -12711,7 +12711,7 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-05</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B369" s="8" t="inlineStr">
@@ -12721,17 +12721,17 @@
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>Tooltip explica el motivo</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Pasar el mouse sobre un chip gris</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr"/>
@@ -12744,7 +12744,7 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-06</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
@@ -12754,17 +12754,17 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Sin el layer de DNS</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr"/>
@@ -12777,7 +12777,7 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-07</t>
+          <t>CP-AUT-01</t>
         </is>
       </c>
       <c r="B371" s="8" t="inlineStr">
@@ -12787,17 +12787,17 @@
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>Correos sueltos sin el panel</t>
+          <t>DKIM verificado en verde</t>
         </is>
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
+          <t>Abrir el detalle de un dominio con DKIM firmando</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr"/>
@@ -12810,7 +12810,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-08</t>
+          <t>CP-AUT-02</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
@@ -12820,17 +12820,17 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>No es bloqueante</t>
+          <t>SPF/DMARC sin publicar en gris</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
+          <t>Abrir el detalle de un dominio recién creado</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr"/>
@@ -12843,27 +12843,27 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-AUT-03</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>SPF verde al publicarlo</t>
         </is>
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr"/>
@@ -12876,27 +12876,27 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-AUT-04</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>DMARC verde al publicarlo</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
@@ -12909,27 +12909,27 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-AUT-05</t>
         </is>
       </c>
       <c r="B375" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>Tooltip explica el motivo</t>
         </is>
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Pasar el mouse sobre un chip gris</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr"/>
@@ -12942,27 +12942,27 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-AUT-06</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>Sin el layer de DNS</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr"/>
@@ -12975,27 +12975,27 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-AUT-07</t>
         </is>
       </c>
       <c r="B377" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>Correos sueltos sin el panel</t>
         </is>
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr"/>
@@ -13008,27 +13008,27 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-AUT-08</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>No es bloqueante</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr"/>
@@ -13041,7 +13041,7 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B379" s="8" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr"/>
@@ -13074,7 +13074,7 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
@@ -13089,12 +13089,12 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr"/>
@@ -13107,7 +13107,7 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B381" s="8" t="inlineStr">
@@ -13122,12 +13122,12 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr"/>
@@ -13140,7 +13140,7 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
@@ -13155,12 +13155,12 @@
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr"/>
@@ -13173,7 +13173,7 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B383" s="8" t="inlineStr">
@@ -13183,17 +13183,17 @@
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr"/>
@@ -13206,7 +13206,7 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-35</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
@@ -13216,17 +13216,17 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>El bloqueo escalado explica por qué fue inmediato</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr"/>
@@ -13239,7 +13239,7 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-36</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B385" s="8" t="inlineStr">
@@ -13254,12 +13254,12 @@
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>El primer bloqueo no repite la explicación</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>En una cuenta nueva, fallar 3 veces</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr"/>
@@ -13272,7 +13272,7 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr"/>
@@ -13305,7 +13305,7 @@
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B387" s="8" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr"/>
@@ -13371,7 +13371,7 @@
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B389" s="8" t="inlineStr">
@@ -13381,17 +13381,17 @@
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr"/>
@@ -13404,7 +13404,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-SEC-35</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
@@ -13414,17 +13414,17 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>El bloqueo escalado explica por qué fue inmediato</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr"/>
@@ -13437,7 +13437,7 @@
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-SEC-36</t>
         </is>
       </c>
       <c r="B391" s="8" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>El primer bloqueo no repite la explicación</t>
         </is>
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>En una cuenta nueva, fallar 3 veces</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -13480,17 +13480,17 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr"/>
@@ -13503,12 +13503,12 @@
     <row r="393">
       <c r="A393" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B393" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C393" s="7" t="inlineStr">
@@ -13518,12 +13518,12 @@
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr"/>
@@ -13536,12 +13536,12 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
@@ -13551,12 +13551,12 @@
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr"/>
@@ -13569,12 +13569,12 @@
     <row r="395">
       <c r="A395" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B395" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C395" s="7" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr"/>
@@ -13602,12 +13602,12 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
@@ -13617,12 +13617,12 @@
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr"/>
@@ -13635,27 +13635,27 @@
     <row r="397">
       <c r="A397" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B397" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C397" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr"/>
@@ -13668,12 +13668,12 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -13683,12 +13683,12 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr"/>
@@ -13701,7 +13701,7 @@
     <row r="399">
       <c r="A399" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B399" s="8" t="inlineStr">
@@ -13711,17 +13711,17 @@
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr"/>
@@ -13734,7 +13734,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
@@ -13744,17 +13744,17 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr"/>
@@ -13767,7 +13767,7 @@
     <row r="401">
       <c r="A401" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B401" s="8" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr"/>
@@ -13800,7 +13800,7 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
@@ -13810,17 +13810,17 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr"/>
@@ -13833,7 +13833,7 @@
     <row r="403">
       <c r="A403" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B403" s="8" t="inlineStr">
@@ -13843,17 +13843,17 @@
       </c>
       <c r="C403" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr"/>
@@ -13866,7 +13866,7 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
@@ -13876,17 +13876,17 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr"/>
@@ -13899,7 +13899,7 @@
     <row r="405">
       <c r="A405" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B405" s="8" t="inlineStr">
@@ -13909,17 +13909,17 @@
       </c>
       <c r="C405" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr"/>
@@ -13932,7 +13932,7 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
@@ -13942,17 +13942,17 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr"/>
@@ -13965,7 +13965,7 @@
     <row r="407">
       <c r="A407" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B407" s="8" t="inlineStr">
@@ -13975,17 +13975,17 @@
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr"/>
@@ -13998,7 +13998,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr"/>
@@ -14031,7 +14031,7 @@
     <row r="409">
       <c r="A409" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B409" s="8" t="inlineStr">
@@ -14046,12 +14046,12 @@
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr"/>
@@ -14064,7 +14064,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -14074,17 +14074,17 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr"/>
@@ -14097,7 +14097,7 @@
     <row r="411">
       <c r="A411" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B411" s="8" t="inlineStr">
@@ -14112,12 +14112,12 @@
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr"/>
@@ -14130,7 +14130,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
@@ -14145,12 +14145,12 @@
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
     <row r="413">
       <c r="A413" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B413" s="8" t="inlineStr">
@@ -14173,17 +14173,17 @@
       </c>
       <c r="C413" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr"/>
@@ -14196,7 +14196,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
@@ -14206,17 +14206,17 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr"/>
@@ -14229,7 +14229,7 @@
     <row r="415">
       <c r="A415" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B415" s="8" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="C415" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr"/>
@@ -14262,7 +14262,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
@@ -14277,12 +14277,12 @@
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr"/>
@@ -14295,7 +14295,7 @@
     <row r="417">
       <c r="A417" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B417" s="8" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F417" s="8" t="inlineStr"/>
@@ -14328,7 +14328,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -14343,12 +14343,12 @@
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr"/>
@@ -14361,7 +14361,7 @@
     <row r="419">
       <c r="A419" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B419" s="8" t="inlineStr">
@@ -14371,17 +14371,17 @@
       </c>
       <c r="C419" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F419" s="8" t="inlineStr"/>
@@ -14394,27 +14394,27 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr"/>
@@ -14427,12 +14427,12 @@
     <row r="421">
       <c r="A421" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B421" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C421" s="7" t="inlineStr">
@@ -14442,12 +14442,12 @@
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F421" s="8" t="inlineStr"/>
@@ -14460,12 +14460,12 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C422" s="2" t="inlineStr">
@@ -14475,12 +14475,12 @@
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr"/>
@@ -14493,27 +14493,27 @@
     <row r="423">
       <c r="A423" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B423" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C423" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F423" s="8" t="inlineStr"/>
@@ -14526,12 +14526,12 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C424" s="2" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr"/>
@@ -14559,27 +14559,27 @@
     <row r="425">
       <c r="A425" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B425" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C425" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F425" s="8" t="inlineStr"/>
@@ -14592,7 +14592,7 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
@@ -14602,17 +14602,17 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr"/>
@@ -14625,7 +14625,7 @@
     <row r="427">
       <c r="A427" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B427" s="8" t="inlineStr">
@@ -14635,17 +14635,17 @@
       </c>
       <c r="C427" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F427" s="8" t="inlineStr"/>
@@ -14658,7 +14658,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
@@ -14673,12 +14673,12 @@
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr"/>
@@ -14691,7 +14691,7 @@
     <row r="429">
       <c r="A429" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B429" s="8" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F429" s="8" t="inlineStr"/>
@@ -14724,7 +14724,7 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
@@ -14739,12 +14739,12 @@
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr"/>
@@ -14757,7 +14757,7 @@
     <row r="431">
       <c r="A431" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B431" s="8" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F431" s="8" t="inlineStr"/>
@@ -14790,7 +14790,7 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
@@ -14805,12 +14805,12 @@
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr"/>
@@ -14823,7 +14823,7 @@
     <row r="433">
       <c r="A433" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B433" s="8" t="inlineStr">
@@ -14838,12 +14838,12 @@
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F433" s="8" t="inlineStr"/>
@@ -14856,12 +14856,12 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
@@ -14871,12 +14871,12 @@
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr"/>
@@ -14889,12 +14889,12 @@
     <row r="435">
       <c r="A435" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B435" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C435" s="7" t="inlineStr">
@@ -14904,12 +14904,12 @@
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr"/>
@@ -14922,12 +14922,12 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C436" s="2" t="inlineStr">
@@ -14937,12 +14937,12 @@
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr"/>
@@ -14955,27 +14955,27 @@
     <row r="437">
       <c r="A437" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B437" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C437" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr"/>
@@ -14988,12 +14988,12 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C438" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr"/>
@@ -15021,12 +15021,12 @@
     <row r="439">
       <c r="A439" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B439" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C439" s="7" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr"/>
@@ -15054,7 +15054,7 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
@@ -15069,12 +15069,12 @@
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr"/>
@@ -15087,7 +15087,7 @@
     <row r="441">
       <c r="A441" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B441" s="8" t="inlineStr">
@@ -15097,17 +15097,17 @@
       </c>
       <c r="C441" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr"/>
@@ -15120,7 +15120,7 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
@@ -15135,12 +15135,12 @@
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr"/>
@@ -15153,7 +15153,7 @@
     <row r="443">
       <c r="A443" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B443" s="8" t="inlineStr">
@@ -15163,17 +15163,17 @@
       </c>
       <c r="C443" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr"/>
@@ -15186,7 +15186,7 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
@@ -15201,12 +15201,12 @@
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr"/>
@@ -15219,7 +15219,7 @@
     <row r="445">
       <c r="A445" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-01</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B445" s="8" t="inlineStr">
@@ -15229,17 +15229,17 @@
       </c>
       <c r="C445" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>Aviso de campaña por aprobar</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr"/>
@@ -15252,7 +15252,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-02</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
@@ -15267,12 +15267,12 @@
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>Solo a quien puede aprobar</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de otro operator del mismo equipo</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr"/>
@@ -15285,7 +15285,7 @@
     <row r="447">
       <c r="A447" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-03</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B447" s="8" t="inlineStr">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Quien la pide no se avisa a sí mismo</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita del operator que la solicitó</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr"/>
@@ -15318,7 +15318,7 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-04</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
@@ -15328,17 +15328,17 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento entre empresas</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de un usuario de OTRA empresa</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr"/>
@@ -15351,7 +15351,7 @@
     <row r="449">
       <c r="A449" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-05</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B449" s="8" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>Aviso de aprobada</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>El owner aprueba la campaña</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr"/>
@@ -15384,7 +15384,7 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-06</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
@@ -15394,17 +15394,17 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>Aviso de rechazada con el motivo</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
     <row r="451">
       <c r="A451" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-07</t>
+          <t>CP-CAM-01</t>
         </is>
       </c>
       <c r="B451" s="8" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>Saldo bajo in-app</t>
+          <t>Aviso de campaña por aprobar</t>
         </is>
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>Hacer un envío que deje el saldo bajo el umbral</t>
+          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr"/>
@@ -15450,7 +15450,7 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-08</t>
+          <t>CP-CAM-02</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -15460,17 +15460,17 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>Avisos nuevos abajo a la derecha</t>
+          <t>Solo a quien puede aprobar</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
+          <t>Revisar la campanita de otro operator del mismo equipo</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr"/>
@@ -15483,7 +15483,7 @@
     <row r="453">
       <c r="A453" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-09</t>
+          <t>CP-CAM-03</t>
         </is>
       </c>
       <c r="B453" s="8" t="inlineStr">
@@ -15493,17 +15493,17 @@
       </c>
       <c r="C453" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>Los nuevos NO saltan al entrar</t>
+          <t>Quien la pide no se avisa a sí mismo</t>
         </is>
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>Con avisos viejos sin leer, entrar al portal</t>
+          <t>Revisar la campanita del operator que la solicitó</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr"/>
@@ -15516,7 +15516,7 @@
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-10</t>
+          <t>CP-CAM-04</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
@@ -15526,17 +15526,17 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>La tarjeta se retira sola</t>
+          <t>Aislamiento entre empresas</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>Esperar unos segundos tras el aviso</t>
+          <t>Revisar la campanita de un usuario de OTRA empresa</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr"/>
@@ -15549,7 +15549,7 @@
     <row r="455">
       <c r="A455" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-11</t>
+          <t>CP-CAM-05</t>
         </is>
       </c>
       <c r="B455" s="8" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>Clic lleva al lugar correcto</t>
+          <t>Aviso de aprobada</t>
         </is>
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>Hacer clic en "Campaña por aprobar"</t>
+          <t>El owner aprueba la campaña</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr"/>
@@ -15582,7 +15582,7 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-12</t>
+          <t>CP-CAM-06</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
@@ -15592,17 +15592,17 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>Marcar leídas</t>
+          <t>Aviso de rechazada con el motivo</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>Abrir el panel y pulsar "Marcar leídas"</t>
+          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
         </is>
       </c>
       <c r="F456" s="3" t="inlineStr"/>
@@ -15615,7 +15615,7 @@
     <row r="457">
       <c r="A457" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-13</t>
+          <t>CP-CAM-07</t>
         </is>
       </c>
       <c r="B457" s="8" t="inlineStr">
@@ -15630,12 +15630,12 @@
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>No se puede marcar la de otro</t>
+          <t>Saldo bajo in-app</t>
         </is>
       </c>
       <c r="E457" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
+          <t>Hacer un envío que deje el saldo bajo el umbral</t>
         </is>
       </c>
       <c r="F457" s="8" t="inlineStr"/>
@@ -15648,7 +15648,7 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-14</t>
+          <t>CP-CAM-08</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
@@ -15663,12 +15663,12 @@
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>Sin notificaciones</t>
+          <t>Avisos nuevos abajo a la derecha</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>Usuario nuevo abre la campanita</t>
+          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr"/>
@@ -15681,7 +15681,7 @@
     <row r="459">
       <c r="A459" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-15</t>
+          <t>CP-CAM-09</t>
         </is>
       </c>
       <c r="B459" s="8" t="inlineStr">
@@ -15691,17 +15691,17 @@
       </c>
       <c r="C459" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>No molesta en impersonación</t>
+          <t>Los nuevos NO saltan al entrar</t>
         </is>
       </c>
       <c r="E459" s="8" t="inlineStr">
         <is>
-          <t>Entrar como admin con "Ver como cliente"</t>
+          <t>Con avisos viejos sin leer, entrar al portal</t>
         </is>
       </c>
       <c r="F459" s="8" t="inlineStr"/>
@@ -15714,7 +15714,7 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-16</t>
+          <t>CP-CAM-10</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
@@ -15724,17 +15724,17 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>La aprobación funciona sin la tabla</t>
+          <t>La tarjeta se retira sola</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
+          <t>Esperar unos segundos tras el aviso</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr"/>
@@ -15747,12 +15747,12 @@
     <row r="461">
       <c r="A461" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-CAM-11</t>
         </is>
       </c>
       <c r="B461" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C461" s="7" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Clic lleva al lugar correcto</t>
         </is>
       </c>
       <c r="E461" s="8" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Hacer clic en "Campaña por aprobar"</t>
         </is>
       </c>
       <c r="F461" s="8" t="inlineStr"/>
@@ -15780,12 +15780,12 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-CAM-12</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C462" s="2" t="inlineStr">
@@ -15795,12 +15795,12 @@
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Marcar leídas</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Abrir el panel y pulsar "Marcar leídas"</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr"/>
@@ -15813,27 +15813,27 @@
     <row r="463">
       <c r="A463" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-CAM-13</t>
         </is>
       </c>
       <c r="B463" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C463" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D463" s="8" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>No se puede marcar la de otro</t>
         </is>
       </c>
       <c r="E463" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
         </is>
       </c>
       <c r="F463" s="8" t="inlineStr"/>
@@ -15846,12 +15846,12 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-CAM-14</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C464" s="2" t="inlineStr">
@@ -15861,12 +15861,12 @@
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Sin notificaciones</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Usuario nuevo abre la campanita</t>
         </is>
       </c>
       <c r="F464" s="3" t="inlineStr"/>
@@ -15879,27 +15879,27 @@
     <row r="465">
       <c r="A465" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-CAM-15</t>
         </is>
       </c>
       <c r="B465" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C465" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D465" s="8" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>No molesta en impersonación</t>
         </is>
       </c>
       <c r="E465" s="8" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>Entrar como admin con "Ver como cliente"</t>
         </is>
       </c>
       <c r="F465" s="8" t="inlineStr"/>
@@ -15912,27 +15912,27 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-CAM-16</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>La aprobación funciona sin la tabla</t>
         </is>
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
         </is>
       </c>
       <c r="F466" s="3" t="inlineStr"/>
@@ -15945,7 +15945,7 @@
     <row r="467">
       <c r="A467" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B467" s="8" t="inlineStr">
@@ -15955,17 +15955,17 @@
       </c>
       <c r="C467" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D467" s="8" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E467" s="8" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F467" s="8" t="inlineStr"/>
@@ -15978,7 +15978,7 @@
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
@@ -15988,17 +15988,17 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr"/>
@@ -16011,7 +16011,7 @@
     <row r="469">
       <c r="A469" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B469" s="8" t="inlineStr">
@@ -16026,12 +16026,12 @@
       </c>
       <c r="D469" s="8" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E469" s="8" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F469" s="8" t="inlineStr"/>
@@ -16044,7 +16044,7 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
@@ -16054,17 +16054,17 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr"/>
@@ -16077,7 +16077,7 @@
     <row r="471">
       <c r="A471" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B471" s="8" t="inlineStr">
@@ -16092,12 +16092,12 @@
       </c>
       <c r="D471" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E471" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F471" s="8" t="inlineStr"/>
@@ -16110,7 +16110,7 @@
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
@@ -16125,12 +16125,12 @@
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F472" s="3" t="inlineStr"/>
@@ -16143,7 +16143,7 @@
     <row r="473">
       <c r="A473" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B473" s="8" t="inlineStr">
@@ -16153,17 +16153,17 @@
       </c>
       <c r="C473" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D473" s="8" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E473" s="8" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F473" s="8" t="inlineStr"/>
@@ -16176,7 +16176,7 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
@@ -16186,17 +16186,17 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F474" s="3" t="inlineStr"/>
@@ -16209,7 +16209,7 @@
     <row r="475">
       <c r="A475" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B475" s="8" t="inlineStr">
@@ -16224,12 +16224,12 @@
       </c>
       <c r="D475" s="8" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E475" s="8" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F475" s="8" t="inlineStr"/>
@@ -16242,7 +16242,7 @@
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-01</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B476" s="3" t="inlineStr">
@@ -16257,12 +16257,12 @@
       </c>
       <c r="D476" s="3" t="inlineStr">
         <is>
-          <t>Segmentos calculados, no declarados</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>Muestras con una campaña SMS</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F476" s="3" t="inlineStr"/>
@@ -16275,7 +16275,7 @@
     <row r="477">
       <c r="A477" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-02</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B477" s="8" t="inlineStr">
@@ -16290,12 +16290,12 @@
       </c>
       <c r="D477" s="8" t="inlineStr">
         <is>
-          <t>Un SMS largo cuesta el doble</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E477" s="8" t="inlineStr">
         <is>
-          <t>Campaña con más de 160 caracteres</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F477" s="8" t="inlineStr"/>
@@ -16308,7 +16308,7 @@
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-03</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
@@ -16318,17 +16318,17 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>Una emoji parte el mensaje</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F478" s="3" t="inlineStr"/>
@@ -16341,7 +16341,7 @@
     <row r="479">
       <c r="A479" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-04</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B479" s="8" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="D479" s="8" t="inlineStr">
         <is>
-          <t>Lo estimado es lo que se cobra</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E479" s="8" t="inlineStr">
         <is>
-          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F479" s="8" t="inlineStr"/>
@@ -16374,7 +16374,7 @@
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-05</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
@@ -16384,17 +16384,17 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>Tarifas nuevas visibles</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → canal SMS y Voz</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F480" s="3" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
     <row r="481">
       <c r="A481" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-06</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B481" s="8" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="D481" s="8" t="inlineStr">
         <is>
-          <t>Ningún cliente por debajo del costo</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E481" s="8" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → revisar overrides por cliente</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F481" s="8" t="inlineStr"/>
@@ -16440,7 +16440,7 @@
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-07</t>
+          <t>CP-TAR-01</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -16450,17 +16450,17 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D482" s="3" t="inlineStr">
         <is>
-          <t>Contador del editor SMS</t>
+          <t>Segmentos calculados, no declarados</t>
         </is>
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>Escribir un SMS con emoji en Plantillas SMS</t>
+          <t>Muestras con una campaña SMS</t>
         </is>
       </c>
       <c r="F482" s="3" t="inlineStr"/>
@@ -16473,7 +16473,7 @@
     <row r="483">
       <c r="A483" s="7" t="inlineStr">
         <is>
-          <t>CP-PUB-01</t>
+          <t>CP-TAR-02</t>
         </is>
       </c>
       <c r="B483" s="8" t="inlineStr">
@@ -16483,17 +16483,17 @@
       </c>
       <c r="C483" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D483" s="8" t="inlineStr">
         <is>
-          <t>La landing no publica precios</t>
+          <t>Un SMS largo cuesta el doble</t>
         </is>
       </c>
       <c r="E483" s="8" t="inlineStr">
         <is>
-          <t>Abrir la landing → sección Precios</t>
+          <t>Campaña con más de 160 caracteres</t>
         </is>
       </c>
       <c r="F483" s="8" t="inlineStr"/>
@@ -16506,7 +16506,7 @@
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-01</t>
+          <t>CP-TAR-03</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
@@ -16521,12 +16521,12 @@
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>Título e idioma</t>
+          <t>Una emoji parte el mensaje</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>Ver el código fuente de la landing</t>
+          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
         </is>
       </c>
       <c r="F484" s="3" t="inlineStr"/>
@@ -16539,7 +16539,7 @@
     <row r="485">
       <c r="A485" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-02</t>
+          <t>CP-TAR-04</t>
         </is>
       </c>
       <c r="B485" s="8" t="inlineStr">
@@ -16554,12 +16554,12 @@
       </c>
       <c r="D485" s="8" t="inlineStr">
         <is>
-          <t>Vista previa al compartir</t>
+          <t>Lo estimado es lo que se cobra</t>
         </is>
       </c>
       <c r="E485" s="8" t="inlineStr">
         <is>
-          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
+          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
         </is>
       </c>
       <c r="F485" s="8" t="inlineStr"/>
@@ -16572,7 +16572,7 @@
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-03</t>
+          <t>CP-TAR-05</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
@@ -16582,17 +16582,17 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Tarifas nuevas visibles</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>Abrir la landing y mirar la pestaña</t>
+          <t>Admin → Tarifas → canal SMS y Voz</t>
         </is>
       </c>
       <c r="F486" s="3" t="inlineStr"/>
@@ -16605,7 +16605,7 @@
     <row r="487">
       <c r="A487" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-04</t>
+          <t>CP-TAR-06</t>
         </is>
       </c>
       <c r="B487" s="8" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="D487" s="8" t="inlineStr">
         <is>
-          <t>Icono en iOS</t>
+          <t>Ningún cliente por debajo del costo</t>
         </is>
       </c>
       <c r="E487" s="8" t="inlineStr">
         <is>
-          <t>"Añadir a pantalla de inicio" desde Safari</t>
+          <t>Admin → Tarifas → revisar overrides por cliente</t>
         </is>
       </c>
       <c r="F487" s="8" t="inlineStr"/>
@@ -16638,7 +16638,7 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-05</t>
+          <t>CP-TAR-07</t>
         </is>
       </c>
       <c r="B488" s="3" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>Datos estructurados</t>
+          <t>Contador del editor SMS</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
+          <t>Escribir un SMS con emoji en Plantillas SMS</t>
         </is>
       </c>
       <c r="F488" s="3" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
     <row r="489">
       <c r="A489" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-06</t>
+          <t>CP-PUB-01</t>
         </is>
       </c>
       <c r="B489" s="8" t="inlineStr">
@@ -16686,12 +16686,12 @@
       </c>
       <c r="D489" s="8" t="inlineStr">
         <is>
-          <t>Canonical y robots</t>
+          <t>La landing no publica precios</t>
         </is>
       </c>
       <c r="E489" s="8" t="inlineStr">
         <is>
-          <t>Abrir /robots.txt y /sitemap.xml</t>
+          <t>Abrir la landing → sección Precios</t>
         </is>
       </c>
       <c r="F489" s="8" t="inlineStr"/>
@@ -16704,7 +16704,7 @@
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-01</t>
+          <t>CP-SEO-01</t>
         </is>
       </c>
       <c r="B490" s="3" t="inlineStr">
@@ -16719,12 +16719,12 @@
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>Tabla de precios por canal</t>
+          <t>Título e idioma</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>Landing → Precios</t>
+          <t>Ver el código fuente de la landing</t>
         </is>
       </c>
       <c r="F490" s="3" t="inlineStr"/>
@@ -16737,7 +16737,7 @@
     <row r="491">
       <c r="A491" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-02</t>
+          <t>CP-SEO-02</t>
         </is>
       </c>
       <c r="B491" s="8" t="inlineStr">
@@ -16747,17 +16747,17 @@
       </c>
       <c r="C491" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D491" s="8" t="inlineStr">
         <is>
-          <t>Letra pequeña de precios</t>
+          <t>Vista previa al compartir</t>
         </is>
       </c>
       <c r="E491" s="8" t="inlineStr">
         <is>
-          <t>Leer bajo la tabla</t>
+          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
         </is>
       </c>
       <c r="F491" s="8" t="inlineStr"/>
@@ -16770,7 +16770,7 @@
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-03</t>
+          <t>CP-SEO-03</t>
         </is>
       </c>
       <c r="B492" s="3" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>Icono de WhatsApp</t>
+          <t>Favicon</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>Sección Canales</t>
+          <t>Abrir la landing y mirar la pestaña</t>
         </is>
       </c>
       <c r="F492" s="3" t="inlineStr"/>
@@ -16803,7 +16803,7 @@
     <row r="493">
       <c r="A493" s="7" t="inlineStr">
         <is>
-          <t>CP-LAN-04</t>
+          <t>CP-SEO-04</t>
         </is>
       </c>
       <c r="B493" s="8" t="inlineStr">
@@ -16818,12 +16818,12 @@
       </c>
       <c r="D493" s="8" t="inlineStr">
         <is>
-          <t>Sin promesa de 500 correos</t>
+          <t>Icono en iOS</t>
         </is>
       </c>
       <c r="E493" s="8" t="inlineStr">
         <is>
-          <t>Recorrer toda la landing</t>
+          <t>"Añadir a pantalla de inicio" desde Safari</t>
         </is>
       </c>
       <c r="F493" s="8" t="inlineStr"/>
@@ -16836,7 +16836,7 @@
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>CP-LAN-05</t>
+          <t>CP-SEO-05</t>
         </is>
       </c>
       <c r="B494" s="3" t="inlineStr">
@@ -16851,12 +16851,12 @@
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>Footer sin enlaces rotos</t>
+          <t>Datos estructurados</t>
         </is>
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>Hacer clic en cada enlace del footer</t>
+          <t>Pasar la URL por el validador de resultados enriquecidos de Google</t>
         </is>
       </c>
       <c r="F494" s="3" t="inlineStr"/>
@@ -16869,7 +16869,7 @@
     <row r="495">
       <c r="A495" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-01</t>
+          <t>CP-SEO-06</t>
         </is>
       </c>
       <c r="B495" s="8" t="inlineStr">
@@ -16879,17 +16879,17 @@
       </c>
       <c r="C495" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D495" s="8" t="inlineStr">
         <is>
-          <t>Cerrar el modal con teclado</t>
+          <t>Canonical y robots</t>
         </is>
       </c>
       <c r="E495" s="8" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Escape</t>
+          <t>Abrir /robots.txt y /sitemap.xml</t>
         </is>
       </c>
       <c r="F495" s="8" t="inlineStr"/>
@@ -16902,7 +16902,7 @@
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
         <is>
-          <t>CP-A11Y-02</t>
+          <t>CP-LAN-01</t>
         </is>
       </c>
       <c r="B496" s="3" t="inlineStr">
@@ -16912,17 +16912,17 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>Foco en el modal</t>
+          <t>Tabla de precios por canal</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>Abrir /?activacion=ok y pulsar Tab</t>
+          <t>Landing → Precios</t>
         </is>
       </c>
       <c r="F496" s="3" t="inlineStr"/>
@@ -16935,7 +16935,7 @@
     <row r="497">
       <c r="A497" s="7" t="inlineStr">
         <is>
-          <t>CP-A11Y-03</t>
+          <t>CP-LAN-02</t>
         </is>
       </c>
       <c r="B497" s="8" t="inlineStr">
@@ -16950,12 +16950,12 @@
       </c>
       <c r="D497" s="8" t="inlineStr">
         <is>
-          <t>Lector de pantalla</t>
+          <t>Letra pequeña de precios</t>
         </is>
       </c>
       <c r="E497" s="8" t="inlineStr">
         <is>
-          <t>Abrir el modal con un lector activo</t>
+          <t>Leer bajo la tabla</t>
         </is>
       </c>
       <c r="F497" s="8" t="inlineStr"/>
@@ -16968,27 +16968,27 @@
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-01</t>
+          <t>CP-LAN-03</t>
         </is>
       </c>
       <c r="B498" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
         <is>
-          <t>Lanzar cascada</t>
+          <t>Icono de WhatsApp</t>
         </is>
       </c>
       <c r="E498" s="3" t="inlineStr">
         <is>
-          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
+          <t>Sección Canales</t>
         </is>
       </c>
       <c r="F498" s="3" t="inlineStr"/>
@@ -17001,27 +17001,27 @@
     <row r="499">
       <c r="A499" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-02</t>
+          <t>CP-LAN-04</t>
         </is>
       </c>
       <c r="B499" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C499" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D499" s="8" t="inlineStr">
         <is>
-          <t>Escalado al siguiente canal</t>
+          <t>Sin promesa de 500 correos</t>
         </is>
       </c>
       <c r="E499" s="8" t="inlineStr">
         <is>
-          <t>Contacto que no cumple el criterio en el paso 0</t>
+          <t>Recorrer toda la landing</t>
         </is>
       </c>
       <c r="F499" s="8" t="inlineStr"/>
@@ -17034,12 +17034,12 @@
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-03</t>
+          <t>CP-LAN-05</t>
         </is>
       </c>
       <c r="B500" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C500" s="2" t="inlineStr">
@@ -17049,12 +17049,12 @@
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>Confirmado no escala</t>
+          <t>Footer sin enlaces rotos</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>Contacto que sí cumple el criterio</t>
+          <t>Hacer clic en cada enlace del footer</t>
         </is>
       </c>
       <c r="F500" s="3" t="inlineStr"/>
@@ -17067,12 +17067,12 @@
     <row r="501">
       <c r="A501" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-04</t>
+          <t>CP-A11Y-01</t>
         </is>
       </c>
       <c r="B501" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C501" s="7" t="inlineStr">
@@ -17082,12 +17082,12 @@
       </c>
       <c r="D501" s="8" t="inlineStr">
         <is>
-          <t>Saldo insuficiente</t>
+          <t>Cerrar el modal con teclado</t>
         </is>
       </c>
       <c r="E501" s="8" t="inlineStr">
         <is>
-          <t>Cascada sin saldo</t>
+          <t>Abrir /?activacion=ok y pulsar Escape</t>
         </is>
       </c>
       <c r="F501" s="8" t="inlineStr"/>
@@ -17100,12 +17100,12 @@
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
         <is>
-          <t>CP-CAS-05</t>
+          <t>CP-A11Y-02</t>
         </is>
       </c>
       <c r="B502" s="3" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C502" s="2" t="inlineStr">
@@ -17115,12 +17115,12 @@
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>Consentimiento por canal</t>
+          <t>Foco en el modal</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>Contacto sin consentimiento del canal 0</t>
+          <t>Abrir /?activacion=ok y pulsar Tab</t>
         </is>
       </c>
       <c r="F502" s="3" t="inlineStr"/>
@@ -17133,12 +17133,12 @@
     <row r="503">
       <c r="A503" s="7" t="inlineStr">
         <is>
-          <t>CP-CAS-06</t>
+          <t>CP-A11Y-03</t>
         </is>
       </c>
       <c r="B503" s="8" t="inlineStr">
         <is>
-          <t>Cascada omnicanal y series</t>
+          <t>Higiene, límites de uso y costo del adjunto</t>
         </is>
       </c>
       <c r="C503" s="7" t="inlineStr">
@@ -17148,12 +17148,12 @@
       </c>
       <c r="D503" s="8" t="inlineStr">
         <is>
-          <t>Listado de cascadas</t>
+          <t>Lector de pantalla</t>
         </is>
       </c>
       <c r="E503" s="8" t="inlineStr">
         <is>
-          <t>Abrir el listado</t>
+          <t>Abrir el modal con un lector activo</t>
         </is>
       </c>
       <c r="F503" s="8" t="inlineStr"/>
@@ -17166,7 +17166,7 @@
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-01</t>
+          <t>CP-CAS-01</t>
         </is>
       </c>
       <c r="B504" s="3" t="inlineStr">
@@ -17181,12 +17181,12 @@
       </c>
       <c r="D504" s="3" t="inlineStr">
         <is>
-          <t>Serie de 30 días (cliente)</t>
+          <t>Lanzar cascada</t>
         </is>
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
+          <t>Configurar pasos (correo → SMS → WhatsApp) y lanzar</t>
         </is>
       </c>
       <c r="F504" s="3" t="inlineStr"/>
@@ -17199,7 +17199,7 @@
     <row r="505">
       <c r="A505" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-02</t>
+          <t>CP-CAS-02</t>
         </is>
       </c>
       <c r="B505" s="8" t="inlineStr">
@@ -17209,17 +17209,17 @@
       </c>
       <c r="C505" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D505" s="8" t="inlineStr">
         <is>
-          <t>Serie global (admin)</t>
+          <t>Escalado al siguiente canal</t>
         </is>
       </c>
       <c r="E505" s="8" t="inlineStr">
         <is>
-          <t>Panel de control → gráfico</t>
+          <t>Contacto que no cumple el criterio en el paso 0</t>
         </is>
       </c>
       <c r="F505" s="8" t="inlineStr"/>
@@ -17232,7 +17232,7 @@
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-03</t>
+          <t>CP-CAS-03</t>
         </is>
       </c>
       <c r="B506" s="3" t="inlineStr">
@@ -17247,12 +17247,12 @@
       </c>
       <c r="D506" s="3" t="inlineStr">
         <is>
-          <t>Muestras excluidas</t>
+          <t>Confirmado no escala</t>
         </is>
       </c>
       <c r="E506" s="3" t="inlineStr">
         <is>
-          <t>Enviar muestras y revisar la serie</t>
+          <t>Contacto que sí cumple el criterio</t>
         </is>
       </c>
       <c r="F506" s="3" t="inlineStr"/>
@@ -17265,7 +17265,7 @@
     <row r="507">
       <c r="A507" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-04</t>
+          <t>CP-CAS-04</t>
         </is>
       </c>
       <c r="B507" s="8" t="inlineStr">
@@ -17275,17 +17275,17 @@
       </c>
       <c r="C507" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D507" s="8" t="inlineStr">
         <is>
-          <t>Aislamiento</t>
+          <t>Saldo insuficiente</t>
         </is>
       </c>
       <c r="E507" s="8" t="inlineStr">
         <is>
-          <t>Comparar la serie de dos clientes</t>
+          <t>Cascada sin saldo</t>
         </is>
       </c>
       <c r="F507" s="8" t="inlineStr"/>
@@ -17298,7 +17298,7 @@
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
         <is>
-          <t>CP-SER-05</t>
+          <t>CP-CAS-05</t>
         </is>
       </c>
       <c r="B508" s="3" t="inlineStr">
@@ -17308,17 +17308,17 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D508" s="3" t="inlineStr">
         <is>
-          <t>Adiós "(parcial)"</t>
+          <t>Consentimiento por canal</t>
         </is>
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
+          <t>Contacto sin consentimiento del canal 0</t>
         </is>
       </c>
       <c r="F508" s="3" t="inlineStr"/>
@@ -17331,7 +17331,7 @@
     <row r="509">
       <c r="A509" s="7" t="inlineStr">
         <is>
-          <t>CP-SER-06</t>
+          <t>CP-CAS-06</t>
         </is>
       </c>
       <c r="B509" s="8" t="inlineStr">
@@ -17341,17 +17341,17 @@
       </c>
       <c r="C509" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D509" s="8" t="inlineStr">
         <is>
-          <t>Leyenda interactiva</t>
+          <t>Listado de cascadas</t>
         </is>
       </c>
       <c r="E509" s="8" t="inlineStr">
         <is>
-          <t>Ocultar/mostrar series en el gráfico</t>
+          <t>Abrir el listado</t>
         </is>
       </c>
       <c r="F509" s="8" t="inlineStr"/>
@@ -17364,12 +17364,12 @@
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-01</t>
+          <t>CP-SER-01</t>
         </is>
       </c>
       <c r="B510" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C510" s="2" t="inlineStr">
@@ -17379,12 +17379,12 @@
       </c>
       <c r="D510" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento multi-tenant</t>
+          <t>Serie de 30 días (cliente)</t>
         </is>
       </c>
       <c r="E510" s="3" t="inlineStr">
         <is>
-          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
+          <t>Estadísticas → gráfico "Actividad de los últimos 30 días"</t>
         </is>
       </c>
       <c r="F510" s="3" t="inlineStr"/>
@@ -17397,12 +17397,12 @@
     <row r="511">
       <c r="A511" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-02</t>
+          <t>CP-SER-02</t>
         </is>
       </c>
       <c r="B511" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C511" s="7" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="D511" s="8" t="inlineStr">
         <is>
-          <t>Suite automática</t>
+          <t>Serie global (admin)</t>
         </is>
       </c>
       <c r="E511" s="8" t="inlineStr">
         <is>
-          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
+          <t>Panel de control → gráfico</t>
         </is>
       </c>
       <c r="F511" s="8" t="inlineStr"/>
@@ -17430,12 +17430,12 @@
     <row r="512">
       <c r="A512" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-03</t>
+          <t>CP-SER-03</t>
         </is>
       </c>
       <c r="B512" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C512" s="2" t="inlineStr">
@@ -17445,12 +17445,12 @@
       </c>
       <c r="D512" s="3" t="inlineStr">
         <is>
-          <t>Build del front</t>
+          <t>Muestras excluidas</t>
         </is>
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>npm run build</t>
+          <t>Enviar muestras y revisar la serie</t>
         </is>
       </c>
       <c r="F512" s="3" t="inlineStr"/>
@@ -17463,12 +17463,12 @@
     <row r="513">
       <c r="A513" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-06</t>
+          <t>CP-SER-04</t>
         </is>
       </c>
       <c r="B513" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C513" s="7" t="inlineStr">
@@ -17478,12 +17478,12 @@
       </c>
       <c r="D513" s="8" t="inlineStr">
         <is>
-          <t>Pruebas del frontend</t>
+          <t>Aislamiento</t>
         </is>
       </c>
       <c r="E513" s="8" t="inlineStr">
         <is>
-          <t>npm test en 05_Frontend/Front/page</t>
+          <t>Comparar la serie de dos clientes</t>
         </is>
       </c>
       <c r="F513" s="8" t="inlineStr"/>
@@ -17496,27 +17496,27 @@
     <row r="514">
       <c r="A514" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-07</t>
+          <t>CP-SER-05</t>
         </is>
       </c>
       <c r="B514" s="3" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D514" s="3" t="inlineStr">
         <is>
-          <t>Sesión y tenant en TODA ruta nueva</t>
+          <t>Adiós "(parcial)"</t>
         </is>
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+          <t>Con el rollup poblado, abrir Estadísticas/Facturación</t>
         </is>
       </c>
       <c r="F514" s="3" t="inlineStr"/>
@@ -17529,12 +17529,12 @@
     <row r="515">
       <c r="A515" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-08</t>
+          <t>CP-SER-06</t>
         </is>
       </c>
       <c r="B515" s="8" t="inlineStr">
         <is>
-          <t>Regresión / transversales</t>
+          <t>Cascada omnicanal y series</t>
         </is>
       </c>
       <c r="C515" s="7" t="inlineStr">
@@ -17544,12 +17544,12 @@
       </c>
       <c r="D515" s="8" t="inlineStr">
         <is>
-          <t>Fechas unificadas</t>
+          <t>Leyenda interactiva</t>
         </is>
       </c>
       <c r="E515" s="8" t="inlineStr">
         <is>
-          <t>Revisar las tablas del portal y del admin</t>
+          <t>Ocultar/mostrar series en el gráfico</t>
         </is>
       </c>
       <c r="F515" s="8" t="inlineStr"/>
@@ -17562,7 +17562,7 @@
     <row r="516">
       <c r="A516" s="2" t="inlineStr">
         <is>
-          <t>CP-REG-04</t>
+          <t>CP-REG-01</t>
         </is>
       </c>
       <c r="B516" s="3" t="inlineStr">
@@ -17572,17 +17572,17 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D516" s="3" t="inlineStr">
         <is>
-          <t>Tema claro/oscuro</t>
+          <t>Aislamiento multi-tenant</t>
         </is>
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>Alternar tema en portal y admin</t>
+          <t>Cliente A intenta ver datos de B (campañas/bases/stats)</t>
         </is>
       </c>
       <c r="F516" s="3" t="inlineStr"/>
@@ -17595,7 +17595,7 @@
     <row r="517">
       <c r="A517" s="7" t="inlineStr">
         <is>
-          <t>CP-REG-05</t>
+          <t>CP-REG-02</t>
         </is>
       </c>
       <c r="B517" s="8" t="inlineStr">
@@ -17605,17 +17605,17 @@
       </c>
       <c r="C517" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D517" s="8" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Suite automática</t>
         </is>
       </c>
       <c r="E517" s="8" t="inlineStr">
         <is>
-          <t>Portal/admin en móvil</t>
+          <t>Correr pytest 08_Pruebas/PruebasSeguridad</t>
         </is>
       </c>
       <c r="F517" s="8" t="inlineStr"/>
@@ -17625,13 +17625,211 @@
       <c r="J517" s="6" t="inlineStr"/>
       <c r="K517" s="5" t="inlineStr"/>
     </row>
+    <row r="518">
+      <c r="A518" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-03</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C518" s="2" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D518" s="3" t="inlineStr">
+        <is>
+          <t>Build del front</t>
+        </is>
+      </c>
+      <c r="E518" s="3" t="inlineStr">
+        <is>
+          <t>npm run build</t>
+        </is>
+      </c>
+      <c r="F518" s="3" t="inlineStr"/>
+      <c r="G518" s="4" t="inlineStr"/>
+      <c r="H518" s="5" t="inlineStr"/>
+      <c r="I518" s="4" t="inlineStr"/>
+      <c r="J518" s="6" t="inlineStr"/>
+      <c r="K518" s="5" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-06</t>
+        </is>
+      </c>
+      <c r="B519" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C519" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="D519" s="8" t="inlineStr">
+        <is>
+          <t>Pruebas del frontend</t>
+        </is>
+      </c>
+      <c r="E519" s="8" t="inlineStr">
+        <is>
+          <t>npm test en 05_Frontend/Front/page</t>
+        </is>
+      </c>
+      <c r="F519" s="8" t="inlineStr"/>
+      <c r="G519" s="4" t="inlineStr"/>
+      <c r="H519" s="5" t="inlineStr"/>
+      <c r="I519" s="4" t="inlineStr"/>
+      <c r="J519" s="6" t="inlineStr"/>
+      <c r="K519" s="5" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-07</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C520" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="D520" s="3" t="inlineStr">
+        <is>
+          <t>Sesión y tenant en TODA ruta nueva</t>
+        </is>
+      </c>
+      <c r="E520" s="3" t="inlineStr">
+        <is>
+          <t>Llamar cualquier endpoint nuevo sin token y con token de otro cliente</t>
+        </is>
+      </c>
+      <c r="F520" s="3" t="inlineStr"/>
+      <c r="G520" s="4" t="inlineStr"/>
+      <c r="H520" s="5" t="inlineStr"/>
+      <c r="I520" s="4" t="inlineStr"/>
+      <c r="J520" s="6" t="inlineStr"/>
+      <c r="K520" s="5" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-08</t>
+        </is>
+      </c>
+      <c r="B521" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C521" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D521" s="8" t="inlineStr">
+        <is>
+          <t>Fechas unificadas</t>
+        </is>
+      </c>
+      <c r="E521" s="8" t="inlineStr">
+        <is>
+          <t>Revisar las tablas del portal y del admin</t>
+        </is>
+      </c>
+      <c r="F521" s="8" t="inlineStr"/>
+      <c r="G521" s="4" t="inlineStr"/>
+      <c r="H521" s="5" t="inlineStr"/>
+      <c r="I521" s="4" t="inlineStr"/>
+      <c r="J521" s="6" t="inlineStr"/>
+      <c r="K521" s="5" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="inlineStr">
+        <is>
+          <t>CP-REG-04</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C522" s="2" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D522" s="3" t="inlineStr">
+        <is>
+          <t>Tema claro/oscuro</t>
+        </is>
+      </c>
+      <c r="E522" s="3" t="inlineStr">
+        <is>
+          <t>Alternar tema en portal y admin</t>
+        </is>
+      </c>
+      <c r="F522" s="3" t="inlineStr"/>
+      <c r="G522" s="4" t="inlineStr"/>
+      <c r="H522" s="5" t="inlineStr"/>
+      <c r="I522" s="4" t="inlineStr"/>
+      <c r="J522" s="6" t="inlineStr"/>
+      <c r="K522" s="5" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="7" t="inlineStr">
+        <is>
+          <t>CP-REG-05</t>
+        </is>
+      </c>
+      <c r="B523" s="8" t="inlineStr">
+        <is>
+          <t>Regresión / transversales</t>
+        </is>
+      </c>
+      <c r="C523" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="D523" s="8" t="inlineStr">
+        <is>
+          <t>Responsive</t>
+        </is>
+      </c>
+      <c r="E523" s="8" t="inlineStr">
+        <is>
+          <t>Portal/admin en móvil</t>
+        </is>
+      </c>
+      <c r="F523" s="8" t="inlineStr"/>
+      <c r="G523" s="4" t="inlineStr"/>
+      <c r="H523" s="5" t="inlineStr"/>
+      <c r="I523" s="4" t="inlineStr"/>
+      <c r="J523" s="6" t="inlineStr"/>
+      <c r="K523" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K517"/>
+  <autoFilter ref="A1:K523"/>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H517" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
+    <dataValidation sqref="H2:H523" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Elige un valor de la lista." promptTitle="Estado del caso" prompt="Pasó / No pasó / Bloqueado / No aplica" type="list">
       <formula1>"Pasó,No pasó,Bloqueado,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K517" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K523" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
   </dataValidations>
@@ -17691,7 +17889,7 @@
         </is>
       </c>
       <c r="B4" s="10">
-        <f>COUNTA(Casos!A2:A517)</f>
+        <f>COUNTA(Casos!A2:A523)</f>
         <v/>
       </c>
       <c r="C4" s="10" t="n"/>
@@ -17705,7 +17903,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$517,A5)</f>
+        <f>COUNTIF(Casos!$H$2:$H$523,A5)</f>
         <v/>
       </c>
       <c r="C5" s="12">
@@ -17722,7 +17920,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$517,A6)</f>
+        <f>COUNTIF(Casos!$H$2:$H$523,A6)</f>
         <v/>
       </c>
       <c r="C6" s="12">
@@ -17739,7 +17937,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$517,A7)</f>
+        <f>COUNTIF(Casos!$H$2:$H$523,A7)</f>
         <v/>
       </c>
       <c r="C7" s="12">
@@ -17756,7 +17954,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>COUNTIF(Casos!$H$2:$H$517,A8)</f>
+        <f>COUNTIF(Casos!$H$2:$H$523,A8)</f>
         <v/>
       </c>
       <c r="C8" s="12">
@@ -17812,11 +18010,11 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$517,A12)</f>
+        <f>COUNTIF(Casos!$C$2:$C$523,A12)</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$517,A12,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$523,A12,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="D12" s="10" t="n"/>
@@ -17829,11 +18027,11 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$517,A13)</f>
+        <f>COUNTIF(Casos!$C$2:$C$523,A13)</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$517,A13,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$523,A13,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="D13" s="10" t="n"/>
@@ -17846,11 +18044,11 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>COUNTIF(Casos!$C$2:$C$517,A14)</f>
+        <f>COUNTIF(Casos!$C$2:$C$523,A14)</f>
         <v/>
       </c>
       <c r="C14" s="10">
-        <f>COUNTIFS(Casos!$C$2:$C$517,A14,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$C$2:$C$523,A14,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="D14" s="10" t="n"/>
@@ -17908,19 +18106,19 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A18)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A18)</f>
         <v/>
       </c>
       <c r="C18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A18,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A18,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D18" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A18,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A18,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E18" s="10">
-        <f>B18-COUNTIFS(Casos!$B$2:$B$517,$A18,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B18-COUNTIFS(Casos!$B$2:$B$523,$A18,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17931,19 +18129,19 @@
         </is>
       </c>
       <c r="B19" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A19)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A19)</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A19,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A19,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A19,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A19,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>B19-COUNTIFS(Casos!$B$2:$B$517,$A19,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B19-COUNTIFS(Casos!$B$2:$B$523,$A19,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17954,19 +18152,19 @@
         </is>
       </c>
       <c r="B20" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A20)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A20,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A20,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A20,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A20,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>B20-COUNTIFS(Casos!$B$2:$B$517,$A20,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B20-COUNTIFS(Casos!$B$2:$B$523,$A20,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -17977,19 +18175,19 @@
         </is>
       </c>
       <c r="B21" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A21)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A21,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A21,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A21,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A21,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>B21-COUNTIFS(Casos!$B$2:$B$517,$A21,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B21-COUNTIFS(Casos!$B$2:$B$523,$A21,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18000,19 +18198,19 @@
         </is>
       </c>
       <c r="B22" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A22)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A22)</f>
         <v/>
       </c>
       <c r="C22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A22,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A22,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D22" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A22,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A22,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E22" s="10">
-        <f>B22-COUNTIFS(Casos!$B$2:$B$517,$A22,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B22-COUNTIFS(Casos!$B$2:$B$523,$A22,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18023,19 +18221,19 @@
         </is>
       </c>
       <c r="B23" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A23)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A23)</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A23,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A23,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A23,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A23,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>B23-COUNTIFS(Casos!$B$2:$B$517,$A23,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B23-COUNTIFS(Casos!$B$2:$B$523,$A23,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18046,19 +18244,19 @@
         </is>
       </c>
       <c r="B24" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A24)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A24)</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A24,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A24,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A24,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A24,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>B24-COUNTIFS(Casos!$B$2:$B$517,$A24,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B24-COUNTIFS(Casos!$B$2:$B$523,$A24,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18069,19 +18267,19 @@
         </is>
       </c>
       <c r="B25" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A25)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A25)</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A25,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A25,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A25,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A25,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>B25-COUNTIFS(Casos!$B$2:$B$517,$A25,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B25-COUNTIFS(Casos!$B$2:$B$523,$A25,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18092,19 +18290,19 @@
         </is>
       </c>
       <c r="B26" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A26)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A26)</f>
         <v/>
       </c>
       <c r="C26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A26,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A26,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D26" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A26,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A26,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E26" s="10">
-        <f>B26-COUNTIFS(Casos!$B$2:$B$517,$A26,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B26-COUNTIFS(Casos!$B$2:$B$523,$A26,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18115,19 +18313,19 @@
         </is>
       </c>
       <c r="B27" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A27)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A27)</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A27,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A27,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A27,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A27,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>B27-COUNTIFS(Casos!$B$2:$B$517,$A27,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B27-COUNTIFS(Casos!$B$2:$B$523,$A27,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18138,19 +18336,19 @@
         </is>
       </c>
       <c r="B28" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A28)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A28)</f>
         <v/>
       </c>
       <c r="C28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A28,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A28,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D28" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A28,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A28,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E28" s="10">
-        <f>B28-COUNTIFS(Casos!$B$2:$B$517,$A28,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B28-COUNTIFS(Casos!$B$2:$B$523,$A28,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18161,19 +18359,19 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A29)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A29)</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A29,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A29,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A29,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A29,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>B29-COUNTIFS(Casos!$B$2:$B$517,$A29,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B29-COUNTIFS(Casos!$B$2:$B$523,$A29,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18184,19 +18382,19 @@
         </is>
       </c>
       <c r="B30" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A30)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A30,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A30,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D30" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A30,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A30,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E30" s="10">
-        <f>B30-COUNTIFS(Casos!$B$2:$B$517,$A30,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B30-COUNTIFS(Casos!$B$2:$B$523,$A30,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18207,19 +18405,19 @@
         </is>
       </c>
       <c r="B31" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A31)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A31,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A31,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A31,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A31,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>B31-COUNTIFS(Casos!$B$2:$B$517,$A31,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B31-COUNTIFS(Casos!$B$2:$B$523,$A31,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18230,19 +18428,19 @@
         </is>
       </c>
       <c r="B32" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A32)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A32,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A32,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D32" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A32,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A32,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E32" s="10">
-        <f>B32-COUNTIFS(Casos!$B$2:$B$517,$A32,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B32-COUNTIFS(Casos!$B$2:$B$523,$A32,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18253,19 +18451,19 @@
         </is>
       </c>
       <c r="B33" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A33)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A33)</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A33,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A33,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A33,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A33,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>B33-COUNTIFS(Casos!$B$2:$B$517,$A33,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B33-COUNTIFS(Casos!$B$2:$B$523,$A33,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18276,19 +18474,19 @@
         </is>
       </c>
       <c r="B34" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A34)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A34)</f>
         <v/>
       </c>
       <c r="C34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A34,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A34,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D34" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A34,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A34,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E34" s="10">
-        <f>B34-COUNTIFS(Casos!$B$2:$B$517,$A34,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B34-COUNTIFS(Casos!$B$2:$B$523,$A34,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18299,19 +18497,19 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A35)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A35)</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A35,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A35,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A35,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A35,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>B35-COUNTIFS(Casos!$B$2:$B$517,$A35,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B35-COUNTIFS(Casos!$B$2:$B$523,$A35,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18322,19 +18520,19 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A36)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A36)</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A36,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A36,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A36,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A36,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>B36-COUNTIFS(Casos!$B$2:$B$517,$A36,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B36-COUNTIFS(Casos!$B$2:$B$523,$A36,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18345,19 +18543,19 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A37)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A37,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A37,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A37,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A37,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>B37-COUNTIFS(Casos!$B$2:$B$517,$A37,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B37-COUNTIFS(Casos!$B$2:$B$523,$A37,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18368,19 +18566,19 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A38)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A38,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A38,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A38,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A38,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>B38-COUNTIFS(Casos!$B$2:$B$517,$A38,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B38-COUNTIFS(Casos!$B$2:$B$523,$A38,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>
@@ -18391,19 +18589,19 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>COUNTIF(Casos!$B$2:$B$517,$A39)</f>
+        <f>COUNTIF(Casos!$B$2:$B$523,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A39,Casos!$H$2:$H$517,"Pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A39,Casos!$H$2:$H$523,"Pasó")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>COUNTIFS(Casos!$B$2:$B$517,$A39,Casos!$H$2:$H$517,"No pasó")</f>
+        <f>COUNTIFS(Casos!$B$2:$B$523,$A39,Casos!$H$2:$H$523,"No pasó")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>B39-COUNTIFS(Casos!$B$2:$B$517,$A39,Casos!$H$2:$H$517,"&lt;&gt;")</f>
+        <f>B39-COUNTIFS(Casos!$B$2:$B$523,$A39,Casos!$H$2:$H$523,"&lt;&gt;")</f>
         <v/>
       </c>
     </row>

--- a/CASOS_PRUEBA_QA.xlsx
+++ b/CASOS_PRUEBA_QA.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cómo usarla" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$523</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Casos'!$A$1:$K$532</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K523"/>
+  <dimension ref="A1:K532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11787,12 +11787,12 @@
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-01</t>
+          <t>CP-PRV-01</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
@@ -11802,12 +11802,12 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>Solicitar aprobación</t>
+          <t>Cambiar el proveedor global de un canal</t>
         </is>
       </c>
       <c r="E341" s="8" t="inlineStr">
         <is>
-          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
+          <t>Admin → Proveedores de envío → SMS → Twilio</t>
         </is>
       </c>
       <c r="F341" s="8" t="inlineStr"/>
@@ -11820,12 +11820,12 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-02</t>
+          <t>CP-PRV-02</t>
         </is>
       </c>
       <c r="B342" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>Sin muestras no se puede pedir</t>
+          <t>Proveedor propio de un cliente</t>
         </is>
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>Campaña sin muestras → solicitar</t>
+          <t>Ámbito = un cliente → Correo → SocketLabs</t>
         </is>
       </c>
       <c r="F342" s="3" t="inlineStr"/>
@@ -11853,12 +11853,12 @@
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-03</t>
+          <t>CP-PRV-03</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>Aprobar habilita el envío real</t>
+          <t>El envío sale por el proveedor elegido</t>
         </is>
       </c>
       <c r="E343" s="8" t="inlineStr">
         <is>
-          <t>Aprobador aprueba</t>
+          <t>Con credenciales configuradas, campaña SMS del cliente</t>
         </is>
       </c>
       <c r="F343" s="8" t="inlineStr"/>
@@ -11886,12 +11886,12 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-04</t>
+          <t>CP-PRV-04</t>
         </is>
       </c>
       <c r="B344" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -11901,12 +11901,12 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>Operator NO puede aprobar</t>
+          <t>Sin credenciales el lote NO se quema</t>
         </is>
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
+          <t>Elegir un proveedor sin sus envs y enviar</t>
         </is>
       </c>
       <c r="F344" s="3" t="inlineStr"/>
@@ -11919,12 +11919,12 @@
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-05</t>
+          <t>CP-PRV-05</t>
         </is>
       </c>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>Operator NO puede enviar real</t>
+          <t>WhatsApp no es cambiable</t>
         </is>
       </c>
       <c r="E345" s="8" t="inlineStr">
         <is>
-          <t>Usuario operator dispara el envío real por API</t>
+          <t>Abrir el desplegable de WhatsApp</t>
         </is>
       </c>
       <c r="F345" s="8" t="inlineStr"/>
@@ -11952,12 +11952,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>CP-APR-06</t>
+          <t>CP-PRV-06</t>
         </is>
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>Rechazar con motivo</t>
+          <t>Heredar</t>
         </is>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>Rechazar sin motivo y con motivo</t>
+          <t>Quitar el proveedor propio del cliente</t>
         </is>
       </c>
       <c r="F346" s="3" t="inlineStr"/>
@@ -11985,12 +11985,12 @@
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>CP-APR-07</t>
+          <t>CP-PRV-07</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C347" s="7" t="inlineStr">
@@ -12000,12 +12000,12 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>Doble aprobación</t>
+          <t>Correo por SocketLabs personaliza</t>
         </is>
       </c>
       <c r="E347" s="8" t="inlineStr">
         <is>
-          <t>Aprobar una campaña ya aprobada</t>
+          <t>EMAIL=socketlabs, plantilla con {{nombre}} y respaldo</t>
         </is>
       </c>
       <c r="F347" s="8" t="inlineStr"/>
@@ -12018,27 +12018,27 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-01</t>
+          <t>CP-PRV-08</t>
         </is>
       </c>
       <c r="B348" s="3" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>Programar envío</t>
+          <t>Los lotes en cola no cambian</t>
         </is>
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>Campaña aprobada → programar a una hora futura</t>
+          <t>Cambiar el proveedor con un envío en curso</t>
         </is>
       </c>
       <c r="F348" s="3" t="inlineStr"/>
@@ -12051,27 +12051,27 @@
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-02</t>
+          <t>CP-PRV-09</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>Aprobaciones (maker-checker) y programación de envíos</t>
+          <t>Plantillas PDF (básicas · Estudio · Diseñador)</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>Disparo a la hora exacta</t>
+          <t>Tabla de ruteo caída</t>
         </is>
       </c>
       <c r="E349" s="8" t="inlineStr">
         <is>
-          <t>Programar a +2 minutos y esperar</t>
+          <t>Sin permiso o sin tabla providerConfig</t>
         </is>
       </c>
       <c r="F349" s="8" t="inlineStr"/>
@@ -12084,7 +12084,7 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-03</t>
+          <t>CP-APR-01</t>
         </is>
       </c>
       <c r="B350" s="3" t="inlineStr">
@@ -12094,17 +12094,17 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>Fecha en el pasado</t>
+          <t>Solicitar aprobación</t>
         </is>
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>Programar a una hora ya pasada</t>
+          <t>Campaña con muestras enviadas → "Solicitar aprobación"</t>
         </is>
       </c>
       <c r="F350" s="3" t="inlineStr"/>
@@ -12117,7 +12117,7 @@
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-04</t>
+          <t>CP-APR-02</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
@@ -12127,17 +12127,17 @@
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>Cancelar</t>
+          <t>Sin muestras no se puede pedir</t>
         </is>
       </c>
       <c r="E351" s="8" t="inlineStr">
         <is>
-          <t>Cancelar una programación pending</t>
+          <t>Campaña sin muestras → solicitar</t>
         </is>
       </c>
       <c r="F351" s="8" t="inlineStr"/>
@@ -12150,7 +12150,7 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-05</t>
+          <t>CP-APR-03</t>
         </is>
       </c>
       <c r="B352" s="3" t="inlineStr">
@@ -12160,17 +12160,17 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una ya disparada</t>
+          <t>Aprobar habilita el envío real</t>
         </is>
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>Cancelar una sent</t>
+          <t>Aprobador aprueba</t>
         </is>
       </c>
       <c r="F352" s="3" t="inlineStr"/>
@@ -12183,7 +12183,7 @@
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>CP-SCH-06</t>
+          <t>CP-APR-04</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
@@ -12193,17 +12193,17 @@
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>Sin aprobación no programa</t>
+          <t>Operator NO puede aprobar</t>
         </is>
       </c>
       <c r="E353" s="8" t="inlineStr">
         <is>
-          <t>Campaña sin aprobar → programar</t>
+          <t>Usuario operator llama a /Campaign/Approve (por API, no por UI)</t>
         </is>
       </c>
       <c r="F353" s="8" t="inlineStr"/>
@@ -12216,7 +12216,7 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>CP-SCH-07</t>
+          <t>CP-APR-05</t>
         </is>
       </c>
       <c r="B354" s="3" t="inlineStr">
@@ -12226,17 +12226,17 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>Zona horaria</t>
+          <t>Operator NO puede enviar real</t>
         </is>
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>Programar 3:00 p. m. hora local</t>
+          <t>Usuario operator dispara el envío real por API</t>
         </is>
       </c>
       <c r="F354" s="3" t="inlineStr"/>
@@ -12249,27 +12249,27 @@
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-01</t>
+          <t>CP-APR-06</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>NIT ya registrado</t>
+          <t>Rechazar con motivo</t>
         </is>
       </c>
       <c r="E355" s="8" t="inlineStr">
         <is>
-          <t>Registrarse con el NIT de una empresa existente</t>
+          <t>Rechazar sin motivo y con motivo</t>
         </is>
       </c>
       <c r="F355" s="8" t="inlineStr"/>
@@ -12282,27 +12282,27 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-02</t>
+          <t>CP-APR-07</t>
         </is>
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>Owner agrega usuario</t>
+          <t>Doble aprobación</t>
         </is>
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>Tab Usuarios → agregar con rol operator/approver</t>
+          <t>Aprobar una campaña ya aprobada</t>
         </is>
       </c>
       <c r="F356" s="3" t="inlineStr"/>
@@ -12315,27 +12315,27 @@
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-03</t>
+          <t>CP-SCH-01</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>Tope de usuarios</t>
+          <t>Programar envío</t>
         </is>
       </c>
       <c r="E357" s="8" t="inlineStr">
         <is>
-          <t>Agregar más allá de MAX_TEAM_USERS</t>
+          <t>Campaña aprobada → programar a una hora futura</t>
         </is>
       </c>
       <c r="F357" s="8" t="inlineStr"/>
@@ -12348,27 +12348,27 @@
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-04</t>
+          <t>CP-SCH-02</t>
         </is>
       </c>
       <c r="B358" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>Correo duplicado</t>
+          <t>Disparo a la hora exacta</t>
         </is>
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>Agregar un correo que ya existe</t>
+          <t>Programar a +2 minutos y esperar</t>
         </is>
       </c>
       <c r="F358" s="3" t="inlineStr"/>
@@ -12381,27 +12381,27 @@
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-05</t>
+          <t>CP-SCH-03</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner gestiona</t>
+          <t>Fecha en el pasado</t>
         </is>
       </c>
       <c r="E359" s="8" t="inlineStr">
         <is>
-          <t>Un operator abre el tab Usuarios / llama la API</t>
+          <t>Programar a una hora ya pasada</t>
         </is>
       </c>
       <c r="F359" s="8" t="inlineStr"/>
@@ -12414,12 +12414,12 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-06</t>
+          <t>CP-SCH-04</t>
         </is>
       </c>
       <c r="B360" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>Eliminar usuario</t>
+          <t>Cancelar</t>
         </is>
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>Eliminar un miembro del equipo</t>
+          <t>Cancelar una programación pending</t>
         </is>
       </c>
       <c r="F360" s="3" t="inlineStr"/>
@@ -12447,12 +12447,12 @@
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>CP-USR-07</t>
+          <t>CP-SCH-05</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
@@ -12462,12 +12462,12 @@
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>Definir contraseña</t>
+          <t>Cancelar una ya disparada</t>
         </is>
       </c>
       <c r="E361" s="8" t="inlineStr">
         <is>
-          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
+          <t>Cancelar una sent</t>
         </is>
       </c>
       <c r="F361" s="8" t="inlineStr"/>
@@ -12480,27 +12480,27 @@
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
         <is>
-          <t>CP-USR-08</t>
+          <t>CP-SCH-06</t>
         </is>
       </c>
       <c r="B362" s="3" t="inlineStr">
         <is>
-          <t>Equipo del cliente y roles</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>Refresh preserva el sub-rol</t>
+          <t>Sin aprobación no programa</t>
         </is>
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
+          <t>Campaña sin aprobar → programar</t>
         </is>
       </c>
       <c r="F362" s="3" t="inlineStr"/>
@@ -12513,27 +12513,27 @@
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-01</t>
+          <t>CP-SCH-07</t>
         </is>
       </c>
       <c r="B363" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Aprobaciones (maker-checker) y programación de envíos</t>
         </is>
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>Agregar dominio</t>
+          <t>Zona horaria</t>
         </is>
       </c>
       <c r="E363" s="8" t="inlineStr">
         <is>
-          <t>Registrar empresa.com</t>
+          <t>Programar 3:00 p. m. hora local</t>
         </is>
       </c>
       <c r="F363" s="8" t="inlineStr"/>
@@ -12546,12 +12546,12 @@
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-02</t>
+          <t>CP-USR-01</t>
         </is>
       </c>
       <c r="B364" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -12561,12 +12561,12 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>Verificación tras publicar DNS</t>
+          <t>NIT ya registrado</t>
         </is>
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>Publicar los registros y refrescar la lista</t>
+          <t>Registrarse con el NIT de una empresa existente</t>
         </is>
       </c>
       <c r="F364" s="3" t="inlineStr"/>
@@ -12579,12 +12579,12 @@
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-03</t>
+          <t>CP-USR-02</t>
         </is>
       </c>
       <c r="B365" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C365" s="7" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>Agregar correo</t>
+          <t>Owner agrega usuario</t>
         </is>
       </c>
       <c r="E365" s="8" t="inlineStr">
         <is>
-          <t>Registrar ventas@empresa.com</t>
+          <t>Tab Usuarios → agregar con rol operator/approver</t>
         </is>
       </c>
       <c r="F365" s="8" t="inlineStr"/>
@@ -12612,12 +12612,12 @@
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-04</t>
+          <t>CP-USR-03</t>
         </is>
       </c>
       <c r="B366" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>Reenviar verificación</t>
+          <t>Tope de usuarios</t>
         </is>
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>Volver a agregar un correo pendiente</t>
+          <t>Agregar más allá de MAX_TEAM_USERS</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr"/>
@@ -12645,27 +12645,27 @@
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-05</t>
+          <t>CP-USR-04</t>
         </is>
       </c>
       <c r="B367" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner</t>
+          <t>Correo duplicado</t>
         </is>
       </c>
       <c r="E367" s="8" t="inlineStr">
         <is>
-          <t>operator intenta agregar o borrar un dominio (por API)</t>
+          <t>Agregar un correo que ya existe</t>
         </is>
       </c>
       <c r="F367" s="8" t="inlineStr"/>
@@ -12678,12 +12678,12 @@
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-06</t>
+          <t>CP-USR-05</t>
         </is>
       </c>
       <c r="B368" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>Anti-spoofing en la campaña</t>
+          <t>Solo el owner gestiona</t>
         </is>
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
+          <t>Un operator abre el tab Usuarios / llama la API</t>
         </is>
       </c>
       <c r="F368" s="3" t="inlineStr"/>
@@ -12711,12 +12711,12 @@
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>CP-DOM-07</t>
+          <t>CP-USR-06</t>
         </is>
       </c>
       <c r="B369" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C369" s="7" t="inlineStr">
@@ -12726,12 +12726,12 @@
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>Remitente verificado en el selector</t>
+          <t>Eliminar usuario</t>
         </is>
       </c>
       <c r="E369" s="8" t="inlineStr">
         <is>
-          <t>Crear campaña y abrir el selector "De (From)"</t>
+          <t>Eliminar un miembro del equipo</t>
         </is>
       </c>
       <c r="F369" s="8" t="inlineStr"/>
@@ -12744,12 +12744,12 @@
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>CP-DOM-08</t>
+          <t>CP-USR-07</t>
         </is>
       </c>
       <c r="B370" s="3" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>Eliminar dominio</t>
+          <t>Definir contraseña</t>
         </is>
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>Borrar un dominio verificado</t>
+          <t>Usuario nuevo usa "¿olvidaste tu contraseña?"</t>
         </is>
       </c>
       <c r="F370" s="3" t="inlineStr"/>
@@ -12777,12 +12777,12 @@
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-01</t>
+          <t>CP-USR-08</t>
         </is>
       </c>
       <c r="B371" s="8" t="inlineStr">
         <is>
-          <t>Dominios y correos remitentes</t>
+          <t>Equipo del cliente y roles</t>
         </is>
       </c>
       <c r="C371" s="7" t="inlineStr">
@@ -12792,12 +12792,12 @@
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>DKIM verificado en verde</t>
+          <t>Refresh preserva el sub-rol</t>
         </is>
       </c>
       <c r="E371" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio con DKIM firmando</t>
+          <t>Loguear como operator, esperar el refresco del token e intentar aprobar</t>
         </is>
       </c>
       <c r="F371" s="8" t="inlineStr"/>
@@ -12810,7 +12810,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-02</t>
+          <t>CP-DOM-01</t>
         </is>
       </c>
       <c r="B372" s="3" t="inlineStr">
@@ -12820,17 +12820,17 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>SPF/DMARC sin publicar en gris</t>
+          <t>Agregar dominio</t>
         </is>
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un dominio recién creado</t>
+          <t>Registrar empresa.com</t>
         </is>
       </c>
       <c r="F372" s="3" t="inlineStr"/>
@@ -12843,7 +12843,7 @@
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-03</t>
+          <t>CP-DOM-02</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
@@ -12853,17 +12853,17 @@
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>SPF verde al publicarlo</t>
+          <t>Verificación tras publicar DNS</t>
         </is>
       </c>
       <c r="E373" s="8" t="inlineStr">
         <is>
-          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
+          <t>Publicar los registros y refrescar la lista</t>
         </is>
       </c>
       <c r="F373" s="8" t="inlineStr"/>
@@ -12876,7 +12876,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-04</t>
+          <t>CP-DOM-03</t>
         </is>
       </c>
       <c r="B374" s="3" t="inlineStr">
@@ -12886,17 +12886,17 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>DMARC verde al publicarlo</t>
+          <t>Agregar correo</t>
         </is>
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
+          <t>Registrar ventas@empresa.com</t>
         </is>
       </c>
       <c r="F374" s="3" t="inlineStr"/>
@@ -12909,7 +12909,7 @@
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-05</t>
+          <t>CP-DOM-04</t>
         </is>
       </c>
       <c r="B375" s="8" t="inlineStr">
@@ -12919,17 +12919,17 @@
       </c>
       <c r="C375" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>Tooltip explica el motivo</t>
+          <t>Reenviar verificación</t>
         </is>
       </c>
       <c r="E375" s="8" t="inlineStr">
         <is>
-          <t>Pasar el mouse sobre un chip gris</t>
+          <t>Volver a agregar un correo pendiente</t>
         </is>
       </c>
       <c r="F375" s="8" t="inlineStr"/>
@@ -12942,7 +12942,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-06</t>
+          <t>CP-DOM-05</t>
         </is>
       </c>
       <c r="B376" s="3" t="inlineStr">
@@ -12952,17 +12952,17 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>Sin el layer de DNS</t>
+          <t>Solo el owner</t>
         </is>
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
+          <t>operator intenta agregar o borrar un dominio (por API)</t>
         </is>
       </c>
       <c r="F376" s="3" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>CP-AUT-07</t>
+          <t>CP-DOM-06</t>
         </is>
       </c>
       <c r="B377" s="8" t="inlineStr">
@@ -12985,17 +12985,17 @@
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>Correos sueltos sin el panel</t>
+          <t>Anti-spoofing en la campaña</t>
         </is>
       </c>
       <c r="E377" s="8" t="inlineStr">
         <is>
-          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
+          <t>Crear campaña con un from de un dominio que NO es del cliente</t>
         </is>
       </c>
       <c r="F377" s="8" t="inlineStr"/>
@@ -13008,7 +13008,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>CP-AUT-08</t>
+          <t>CP-DOM-07</t>
         </is>
       </c>
       <c r="B378" s="3" t="inlineStr">
@@ -13018,17 +13018,17 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>No es bloqueante</t>
+          <t>Remitente verificado en el selector</t>
         </is>
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
+          <t>Crear campaña y abrir el selector "De (From)"</t>
         </is>
       </c>
       <c r="F378" s="3" t="inlineStr"/>
@@ -13041,27 +13041,27 @@
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-01</t>
+          <t>CP-DOM-08</t>
         </is>
       </c>
       <c r="B379" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>Activar 2FA</t>
+          <t>Eliminar dominio</t>
         </is>
       </c>
       <c r="E379" s="8" t="inlineStr">
         <is>
-          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
+          <t>Borrar un dominio verificado</t>
         </is>
       </c>
       <c r="F379" s="8" t="inlineStr"/>
@@ -13074,12 +13074,12 @@
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-02</t>
+          <t>CP-AUT-01</t>
         </is>
       </c>
       <c r="B380" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -13089,12 +13089,12 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>Login con 2FA</t>
+          <t>DKIM verificado en verde</t>
         </is>
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
+          <t>Abrir el detalle de un dominio con DKIM firmando</t>
         </is>
       </c>
       <c r="F380" s="3" t="inlineStr"/>
@@ -13107,27 +13107,27 @@
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-03</t>
+          <t>CP-AUT-02</t>
         </is>
       </c>
       <c r="B381" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C381" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>Código correcto</t>
+          <t>SPF/DMARC sin publicar en gris</t>
         </is>
       </c>
       <c r="E381" s="8" t="inlineStr">
         <is>
-          <t>Introducir el TOTP vigente</t>
+          <t>Abrir el detalle de un dominio recién creado</t>
         </is>
       </c>
       <c r="F381" s="8" t="inlineStr"/>
@@ -13140,27 +13140,27 @@
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-04</t>
+          <t>CP-AUT-03</t>
         </is>
       </c>
       <c r="B382" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>Código de respaldo</t>
+          <t>SPF verde al publicarlo</t>
         </is>
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>Entrar con un código de respaldo</t>
+          <t>Publicar v=spf1 include:amazonses.com ~all y pulsar Actualizar estado</t>
         </is>
       </c>
       <c r="F382" s="3" t="inlineStr"/>
@@ -13173,27 +13173,27 @@
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-05</t>
+          <t>CP-AUT-04</t>
         </is>
       </c>
       <c r="B383" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>Anti-fuerza-bruta</t>
+          <t>DMARC verde al publicarlo</t>
         </is>
       </c>
       <c r="E383" s="8" t="inlineStr">
         <is>
-          <t>Fallar el código 5 veces</t>
+          <t>Publicar _dmarc.&lt;dominio&gt; con v=DMARC1;… y actualizar</t>
         </is>
       </c>
       <c r="F383" s="8" t="inlineStr"/>
@@ -13206,27 +13206,27 @@
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
         <is>
-          <t>CP-2FA-06</t>
+          <t>CP-AUT-05</t>
         </is>
       </c>
       <c r="B384" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>Desactivar 2FA</t>
+          <t>Tooltip explica el motivo</t>
         </is>
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>Desactivar exigiendo un código válido</t>
+          <t>Pasar el mouse sobre un chip gris</t>
         </is>
       </c>
       <c r="F384" s="3" t="inlineStr"/>
@@ -13239,27 +13239,27 @@
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>CP-2FA-07</t>
+          <t>CP-AUT-06</t>
         </is>
       </c>
       <c r="B385" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>Auditoría del 2FA</t>
+          <t>Sin el layer de DNS</t>
         </is>
       </c>
       <c r="E385" s="8" t="inlineStr">
         <is>
-          <t>Activar y desactivar → tab Auditoría</t>
+          <t>Con el layer de dnspython no desplegado, ver un dominio</t>
         </is>
       </c>
       <c r="F385" s="8" t="inlineStr"/>
@@ -13272,27 +13272,27 @@
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-24</t>
+          <t>CP-AUT-07</t>
         </is>
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo progresivo de login</t>
+          <t>Correos sueltos sin el panel</t>
         </is>
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>Fallar la contraseña 3 veces</t>
+          <t>Abrir el detalle de un remitente tipo correo (no dominio)</t>
         </is>
       </c>
       <c r="F386" s="3" t="inlineStr"/>
@@ -13305,27 +13305,27 @@
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-25</t>
+          <t>CP-AUT-08</t>
         </is>
       </c>
       <c r="B387" s="8" t="inlineStr">
         <is>
-          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
+          <t>Dominios y correos remitentes</t>
         </is>
       </c>
       <c r="C387" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>Escalada del bloqueo</t>
+          <t>No es bloqueante</t>
         </is>
       </c>
       <c r="E387" s="8" t="inlineStr">
         <is>
-          <t>Tras los 5 min, fallar otra vez, y otra</t>
+          <t>Con SPF y DMARC en gris, intentar enviar una campaña real desde ese dominio verificado</t>
         </is>
       </c>
       <c r="F387" s="8" t="inlineStr"/>
@@ -13338,7 +13338,7 @@
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-26</t>
+          <t>CP-2FA-01</t>
         </is>
       </c>
       <c r="B388" s="3" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>Bloqueo con clave correcta</t>
+          <t>Activar 2FA</t>
         </is>
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
+          <t>Mi cuenta → escanear el QR con Google Authenticator → introducir el código</t>
         </is>
       </c>
       <c r="F388" s="3" t="inlineStr"/>
@@ -13371,7 +13371,7 @@
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-27</t>
+          <t>CP-2FA-02</t>
         </is>
       </c>
       <c r="B389" s="8" t="inlineStr">
@@ -13381,17 +13381,17 @@
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>Reset del contador</t>
+          <t>Login con 2FA</t>
         </is>
       </c>
       <c r="E389" s="8" t="inlineStr">
         <is>
-          <t>Login correcto con la cuenta desbloqueada</t>
+          <t>Loguear con usuario/clave de una cuenta con 2FA</t>
         </is>
       </c>
       <c r="F389" s="8" t="inlineStr"/>
@@ -13404,7 +13404,7 @@
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-35</t>
+          <t>CP-2FA-03</t>
         </is>
       </c>
       <c r="B390" s="3" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>El bloqueo escalado explica por qué fue inmediato</t>
+          <t>Código correcto</t>
         </is>
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
+          <t>Introducir el TOTP vigente</t>
         </is>
       </c>
       <c r="F390" s="3" t="inlineStr"/>
@@ -13437,7 +13437,7 @@
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-36</t>
+          <t>CP-2FA-04</t>
         </is>
       </c>
       <c r="B391" s="8" t="inlineStr">
@@ -13447,17 +13447,17 @@
       </c>
       <c r="C391" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>El primer bloqueo no repite la explicación</t>
+          <t>Código de respaldo</t>
         </is>
       </c>
       <c r="E391" s="8" t="inlineStr">
         <is>
-          <t>En una cuenta nueva, fallar 3 veces</t>
+          <t>Entrar con un código de respaldo</t>
         </is>
       </c>
       <c r="F391" s="8" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-28</t>
+          <t>CP-2FA-05</t>
         </is>
       </c>
       <c r="B392" s="3" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>Revocación real de tokens</t>
+          <t>Anti-fuerza-bruta</t>
         </is>
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
+          <t>Fallar el código 5 veces</t>
         </is>
       </c>
       <c r="F392" s="3" t="inlineStr"/>
@@ -13503,7 +13503,7 @@
     <row r="393">
       <c r="A393" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-29</t>
+          <t>CP-2FA-06</t>
         </is>
       </c>
       <c r="B393" s="8" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="C393" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>Cambio de clave revoca</t>
+          <t>Desactivar 2FA</t>
         </is>
       </c>
       <c r="E393" s="8" t="inlineStr">
         <is>
-          <t>Cambiar la contraseña y usar un token emitido antes</t>
+          <t>Desactivar exigiendo un código válido</t>
         </is>
       </c>
       <c r="F393" s="8" t="inlineStr"/>
@@ -13536,7 +13536,7 @@
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-30</t>
+          <t>CP-2FA-07</t>
         </is>
       </c>
       <c r="B394" s="3" t="inlineStr">
@@ -13546,17 +13546,17 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>Segunda barrera admin</t>
+          <t>Auditoría del 2FA</t>
         </is>
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
+          <t>Activar y desactivar → tab Auditoría</t>
         </is>
       </c>
       <c r="F394" s="3" t="inlineStr"/>
@@ -13569,7 +13569,7 @@
     <row r="395">
       <c r="A395" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-31</t>
+          <t>CP-SEC-24</t>
         </is>
       </c>
       <c r="B395" s="8" t="inlineStr">
@@ -13584,12 +13584,12 @@
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>Token de cliente en ruta admin</t>
+          <t>Bloqueo progresivo de login</t>
         </is>
       </c>
       <c r="E395" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Customer/List con un token role=client</t>
+          <t>Fallar la contraseña 3 veces</t>
         </is>
       </c>
       <c r="F395" s="8" t="inlineStr"/>
@@ -13602,7 +13602,7 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-32</t>
+          <t>CP-SEC-25</t>
         </is>
       </c>
       <c r="B396" s="3" t="inlineStr">
@@ -13612,17 +13612,17 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>Sesión por pestaña</t>
+          <t>Escalada del bloqueo</t>
         </is>
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>Cerrar la pestaña y volver a abrir la app</t>
+          <t>Tras los 5 min, fallar otra vez, y otra</t>
         </is>
       </c>
       <c r="F396" s="3" t="inlineStr"/>
@@ -13635,7 +13635,7 @@
     <row r="397">
       <c r="A397" s="7" t="inlineStr">
         <is>
-          <t>CP-SEC-33</t>
+          <t>CP-SEC-26</t>
         </is>
       </c>
       <c r="B397" s="8" t="inlineStr">
@@ -13645,17 +13645,17 @@
       </c>
       <c r="C397" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>Sesión compartida entre pestañas</t>
+          <t>Bloqueo con clave correcta</t>
         </is>
       </c>
       <c r="E397" s="8" t="inlineStr">
         <is>
-          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
+          <t>Con bloqueo vigente, entrar con la clave CORRECTA</t>
         </is>
       </c>
       <c r="F397" s="8" t="inlineStr"/>
@@ -13668,7 +13668,7 @@
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
         <is>
-          <t>CP-SEC-34</t>
+          <t>CP-SEC-27</t>
         </is>
       </c>
       <c r="B398" s="3" t="inlineStr">
@@ -13683,12 +13683,12 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>Logout difundido</t>
+          <t>Reset del contador</t>
         </is>
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>Cerrar sesión en una pestaña con otras abiertas</t>
+          <t>Login correcto con la cuenta desbloqueada</t>
         </is>
       </c>
       <c r="F398" s="3" t="inlineStr"/>
@@ -13701,12 +13701,12 @@
     <row r="399">
       <c r="A399" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-01</t>
+          <t>CP-SEC-35</t>
         </is>
       </c>
       <c r="B399" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C399" s="7" t="inlineStr">
@@ -13716,12 +13716,12 @@
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>Centro de mando carga</t>
+          <t>El bloqueo escalado explica por qué fue inmediato</t>
         </is>
       </c>
       <c r="E399" s="8" t="inlineStr">
         <is>
-          <t>Entrar a /admin</t>
+          <t>Fallar 3 veces (bloqueo de 5 min), esperar a que venza y fallar UNA vez</t>
         </is>
       </c>
       <c r="F399" s="8" t="inlineStr"/>
@@ -13734,27 +13734,27 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-02</t>
+          <t>CP-SEC-36</t>
         </is>
       </c>
       <c r="B400" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>Procesos atascados</t>
+          <t>El primer bloqueo no repite la explicación</t>
         </is>
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
+          <t>En una cuenta nueva, fallar 3 veces</t>
         </is>
       </c>
       <c r="F400" s="3" t="inlineStr"/>
@@ -13767,12 +13767,12 @@
     <row r="401">
       <c r="A401" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-03</t>
+          <t>CP-SEC-28</t>
         </is>
       </c>
       <c r="B401" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C401" s="7" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>DLQ con mensajes = crítico</t>
+          <t>Revocación real de tokens</t>
         </is>
       </c>
       <c r="E401" s="8" t="inlineStr">
         <is>
-          <t>Meter un mensaje en una DLQ</t>
+          <t>Loguear, copiar el token, cerrar sesión y usar el token viejo en la API</t>
         </is>
       </c>
       <c r="F401" s="8" t="inlineStr"/>
@@ -13800,27 +13800,27 @@
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-04</t>
+          <t>CP-SEC-29</t>
         </is>
       </c>
       <c r="B402" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>Dinero del día</t>
+          <t>Cambio de clave revoca</t>
         </is>
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>Revisar débitos/recargas de hoy</t>
+          <t>Cambiar la contraseña y usar un token emitido antes</t>
         </is>
       </c>
       <c r="F402" s="3" t="inlineStr"/>
@@ -13833,12 +13833,12 @@
     <row r="403">
       <c r="A403" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-05</t>
+          <t>CP-SEC-30</t>
         </is>
       </c>
       <c r="B403" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C403" s="7" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>Saldo de plataforma sin huérfanos</t>
+          <t>Segunda barrera admin</t>
         </is>
       </c>
       <c r="E403" s="8" t="inlineStr">
         <is>
-          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
+          <t>Llamar una ruta admin con el context falsificado pero SIN token válido</t>
         </is>
       </c>
       <c r="F403" s="8" t="inlineStr"/>
@@ -13866,27 +13866,27 @@
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-06</t>
+          <t>CP-SEC-31</t>
         </is>
       </c>
       <c r="B404" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>Reputación con tendencia</t>
+          <t>Token de cliente en ruta admin</t>
         </is>
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>Sección de reputación</t>
+          <t>Llamar /Customer/List con un token role=client</t>
         </is>
       </c>
       <c r="F404" s="3" t="inlineStr"/>
@@ -13899,12 +13899,12 @@
     <row r="405">
       <c r="A405" s="7" t="inlineStr">
         <is>
-          <t>CP-CMD-07</t>
+          <t>CP-SEC-32</t>
         </is>
       </c>
       <c r="B405" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C405" s="7" t="inlineStr">
@@ -13914,12 +13914,12 @@
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>Salud de servicios</t>
+          <t>Sesión por pestaña</t>
         </is>
       </c>
       <c r="E405" s="8" t="inlineStr">
         <is>
-          <t>Revisar la cuota SES y las tablas/colas</t>
+          <t>Cerrar la pestaña y volver a abrir la app</t>
         </is>
       </c>
       <c r="F405" s="8" t="inlineStr"/>
@@ -13932,27 +13932,27 @@
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
         <is>
-          <t>CP-CMD-08</t>
+          <t>CP-SEC-33</t>
         </is>
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>Auto-refresco</t>
+          <t>Sesión compartida entre pestañas</t>
         </is>
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>Dejar el switch de auto-refresco activo</t>
+          <t>Con sesión abierta, abrir una pestaña nueva de la app</t>
         </is>
       </c>
       <c r="F406" s="3" t="inlineStr"/>
@@ -13965,27 +13965,27 @@
     <row r="407">
       <c r="A407" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-01</t>
+          <t>CP-SEC-34</t>
         </is>
       </c>
       <c r="B407" s="8" t="inlineStr">
         <is>
-          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
+          <t>Seguridad avanzada (2FA · bloqueo · revocación)</t>
         </is>
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>Salud de despliegue</t>
+          <t>Logout difundido</t>
         </is>
       </c>
       <c r="E407" s="8" t="inlineStr">
         <is>
-          <t>Abrir el tab y esperar la verificación</t>
+          <t>Cerrar sesión en una pestaña con otras abiertas</t>
         </is>
       </c>
       <c r="F407" s="8" t="inlineStr"/>
@@ -13998,7 +13998,7 @@
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-02</t>
+          <t>CP-CMD-01</t>
         </is>
       </c>
       <c r="B408" s="3" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>Recurso faltante</t>
+          <t>Centro de mando carga</t>
         </is>
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>Con una tabla crítica sin crear</t>
+          <t>Entrar a /admin</t>
         </is>
       </c>
       <c r="F408" s="3" t="inlineStr"/>
@@ -14031,7 +14031,7 @@
     <row r="409">
       <c r="A409" s="7" t="inlineStr">
         <is>
-          <t>CP-DEP-03</t>
+          <t>CP-CMD-02</t>
         </is>
       </c>
       <c r="B409" s="8" t="inlineStr">
@@ -14041,17 +14041,17 @@
       </c>
       <c r="C409" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>Sin permiso IAM ≠ faltante</t>
+          <t>Procesos atascados</t>
         </is>
       </c>
       <c r="E409" s="8" t="inlineStr">
         <is>
-          <t>Quitar el permiso de lectura de lambdas</t>
+          <t>Con un proceso en Enviando desde hace &gt; 2 h</t>
         </is>
       </c>
       <c r="F409" s="8" t="inlineStr"/>
@@ -14064,7 +14064,7 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>CP-DEP-04</t>
+          <t>CP-CMD-03</t>
         </is>
       </c>
       <c r="B410" s="3" t="inlineStr">
@@ -14074,17 +14074,17 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D410" s="3" t="inlineStr">
         <is>
-          <t>Carga no bloqueante</t>
+          <t>DLQ con mensajes = crítico</t>
         </is>
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>Abrir el tab</t>
+          <t>Meter un mensaje en una DLQ</t>
         </is>
       </c>
       <c r="F410" s="3" t="inlineStr"/>
@@ -14097,7 +14097,7 @@
     <row r="411">
       <c r="A411" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-01</t>
+          <t>CP-CMD-04</t>
         </is>
       </c>
       <c r="B411" s="8" t="inlineStr">
@@ -14107,17 +14107,17 @@
       </c>
       <c r="C411" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>Buscar destinatario</t>
+          <t>Dinero del día</t>
         </is>
       </c>
       <c r="E411" s="8" t="inlineStr">
         <is>
-          <t>Soporte → buscar un correo de un cliente</t>
+          <t>Revisar débitos/recargas de hoy</t>
         </is>
       </c>
       <c r="F411" s="8" t="inlineStr"/>
@@ -14130,7 +14130,7 @@
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-02</t>
+          <t>CP-CMD-05</t>
         </is>
       </c>
       <c r="B412" s="3" t="inlineStr">
@@ -14140,17 +14140,17 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D412" s="3" t="inlineStr">
         <is>
-          <t>Buscar por celular</t>
+          <t>Saldo de plataforma sin huérfanos</t>
         </is>
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>Buscar 3001234567 sin prefijo</t>
+          <t>Comparar "Saldo total" del centro de mando con el tab Saldos</t>
         </is>
       </c>
       <c r="F412" s="3" t="inlineStr"/>
@@ -14163,7 +14163,7 @@
     <row r="413">
       <c r="A413" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-03</t>
+          <t>CP-CMD-06</t>
         </is>
       </c>
       <c r="B413" s="8" t="inlineStr">
@@ -14178,12 +14178,12 @@
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>Banderas de listas</t>
+          <t>Reputación con tendencia</t>
         </is>
       </c>
       <c r="E413" s="8" t="inlineStr">
         <is>
-          <t>Buscar un contacto en lista negra / desuscrito</t>
+          <t>Sección de reputación</t>
         </is>
       </c>
       <c r="F413" s="8" t="inlineStr"/>
@@ -14196,7 +14196,7 @@
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-04</t>
+          <t>CP-CMD-07</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
@@ -14206,17 +14206,17 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>Reenviar activación</t>
+          <t>Salud de servicios</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
+          <t>Revisar la cuota SES y las tablas/colas</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr"/>
@@ -14229,7 +14229,7 @@
     <row r="415">
       <c r="A415" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-05</t>
+          <t>CP-CMD-08</t>
         </is>
       </c>
       <c r="B415" s="8" t="inlineStr">
@@ -14239,17 +14239,17 @@
       </c>
       <c r="C415" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>Activación en cuenta ya activa</t>
+          <t>Auto-refresco</t>
         </is>
       </c>
       <c r="E415" s="8" t="inlineStr">
         <is>
-          <t>Reenviar activación a una cuenta activa</t>
+          <t>Dejar el switch de auto-refresco activo</t>
         </is>
       </c>
       <c r="F415" s="8" t="inlineStr"/>
@@ -14262,7 +14262,7 @@
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-06</t>
+          <t>CP-DEP-01</t>
         </is>
       </c>
       <c r="B416" s="3" t="inlineStr">
@@ -14277,12 +14277,12 @@
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>Forzar reseteo</t>
+          <t>Salud de despliegue</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>Ficha → forzar reseteo de contraseña</t>
+          <t>Abrir el tab y esperar la verificación</t>
         </is>
       </c>
       <c r="F416" s="3" t="inlineStr"/>
@@ -14295,7 +14295,7 @@
     <row r="417">
       <c r="A417" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-07</t>
+          <t>CP-DEP-02</t>
         </is>
       </c>
       <c r="B417" s="8" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>Cerrar sesiones</t>
+          <t>Recurso faltante</t>
         </is>
       </c>
       <c r="E417" s="8" t="inlineStr">
         <is>
-          <t>Ficha → cerrar sesiones de un usuario</t>
+          <t>Con una tabla crítica sin crear</t>
         </is>
       </c>
       <c r="F417" s="8" t="inlineStr"/>
@@ -14328,7 +14328,7 @@
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-08</t>
+          <t>CP-DEP-03</t>
         </is>
       </c>
       <c r="B418" s="3" t="inlineStr">
@@ -14343,12 +14343,12 @@
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>Plantillas SES globales</t>
+          <t>Sin permiso IAM ≠ faltante</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Plantillas SES</t>
+          <t>Quitar el permiso de lectura de lambdas</t>
         </is>
       </c>
       <c r="F418" s="3" t="inlineStr"/>
@@ -14361,7 +14361,7 @@
     <row r="419">
       <c r="A419" s="7" t="inlineStr">
         <is>
-          <t>CP-SOP-09</t>
+          <t>CP-DEP-04</t>
         </is>
       </c>
       <c r="B419" s="8" t="inlineStr">
@@ -14371,17 +14371,17 @@
       </c>
       <c r="C419" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>Ver plantilla de otro cliente</t>
+          <t>Carga no bloqueante</t>
         </is>
       </c>
       <c r="E419" s="8" t="inlineStr">
         <is>
-          <t>Admin abre el contenido de una plantilla de otra empresa</t>
+          <t>Abrir el tab</t>
         </is>
       </c>
       <c r="F419" s="8" t="inlineStr"/>
@@ -14394,7 +14394,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>CP-SOP-10</t>
+          <t>CP-SOP-01</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
@@ -14404,17 +14404,17 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>Dominios globales</t>
+          <t>Buscar destinatario</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>Soporte → Dominios</t>
+          <t>Soporte → buscar un correo de un cliente</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr"/>
@@ -14427,7 +14427,7 @@
     <row r="421">
       <c r="A421" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-01</t>
+          <t>CP-SOP-02</t>
         </is>
       </c>
       <c r="B421" s="8" t="inlineStr">
@@ -14437,17 +14437,17 @@
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>Ver como cliente</t>
+          <t>Buscar por celular</t>
         </is>
       </c>
       <c r="E421" s="8" t="inlineStr">
         <is>
-          <t>Ficha de cliente → "Ver como cliente"</t>
+          <t>Buscar 3001234567 sin prefijo</t>
         </is>
       </c>
       <c r="F421" s="8" t="inlineStr"/>
@@ -14460,7 +14460,7 @@
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-02</t>
+          <t>CP-SOP-03</t>
         </is>
       </c>
       <c r="B422" s="3" t="inlineStr">
@@ -14470,17 +14470,17 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>La impersonación no envía</t>
+          <t>Banderas de listas</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>Estando impersonado, intentar enviar muestras o envío real</t>
+          <t>Buscar un contacto en lista negra / desuscrito</t>
         </is>
       </c>
       <c r="F422" s="3" t="inlineStr"/>
@@ -14493,7 +14493,7 @@
     <row r="423">
       <c r="A423" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-03</t>
+          <t>CP-SOP-04</t>
         </is>
       </c>
       <c r="B423" s="8" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>Salir de la vista</t>
+          <t>Reenviar activación</t>
         </is>
       </c>
       <c r="E423" s="8" t="inlineStr">
         <is>
-          <t>Botón "Salir de la vista"</t>
+          <t>Ficha de cliente → reenviar activación a una cuenta inactiva</t>
         </is>
       </c>
       <c r="F423" s="8" t="inlineStr"/>
@@ -14526,7 +14526,7 @@
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
         <is>
-          <t>CP-IMP-04</t>
+          <t>CP-SOP-05</t>
         </is>
       </c>
       <c r="B424" s="3" t="inlineStr">
@@ -14541,12 +14541,12 @@
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>Expira sola</t>
+          <t>Activación en cuenta ya activa</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>Dejar pasar más de 30 minutos impersonado</t>
+          <t>Reenviar activación a una cuenta activa</t>
         </is>
       </c>
       <c r="F424" s="3" t="inlineStr"/>
@@ -14559,7 +14559,7 @@
     <row r="425">
       <c r="A425" s="7" t="inlineStr">
         <is>
-          <t>CP-IMP-05</t>
+          <t>CP-SOP-06</t>
         </is>
       </c>
       <c r="B425" s="8" t="inlineStr">
@@ -14569,17 +14569,17 @@
       </c>
       <c r="C425" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>Auditoría</t>
+          <t>Forzar reseteo</t>
         </is>
       </c>
       <c r="E425" s="8" t="inlineStr">
         <is>
-          <t>Impersonar → tab Auditoría</t>
+          <t>Ficha → forzar reseteo de contraseña</t>
         </is>
       </c>
       <c r="F425" s="8" t="inlineStr"/>
@@ -14592,12 +14592,12 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-01</t>
+          <t>CP-SOP-07</t>
         </is>
       </c>
       <c r="B426" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C426" s="2" t="inlineStr">
@@ -14607,12 +14607,12 @@
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>Interruptor global del IVA</t>
+          <t>Cerrar sesiones</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>Configuración → apagar "Cobrar IVA"</t>
+          <t>Ficha → cerrar sesiones de un usuario</t>
         </is>
       </c>
       <c r="F426" s="3" t="inlineStr"/>
@@ -14625,27 +14625,27 @@
     <row r="427">
       <c r="A427" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-02</t>
+          <t>CP-SOP-08</t>
         </is>
       </c>
       <c r="B427" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C427" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>IVA apagado: estimador y débito coinciden</t>
+          <t>Plantillas SES globales</t>
         </is>
       </c>
       <c r="E427" s="8" t="inlineStr">
         <is>
-          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
+          <t>Soporte → Plantillas SES</t>
         </is>
       </c>
       <c r="F427" s="8" t="inlineStr"/>
@@ -14658,12 +14658,12 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-03</t>
+          <t>CP-SOP-09</t>
         </is>
       </c>
       <c r="B428" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C428" s="2" t="inlineStr">
@@ -14673,12 +14673,12 @@
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>IVA encendido</t>
+          <t>Ver plantilla de otro cliente</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>Volver a encenderlo y repetir</t>
+          <t>Admin abre el contenido de una plantilla de otra empresa</t>
         </is>
       </c>
       <c r="F428" s="3" t="inlineStr"/>
@@ -14691,12 +14691,12 @@
     <row r="429">
       <c r="A429" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-04</t>
+          <t>CP-SOP-10</t>
         </is>
       </c>
       <c r="B429" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C429" s="7" t="inlineStr">
@@ -14706,12 +14706,12 @@
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>Tarifas con IVA apagado</t>
+          <t>Dominios globales</t>
         </is>
       </c>
       <c r="E429" s="8" t="inlineStr">
         <is>
-          <t>Abrir Tarifas</t>
+          <t>Soporte → Dominios</t>
         </is>
       </c>
       <c r="F429" s="8" t="inlineStr"/>
@@ -14724,27 +14724,27 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-05</t>
+          <t>CP-IMP-01</t>
         </is>
       </c>
       <c r="B430" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>Otros ajustes</t>
+          <t>Ver como cliente</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
+          <t>Ficha de cliente → "Ver como cliente"</t>
         </is>
       </c>
       <c r="F430" s="3" t="inlineStr"/>
@@ -14757,12 +14757,12 @@
     <row r="431">
       <c r="A431" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-06</t>
+          <t>CP-IMP-02</t>
         </is>
       </c>
       <c r="B431" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C431" s="7" t="inlineStr">
@@ -14772,12 +14772,12 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>Funciones por cliente</t>
+          <t>La impersonación no envía</t>
         </is>
       </c>
       <c r="E431" s="8" t="inlineStr">
         <is>
-          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
+          <t>Estando impersonado, intentar enviar muestras o envío real</t>
         </is>
       </c>
       <c r="F431" s="8" t="inlineStr"/>
@@ -14790,27 +14790,27 @@
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-07</t>
+          <t>CP-IMP-03</t>
         </is>
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>Cliente nuevo sin funciones avanzadas</t>
+          <t>Salir de la vista</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>Registrar una empresa nueva</t>
+          <t>Botón "Salir de la vista"</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr"/>
@@ -14823,12 +14823,12 @@
     <row r="433">
       <c r="A433" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-08</t>
+          <t>CP-IMP-04</t>
         </is>
       </c>
       <c r="B433" s="8" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C433" s="7" t="inlineStr">
@@ -14838,12 +14838,12 @@
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>Clientes existentes no cambian</t>
+          <t>Expira sola</t>
         </is>
       </c>
       <c r="E433" s="8" t="inlineStr">
         <is>
-          <t>Revisar un cliente antiguo</t>
+          <t>Dejar pasar más de 30 minutos impersonado</t>
         </is>
       </c>
       <c r="F433" s="8" t="inlineStr"/>
@@ -14856,27 +14856,27 @@
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-09</t>
+          <t>CP-IMP-05</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>Configuración de plataforma y por cliente</t>
+          <t>Admin — Centro de mando, salud, soporte e impersonación</t>
         </is>
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>Cuotas de envío</t>
+          <t>Auditoría</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>Fijar tope por campaña y diario, y superarlos</t>
+          <t>Impersonar → tab Auditoría</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr"/>
@@ -14889,7 +14889,7 @@
     <row r="435">
       <c r="A435" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-10</t>
+          <t>CP-CFG-01</t>
         </is>
       </c>
       <c r="B435" s="8" t="inlineStr">
@@ -14899,17 +14899,17 @@
       </c>
       <c r="C435" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>Cuota diaria excluye muestras</t>
+          <t>Interruptor global del IVA</t>
         </is>
       </c>
       <c r="E435" s="8" t="inlineStr">
         <is>
-          <t>Enviar muestras y luego el envío real</t>
+          <t>Configuración → apagar "Cobrar IVA"</t>
         </is>
       </c>
       <c r="F435" s="8" t="inlineStr"/>
@@ -14922,7 +14922,7 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-11</t>
+          <t>CP-CFG-02</t>
         </is>
       </c>
       <c r="B436" s="3" t="inlineStr">
@@ -14932,17 +14932,17 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>Sin tope configurado</t>
+          <t>IVA apagado: estimador y débito coinciden</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>Cliente con cuotas en 0/vacío</t>
+          <t>Con el IVA apagado, comparar el estimado con lo debitado en un envío real</t>
         </is>
       </c>
       <c r="F436" s="3" t="inlineStr"/>
@@ -14955,7 +14955,7 @@
     <row r="437">
       <c r="A437" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-12</t>
+          <t>CP-CFG-03</t>
         </is>
       </c>
       <c r="B437" s="8" t="inlineStr">
@@ -14970,12 +14970,12 @@
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>IP de envío dedicada</t>
+          <t>IVA encendido</t>
         </is>
       </c>
       <c r="E437" s="8" t="inlineStr">
         <is>
-          <t>Asignar un configuration set a un cliente y enviar</t>
+          <t>Volver a encenderlo y repetir</t>
         </is>
       </c>
       <c r="F437" s="8" t="inlineStr"/>
@@ -14988,7 +14988,7 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>CP-CFG-13</t>
+          <t>CP-CFG-04</t>
         </is>
       </c>
       <c r="B438" s="3" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>Volver al pool general</t>
+          <t>Tarifas con IVA apagado</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>Quitar la IP dedicada del cliente</t>
+          <t>Abrir Tarifas</t>
         </is>
       </c>
       <c r="F438" s="3" t="inlineStr"/>
@@ -15021,7 +15021,7 @@
     <row r="439">
       <c r="A439" s="7" t="inlineStr">
         <is>
-          <t>CP-CFG-14</t>
+          <t>CP-CFG-05</t>
         </is>
       </c>
       <c r="B439" s="8" t="inlineStr">
@@ -15036,12 +15036,12 @@
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>Eliminar cliente</t>
+          <t>Otros ajustes</t>
         </is>
       </c>
       <c r="E439" s="8" t="inlineStr">
         <is>
-          <t>Admin → eliminar una empresa</t>
+          <t>Cambiar SENDER_EMAIL y OTP_EXPIRATION_MIN</t>
         </is>
       </c>
       <c r="F439" s="8" t="inlineStr"/>
@@ -15054,12 +15054,12 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-01</t>
+          <t>CP-CFG-06</t>
         </is>
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C440" s="2" t="inlineStr">
@@ -15069,12 +15069,12 @@
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>Aviso de saldo bajo</t>
+          <t>Funciones por cliente</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
+          <t>Apagar "Plantillas PDF avanzadas" a un cliente y que ese cliente vuelva a entrar</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr"/>
@@ -15087,12 +15087,12 @@
     <row r="441">
       <c r="A441" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-02</t>
+          <t>CP-CFG-07</t>
         </is>
       </c>
       <c r="B441" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C441" s="7" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>No se repite el mismo día</t>
+          <t>Cliente nuevo sin funciones avanzadas</t>
         </is>
       </c>
       <c r="E441" s="8" t="inlineStr">
         <is>
-          <t>Hacer otro envío el mismo día</t>
+          <t>Registrar una empresa nueva</t>
         </is>
       </c>
       <c r="F441" s="8" t="inlineStr"/>
@@ -15120,12 +15120,12 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-03</t>
+          <t>CP-CFG-08</t>
         </is>
       </c>
       <c r="B442" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C442" s="2" t="inlineStr">
@@ -15135,12 +15135,12 @@
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>Aviso desactivado</t>
+          <t>Clientes existentes no cambian</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
+          <t>Revisar un cliente antiguo</t>
         </is>
       </c>
       <c r="F442" s="3" t="inlineStr"/>
@@ -15153,27 +15153,27 @@
     <row r="443">
       <c r="A443" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-04</t>
+          <t>CP-CFG-09</t>
         </is>
       </c>
       <c r="B443" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C443" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>Resumen diario</t>
+          <t>Cuotas de envío</t>
         </is>
       </c>
       <c r="E443" s="8" t="inlineStr">
         <is>
-          <t>Activar el resumen y esperar el cron</t>
+          <t>Fijar tope por campaña y diario, y superarlos</t>
         </is>
       </c>
       <c r="F443" s="8" t="inlineStr"/>
@@ -15186,12 +15186,12 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>CP-NOT-05</t>
+          <t>CP-CFG-10</t>
         </is>
       </c>
       <c r="B444" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C444" s="2" t="inlineStr">
@@ -15201,12 +15201,12 @@
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>Reputación en riesgo</t>
+          <t>Cuota diaria excluye muestras</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>Cliente con rebote por encima del umbral</t>
+          <t>Enviar muestras y luego el envío real</t>
         </is>
       </c>
       <c r="F444" s="3" t="inlineStr"/>
@@ -15219,12 +15219,12 @@
     <row r="445">
       <c r="A445" s="7" t="inlineStr">
         <is>
-          <t>CP-NOT-06</t>
+          <t>CP-CFG-11</t>
         </is>
       </c>
       <c r="B445" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C445" s="7" t="inlineStr">
@@ -15234,12 +15234,12 @@
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>Solo el owner configura</t>
+          <t>Sin tope configurado</t>
         </is>
       </c>
       <c r="E445" s="8" t="inlineStr">
         <is>
-          <t>operator intenta cambiar las preferencias</t>
+          <t>Cliente con cuotas en 0/vacío</t>
         </is>
       </c>
       <c r="F445" s="8" t="inlineStr"/>
@@ -15252,12 +15252,12 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-01</t>
+          <t>CP-CFG-12</t>
         </is>
       </c>
       <c r="B446" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C446" s="2" t="inlineStr">
@@ -15267,12 +15267,12 @@
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>Centro de preferencias</t>
+          <t>IP de envío dedicada</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
+          <t>Asignar un configuration set a un cliente y enviar</t>
         </is>
       </c>
       <c r="F446" s="3" t="inlineStr"/>
@@ -15285,27 +15285,27 @@
     <row r="447">
       <c r="A447" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-02</t>
+          <t>CP-CFG-13</t>
         </is>
       </c>
       <c r="B447" s="8" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C447" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>Elegir "ninguna" da de baja</t>
+          <t>Volver al pool general</t>
         </is>
       </c>
       <c r="E447" s="8" t="inlineStr">
         <is>
-          <t>Marcar "ninguna" y guardar</t>
+          <t>Quitar la IP dedicada del cliente</t>
         </is>
       </c>
       <c r="F447" s="8" t="inlineStr"/>
@@ -15318,12 +15318,12 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-03</t>
+          <t>CP-CFG-14</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>Notificaciones y preferencias del suscriptor</t>
+          <t>Configuración de plataforma y por cliente</t>
         </is>
       </c>
       <c r="C448" s="2" t="inlineStr">
@@ -15333,12 +15333,12 @@
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>Re-suscribir</t>
+          <t>Eliminar cliente</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>Volver a elegir otra frecuencia</t>
+          <t>Admin → eliminar una empresa</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr"/>
@@ -15351,7 +15351,7 @@
     <row r="449">
       <c r="A449" s="7" t="inlineStr">
         <is>
-          <t>CP-PREF-04</t>
+          <t>CP-NOT-01</t>
         </is>
       </c>
       <c r="B449" s="8" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>Token inválido</t>
+          <t>Aviso de saldo bajo</t>
         </is>
       </c>
       <c r="E449" s="8" t="inlineStr">
         <is>
-          <t>Abrir la página con un token manipulado</t>
+          <t>Con el umbral en 20.000, hacer un envío que deje el saldo por debajo</t>
         </is>
       </c>
       <c r="F449" s="8" t="inlineStr"/>
@@ -15384,7 +15384,7 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>CP-PREF-05</t>
+          <t>CP-NOT-02</t>
         </is>
       </c>
       <c r="B450" s="3" t="inlineStr">
@@ -15399,12 +15399,12 @@
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>Baja directa</t>
+          <t>No se repite el mismo día</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>Usar el enlace de "Cancelar suscripción"</t>
+          <t>Hacer otro envío el mismo día</t>
         </is>
       </c>
       <c r="F450" s="3" t="inlineStr"/>
@@ -15417,7 +15417,7 @@
     <row r="451">
       <c r="A451" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-01</t>
+          <t>CP-NOT-03</t>
         </is>
       </c>
       <c r="B451" s="8" t="inlineStr">
@@ -15427,17 +15427,17 @@
       </c>
       <c r="C451" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>Aviso de campaña por aprobar</t>
+          <t>Aviso desactivado</t>
         </is>
       </c>
       <c r="E451" s="8" t="inlineStr">
         <is>
-          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
+          <t>Apagar el aviso de saldo bajo en Mi cuenta y repetir</t>
         </is>
       </c>
       <c r="F451" s="8" t="inlineStr"/>
@@ -15450,7 +15450,7 @@
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-02</t>
+          <t>CP-NOT-04</t>
         </is>
       </c>
       <c r="B452" s="3" t="inlineStr">
@@ -15460,17 +15460,17 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>Solo a quien puede aprobar</t>
+          <t>Resumen diario</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de otro operator del mismo equipo</t>
+          <t>Activar el resumen y esperar el cron</t>
         </is>
       </c>
       <c r="F452" s="3" t="inlineStr"/>
@@ -15483,7 +15483,7 @@
     <row r="453">
       <c r="A453" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-03</t>
+          <t>CP-NOT-05</t>
         </is>
       </c>
       <c r="B453" s="8" t="inlineStr">
@@ -15493,17 +15493,17 @@
       </c>
       <c r="C453" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>Quien la pide no se avisa a sí mismo</t>
+          <t>Reputación en riesgo</t>
         </is>
       </c>
       <c r="E453" s="8" t="inlineStr">
         <is>
-          <t>Revisar la campanita del operator que la solicitó</t>
+          <t>Cliente con rebote por encima del umbral</t>
         </is>
       </c>
       <c r="F453" s="8" t="inlineStr"/>
@@ -15516,7 +15516,7 @@
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-04</t>
+          <t>CP-NOT-06</t>
         </is>
       </c>
       <c r="B454" s="3" t="inlineStr">
@@ -15526,17 +15526,17 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>Aislamiento entre empresas</t>
+          <t>Solo el owner configura</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>Revisar la campanita de un usuario de OTRA empresa</t>
+          <t>operator intenta cambiar las preferencias</t>
         </is>
       </c>
       <c r="F454" s="3" t="inlineStr"/>
@@ -15549,7 +15549,7 @@
     <row r="455">
       <c r="A455" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-05</t>
+          <t>CP-PREF-01</t>
         </is>
       </c>
       <c r="B455" s="8" t="inlineStr">
@@ -15564,12 +15564,12 @@
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>Aviso de aprobada</t>
+          <t>Centro de preferencias</t>
         </is>
       </c>
       <c r="E455" s="8" t="inlineStr">
         <is>
-          <t>El owner aprueba la campaña</t>
+          <t>Abrir el enlace "Administrar preferencias" de un correo</t>
         </is>
       </c>
       <c r="F455" s="8" t="inlineStr"/>
@@ -15582,7 +15582,7 @@
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-06</t>
+          <t>CP-PREF-02</t>
         </is>
       </c>
       <c r="B456" s="3" t="inlineStr">
@@ -15597,12 +15597,12 @@
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>Aviso de rechazada con el motivo</t>
+          <t>Elegir "ninguna" da de baja</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
+          <t>Marcar "ninguna" y guardar</t>
         </is>
       </c>
       <c r="F456" s="3" t="inlineStr"/>
@@ -15615,7 +15615,7 @@
     <row r="457">
       <c r="A457" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-07</t>
+          <t>CP-PREF-03</t>
         </is>
       </c>
       <c r="B457" s="8" t="inlineStr">
@@ -15625,17 +15625,17 @@
       </c>
       <c r="C457" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>Saldo bajo in-app</t>
+          <t>Re-suscribir</t>
         </is>
       </c>
       <c r="E457" s="8" t="inlineStr">
         <is>
-          <t>Hacer un envío que deje el saldo bajo el umbral</t>
+          <t>Volver a elegir otra frecuencia</t>
         </is>
       </c>
       <c r="F457" s="8" t="inlineStr"/>
@@ -15648,7 +15648,7 @@
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-08</t>
+          <t>CP-PREF-04</t>
         </is>
       </c>
       <c r="B458" s="3" t="inlineStr">
@@ -15658,17 +15658,17 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
         <is>
-          <t>Avisos nuevos abajo a la derecha</t>
+          <t>Token inválido</t>
         </is>
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
+          <t>Abrir la página con un token manipulado</t>
         </is>
       </c>
       <c r="F458" s="3" t="inlineStr"/>
@@ -15681,7 +15681,7 @@
     <row r="459">
       <c r="A459" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-09</t>
+          <t>CP-PREF-05</t>
         </is>
       </c>
       <c r="B459" s="8" t="inlineStr">
@@ -15696,12 +15696,12 @@
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>Los nuevos NO saltan al entrar</t>
+          <t>Baja directa</t>
         </is>
       </c>
       <c r="E459" s="8" t="inlineStr">
         <is>
-          <t>Con avisos viejos sin leer, entrar al portal</t>
+          <t>Usar el enlace de "Cancelar suscripción"</t>
         </is>
       </c>
       <c r="F459" s="8" t="inlineStr"/>
@@ -15714,7 +15714,7 @@
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-10</t>
+          <t>CP-CAM-01</t>
         </is>
       </c>
       <c r="B460" s="3" t="inlineStr">
@@ -15724,17 +15724,17 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
         <is>
-          <t>La tarjeta se retira sola</t>
+          <t>Aviso de campaña por aprobar</t>
         </is>
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>Esperar unos segundos tras el aviso</t>
+          <t>Un operator solicita la aprobación de una campaña con muestras enviadas</t>
         </is>
       </c>
       <c r="F460" s="3" t="inlineStr"/>
@@ -15747,7 +15747,7 @@
     <row r="461">
       <c r="A461" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-11</t>
+          <t>CP-CAM-02</t>
         </is>
       </c>
       <c r="B461" s="8" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>Clic lleva al lugar correcto</t>
+          <t>Solo a quien puede aprobar</t>
         </is>
       </c>
       <c r="E461" s="8" t="inlineStr">
         <is>
-          <t>Hacer clic en "Campaña por aprobar"</t>
+          <t>Revisar la campanita de otro operator del mismo equipo</t>
         </is>
       </c>
       <c r="F461" s="8" t="inlineStr"/>
@@ -15780,7 +15780,7 @@
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-12</t>
+          <t>CP-CAM-03</t>
         </is>
       </c>
       <c r="B462" s="3" t="inlineStr">
@@ -15790,17 +15790,17 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
         <is>
-          <t>Marcar leídas</t>
+          <t>Quien la pide no se avisa a sí mismo</t>
         </is>
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>Abrir el panel y pulsar "Marcar leídas"</t>
+          <t>Revisar la campanita del operator que la solicitó</t>
         </is>
       </c>
       <c r="F462" s="3" t="inlineStr"/>
@@ -15813,7 +15813,7 @@
     <row r="463">
       <c r="A463" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-13</t>
+          <t>CP-CAM-04</t>
         </is>
       </c>
       <c r="B463" s="8" t="inlineStr">
@@ -15828,12 +15828,12 @@
       </c>
       <c r="D463" s="8" t="inlineStr">
         <is>
-          <t>No se puede marcar la de otro</t>
+          <t>Aislamiento entre empresas</t>
         </is>
       </c>
       <c r="E463" s="8" t="inlineStr">
         <is>
-          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
+          <t>Revisar la campanita de un usuario de OTRA empresa</t>
         </is>
       </c>
       <c r="F463" s="8" t="inlineStr"/>
@@ -15846,7 +15846,7 @@
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-14</t>
+          <t>CP-CAM-05</t>
         </is>
       </c>
       <c r="B464" s="3" t="inlineStr">
@@ -15856,17 +15856,17 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
         <is>
-          <t>Sin notificaciones</t>
+          <t>Aviso de aprobada</t>
         </is>
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>Usuario nuevo abre la campanita</t>
+          <t>El owner aprueba la campaña</t>
         </is>
       </c>
       <c r="F464" s="3" t="inlineStr"/>
@@ -15879,7 +15879,7 @@
     <row r="465">
       <c r="A465" s="7" t="inlineStr">
         <is>
-          <t>CP-CAM-15</t>
+          <t>CP-CAM-06</t>
         </is>
       </c>
       <c r="B465" s="8" t="inlineStr">
@@ -15889,17 +15889,17 @@
       </c>
       <c r="C465" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D465" s="8" t="inlineStr">
         <is>
-          <t>No molesta en impersonación</t>
+          <t>Aviso de rechazada con el motivo</t>
         </is>
       </c>
       <c r="E465" s="8" t="inlineStr">
         <is>
-          <t>Entrar como admin con "Ver como cliente"</t>
+          <t>El owner rechaza con el motivo "Falta el descargo legal"</t>
         </is>
       </c>
       <c r="F465" s="8" t="inlineStr"/>
@@ -15912,7 +15912,7 @@
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
         <is>
-          <t>CP-CAM-16</t>
+          <t>CP-CAM-07</t>
         </is>
       </c>
       <c r="B466" s="3" t="inlineStr">
@@ -15922,17 +15922,17 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
         <is>
-          <t>La aprobación funciona sin la tabla</t>
+          <t>Saldo bajo in-app</t>
         </is>
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
+          <t>Hacer un envío que deje el saldo bajo el umbral</t>
         </is>
       </c>
       <c r="F466" s="3" t="inlineStr"/>
@@ -15945,27 +15945,27 @@
     <row r="467">
       <c r="A467" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-01</t>
+          <t>CP-CAM-08</t>
         </is>
       </c>
       <c r="B467" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C467" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D467" s="8" t="inlineStr">
         <is>
-          <t>Verificar higiene</t>
+          <t>Avisos nuevos abajo a la derecha</t>
         </is>
       </c>
       <c r="E467" s="8" t="inlineStr">
         <is>
-          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
+          <t>Dejar el portal abierto y generar un aviso desde otra sesión</t>
         </is>
       </c>
       <c r="F467" s="8" t="inlineStr"/>
@@ -15978,12 +15978,12 @@
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-02</t>
+          <t>CP-CAM-09</t>
         </is>
       </c>
       <c r="B468" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C468" s="2" t="inlineStr">
@@ -15993,12 +15993,12 @@
       </c>
       <c r="D468" s="3" t="inlineStr">
         <is>
-          <t>Base limpia</t>
+          <t>Los nuevos NO saltan al entrar</t>
         </is>
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>Verificar una base correcta</t>
+          <t>Con avisos viejos sin leer, entrar al portal</t>
         </is>
       </c>
       <c r="F468" s="3" t="inlineStr"/>
@@ -16011,12 +16011,12 @@
     <row r="469">
       <c r="A469" s="7" t="inlineStr">
         <is>
-          <t>CP-HIG-03</t>
+          <t>CP-CAM-10</t>
         </is>
       </c>
       <c r="B469" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C469" s="7" t="inlineStr">
@@ -16026,12 +16026,12 @@
       </c>
       <c r="D469" s="8" t="inlineStr">
         <is>
-          <t>Base de celulares</t>
+          <t>La tarjeta se retira sola</t>
         </is>
       </c>
       <c r="E469" s="8" t="inlineStr">
         <is>
-          <t>Verificar una base de canal SMS</t>
+          <t>Esperar unos segundos tras el aviso</t>
         </is>
       </c>
       <c r="F469" s="8" t="inlineStr"/>
@@ -16044,27 +16044,27 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>CP-HIG-04</t>
+          <t>CP-CAM-11</t>
         </is>
       </c>
       <c r="B470" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
         <is>
-          <t>Base de otro cliente</t>
+          <t>Clic lleva al lugar correcto</t>
         </is>
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>Verificar por API una base ajena</t>
+          <t>Hacer clic en "Campaña por aprobar"</t>
         </is>
       </c>
       <c r="F470" s="3" t="inlineStr"/>
@@ -16077,27 +16077,27 @@
     <row r="471">
       <c r="A471" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-01</t>
+          <t>CP-CAM-12</t>
         </is>
       </c>
       <c r="B471" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C471" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D471" s="8" t="inlineStr">
         <is>
-          <t>Límite del asistente público</t>
+          <t>Marcar leídas</t>
         </is>
       </c>
       <c r="E471" s="8" t="inlineStr">
         <is>
-          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
+          <t>Abrir el panel y pulsar "Marcar leídas"</t>
         </is>
       </c>
       <c r="F471" s="8" t="inlineStr"/>
@@ -16110,27 +16110,27 @@
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-02</t>
+          <t>CP-CAM-13</t>
         </is>
       </c>
       <c r="B472" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D472" s="3" t="inlineStr">
         <is>
-          <t>Tope diario</t>
+          <t>No se puede marcar la de otro</t>
         </is>
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>Superar el tope diario por IP</t>
+          <t>Llamar /Notifications/List con action:read y el id de otro usuario</t>
         </is>
       </c>
       <c r="F472" s="3" t="inlineStr"/>
@@ -16143,12 +16143,12 @@
     <row r="473">
       <c r="A473" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-03</t>
+          <t>CP-CAM-14</t>
         </is>
       </c>
       <c r="B473" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C473" s="7" t="inlineStr">
@@ -16158,12 +16158,12 @@
       </c>
       <c r="D473" s="8" t="inlineStr">
         <is>
-          <t>IPs independientes</t>
+          <t>Sin notificaciones</t>
         </is>
       </c>
       <c r="E473" s="8" t="inlineStr">
         <is>
-          <t>Otra IP escribe tras agotarse la primera</t>
+          <t>Usuario nuevo abre la campanita</t>
         </is>
       </c>
       <c r="F473" s="8" t="inlineStr"/>
@@ -16176,12 +16176,12 @@
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
         <is>
-          <t>CP-RL-04</t>
+          <t>CP-CAM-15</t>
         </is>
       </c>
       <c r="B474" s="3" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C474" s="2" t="inlineStr">
@@ -16191,12 +16191,12 @@
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>El asistente responde</t>
+          <t>No molesta en impersonación</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>Preguntar por precios/canales</t>
+          <t>Entrar como admin con "Ver como cliente"</t>
         </is>
       </c>
       <c r="F474" s="3" t="inlineStr"/>
@@ -16209,27 +16209,27 @@
     <row r="475">
       <c r="A475" s="7" t="inlineStr">
         <is>
-          <t>CP-RL-05</t>
+          <t>CP-CAM-16</t>
         </is>
       </c>
       <c r="B475" s="8" t="inlineStr">
         <is>
-          <t>Higiene, límites de uso y costo del adjunto</t>
+          <t>Notificaciones y preferencias del suscriptor</t>
         </is>
       </c>
       <c r="C475" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D475" s="8" t="inlineStr">
         <is>
-          <t>Guardrails</t>
+          <t>La aprobación funciona sin la tabla</t>
         </is>
       </c>
       <c r="E475" s="8" t="inlineStr">
         <is>
-          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
+          <t>Sin desplegar la tabla notification, solicitar una aprobación</t>
         </is>
       </c>
       <c r="F475" s="8" t="inlineStr"/>
@@ -16242,7 +16242,7 @@
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-01</t>
+          <t>CP-HIG-01</t>
         </is>
       </c>
       <c r="B476" s="3" t="inlineStr">
@@ -16257,12 +16257,12 @@
       </c>
       <c r="D476" s="3" t="inlineStr">
         <is>
-          <t>Medir peso real (EAU)</t>
+          <t>Verificar higiene</t>
         </is>
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAU → "Medir peso real"</t>
+          <t>Bases de datos → botón escudo sobre una base con correos malos</t>
         </is>
       </c>
       <c r="F476" s="3" t="inlineStr"/>
@@ -16275,7 +16275,7 @@
     <row r="477">
       <c r="A477" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-02</t>
+          <t>CP-HIG-02</t>
         </is>
       </c>
       <c r="B477" s="8" t="inlineStr">
@@ -16285,17 +16285,17 @@
       </c>
       <c r="C477" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D477" s="8" t="inlineStr">
         <is>
-          <t>Medir peso real (EAP-PDF)</t>
+          <t>Base limpia</t>
         </is>
       </c>
       <c r="E477" s="8" t="inlineStr">
         <is>
-          <t>Campaña EAP-PDF → "Medir peso real"</t>
+          <t>Verificar una base correcta</t>
         </is>
       </c>
       <c r="F477" s="8" t="inlineStr"/>
@@ -16308,7 +16308,7 @@
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-03</t>
+          <t>CP-HIG-03</t>
         </is>
       </c>
       <c r="B478" s="3" t="inlineStr">
@@ -16323,12 +16323,12 @@
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>EAP-DOCX</t>
+          <t>Base de celulares</t>
         </is>
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>Campaña EAP-DOCX → medir</t>
+          <t>Verificar una base de canal SMS</t>
         </is>
       </c>
       <c r="F478" s="3" t="inlineStr"/>
@@ -16341,7 +16341,7 @@
     <row r="479">
       <c r="A479" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-04</t>
+          <t>CP-HIG-04</t>
         </is>
       </c>
       <c r="B479" s="8" t="inlineStr">
@@ -16351,17 +16351,17 @@
       </c>
       <c r="C479" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D479" s="8" t="inlineStr">
         <is>
-          <t>El botón aparece al elegir campaña</t>
+          <t>Base de otro cliente</t>
         </is>
       </c>
       <c r="E479" s="8" t="inlineStr">
         <is>
-          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
+          <t>Verificar por API una base ajena</t>
         </is>
       </c>
       <c r="F479" s="8" t="inlineStr"/>
@@ -16374,7 +16374,7 @@
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>CP-PES-05</t>
+          <t>CP-RL-01</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
@@ -16384,17 +16384,17 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>Cambiar de campaña limpia el estimado</t>
+          <t>Límite del asistente público</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>Elegir otra campaña tras haber medido</t>
+          <t>Escribirle al chat de la landing más de 6 veces en un minuto</t>
         </is>
       </c>
       <c r="F480" s="3" t="inlineStr"/>
@@ -16407,7 +16407,7 @@
     <row r="481">
       <c r="A481" s="7" t="inlineStr">
         <is>
-          <t>CP-PES-06</t>
+          <t>CP-RL-02</t>
         </is>
       </c>
       <c r="B481" s="8" t="inlineStr">
@@ -16422,12 +16422,12 @@
       </c>
       <c r="D481" s="8" t="inlineStr">
         <is>
-          <t>Canal sin adjunto</t>
+          <t>Tope diario</t>
         </is>
       </c>
       <c r="E481" s="8" t="inlineStr">
         <is>
-          <t>Campaña EM</t>
+          <t>Superar el tope diario por IP</t>
         </is>
       </c>
       <c r="F481" s="8" t="inlineStr"/>
@@ -16440,7 +16440,7 @@
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-01</t>
+          <t>CP-RL-03</t>
         </is>
       </c>
       <c r="B482" s="3" t="inlineStr">
@@ -16450,17 +16450,17 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D482" s="3" t="inlineStr">
         <is>
-          <t>Segmentos calculados, no declarados</t>
+          <t>IPs independientes</t>
         </is>
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>Muestras con una campaña SMS</t>
+          <t>Otra IP escribe tras agotarse la primera</t>
         </is>
       </c>
       <c r="F482" s="3" t="inlineStr"/>
@@ -16473,7 +16473,7 @@
     <row r="483">
       <c r="A483" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-02</t>
+          <t>CP-RL-04</t>
         </is>
       </c>
       <c r="B483" s="8" t="inlineStr">
@@ -16483,17 +16483,17 @@
       </c>
       <c r="C483" s="7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="D483" s="8" t="inlineStr">
         <is>
-          <t>Un SMS largo cuesta el doble</t>
+          <t>El asistente responde</t>
         </is>
       </c>
       <c r="E483" s="8" t="inlineStr">
         <is>
-          <t>Campaña con más de 160 caracteres</t>
+          <t>Preguntar por precios/canales</t>
         </is>
       </c>
       <c r="F483" s="8" t="inlineStr"/>
@@ -16506,7 +16506,7 @@
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-03</t>
+          <t>CP-RL-05</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
@@ -16516,17 +16516,17 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>Una emoji parte el mensaje</t>
+          <t>Guardrails</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
+          <t>Pedirle el saldo de una cuenta real o el mensaje de sistema</t>
         </is>
       </c>
       <c r="F484" s="3" t="inlineStr"/>
@@ -16539,7 +16539,7 @@
     <row r="485">
       <c r="A485" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-04</t>
+          <t>CP-PES-01</t>
         </is>
       </c>
       <c r="B485" s="8" t="inlineStr">
@@ -16554,12 +16554,12 @@
       </c>
       <c r="D485" s="8" t="inlineStr">
         <is>
-          <t>Lo estimado es lo que se cobra</t>
+          <t>Medir peso real (EAU)</t>
         </is>
       </c>
       <c r="E485" s="8" t="inlineStr">
         <is>
-          <t>Enviar real una campaña SMS de 2 segmentos y ver Saldo → Movimientos</t>
+          <t>Campaña EAU → "Medir peso real"</t>
         </is>
       </c>
       <c r="F485" s="8" t="inlineStr"/>
@@ -16572,7 +16572,7 @@
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-05</t>
+          <t>CP-PES-02</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
@@ -16587,12 +16587,12 @@
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>Tarifas nuevas visibles</t>
+          <t>Medir peso real (EAP-PDF)</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → canal SMS y Voz</t>
+          <t>Campaña EAP-PDF → "Medir peso real"</t>
         </is>
       </c>
       <c r="F486" s="3" t="inlineStr"/>
@@ -16605,7 +16605,7 @@
     <row r="487">
       <c r="A487" s="7" t="inlineStr">
         <is>
-          <t>CP-TAR-06</t>
+          <t>CP-PES-03</t>
         </is>
       </c>
       <c r="B487" s="8" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="D487" s="8" t="inlineStr">
         <is>
-          <t>Ningún cliente por debajo del costo</t>
+          <t>EAP-DOCX</t>
         </is>
       </c>
       <c r="E487" s="8" t="inlineStr">
         <is>
-          <t>Admin → Tarifas → revisar overrides por cliente</t>
+          <t>Campaña EAP-DOCX → medir</t>
         </is>
       </c>
       <c r="F487" s="8" t="inlineStr"/>
@@ -16638,7 +16638,7 @@
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>CP-TAR-07</t>
+          <t>CP-PES-04</t>
         </is>
       </c>
       <c r="B488" s="3" t="inlineStr">
@@ -16648,17 +16648,17 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>Contador del editor SMS</t>
+          <t>El botón aparece al elegir campaña</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>Escribir un SMS con emoji en Plantillas SMS</t>
+          <t>Entrar a Muestras SIN campaña, luego elegir una EAU/EAP</t>
         </is>
       </c>
       <c r="F488" s="3" t="inlineStr"/>
@@ -16671,7 +16671,7 @@
     <row r="489">
       <c r="A489" s="7" t="inlineStr">
         <is>
-          <t>CP-PUB-01</t>
+          <t>CP-PES-05</t>
         </is>
       </c>
       <c r="B489" s="8" t="inlineStr">
@@ -16686,12 +16686,12 @@
       </c>
       <c r="D489" s="8" t="inlineStr">
         <is>
-          <t>La landing no publica precios</t>
+          <t>Cambiar de campaña limpia el estimado</t>
         </is>
       </c>
       <c r="E489" s="8" t="inlineStr">
         <is>
-          <t>Abrir la landing → sección Precios</t>
+          <t>Elegir otra campaña tras haber medido</t>
         </is>
       </c>
       <c r="F489" s="8" t="inlineStr"/>
@@ -16704,7 +16704,7 @@
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-01</t>
+          <t>CP-PES-06</t>
         </is>
       </c>
       <c r="B490" s="3" t="inlineStr">
@@ -16714,17 +16714,17 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>Título e idioma</t>
+          <t>Canal sin adjunto</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>Ver el código fuente de la landing</t>
+          <t>Campaña EM</t>
         </is>
       </c>
       <c r="F490" s="3" t="inlineStr"/>
@@ -16737,7 +16737,7 @@
     <row r="491">
       <c r="A491" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-02</t>
+          <t>CP-TAR-01</t>
         </is>
       </c>
       <c r="B491" s="8" t="inlineStr">
@@ -16752,12 +16752,12 @@
       </c>
       <c r="D491" s="8" t="inlineStr">
         <is>
-          <t>Vista previa al compartir</t>
+          <t>Segmentos calculados, no declarados</t>
         </is>
       </c>
       <c r="E491" s="8" t="inlineStr">
         <is>
-          <t>Pegar https://www.mailconnect.com.co/ en WhatsApp o LinkedIn</t>
+          <t>Muestras con una campaña SMS</t>
         </is>
       </c>
       <c r="F491" s="8" t="inlineStr"/>
@@ -16770,7 +16770,7 @@
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>CP-SEO-03</t>
+          <t>CP-TAR-02</t>
         </is>
       </c>
       <c r="B492" s="3" t="inlineStr">
@@ -16780,17 +16780,17 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>Favicon</t>
+          <t>Un SMS largo cuesta el doble</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>Abrir la landing y mirar la pestaña</t>
+          <t>Campaña con más de 160 caracteres</t>
         </is>
       </c>
       <c r="F492" s="3" t="inlineStr"/>
@@ -16803,7 +16803,7 @@
     <row r="493">
       <c r="A493" s="7" t="inlineStr">
         <is>
-          <t>CP-SEO-04</t>
+          <t>CP-TAR-03</t>
         </is>
       </c>
       <c r="B493" s="8" t="inlineStr">
@@ -16813,17 +16813,17 @@
       </c>
       <c r="C493" s="7" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="D493" s="8" t="inlineStr">
         <is>
-          <t>Icono en iOS</t>
+          <t>Una emoji parte el mensaje</t>
         </is>
       </c>
       <c r="E493" s="8" t="inlineStr">
         <is>
-          <t>"Añadir a pantalla de inicio" desde Safari</t>
+          <t>Agregar una emoji a un SMS de ~100 caracteres</t>
         </is>
       </c>
       <c r="F493" s="8" t="inlineStr"/>
@@ -16836,7 +16836,7 